--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB32F9B3-04B3-4324-AAD7-5736B8F843CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A828449-4B54-4DE0-B4A4-1AB5F4C6BF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5810,32 +5810,32 @@
             <v>SARTI</v>
           </cell>
           <cell r="AS305" t="str">
-            <v>GHIOTTI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT305" t="str">
-            <v>GHIOTTI</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="306">
           <cell r="AQ306" t="str">
+            <v>VOLPINI</v>
+          </cell>
+          <cell r="AR306" t="str">
+            <v>VOLPINI</v>
+          </cell>
+          <cell r="AS306" t="str">
             <v>GHIOTTI</v>
           </cell>
-          <cell r="AR306" t="str">
+          <cell r="AT306" t="str">
             <v>GHIOTTI</v>
-          </cell>
-          <cell r="AS306" t="str">
-            <v>FABBRI</v>
-          </cell>
-          <cell r="AT306" t="str">
-            <v>FABBRI</v>
           </cell>
         </row>
         <row r="307">
           <cell r="AQ307" t="str">
-            <v>FABBRI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR307" t="str">
-            <v>FABBRI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS307" t="str">
             <v>PAZZAGLIA</v>
@@ -5922,836 +5922,836 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS313" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT313" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="314">
           <cell r="AQ314" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR314" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS314" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT314" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="315">
           <cell r="AQ315" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR315" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS315" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT315" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="316">
           <cell r="AQ316" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR316" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS316" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT316" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="317">
           <cell r="AQ317" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR317" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS317" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT317" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="318">
           <cell r="AQ318" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR318" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS318" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT318" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="319">
           <cell r="AQ319" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR319" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS319" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT319" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="320">
           <cell r="AQ320" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR320" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS320" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT320" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="321">
           <cell r="AQ321" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR321" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS321" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT321" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="322">
           <cell r="AQ322" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR322" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS322" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT322" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="323">
           <cell r="AQ323" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR323" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS323" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT323" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="324">
           <cell r="AQ324" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR324" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS324" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT324" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="325">
           <cell r="AQ325" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR325" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS325" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT325" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="326">
           <cell r="AQ326" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR326" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS326" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT326" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="327">
           <cell r="AQ327" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR327" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS327" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT327" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="328">
           <cell r="AQ328" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR328" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS328" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT328" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="329">
           <cell r="AQ329" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR329" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS329" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT329" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="330">
           <cell r="AQ330" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR330" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS330" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT330" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="331">
           <cell r="AQ331" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR331" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS331" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT331" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="332">
           <cell r="AQ332" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR332" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS332" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT332" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="333">
           <cell r="AQ333" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR333" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS333" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT333" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="334">
           <cell r="AQ334" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR334" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS334" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT334" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="335">
           <cell r="AQ335" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR335" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS335" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT335" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="336">
           <cell r="AQ336" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR336" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS336" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT336" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="337">
           <cell r="AQ337" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR337" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS337" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT337" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="338">
           <cell r="AQ338" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR338" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS338" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT338" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="339">
           <cell r="AQ339" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR339" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS339" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT339" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="340">
           <cell r="AQ340" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR340" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS340" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT340" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="341">
           <cell r="AQ341" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR341" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS341" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT341" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="342">
           <cell r="AQ342" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR342" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS342" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT342" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="343">
           <cell r="AQ343" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR343" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS343" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT343" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="344">
           <cell r="AQ344" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR344" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS344" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT344" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="345">
           <cell r="AQ345" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR345" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS345" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT345" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="346">
           <cell r="AQ346" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR346" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS346" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT346" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="347">
           <cell r="AQ347" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR347" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS347" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT347" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="348">
           <cell r="AQ348" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR348" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS348" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT348" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="349">
           <cell r="AQ349" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR349" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS349" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT349" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="350">
           <cell r="AQ350" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR350" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS350" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT350" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="351">
           <cell r="AQ351" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR351" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS351" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT351" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="352">
           <cell r="AQ352" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR352" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS352" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT352" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="353">
           <cell r="AQ353" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR353" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS353" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT353" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="354">
           <cell r="AQ354" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR354" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS354" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT354" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="355">
           <cell r="AQ355" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR355" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS355" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT355" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="356">
           <cell r="AQ356" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR356" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS356" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT356" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="357">
           <cell r="AQ357" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR357" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS357" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT357" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="358">
           <cell r="AQ358" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR358" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS358" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT358" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="359">
           <cell r="AQ359" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR359" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS359" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT359" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="360">
           <cell r="AQ360" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR360" t="str">
-            <v/>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS360" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT360" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="361">
           <cell r="AQ361" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR361" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS361" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT361" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="362">
           <cell r="AQ362" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR362" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS362" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT362" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="363">
           <cell r="AQ363" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR363" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS363" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT363" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="364">
           <cell r="AQ364" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR364" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS364" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT364" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="365">
           <cell r="AQ365" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR365" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS365" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AT365" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="366">
           <cell r="AQ366" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AR366" t="str">
-            <v/>
+            <v>SARTI</v>
           </cell>
           <cell r="AS366" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT366" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="367">
           <cell r="AQ367" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR367" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS367" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT367" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="368">
           <cell r="AQ368" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR368" t="str">
-            <v/>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS368" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT368" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="369">
           <cell r="AQ369" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR369" t="str">
-            <v/>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS369" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT369" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="370">
           <cell r="AQ370" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR370" t="str">
-            <v/>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS370" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT370" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="371">
           <cell r="AQ371" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR371" t="str">
-            <v/>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS371" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT371" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="372">
           <cell r="AQ372" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR372" t="str">
-            <v/>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS372" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT372" t="str">
-            <v/>
+            <v>BIANCHI</v>
           </cell>
         </row>
       </sheetData>
@@ -7569,13 +7569,13 @@
             <v>M/R</v>
           </cell>
           <cell r="JL3" t="str">
-            <v>N</v>
+            <v>p</v>
           </cell>
           <cell r="JM3" t="str">
-            <v>S</v>
+            <v>p</v>
           </cell>
           <cell r="JN3" t="str">
-            <v>R</v>
+            <v>m</v>
           </cell>
           <cell r="JO3" t="str">
             <v>p</v>
@@ -7587,13 +7587,13 @@
             <v>r</v>
           </cell>
           <cell r="JR3" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="JS3" t="str">
             <v>m</v>
           </cell>
           <cell r="JT3" t="str">
-            <v>r</v>
+            <v>P</v>
           </cell>
           <cell r="JU3" t="str">
             <v>M/R</v>
@@ -7602,7 +7602,7 @@
             <v>p</v>
           </cell>
           <cell r="JW3" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="JX3" t="str">
             <v>r</v>
@@ -7620,7 +7620,7 @@
             <v>m</v>
           </cell>
           <cell r="KC3" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="KD3" t="str">
             <v>r</v>
@@ -7677,7 +7677,7 @@
             <v>R</v>
           </cell>
           <cell r="KV3" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="KW3" t="str">
             <v>M/R</v>
@@ -7695,7 +7695,7 @@
             <v>P</v>
           </cell>
           <cell r="LB3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LC3" t="str">
             <v>N</v>
@@ -7755,7 +7755,7 @@
             <v>P</v>
           </cell>
           <cell r="LV3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LW3" t="str">
             <v>N</v>
@@ -7782,19 +7782,19 @@
             <v>R</v>
           </cell>
           <cell r="ME3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="MF3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MG3" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="MH3" t="str">
             <v>p</v>
           </cell>
           <cell r="MI3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MJ3" t="str">
             <v>M</v>
@@ -7842,7 +7842,7 @@
             <v>P</v>
           </cell>
           <cell r="MY3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MZ3" t="str">
             <v>N</v>
@@ -7857,82 +7857,82 @@
             <v>P</v>
           </cell>
           <cell r="ND3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NE3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NF3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NG3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NH3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="NI3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NJ3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NK3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NL3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="NM3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NN3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NO3" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="NP3" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="NQ3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NR3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NS3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NT3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NU3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NV3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NW3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NX3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NY3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NZ3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="OA3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="OB3" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="OC3" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="OD3" t="str">
             <v>-</v>
@@ -9946,7 +9946,7 @@
             <v>p</v>
           </cell>
           <cell r="JL6" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="JM6" t="str">
             <v>r</v>
@@ -9970,16 +9970,16 @@
             <v>r</v>
           </cell>
           <cell r="JT6" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="JU6" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="JV6" t="str">
             <v>r</v>
           </cell>
           <cell r="JW6" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="JX6" t="str">
             <v>m</v>
@@ -10081,7 +10081,7 @@
             <v>-</v>
           </cell>
           <cell r="LE6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LF6" t="str">
             <v>N</v>
@@ -10096,7 +10096,7 @@
             <v>P</v>
           </cell>
           <cell r="LJ6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LK6" t="str">
             <v>N</v>
@@ -10111,7 +10111,7 @@
             <v>P</v>
           </cell>
           <cell r="LO6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LP6" t="str">
             <v>N</v>
@@ -10123,73 +10123,73 @@
             <v>R</v>
           </cell>
           <cell r="LS6" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LT6" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="LU6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LV6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LW6" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LX6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LY6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LZ6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="MA6" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="MB6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MC6" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="MD6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="ME6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="MF6" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="MG6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MH6" t="str">
             <v>m</v>
           </cell>
           <cell r="MI6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="MJ6" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="MK6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="ML6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="MM6" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="MN6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MO6" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="MP6" t="str">
             <v>N</v>
@@ -10204,7 +10204,7 @@
             <v>P</v>
           </cell>
           <cell r="MT6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MU6" t="str">
             <v>N</v>
@@ -10225,19 +10225,19 @@
             <v>-</v>
           </cell>
           <cell r="NA6" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="NB6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NC6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="ND6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NE6" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="NF6" t="str">
             <v>N</v>
@@ -10252,7 +10252,7 @@
             <v>P</v>
           </cell>
           <cell r="NJ6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NK6" t="str">
             <v>N</v>
@@ -10282,7 +10282,7 @@
             <v>P</v>
           </cell>
           <cell r="NT6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NU6" t="str">
             <v>N</v>
@@ -12344,7 +12344,7 @@
             <v>m/R</v>
           </cell>
           <cell r="JR9" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="JS9" t="str">
             <v>p</v>
@@ -12365,10 +12365,10 @@
             <v>R</v>
           </cell>
           <cell r="JY9" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="JZ9" t="str">
-            <v>M</v>
+            <v>p</v>
           </cell>
           <cell r="KA9" t="str">
             <v>N</v>
@@ -12461,52 +12461,52 @@
             <v>-</v>
           </cell>
           <cell r="LE9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LF9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LG9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LH9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LI9" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LJ9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LK9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LL9" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LM9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LN9" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="LO9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LP9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LQ9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LR9" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LS9" t="str">
             <v>P</v>
           </cell>
           <cell r="LT9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LU9" t="str">
             <v>N</v>
@@ -12521,7 +12521,7 @@
             <v>P</v>
           </cell>
           <cell r="LY9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LZ9" t="str">
             <v>N</v>
@@ -12536,7 +12536,7 @@
             <v>P</v>
           </cell>
           <cell r="MD9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="ME9" t="str">
             <v>N</v>
@@ -12551,7 +12551,7 @@
             <v>P</v>
           </cell>
           <cell r="MI9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MJ9" t="str">
             <v>N</v>
@@ -12581,7 +12581,7 @@
             <v>P</v>
           </cell>
           <cell r="MS9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MT9" t="str">
             <v>N</v>
@@ -12596,7 +12596,7 @@
             <v>P</v>
           </cell>
           <cell r="MX9" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MY9" t="str">
             <v>N</v>
@@ -12626,70 +12626,70 @@
             <v>R</v>
           </cell>
           <cell r="NH9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NI9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NJ9" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="NK9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NL9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NM9" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="NN9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NO9" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="NP9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NQ9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NR9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NS9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NT9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NU9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NV9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NW9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NX9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NY9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NZ9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="OA9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="OB9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="OC9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="OD9" t="str">
             <v>-</v>
@@ -14796,10 +14796,10 @@
             <v>p</v>
           </cell>
           <cell r="KP12" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="KQ12" t="str">
             <v>p</v>
-          </cell>
-          <cell r="KQ12" t="str">
-            <v>m</v>
           </cell>
           <cell r="KR12" t="str">
             <v>r</v>
@@ -14817,55 +14817,55 @@
             <v>r</v>
           </cell>
           <cell r="KW12" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="KX12" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="KY12" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="KZ12" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="LA12" t="str">
             <v>m</v>
           </cell>
-          <cell r="KX12" t="str">
+          <cell r="LB12" t="str">
             <v>p</v>
           </cell>
-          <cell r="KY12" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="KZ12" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="LA12" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="LB12" t="str">
-            <v>-</v>
-          </cell>
           <cell r="LC12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LD12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LE12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LF12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LG12" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="LH12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LI12" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LJ12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LK12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LL12" t="str">
             <v>P</v>
           </cell>
           <cell r="LM12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LN12" t="str">
             <v>N</v>
@@ -14892,7 +14892,7 @@
             <v>R</v>
           </cell>
           <cell r="LV12" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="LW12" t="str">
             <v>M</v>
@@ -14910,7 +14910,7 @@
             <v>P</v>
           </cell>
           <cell r="MB12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MC12" t="str">
             <v>N</v>
@@ -14940,7 +14940,7 @@
             <v>P</v>
           </cell>
           <cell r="ML12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MM12" t="str">
             <v>N</v>
@@ -14955,7 +14955,7 @@
             <v>P</v>
           </cell>
           <cell r="MQ12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MR12" t="str">
             <v>N</v>
@@ -14967,22 +14967,22 @@
             <v>R</v>
           </cell>
           <cell r="MU12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MV12" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="MW12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MX12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="MY12" t="str">
             <v>P</v>
           </cell>
           <cell r="MZ12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NA12" t="str">
             <v>N</v>
@@ -14994,22 +14994,22 @@
             <v>R</v>
           </cell>
           <cell r="ND12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NE12" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NF12" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NG12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="NH12" t="str">
             <v>P</v>
           </cell>
           <cell r="NI12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NJ12" t="str">
             <v>N</v>
@@ -15024,7 +15024,7 @@
             <v>P</v>
           </cell>
           <cell r="NN12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NO12" t="str">
             <v>N</v>
@@ -17089,7 +17089,7 @@
             <v>P</v>
           </cell>
           <cell r="JM15" t="str">
-            <v>p</v>
+            <v>M</v>
           </cell>
           <cell r="JN15" t="str">
             <v>N</v>
@@ -17119,7 +17119,7 @@
             <v>P</v>
           </cell>
           <cell r="JW15" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="JX15" t="str">
             <v>r</v>
@@ -17176,13 +17176,13 @@
             <v>r</v>
           </cell>
           <cell r="KP15" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="KQ15" t="str">
             <v>m/R</v>
           </cell>
-          <cell r="KQ15" t="str">
+          <cell r="KR15" t="str">
             <v>p</v>
-          </cell>
-          <cell r="KR15" t="str">
-            <v>m</v>
           </cell>
           <cell r="KS15" t="str">
             <v>r</v>
@@ -17194,7 +17194,7 @@
             <v>p</v>
           </cell>
           <cell r="KV15" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="KW15" t="str">
             <v>r</v>
@@ -17203,7 +17203,7 @@
             <v>P</v>
           </cell>
           <cell r="KY15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KZ15" t="str">
             <v>N</v>
@@ -17218,7 +17218,7 @@
             <v>P</v>
           </cell>
           <cell r="LD15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LE15" t="str">
             <v>N</v>
@@ -17233,7 +17233,7 @@
             <v>P</v>
           </cell>
           <cell r="LI15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LJ15" t="str">
             <v>N</v>
@@ -17260,10 +17260,10 @@
             <v>R</v>
           </cell>
           <cell r="LR15" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="LS15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LT15" t="str">
             <v>N</v>
@@ -17278,7 +17278,7 @@
             <v>P</v>
           </cell>
           <cell r="LX15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LY15" t="str">
             <v>N</v>
@@ -17320,43 +17320,43 @@
             <v>R</v>
           </cell>
           <cell r="ML15" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="MM15" t="str">
             <v>p</v>
           </cell>
-          <cell r="MM15" t="str">
+          <cell r="MN15" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="MO15" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="MP15" t="str">
             <v>m</v>
           </cell>
-          <cell r="MN15" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="MO15" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="MP15" t="str">
-            <v>-</v>
-          </cell>
           <cell r="MQ15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MR15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="MS15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="MT15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="MU15" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="MV15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MW15" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="MX15" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MY15" t="str">
             <v>p</v>
@@ -17365,13 +17365,13 @@
             <v>m</v>
           </cell>
           <cell r="NA15" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="NB15" t="str">
             <v>P</v>
           </cell>
           <cell r="NC15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="ND15" t="str">
             <v>N</v>
@@ -17386,7 +17386,7 @@
             <v>P</v>
           </cell>
           <cell r="NH15" t="str">
-            <v>M</v>
+            <v>m/R</v>
           </cell>
           <cell r="NI15" t="str">
             <v>N</v>
@@ -17401,7 +17401,7 @@
             <v>P</v>
           </cell>
           <cell r="NM15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NN15" t="str">
             <v>N</v>
@@ -19622,58 +19622,58 @@
             <v>-</v>
           </cell>
           <cell r="LL18" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="LM18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LN18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LO18" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LP18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LQ18" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="LR18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LS18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LT18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LU18" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LV18" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LW18" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="LX18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LY18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LZ18" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="MA18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MB18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="MC18" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="MD18" t="str">
             <v>N</v>
@@ -19688,7 +19688,7 @@
             <v>P</v>
           </cell>
           <cell r="MH18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MI18" t="str">
             <v>N</v>
@@ -19703,7 +19703,7 @@
             <v>P</v>
           </cell>
           <cell r="MM18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MN18" t="str">
             <v>N</v>
@@ -19748,7 +19748,7 @@
             <v>P</v>
           </cell>
           <cell r="NB18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NC18" t="str">
             <v>N</v>
@@ -19763,7 +19763,7 @@
             <v>P</v>
           </cell>
           <cell r="NG18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NH18" t="str">
             <v>N</v>
@@ -19778,7 +19778,7 @@
             <v>P</v>
           </cell>
           <cell r="NL18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NM18" t="str">
             <v>N</v>
@@ -19790,46 +19790,46 @@
             <v>R</v>
           </cell>
           <cell r="NP18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NQ18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NR18" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="NS18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NT18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NU18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NV18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NW18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NX18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NY18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NZ18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="OA18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="OB18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="OC18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="OD18" t="str">
             <v>-</v>
@@ -21942,7 +21942,7 @@
             <v>r</v>
           </cell>
           <cell r="KR21" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="KS21" t="str">
             <v>m</v>
@@ -21960,46 +21960,46 @@
             <v>P</v>
           </cell>
           <cell r="KX21" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="KY21" t="str">
             <v>m</v>
           </cell>
-          <cell r="KY21" t="str">
-            <v>-</v>
-          </cell>
           <cell r="KZ21" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="LA21" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LB21" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LC21" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LD21" t="str">
             <v>P</v>
           </cell>
           <cell r="LE21" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="LF21" t="str">
-            <v>M</v>
+            <v>r</v>
           </cell>
           <cell r="LG21" t="str">
-            <v>N</v>
+            <v>r</v>
           </cell>
           <cell r="LH21" t="str">
-            <v>S</v>
+            <v>r</v>
           </cell>
           <cell r="LI21" t="str">
-            <v>R</v>
+            <v>p</v>
           </cell>
           <cell r="LJ21" t="str">
             <v>P</v>
           </cell>
           <cell r="LK21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LL21" t="str">
             <v>N</v>
@@ -22014,7 +22014,7 @@
             <v>P</v>
           </cell>
           <cell r="LP21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LQ21" t="str">
             <v>N</v>
@@ -22026,10 +22026,10 @@
             <v>R</v>
           </cell>
           <cell r="LT21" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="LU21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LV21" t="str">
             <v>N</v>
@@ -22044,7 +22044,7 @@
             <v>P</v>
           </cell>
           <cell r="LZ21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MA21" t="str">
             <v>N</v>
@@ -22059,7 +22059,7 @@
             <v>P</v>
           </cell>
           <cell r="ME21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MF21" t="str">
             <v>N</v>
@@ -22092,25 +22092,25 @@
             <v>-</v>
           </cell>
           <cell r="MP21" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MQ21" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="MR21" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MS21" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="MT21" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="MU21" t="str">
             <v>P</v>
           </cell>
           <cell r="MV21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MW21" t="str">
             <v>R</v>
@@ -22125,7 +22125,7 @@
             <v>P</v>
           </cell>
           <cell r="NA21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NB21" t="str">
             <v>-</v>
@@ -22155,25 +22155,25 @@
             <v>-</v>
           </cell>
           <cell r="NK21" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="NL21" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NM21" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NN21" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="NO21" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NP21" t="str">
             <v>P</v>
           </cell>
           <cell r="NQ21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NR21" t="str">
             <v>N</v>
@@ -22927,8 +22927,8 @@
           <cell r="IA22">
             <v>0</v>
           </cell>
-          <cell r="IB22">
-            <v>0</v>
+          <cell r="IB22" t="str">
+            <v>r</v>
           </cell>
           <cell r="IC22">
             <v>0</v>
@@ -23341,11 +23341,11 @@
           <cell r="NI22" t="str">
             <v>V</v>
           </cell>
-          <cell r="NJ22">
-            <v>0</v>
-          </cell>
-          <cell r="NK22">
-            <v>0</v>
+          <cell r="NJ22" t="str">
+            <v>V</v>
+          </cell>
+          <cell r="NK22" t="str">
+            <v>V</v>
           </cell>
           <cell r="NL22">
             <v>0</v>
@@ -24223,16 +24223,16 @@
             <v>r</v>
           </cell>
           <cell r="JK24" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="JL24" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="JM24" t="str">
-            <v>M</v>
+            <v>S</v>
           </cell>
           <cell r="JN24" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="JO24" t="str">
             <v>r</v>
@@ -24250,10 +24250,10 @@
             <v>R</v>
           </cell>
           <cell r="JT24" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="JU24" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="JV24" t="str">
             <v>m</v>
@@ -24265,10 +24265,10 @@
             <v>p</v>
           </cell>
           <cell r="JY24" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="JZ24" t="str">
-            <v>p</v>
+            <v>M</v>
           </cell>
           <cell r="KA24" t="str">
             <v>m</v>
@@ -24277,7 +24277,7 @@
             <v>p</v>
           </cell>
           <cell r="KC24" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="KD24" t="str">
             <v>r</v>
@@ -24355,7 +24355,7 @@
             <v>P</v>
           </cell>
           <cell r="LC24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LD24" t="str">
             <v>N</v>
@@ -24370,7 +24370,7 @@
             <v>P</v>
           </cell>
           <cell r="LH24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LI24" t="str">
             <v>N</v>
@@ -24382,52 +24382,52 @@
             <v>R</v>
           </cell>
           <cell r="LL24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LM24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LN24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LO24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LP24" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LQ24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LR24" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="LS24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LT24" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LU24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LV24" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="LW24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LX24" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LY24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LZ24" t="str">
             <v>P</v>
           </cell>
           <cell r="MA24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MB24" t="str">
             <v>N</v>
@@ -24457,7 +24457,7 @@
             <v>P</v>
           </cell>
           <cell r="MK24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="ML24" t="str">
             <v>N</v>
@@ -24472,7 +24472,7 @@
             <v>P</v>
           </cell>
           <cell r="MP24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MQ24" t="str">
             <v>N</v>
@@ -24487,7 +24487,7 @@
             <v>P</v>
           </cell>
           <cell r="MU24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MV24" t="str">
             <v>N</v>
@@ -24517,7 +24517,7 @@
             <v>P</v>
           </cell>
           <cell r="NE24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NF24" t="str">
             <v>-</v>
@@ -24559,37 +24559,37 @@
             <v>R</v>
           </cell>
           <cell r="NS24" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="NT24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NU24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NV24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NW24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NX24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NY24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NZ24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="OA24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="OB24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="OC24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="OD24" t="str">
             <v>-</v>
@@ -25421,8 +25421,8 @@
           <cell r="JM25">
             <v>0</v>
           </cell>
-          <cell r="JN25" t="str">
-            <v>p</v>
+          <cell r="JN25">
+            <v>0</v>
           </cell>
           <cell r="JO25">
             <v>0</v>
@@ -25439,11 +25439,11 @@
           <cell r="JS25">
             <v>0</v>
           </cell>
-          <cell r="JT25">
-            <v>0</v>
-          </cell>
-          <cell r="JU25">
-            <v>0</v>
+          <cell r="JT25" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="JU25" t="str">
+            <v>f</v>
           </cell>
           <cell r="JV25">
             <v>0</v>
@@ -26699,7 +26699,7 @@
             <v>P</v>
           </cell>
           <cell r="KQ27" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="KR27" t="str">
             <v>N</v>
@@ -26729,7 +26729,7 @@
             <v>P</v>
           </cell>
           <cell r="LA27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LB27" t="str">
             <v>N</v>
@@ -26741,22 +26741,22 @@
             <v>R</v>
           </cell>
           <cell r="LE27" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="LF27" t="str">
-            <v>-</v>
+            <v>M/R</v>
           </cell>
           <cell r="LG27" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="LH27" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="LI27" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="LJ27" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LK27" t="str">
             <v>P</v>
@@ -26771,58 +26771,58 @@
             <v>S</v>
           </cell>
           <cell r="LO27" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="LP27" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LQ27" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LR27" t="str">
-            <v>-</v>
+            <v>m/R</v>
           </cell>
           <cell r="LS27" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LT27" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LU27" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LV27" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LW27" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LX27" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LY27" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="LZ27" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MA27" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="MB27" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="MC27" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="MD27" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="ME27" t="str">
             <v>P</v>
           </cell>
           <cell r="MF27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MG27" t="str">
             <v>N</v>
@@ -26858,7 +26858,7 @@
             <v>P</v>
           </cell>
           <cell r="MR27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MS27" t="str">
             <v>N</v>
@@ -26900,7 +26900,7 @@
             <v>P</v>
           </cell>
           <cell r="NF27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NG27" t="str">
             <v>N</v>
@@ -26915,7 +26915,7 @@
             <v>P</v>
           </cell>
           <cell r="NK27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NL27" t="str">
             <v>N</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31224,15 +31224,15 @@
       </c>
       <c r="JI3" s="16" t="str">
         <f>[1]CARTELLINO!JL$3</f>
-        <v>N</v>
+        <v>p</v>
       </c>
       <c r="JJ3" s="16" t="str">
         <f>[1]CARTELLINO!JM$3</f>
-        <v>S</v>
+        <v>p</v>
       </c>
       <c r="JK3" s="16" t="str">
         <f>[1]CARTELLINO!JN$3</f>
-        <v>R</v>
+        <v>m</v>
       </c>
       <c r="JL3" s="16" t="str">
         <f>[1]CARTELLINO!JO$3</f>
@@ -31248,7 +31248,7 @@
       </c>
       <c r="JO3" s="16" t="str">
         <f>[1]CARTELLINO!JR$3</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="JP3" s="16" t="str">
         <f>[1]CARTELLINO!JS$3</f>
@@ -31256,7 +31256,7 @@
       </c>
       <c r="JQ3" s="16" t="str">
         <f>[1]CARTELLINO!JT$3</f>
-        <v>r</v>
+        <v>P</v>
       </c>
       <c r="JR3" s="16" t="str">
         <f>[1]CARTELLINO!JU$3</f>
@@ -31268,7 +31268,7 @@
       </c>
       <c r="JT3" s="16" t="str">
         <f>[1]CARTELLINO!JW$3</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="JU3" s="16" t="str">
         <f>[1]CARTELLINO!JX$3</f>
@@ -31292,7 +31292,7 @@
       </c>
       <c r="JZ3" s="16" t="str">
         <f>[1]CARTELLINO!KC$3</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="KA3" s="16" t="str">
         <f>[1]CARTELLINO!KD$3</f>
@@ -31368,7 +31368,7 @@
       </c>
       <c r="KS3" s="16" t="str">
         <f>[1]CARTELLINO!KV$3</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="KT3" s="16" t="str">
         <f>[1]CARTELLINO!KW$3</f>
@@ -31392,7 +31392,7 @@
       </c>
       <c r="KY3" s="16" t="str">
         <f>[1]CARTELLINO!LB$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KZ3" s="16" t="str">
         <f>[1]CARTELLINO!LC$3</f>
@@ -31472,7 +31472,7 @@
       </c>
       <c r="LS3" s="16" t="str">
         <f>[1]CARTELLINO!LV$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LT3" s="16" t="str">
         <f>[1]CARTELLINO!LW$3</f>
@@ -31508,15 +31508,15 @@
       </c>
       <c r="MB3" s="16" t="str">
         <f>[1]CARTELLINO!ME$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="MC3" s="16" t="str">
         <f>[1]CARTELLINO!MF$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MD3" s="16" t="str">
         <f>[1]CARTELLINO!MG$3</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="ME3" s="16" t="str">
         <f>[1]CARTELLINO!MH$3</f>
@@ -31524,7 +31524,7 @@
       </c>
       <c r="MF3" s="16" t="str">
         <f>[1]CARTELLINO!MI$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MG3" s="16" t="str">
         <f>[1]CARTELLINO!MJ$3</f>
@@ -31588,7 +31588,7 @@
       </c>
       <c r="MV3" s="16" t="str">
         <f>[1]CARTELLINO!MY$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MW3" s="16" t="str">
         <f>[1]CARTELLINO!MZ$3</f>
@@ -31608,107 +31608,107 @@
       </c>
       <c r="NA3" s="16" t="str">
         <f>[1]CARTELLINO!ND$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NB3" s="16" t="str">
         <f>[1]CARTELLINO!NE$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NC3" s="16" t="str">
         <f>[1]CARTELLINO!NF$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="ND3" s="16" t="str">
         <f>[1]CARTELLINO!NG$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NE3" s="16" t="str">
         <f>[1]CARTELLINO!NH$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="NF3" s="16" t="str">
         <f>[1]CARTELLINO!NI$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NG3" s="16" t="str">
         <f>[1]CARTELLINO!NJ$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NH3" s="16" t="str">
         <f>[1]CARTELLINO!NK$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NI3" s="16" t="str">
         <f>[1]CARTELLINO!NL$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="NJ3" s="16" t="str">
         <f>[1]CARTELLINO!NM$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NK3" s="16" t="str">
         <f>[1]CARTELLINO!NN$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NL3" s="16" t="str">
         <f>[1]CARTELLINO!NO$3</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="NM3" s="16" t="str">
         <f>[1]CARTELLINO!NP$3</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="NN3" s="16" t="str">
         <f>[1]CARTELLINO!NQ$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NO3" s="16" t="str">
         <f>[1]CARTELLINO!NR$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NP3" s="16" t="str">
         <f>[1]CARTELLINO!NS$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NQ3" s="16" t="str">
         <f>[1]CARTELLINO!NT$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NR3" s="16" t="str">
         <f>[1]CARTELLINO!NU$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NS3" s="16" t="str">
         <f>[1]CARTELLINO!NV$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NT3" s="16" t="str">
         <f>[1]CARTELLINO!NW$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NU3" s="16" t="str">
         <f>[1]CARTELLINO!NX$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NV3" s="16" t="str">
         <f>[1]CARTELLINO!NY$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NW3" s="16" t="str">
         <f>[1]CARTELLINO!NZ$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NX3" s="16" t="str">
         <f>[1]CARTELLINO!OA$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NY3" s="16" t="str">
         <f>[1]CARTELLINO!OB$3</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NZ3" s="16" t="str">
         <f>[1]CARTELLINO!OC$3</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="OA3" s="16" t="str">
         <f>[1]CARTELLINO!OD$3</f>
@@ -34819,7 +34819,7 @@
       </c>
       <c r="JI6" s="22" t="str">
         <f>[1]CARTELLINO!JL$6</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="JJ6" s="22" t="str">
         <f>[1]CARTELLINO!JM$6</f>
@@ -34851,11 +34851,11 @@
       </c>
       <c r="JQ6" s="22" t="str">
         <f>[1]CARTELLINO!JT$6</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="JR6" s="22" t="str">
         <f>[1]CARTELLINO!JU$6</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="JS6" s="22" t="str">
         <f>[1]CARTELLINO!JV$6</f>
@@ -34863,7 +34863,7 @@
       </c>
       <c r="JT6" s="22" t="str">
         <f>[1]CARTELLINO!JW$6</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="JU6" s="22" t="str">
         <f>[1]CARTELLINO!JX$6</f>
@@ -34999,7 +34999,7 @@
       </c>
       <c r="LB6" s="22" t="str">
         <f>[1]CARTELLINO!LE$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LC6" s="22" t="str">
         <f>[1]CARTELLINO!LF$6</f>
@@ -35019,7 +35019,7 @@
       </c>
       <c r="LG6" s="22" t="str">
         <f>[1]CARTELLINO!LJ$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LH6" s="22" t="str">
         <f>[1]CARTELLINO!LK$6</f>
@@ -35039,7 +35039,7 @@
       </c>
       <c r="LL6" s="22" t="str">
         <f>[1]CARTELLINO!LO$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LM6" s="22" t="str">
         <f>[1]CARTELLINO!LP$6</f>
@@ -35055,63 +35055,63 @@
       </c>
       <c r="LP6" s="22" t="str">
         <f>[1]CARTELLINO!LS$6</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LQ6" s="22" t="str">
         <f>[1]CARTELLINO!LT$6</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="LR6" s="22" t="str">
         <f>[1]CARTELLINO!LU$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LS6" s="22" t="str">
         <f>[1]CARTELLINO!LV$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LT6" s="22" t="str">
         <f>[1]CARTELLINO!LW$6</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LU6" s="22" t="str">
         <f>[1]CARTELLINO!LX$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LV6" s="22" t="str">
         <f>[1]CARTELLINO!LY$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LW6" s="22" t="str">
         <f>[1]CARTELLINO!LZ$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LX6" s="22" t="str">
         <f>[1]CARTELLINO!MA$6</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LY6" s="22" t="str">
         <f>[1]CARTELLINO!MB$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LZ6" s="22" t="str">
         <f>[1]CARTELLINO!MC$6</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="MA6" s="22" t="str">
         <f>[1]CARTELLINO!MD$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MB6" s="22" t="str">
         <f>[1]CARTELLINO!ME$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MC6" s="22" t="str">
         <f>[1]CARTELLINO!MF$6</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="MD6" s="22" t="str">
         <f>[1]CARTELLINO!MG$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="ME6" s="22" t="str">
         <f>[1]CARTELLINO!MH$6</f>
@@ -35119,31 +35119,31 @@
       </c>
       <c r="MF6" s="22" t="str">
         <f>[1]CARTELLINO!MI$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MG6" s="22" t="str">
         <f>[1]CARTELLINO!MJ$6</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="MH6" s="22" t="str">
         <f>[1]CARTELLINO!MK$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MI6" s="22" t="str">
         <f>[1]CARTELLINO!ML$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MJ6" s="22" t="str">
         <f>[1]CARTELLINO!MM$6</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="MK6" s="22" t="str">
         <f>[1]CARTELLINO!MN$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="ML6" s="22" t="str">
         <f>[1]CARTELLINO!MO$6</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="MM6" s="22" t="str">
         <f>[1]CARTELLINO!MP$6</f>
@@ -35163,7 +35163,7 @@
       </c>
       <c r="MQ6" s="22" t="str">
         <f>[1]CARTELLINO!MT$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MR6" s="22" t="str">
         <f>[1]CARTELLINO!MU$6</f>
@@ -35191,23 +35191,23 @@
       </c>
       <c r="MX6" s="22" t="str">
         <f>[1]CARTELLINO!NA$6</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="MY6" s="22" t="str">
         <f>[1]CARTELLINO!NB$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MZ6" s="22" t="str">
         <f>[1]CARTELLINO!NC$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NA6" s="22" t="str">
         <f>[1]CARTELLINO!ND$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NB6" s="22" t="str">
         <f>[1]CARTELLINO!NE$6</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="NC6" s="22" t="str">
         <f>[1]CARTELLINO!NF$6</f>
@@ -35227,7 +35227,7 @@
       </c>
       <c r="NG6" s="22" t="str">
         <f>[1]CARTELLINO!NJ$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NH6" s="22" t="str">
         <f>[1]CARTELLINO!NK$6</f>
@@ -35267,7 +35267,7 @@
       </c>
       <c r="NQ6" s="22" t="str">
         <f>[1]CARTELLINO!NT$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NR6" s="22" t="str">
         <f>[1]CARTELLINO!NU$6</f>
@@ -38439,7 +38439,7 @@
       </c>
       <c r="JO9" s="24" t="str">
         <f>[1]CARTELLINO!JR$9</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="JP9" s="24" t="str">
         <f>[1]CARTELLINO!JS$9</f>
@@ -38467,11 +38467,11 @@
       </c>
       <c r="JV9" s="24" t="str">
         <f>[1]CARTELLINO!JY$9</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="JW9" s="24" t="str">
         <f>[1]CARTELLINO!JZ$9</f>
-        <v>M</v>
+        <v>p</v>
       </c>
       <c r="JX9" s="24" t="str">
         <f>[1]CARTELLINO!KA$9</f>
@@ -38595,59 +38595,59 @@
       </c>
       <c r="LB9" s="24" t="str">
         <f>[1]CARTELLINO!LE$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LC9" s="24" t="str">
         <f>[1]CARTELLINO!LF$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LD9" s="24" t="str">
         <f>[1]CARTELLINO!LG$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LE9" s="24" t="str">
         <f>[1]CARTELLINO!LH$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LF9" s="24" t="str">
         <f>[1]CARTELLINO!LI$9</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LG9" s="24" t="str">
         <f>[1]CARTELLINO!LJ$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LH9" s="24" t="str">
         <f>[1]CARTELLINO!LK$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LI9" s="24" t="str">
         <f>[1]CARTELLINO!LL$9</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LJ9" s="24" t="str">
         <f>[1]CARTELLINO!LM$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LK9" s="24" t="str">
         <f>[1]CARTELLINO!LN$9</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="LL9" s="24" t="str">
         <f>[1]CARTELLINO!LO$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LM9" s="24" t="str">
         <f>[1]CARTELLINO!LP$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LN9" s="24" t="str">
         <f>[1]CARTELLINO!LQ$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LO9" s="24" t="str">
         <f>[1]CARTELLINO!LR$9</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LP9" s="24" t="str">
         <f>[1]CARTELLINO!LS$9</f>
@@ -38655,7 +38655,7 @@
       </c>
       <c r="LQ9" s="24" t="str">
         <f>[1]CARTELLINO!LT$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LR9" s="24" t="str">
         <f>[1]CARTELLINO!LU$9</f>
@@ -38675,7 +38675,7 @@
       </c>
       <c r="LV9" s="24" t="str">
         <f>[1]CARTELLINO!LY$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LW9" s="24" t="str">
         <f>[1]CARTELLINO!LZ$9</f>
@@ -38695,7 +38695,7 @@
       </c>
       <c r="MA9" s="24" t="str">
         <f>[1]CARTELLINO!MD$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MB9" s="24" t="str">
         <f>[1]CARTELLINO!ME$9</f>
@@ -38715,7 +38715,7 @@
       </c>
       <c r="MF9" s="24" t="str">
         <f>[1]CARTELLINO!MI$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MG9" s="24" t="str">
         <f>[1]CARTELLINO!MJ$9</f>
@@ -38755,7 +38755,7 @@
       </c>
       <c r="MP9" s="24" t="str">
         <f>[1]CARTELLINO!MS$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MQ9" s="24" t="str">
         <f>[1]CARTELLINO!MT$9</f>
@@ -38775,7 +38775,7 @@
       </c>
       <c r="MU9" s="24" t="str">
         <f>[1]CARTELLINO!MX$9</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MV9" s="24" t="str">
         <f>[1]CARTELLINO!MY$9</f>
@@ -38815,91 +38815,91 @@
       </c>
       <c r="NE9" s="24" t="str">
         <f>[1]CARTELLINO!NH$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NF9" s="24" t="str">
         <f>[1]CARTELLINO!NI$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NG9" s="24" t="str">
         <f>[1]CARTELLINO!NJ$9</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="NH9" s="24" t="str">
         <f>[1]CARTELLINO!NK$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NI9" s="24" t="str">
         <f>[1]CARTELLINO!NL$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NJ9" s="24" t="str">
         <f>[1]CARTELLINO!NM$9</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="NK9" s="24" t="str">
         <f>[1]CARTELLINO!NN$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NL9" s="24" t="str">
         <f>[1]CARTELLINO!NO$9</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="NM9" s="24" t="str">
         <f>[1]CARTELLINO!NP$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NN9" s="24" t="str">
         <f>[1]CARTELLINO!NQ$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NO9" s="24" t="str">
         <f>[1]CARTELLINO!NR$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NP9" s="24" t="str">
         <f>[1]CARTELLINO!NS$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NQ9" s="24" t="str">
         <f>[1]CARTELLINO!NT$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NR9" s="24" t="str">
         <f>[1]CARTELLINO!NU$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NS9" s="24" t="str">
         <f>[1]CARTELLINO!NV$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NT9" s="24" t="str">
         <f>[1]CARTELLINO!NW$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NU9" s="24" t="str">
         <f>[1]CARTELLINO!NX$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NV9" s="24" t="str">
         <f>[1]CARTELLINO!NY$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NW9" s="24" t="str">
         <f>[1]CARTELLINO!NZ$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NX9" s="24" t="str">
         <f>[1]CARTELLINO!OA$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NY9" s="24" t="str">
         <f>[1]CARTELLINO!OB$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NZ9" s="24" t="str">
         <f>[1]CARTELLINO!OC$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="OA9" s="24" t="str">
         <f>[1]CARTELLINO!OD$9</f>
@@ -42131,11 +42131,11 @@
       </c>
       <c r="KM12" s="25" t="str">
         <f>[1]CARTELLINO!KP$12</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="KN12" s="25" t="str">
         <f>[1]CARTELLINO!KQ$12</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KO12" s="25" t="str">
         <f>[1]CARTELLINO!KR$12</f>
@@ -42159,63 +42159,63 @@
       </c>
       <c r="KT12" s="25" t="str">
         <f>[1]CARTELLINO!KW$12</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KU12" s="25" t="str">
         <f>[1]CARTELLINO!KX$12</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="KV12" s="25" t="str">
         <f>[1]CARTELLINO!KY$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KW12" s="25" t="str">
         <f>[1]CARTELLINO!KZ$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KX12" s="25" t="str">
         <f>[1]CARTELLINO!LA$12</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KY12" s="25" t="str">
         <f>[1]CARTELLINO!LB$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KZ12" s="25" t="str">
         <f>[1]CARTELLINO!LC$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LA12" s="25" t="str">
         <f>[1]CARTELLINO!LD$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LB12" s="25" t="str">
         <f>[1]CARTELLINO!LE$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LC12" s="25" t="str">
         <f>[1]CARTELLINO!LF$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LD12" s="25" t="str">
         <f>[1]CARTELLINO!LG$12</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="LE12" s="25" t="str">
         <f>[1]CARTELLINO!LH$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LF12" s="25" t="str">
         <f>[1]CARTELLINO!LI$12</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LG12" s="25" t="str">
         <f>[1]CARTELLINO!LJ$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LH12" s="25" t="str">
         <f>[1]CARTELLINO!LK$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LI12" s="25" t="str">
         <f>[1]CARTELLINO!LL$12</f>
@@ -42223,7 +42223,7 @@
       </c>
       <c r="LJ12" s="25" t="str">
         <f>[1]CARTELLINO!LM$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LK12" s="25" t="str">
         <f>[1]CARTELLINO!LN$12</f>
@@ -42259,7 +42259,7 @@
       </c>
       <c r="LS12" s="25" t="str">
         <f>[1]CARTELLINO!LV$12</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="LT12" s="25" t="str">
         <f>[1]CARTELLINO!LW$12</f>
@@ -42283,7 +42283,7 @@
       </c>
       <c r="LY12" s="25" t="str">
         <f>[1]CARTELLINO!MB$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LZ12" s="25" t="str">
         <f>[1]CARTELLINO!MC$12</f>
@@ -42323,7 +42323,7 @@
       </c>
       <c r="MI12" s="25" t="str">
         <f>[1]CARTELLINO!ML$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MJ12" s="25" t="str">
         <f>[1]CARTELLINO!MM$12</f>
@@ -42343,7 +42343,7 @@
       </c>
       <c r="MN12" s="25" t="str">
         <f>[1]CARTELLINO!MQ$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MO12" s="25" t="str">
         <f>[1]CARTELLINO!MR$12</f>
@@ -42359,19 +42359,19 @@
       </c>
       <c r="MR12" s="25" t="str">
         <f>[1]CARTELLINO!MU$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MS12" s="25" t="str">
         <f>[1]CARTELLINO!MV$12</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MT12" s="25" t="str">
         <f>[1]CARTELLINO!MW$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MU12" s="25" t="str">
         <f>[1]CARTELLINO!MX$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="MV12" s="25" t="str">
         <f>[1]CARTELLINO!MY$12</f>
@@ -42379,7 +42379,7 @@
       </c>
       <c r="MW12" s="25" t="str">
         <f>[1]CARTELLINO!MZ$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MX12" s="25" t="str">
         <f>[1]CARTELLINO!NA$12</f>
@@ -42395,19 +42395,19 @@
       </c>
       <c r="NA12" s="25" t="str">
         <f>[1]CARTELLINO!ND$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NB12" s="25" t="str">
         <f>[1]CARTELLINO!NE$12</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NC12" s="25" t="str">
         <f>[1]CARTELLINO!NF$12</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="ND12" s="25" t="str">
         <f>[1]CARTELLINO!NG$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="NE12" s="25" t="str">
         <f>[1]CARTELLINO!NH$12</f>
@@ -42415,7 +42415,7 @@
       </c>
       <c r="NF12" s="25" t="str">
         <f>[1]CARTELLINO!NI$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NG12" s="25" t="str">
         <f>[1]CARTELLINO!NJ$12</f>
@@ -42435,7 +42435,7 @@
       </c>
       <c r="NK12" s="25" t="str">
         <f>[1]CARTELLINO!NN$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NL12" s="25" t="str">
         <f>[1]CARTELLINO!NO$12</f>
@@ -45611,7 +45611,7 @@
       </c>
       <c r="JJ15" s="26" t="str">
         <f>[1]CARTELLINO!JM$15</f>
-        <v>p</v>
+        <v>M</v>
       </c>
       <c r="JK15" s="26" t="str">
         <f>[1]CARTELLINO!JN$15</f>
@@ -45651,7 +45651,7 @@
       </c>
       <c r="JT15" s="26" t="str">
         <f>[1]CARTELLINO!JW$15</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="JU15" s="26" t="str">
         <f>[1]CARTELLINO!JX$15</f>
@@ -45727,15 +45727,15 @@
       </c>
       <c r="KM15" s="26" t="str">
         <f>[1]CARTELLINO!KP$15</f>
-        <v>m/R</v>
+        <v>p</v>
       </c>
       <c r="KN15" s="26" t="str">
         <f>[1]CARTELLINO!KQ$15</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="KO15" s="26" t="str">
         <f>[1]CARTELLINO!KR$15</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KP15" s="26" t="str">
         <f>[1]CARTELLINO!KS$15</f>
@@ -45751,7 +45751,7 @@
       </c>
       <c r="KS15" s="26" t="str">
         <f>[1]CARTELLINO!KV$15</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="KT15" s="26" t="str">
         <f>[1]CARTELLINO!KW$15</f>
@@ -45763,7 +45763,7 @@
       </c>
       <c r="KV15" s="26" t="str">
         <f>[1]CARTELLINO!KY$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KW15" s="26" t="str">
         <f>[1]CARTELLINO!KZ$15</f>
@@ -45783,7 +45783,7 @@
       </c>
       <c r="LA15" s="26" t="str">
         <f>[1]CARTELLINO!LD$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LB15" s="26" t="str">
         <f>[1]CARTELLINO!LE$15</f>
@@ -45803,7 +45803,7 @@
       </c>
       <c r="LF15" s="26" t="str">
         <f>[1]CARTELLINO!LI$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LG15" s="26" t="str">
         <f>[1]CARTELLINO!LJ$15</f>
@@ -45839,11 +45839,11 @@
       </c>
       <c r="LO15" s="26" t="str">
         <f>[1]CARTELLINO!LR$15</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="LP15" s="26" t="str">
         <f>[1]CARTELLINO!LS$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LQ15" s="26" t="str">
         <f>[1]CARTELLINO!LT$15</f>
@@ -45863,7 +45863,7 @@
       </c>
       <c r="LU15" s="26" t="str">
         <f>[1]CARTELLINO!LX$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LV15" s="26" t="str">
         <f>[1]CARTELLINO!LY$15</f>
@@ -45919,55 +45919,55 @@
       </c>
       <c r="MI15" s="26" t="str">
         <f>[1]CARTELLINO!ML$15</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="MJ15" s="26" t="str">
         <f>[1]CARTELLINO!MM$15</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="MK15" s="26" t="str">
         <f>[1]CARTELLINO!MN$15</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="ML15" s="26" t="str">
         <f>[1]CARTELLINO!MO$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MM15" s="26" t="str">
         <f>[1]CARTELLINO!MP$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MN15" s="26" t="str">
         <f>[1]CARTELLINO!MQ$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MO15" s="26" t="str">
         <f>[1]CARTELLINO!MR$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MP15" s="26" t="str">
         <f>[1]CARTELLINO!MS$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="MQ15" s="26" t="str">
         <f>[1]CARTELLINO!MT$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="MR15" s="26" t="str">
         <f>[1]CARTELLINO!MU$15</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MS15" s="26" t="str">
         <f>[1]CARTELLINO!MV$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MT15" s="26" t="str">
         <f>[1]CARTELLINO!MW$15</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="MU15" s="26" t="str">
         <f>[1]CARTELLINO!MX$15</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MV15" s="26" t="str">
         <f>[1]CARTELLINO!MY$15</f>
@@ -45979,7 +45979,7 @@
       </c>
       <c r="MX15" s="26" t="str">
         <f>[1]CARTELLINO!NA$15</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="MY15" s="26" t="str">
         <f>[1]CARTELLINO!NB$15</f>
@@ -45987,7 +45987,7 @@
       </c>
       <c r="MZ15" s="26" t="str">
         <f>[1]CARTELLINO!NC$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NA15" s="26" t="str">
         <f>[1]CARTELLINO!ND$15</f>
@@ -46007,7 +46007,7 @@
       </c>
       <c r="NE15" s="26" t="str">
         <f>[1]CARTELLINO!NH$15</f>
-        <v>M</v>
+        <v>m/R</v>
       </c>
       <c r="NF15" s="26" t="str">
         <f>[1]CARTELLINO!NI$15</f>
@@ -46027,7 +46027,7 @@
       </c>
       <c r="NJ15" s="26" t="str">
         <f>[1]CARTELLINO!NM$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NK15" s="26" t="str">
         <f>[1]CARTELLINO!NN$15</f>
@@ -49411,75 +49411,75 @@
       </c>
       <c r="LI18" s="27" t="str">
         <f>[1]CARTELLINO!LL$18</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="LJ18" s="27" t="str">
         <f>[1]CARTELLINO!LM$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LK18" s="27" t="str">
         <f>[1]CARTELLINO!LN$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LL18" s="27" t="str">
         <f>[1]CARTELLINO!LO$18</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LM18" s="27" t="str">
         <f>[1]CARTELLINO!LP$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LN18" s="27" t="str">
         <f>[1]CARTELLINO!LQ$18</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="LO18" s="27" t="str">
         <f>[1]CARTELLINO!LR$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LP18" s="27" t="str">
         <f>[1]CARTELLINO!LS$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LQ18" s="27" t="str">
         <f>[1]CARTELLINO!LT$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LR18" s="27" t="str">
         <f>[1]CARTELLINO!LU$18</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LS18" s="27" t="str">
         <f>[1]CARTELLINO!LV$18</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LT18" s="27" t="str">
         <f>[1]CARTELLINO!LW$18</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="LU18" s="27" t="str">
         <f>[1]CARTELLINO!LX$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LV18" s="27" t="str">
         <f>[1]CARTELLINO!LY$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LW18" s="27" t="str">
         <f>[1]CARTELLINO!LZ$18</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LX18" s="27" t="str">
         <f>[1]CARTELLINO!MA$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LY18" s="27" t="str">
         <f>[1]CARTELLINO!MB$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LZ18" s="27" t="str">
         <f>[1]CARTELLINO!MC$18</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="MA18" s="27" t="str">
         <f>[1]CARTELLINO!MD$18</f>
@@ -49499,7 +49499,7 @@
       </c>
       <c r="ME18" s="27" t="str">
         <f>[1]CARTELLINO!MH$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MF18" s="27" t="str">
         <f>[1]CARTELLINO!MI$18</f>
@@ -49519,7 +49519,7 @@
       </c>
       <c r="MJ18" s="27" t="str">
         <f>[1]CARTELLINO!MM$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MK18" s="27" t="str">
         <f>[1]CARTELLINO!MN$18</f>
@@ -49579,7 +49579,7 @@
       </c>
       <c r="MY18" s="27" t="str">
         <f>[1]CARTELLINO!NB$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MZ18" s="27" t="str">
         <f>[1]CARTELLINO!NC$18</f>
@@ -49599,7 +49599,7 @@
       </c>
       <c r="ND18" s="27" t="str">
         <f>[1]CARTELLINO!NG$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NE18" s="27" t="str">
         <f>[1]CARTELLINO!NH$18</f>
@@ -49619,7 +49619,7 @@
       </c>
       <c r="NI18" s="27" t="str">
         <f>[1]CARTELLINO!NL$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NJ18" s="27" t="str">
         <f>[1]CARTELLINO!NM$18</f>
@@ -49635,59 +49635,59 @@
       </c>
       <c r="NM18" s="27" t="str">
         <f>[1]CARTELLINO!NP$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NN18" s="27" t="str">
         <f>[1]CARTELLINO!NQ$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NO18" s="27" t="str">
         <f>[1]CARTELLINO!NR$18</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="NP18" s="27" t="str">
         <f>[1]CARTELLINO!NS$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NQ18" s="27" t="str">
         <f>[1]CARTELLINO!NT$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NR18" s="27" t="str">
         <f>[1]CARTELLINO!NU$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NS18" s="27" t="str">
         <f>[1]CARTELLINO!NV$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NT18" s="27" t="str">
         <f>[1]CARTELLINO!NW$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NU18" s="27" t="str">
         <f>[1]CARTELLINO!NX$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NV18" s="27" t="str">
         <f>[1]CARTELLINO!NY$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NW18" s="27" t="str">
         <f>[1]CARTELLINO!NZ$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NX18" s="27" t="str">
         <f>[1]CARTELLINO!OA$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NY18" s="27" t="str">
         <f>[1]CARTELLINO!OB$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NZ18" s="27" t="str">
         <f>[1]CARTELLINO!OC$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="OA18" s="27" t="str">
         <f>[1]CARTELLINO!OD$18</f>
@@ -52927,7 +52927,7 @@
       </c>
       <c r="KO21" s="28" t="str">
         <f>[1]CARTELLINO!KR$21</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="KP21" s="28" t="str">
         <f>[1]CARTELLINO!KS$21</f>
@@ -52951,27 +52951,27 @@
       </c>
       <c r="KU21" s="28" t="str">
         <f>[1]CARTELLINO!KX$21</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KV21" s="28" t="str">
         <f>[1]CARTELLINO!KY$21</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KW21" s="28" t="str">
         <f>[1]CARTELLINO!KZ$21</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="KX21" s="28" t="str">
         <f>[1]CARTELLINO!LA$21</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KY21" s="28" t="str">
         <f>[1]CARTELLINO!LB$21</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KZ21" s="28" t="str">
         <f>[1]CARTELLINO!LC$21</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LA21" s="28" t="str">
         <f>[1]CARTELLINO!LD$21</f>
@@ -52979,23 +52979,23 @@
       </c>
       <c r="LB21" s="28" t="str">
         <f>[1]CARTELLINO!LE$21</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="LC21" s="28" t="str">
         <f>[1]CARTELLINO!LF$21</f>
-        <v>M</v>
+        <v>r</v>
       </c>
       <c r="LD21" s="28" t="str">
         <f>[1]CARTELLINO!LG$21</f>
-        <v>N</v>
+        <v>r</v>
       </c>
       <c r="LE21" s="28" t="str">
         <f>[1]CARTELLINO!LH$21</f>
-        <v>S</v>
+        <v>r</v>
       </c>
       <c r="LF21" s="28" t="str">
         <f>[1]CARTELLINO!LI$21</f>
-        <v>R</v>
+        <v>p</v>
       </c>
       <c r="LG21" s="28" t="str">
         <f>[1]CARTELLINO!LJ$21</f>
@@ -53003,7 +53003,7 @@
       </c>
       <c r="LH21" s="28" t="str">
         <f>[1]CARTELLINO!LK$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LI21" s="28" t="str">
         <f>[1]CARTELLINO!LL$21</f>
@@ -53023,7 +53023,7 @@
       </c>
       <c r="LM21" s="28" t="str">
         <f>[1]CARTELLINO!LP$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LN21" s="28" t="str">
         <f>[1]CARTELLINO!LQ$21</f>
@@ -53039,11 +53039,11 @@
       </c>
       <c r="LQ21" s="28" t="str">
         <f>[1]CARTELLINO!LT$21</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="LR21" s="28" t="str">
         <f>[1]CARTELLINO!LU$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LS21" s="28" t="str">
         <f>[1]CARTELLINO!LV$21</f>
@@ -53063,7 +53063,7 @@
       </c>
       <c r="LW21" s="28" t="str">
         <f>[1]CARTELLINO!LZ$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LX21" s="28" t="str">
         <f>[1]CARTELLINO!MA$21</f>
@@ -53083,7 +53083,7 @@
       </c>
       <c r="MB21" s="28" t="str">
         <f>[1]CARTELLINO!ME$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MC21" s="28" t="str">
         <f>[1]CARTELLINO!MF$21</f>
@@ -53127,23 +53127,23 @@
       </c>
       <c r="MM21" s="28" t="str">
         <f>[1]CARTELLINO!MP$21</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MN21" s="28" t="str">
         <f>[1]CARTELLINO!MQ$21</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MO21" s="28" t="str">
         <f>[1]CARTELLINO!MR$21</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MP21" s="28" t="str">
         <f>[1]CARTELLINO!MS$21</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MQ21" s="28" t="str">
         <f>[1]CARTELLINO!MT$21</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="MR21" s="28" t="str">
         <f>[1]CARTELLINO!MU$21</f>
@@ -53151,7 +53151,7 @@
       </c>
       <c r="MS21" s="28" t="str">
         <f>[1]CARTELLINO!MV$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MT21" s="28" t="str">
         <f>[1]CARTELLINO!MW$21</f>
@@ -53171,7 +53171,7 @@
       </c>
       <c r="MX21" s="28" t="str">
         <f>[1]CARTELLINO!NA$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MY21" s="28" t="str">
         <f>[1]CARTELLINO!NB$21</f>
@@ -53211,23 +53211,23 @@
       </c>
       <c r="NH21" s="28" t="str">
         <f>[1]CARTELLINO!NK$21</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="NI21" s="28" t="str">
         <f>[1]CARTELLINO!NL$21</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NJ21" s="28" t="str">
         <f>[1]CARTELLINO!NM$21</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NK21" s="28" t="str">
         <f>[1]CARTELLINO!NN$21</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="NL21" s="28" t="str">
         <f>[1]CARTELLINO!NO$21</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NM21" s="28" t="str">
         <f>[1]CARTELLINO!NP$21</f>
@@ -53235,7 +53235,7 @@
       </c>
       <c r="NN21" s="28" t="str">
         <f>[1]CARTELLINO!NQ$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NO21" s="28" t="str">
         <f>[1]CARTELLINO!NR$21</f>
@@ -54247,9 +54247,9 @@
         <f>[1]CARTELLINO!IA$22</f>
         <v>0</v>
       </c>
-      <c r="HY22" s="46">
+      <c r="HY22" s="46" t="str">
         <f>[1]CARTELLINO!IB$22</f>
-        <v>0</v>
+        <v>r</v>
       </c>
       <c r="HZ22" s="46">
         <f>[1]CARTELLINO!IC$22</f>
@@ -54799,13 +54799,13 @@
         <f>[1]CARTELLINO!NI$22</f>
         <v>V</v>
       </c>
-      <c r="NG22" s="46">
+      <c r="NG22" s="46" t="str">
         <f>[1]CARTELLINO!NJ$22</f>
-        <v>0</v>
-      </c>
-      <c r="NH22" s="46">
+        <v>V</v>
+      </c>
+      <c r="NH22" s="46" t="str">
         <f>[1]CARTELLINO!NK$22</f>
-        <v>0</v>
+        <v>V</v>
       </c>
       <c r="NI22" s="46">
         <f>[1]CARTELLINO!NL$22</f>
@@ -56391,19 +56391,19 @@
       </c>
       <c r="JH24" s="29" t="str">
         <f>[1]CARTELLINO!JK$24</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="JI24" s="29" t="str">
         <f>[1]CARTELLINO!JL$24</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="JJ24" s="29" t="str">
         <f>[1]CARTELLINO!JM$24</f>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="JK24" s="29" t="str">
         <f>[1]CARTELLINO!JN$24</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="JL24" s="29" t="str">
         <f>[1]CARTELLINO!JO$24</f>
@@ -56427,11 +56427,11 @@
       </c>
       <c r="JQ24" s="29" t="str">
         <f>[1]CARTELLINO!JT$24</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="JR24" s="29" t="str">
         <f>[1]CARTELLINO!JU$24</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="JS24" s="29" t="str">
         <f>[1]CARTELLINO!JV$24</f>
@@ -56447,11 +56447,11 @@
       </c>
       <c r="JV24" s="29" t="str">
         <f>[1]CARTELLINO!JY$24</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="JW24" s="29" t="str">
         <f>[1]CARTELLINO!JZ$24</f>
-        <v>p</v>
+        <v>M</v>
       </c>
       <c r="JX24" s="29" t="str">
         <f>[1]CARTELLINO!KA$24</f>
@@ -56463,7 +56463,7 @@
       </c>
       <c r="JZ24" s="29" t="str">
         <f>[1]CARTELLINO!KC$24</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="KA24" s="29" t="str">
         <f>[1]CARTELLINO!KD$24</f>
@@ -56567,7 +56567,7 @@
       </c>
       <c r="KZ24" s="29" t="str">
         <f>[1]CARTELLINO!LC$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LA24" s="29" t="str">
         <f>[1]CARTELLINO!LD$24</f>
@@ -56587,7 +56587,7 @@
       </c>
       <c r="LE24" s="29" t="str">
         <f>[1]CARTELLINO!LH$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LF24" s="29" t="str">
         <f>[1]CARTELLINO!LI$24</f>
@@ -56603,59 +56603,59 @@
       </c>
       <c r="LI24" s="29" t="str">
         <f>[1]CARTELLINO!LL$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LJ24" s="29" t="str">
         <f>[1]CARTELLINO!LM$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LK24" s="29" t="str">
         <f>[1]CARTELLINO!LN$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LL24" s="29" t="str">
         <f>[1]CARTELLINO!LO$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LM24" s="29" t="str">
         <f>[1]CARTELLINO!LP$24</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LN24" s="29" t="str">
         <f>[1]CARTELLINO!LQ$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LO24" s="29" t="str">
         <f>[1]CARTELLINO!LR$24</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="LP24" s="29" t="str">
         <f>[1]CARTELLINO!LS$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LQ24" s="29" t="str">
         <f>[1]CARTELLINO!LT$24</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LR24" s="29" t="str">
         <f>[1]CARTELLINO!LU$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LS24" s="29" t="str">
         <f>[1]CARTELLINO!LV$24</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="LT24" s="29" t="str">
         <f>[1]CARTELLINO!LW$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LU24" s="29" t="str">
         <f>[1]CARTELLINO!LX$24</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LV24" s="29" t="str">
         <f>[1]CARTELLINO!LY$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LW24" s="29" t="str">
         <f>[1]CARTELLINO!LZ$24</f>
@@ -56663,7 +56663,7 @@
       </c>
       <c r="LX24" s="29" t="str">
         <f>[1]CARTELLINO!MA$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LY24" s="29" t="str">
         <f>[1]CARTELLINO!MB$24</f>
@@ -56703,7 +56703,7 @@
       </c>
       <c r="MH24" s="29" t="str">
         <f>[1]CARTELLINO!MK$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MI24" s="29" t="str">
         <f>[1]CARTELLINO!ML$24</f>
@@ -56723,7 +56723,7 @@
       </c>
       <c r="MM24" s="29" t="str">
         <f>[1]CARTELLINO!MP$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MN24" s="29" t="str">
         <f>[1]CARTELLINO!MQ$24</f>
@@ -56743,7 +56743,7 @@
       </c>
       <c r="MR24" s="29" t="str">
         <f>[1]CARTELLINO!MU$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MS24" s="29" t="str">
         <f>[1]CARTELLINO!MV$24</f>
@@ -56783,7 +56783,7 @@
       </c>
       <c r="NB24" s="29" t="str">
         <f>[1]CARTELLINO!NE$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NC24" s="29" t="str">
         <f>[1]CARTELLINO!NF$24</f>
@@ -56839,47 +56839,47 @@
       </c>
       <c r="NP24" s="29" t="str">
         <f>[1]CARTELLINO!NS$24</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="NQ24" s="29" t="str">
         <f>[1]CARTELLINO!NT$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NR24" s="29" t="str">
         <f>[1]CARTELLINO!NU$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NS24" s="29" t="str">
         <f>[1]CARTELLINO!NV$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NT24" s="29" t="str">
         <f>[1]CARTELLINO!NW$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NU24" s="29" t="str">
         <f>[1]CARTELLINO!NX$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NV24" s="29" t="str">
         <f>[1]CARTELLINO!NY$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NW24" s="29" t="str">
         <f>[1]CARTELLINO!NZ$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NX24" s="29" t="str">
         <f>[1]CARTELLINO!OA$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NY24" s="29" t="str">
         <f>[1]CARTELLINO!OB$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NZ24" s="29" t="str">
         <f>[1]CARTELLINO!OC$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="OA24" s="29" t="str">
         <f>[1]CARTELLINO!OD$24</f>
@@ -57995,9 +57995,9 @@
         <f>[1]CARTELLINO!JM$25</f>
         <v>0</v>
       </c>
-      <c r="JK25" s="46" t="str">
+      <c r="JK25" s="46">
         <f>[1]CARTELLINO!JN$25</f>
-        <v>p</v>
+        <v>0</v>
       </c>
       <c r="JL25" s="46">
         <f>[1]CARTELLINO!JO$25</f>
@@ -58019,13 +58019,13 @@
         <f>[1]CARTELLINO!JS$25</f>
         <v>0</v>
       </c>
-      <c r="JQ25" s="46">
+      <c r="JQ25" s="46" t="str">
         <f>[1]CARTELLINO!JT$25</f>
-        <v>0</v>
-      </c>
-      <c r="JR25" s="46">
+        <v>f</v>
+      </c>
+      <c r="JR25" s="46" t="str">
         <f>[1]CARTELLINO!JU$25</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="JS25" s="46">
         <f>[1]CARTELLINO!JV$25</f>
@@ -60115,7 +60115,7 @@
       </c>
       <c r="KN27" s="30" t="str">
         <f>[1]CARTELLINO!KQ$27</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="KO27" s="30" t="str">
         <f>[1]CARTELLINO!KR$27</f>
@@ -60155,7 +60155,7 @@
       </c>
       <c r="KX27" s="30" t="str">
         <f>[1]CARTELLINO!LA$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KY27" s="30" t="str">
         <f>[1]CARTELLINO!LB$27</f>
@@ -60171,27 +60171,27 @@
       </c>
       <c r="LB27" s="30" t="str">
         <f>[1]CARTELLINO!LE$27</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="LC27" s="30" t="str">
         <f>[1]CARTELLINO!LF$27</f>
-        <v>-</v>
+        <v>M/R</v>
       </c>
       <c r="LD27" s="30" t="str">
         <f>[1]CARTELLINO!LG$27</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="LE27" s="30" t="str">
         <f>[1]CARTELLINO!LH$27</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="LF27" s="30" t="str">
         <f>[1]CARTELLINO!LI$27</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="LG27" s="30" t="str">
         <f>[1]CARTELLINO!LJ$27</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LH27" s="30" t="str">
         <f>[1]CARTELLINO!LK$27</f>
@@ -60211,67 +60211,67 @@
       </c>
       <c r="LL27" s="30" t="str">
         <f>[1]CARTELLINO!LO$27</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="LM27" s="30" t="str">
         <f>[1]CARTELLINO!LP$27</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LN27" s="30" t="str">
         <f>[1]CARTELLINO!LQ$27</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LO27" s="30" t="str">
         <f>[1]CARTELLINO!LR$27</f>
-        <v>-</v>
+        <v>m/R</v>
       </c>
       <c r="LP27" s="30" t="str">
         <f>[1]CARTELLINO!LS$27</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LQ27" s="30" t="str">
         <f>[1]CARTELLINO!LT$27</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LR27" s="30" t="str">
         <f>[1]CARTELLINO!LU$27</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LS27" s="30" t="str">
         <f>[1]CARTELLINO!LV$27</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LT27" s="30" t="str">
         <f>[1]CARTELLINO!LW$27</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LU27" s="30" t="str">
         <f>[1]CARTELLINO!LX$27</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LV27" s="30" t="str">
         <f>[1]CARTELLINO!LY$27</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LW27" s="30" t="str">
         <f>[1]CARTELLINO!LZ$27</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LX27" s="30" t="str">
         <f>[1]CARTELLINO!MA$27</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LY27" s="30" t="str">
         <f>[1]CARTELLINO!MB$27</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="LZ27" s="30" t="str">
         <f>[1]CARTELLINO!MC$27</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MA27" s="30" t="str">
         <f>[1]CARTELLINO!MD$27</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MB27" s="30" t="str">
         <f>[1]CARTELLINO!ME$27</f>
@@ -60279,7 +60279,7 @@
       </c>
       <c r="MC27" s="30" t="str">
         <f>[1]CARTELLINO!MF$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MD27" s="30" t="str">
         <f>[1]CARTELLINO!MG$27</f>
@@ -60327,7 +60327,7 @@
       </c>
       <c r="MO27" s="30" t="str">
         <f>[1]CARTELLINO!MR$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MP27" s="30" t="str">
         <f>[1]CARTELLINO!MS$27</f>
@@ -60383,7 +60383,7 @@
       </c>
       <c r="NC27" s="30" t="str">
         <f>[1]CARTELLINO!NF$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="ND27" s="30" t="str">
         <f>[1]CARTELLINO!NG$27</f>
@@ -60403,7 +60403,7 @@
       </c>
       <c r="NH27" s="30" t="str">
         <f>[1]CARTELLINO!NK$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NI27" s="30" t="str">
         <f>[1]CARTELLINO!NL$27</f>
@@ -63007,10 +63007,10 @@
         <v>SARTI</v>
       </c>
       <c r="KN29" s="63" t="str">
+        <v>VOLPINI</v>
+      </c>
+      <c r="KO29" s="63" t="str">
         <v>GHIOTTI</v>
-      </c>
-      <c r="KO29" s="63" t="str">
-        <v>FABBRI</v>
       </c>
       <c r="KP29" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -63031,181 +63031,181 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="KV29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="KW29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="KX29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="KY29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="KZ29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LA29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="LB29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="LC29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="LD29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="LE29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="LF29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="LG29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="LH29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="LI29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="LJ29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="LK29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="LL29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="LM29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="LN29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="LO29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="LP29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="LQ29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="LR29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="LS29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="LT29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LU29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="LV29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="LW29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="LX29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="LY29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="LZ29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="MA29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="MB29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="MC29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="MD29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="ME29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="MF29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="MG29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="MH29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="MI29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="MJ29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="MK29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="ML29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="MM29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="MN29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="MO29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="MP29" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="MQ29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="MR29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="MS29" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="MT29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="MU29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="MV29" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="MW29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="MX29" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="MY29" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="MZ29" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="NA29" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="NB29" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
     </row>
     <row r="30" spans="1:404" x14ac:dyDescent="0.25">
@@ -64107,10 +64107,10 @@
         <v>SARTI</v>
       </c>
       <c r="KN30" s="63" t="str">
+        <v>VOLPINI</v>
+      </c>
+      <c r="KO30" s="63" t="str">
         <v>GHIOTTI</v>
-      </c>
-      <c r="KO30" s="63" t="str">
-        <v>FABBRI</v>
       </c>
       <c r="KP30" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -64131,181 +64131,181 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="KV30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="KW30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="KX30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="KY30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="KZ30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LA30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="LB30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="LC30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="LD30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="LE30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="LF30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="LG30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="LH30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="LI30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="LJ30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="LK30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="LL30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="LM30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="LN30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="LO30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="LP30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="LQ30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="LR30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="LS30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="LT30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LU30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="LV30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="LW30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="LX30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="LY30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="LZ30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="MA30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="MB30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="MC30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="MD30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="ME30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="MF30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="MG30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="MH30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="MI30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="MJ30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="MK30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="ML30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="MM30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="MN30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="MO30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="MP30" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="MQ30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="MR30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="MS30" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="MT30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="MU30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="MV30" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="MW30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="MX30" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="MY30" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="MZ30" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="NA30" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="NB30" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
     </row>
     <row r="31" spans="1:404" x14ac:dyDescent="0.25">
@@ -65204,10 +65204,10 @@
         <v>SARTI</v>
       </c>
       <c r="KM31" s="63" t="str">
+        <v>VOLPINI</v>
+      </c>
+      <c r="KN31" s="63" t="str">
         <v>GHIOTTI</v>
-      </c>
-      <c r="KN31" s="63" t="str">
-        <v>FABBRI</v>
       </c>
       <c r="KO31" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -65228,184 +65228,184 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="KU31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="KV31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="KW31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="KX31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="KY31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="KZ31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="LA31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="LB31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="LC31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="LD31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="LE31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="LF31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="LG31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="LH31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="LI31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="LJ31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="LK31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="LL31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="LM31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="LN31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="LO31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="LP31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="LQ31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="LR31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="LS31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LT31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="LU31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="LV31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="LW31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="LX31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="LY31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="LZ31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="MA31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="MB31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="MC31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="MD31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="ME31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="MF31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="MG31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="MH31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="MI31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="MJ31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="MK31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="ML31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="MM31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="MN31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="MO31" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="MP31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="MQ31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="MR31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="MS31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="MT31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="MU31" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="MV31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="MW31" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="MX31" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="MY31" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="MZ31" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="NA31" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="NB31" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
     </row>
     <row r="32" spans="1:404" x14ac:dyDescent="0.25">
@@ -66304,10 +66304,10 @@
         <v>SARTI</v>
       </c>
       <c r="KM32" s="63" t="str">
+        <v>VOLPINI</v>
+      </c>
+      <c r="KN32" s="63" t="str">
         <v>GHIOTTI</v>
-      </c>
-      <c r="KN32" s="63" t="str">
-        <v>FABBRI</v>
       </c>
       <c r="KO32" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -66328,184 +66328,184 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="KU32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="KV32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="KW32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="KX32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="KY32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="KZ32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="LA32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="LB32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="LC32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="LD32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="LE32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="LF32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="LG32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="LH32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="LI32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="LJ32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="LK32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="LL32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="LM32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="LN32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="LO32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="LP32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="LQ32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="LR32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="LS32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LT32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="LU32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="LV32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="LW32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="LX32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="LY32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="LZ32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="MA32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="MB32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="MC32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="MD32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="ME32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="MF32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="MG32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="MH32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="MI32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="MJ32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="MK32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="ML32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="MM32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="MN32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="MO32" s="63" t="str">
-        <v/>
+        <v>FABBRI</v>
       </c>
       <c r="MP32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="MQ32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="MR32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
       <c r="MS32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="MT32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="MU32" s="63" t="str">
-        <v/>
+        <v>SARTI</v>
       </c>
       <c r="MV32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="MW32" s="63" t="str">
-        <v/>
+        <v>VOLPINI</v>
       </c>
       <c r="MX32" s="63" t="str">
-        <v/>
+        <v>BERARDI</v>
       </c>
       <c r="MY32" s="63" t="str">
-        <v/>
+        <v>MICHELOT.</v>
       </c>
       <c r="MZ32" s="63" t="str">
-        <v/>
+        <v>GHIOTTI</v>
       </c>
       <c r="NA32" s="63" t="str">
-        <v/>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="NB32" s="63" t="str">
-        <v/>
+        <v>BIANCHI</v>
       </c>
     </row>
     <row r="33" spans="1:285" x14ac:dyDescent="0.25">
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,13 +71029,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71044,6 +71037,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A828449-4B54-4DE0-B4A4-1AB5F4C6BF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE82FA9-A218-4E09-93EA-BDF84E0C4DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5037,7 +5037,7 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR250" t="str">
-            <v>PAZZAGLIA</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS250" t="str">
             <v>VOLPINI</v>
@@ -5177,7 +5177,7 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR260" t="str">
-            <v>PAZZAGLIA</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS260" t="str">
             <v>VOLPINI</v>
@@ -6552,18 +6552,18 @@
             <v>BIANCHI</v>
           </cell>
           <cell r="AS358" t="str">
-            <v>VOLPINI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT358" t="str">
-            <v>VOLPINI</v>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="359">
           <cell r="AQ359" t="str">
-            <v>VOLPINI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR359" t="str">
-            <v>VOLPINI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS359" t="str">
             <v>FABBRI</v>
@@ -6622,19 +6622,15 @@
             <v>BIANCHI</v>
           </cell>
           <cell r="AS363" t="str">
-            <v>BERARDI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT363" t="str">
-            <v>BERARDI</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="364">
-          <cell r="AQ364" t="str">
-            <v>BERARDI</v>
-          </cell>
-          <cell r="AR364" t="str">
-            <v>BERARDI</v>
-          </cell>
+          <cell r="AQ364"/>
+          <cell r="AR364"/>
           <cell r="AS364" t="str">
             <v>GHIOTTI</v>
           </cell>
@@ -6699,12 +6695,8 @@
           </cell>
         </row>
         <row r="369">
-          <cell r="AQ369" t="str">
-            <v>BERARDI</v>
-          </cell>
-          <cell r="AR369" t="str">
-            <v>BERARDI</v>
-          </cell>
+          <cell r="AQ369"/>
+          <cell r="AR369"/>
           <cell r="AS369" t="str">
             <v>MICHELOT.</v>
           </cell>
@@ -7536,7 +7528,7 @@
             <v>P</v>
           </cell>
           <cell r="JA3" t="str">
-            <v>M</v>
+            <v>P</v>
           </cell>
           <cell r="JB3" t="str">
             <v>-</v>
@@ -7575,7 +7567,7 @@
             <v>p</v>
           </cell>
           <cell r="JN3" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="JO3" t="str">
             <v>p</v>
@@ -7590,7 +7582,7 @@
             <v>m</v>
           </cell>
           <cell r="JS3" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="JT3" t="str">
             <v>P</v>
@@ -7641,7 +7633,7 @@
             <v>R</v>
           </cell>
           <cell r="KJ3" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="KK3" t="str">
             <v>p</v>
@@ -7758,10 +7750,10 @@
             <v>M/R</v>
           </cell>
           <cell r="LW3" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="LX3" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="LY3" t="str">
             <v>R</v>
@@ -7884,25 +7876,25 @@
             <v>r</v>
           </cell>
           <cell r="NM3" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="NN3" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="NO3" t="str">
-            <v>r</v>
+            <v>-</v>
           </cell>
           <cell r="NP3" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="NQ3" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="NR3" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="NS3" t="str">
             <v>m/R</v>
-          </cell>
-          <cell r="NQ3" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="NR3" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="NS3" t="str">
-            <v>m</v>
           </cell>
           <cell r="NT3" t="str">
             <v>p</v>
@@ -8947,11 +8939,11 @@
           <cell r="LV4">
             <v>0</v>
           </cell>
-          <cell r="LW4">
-            <v>0</v>
-          </cell>
-          <cell r="LX4">
-            <v>0</v>
+          <cell r="LW4" t="str">
+            <v>pn</v>
+          </cell>
+          <cell r="LX4" t="str">
+            <v>x</v>
           </cell>
           <cell r="LY4">
             <v>0</v>
@@ -9073,23 +9065,23 @@
           <cell r="NL4">
             <v>0</v>
           </cell>
-          <cell r="NM4">
-            <v>0</v>
-          </cell>
-          <cell r="NN4">
-            <v>0</v>
-          </cell>
-          <cell r="NO4">
-            <v>0</v>
-          </cell>
-          <cell r="NP4">
-            <v>0</v>
-          </cell>
-          <cell r="NQ4">
-            <v>0</v>
-          </cell>
-          <cell r="NR4">
-            <v>0</v>
+          <cell r="NM4" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NN4" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NO4" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NP4" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NQ4" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NR4" t="str">
+            <v>v</v>
           </cell>
           <cell r="NS4">
             <v>0</v>
@@ -10018,7 +10010,7 @@
             <v>r</v>
           </cell>
           <cell r="KJ6" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="KK6" t="str">
             <v>M/R</v>
@@ -10138,7 +10130,7 @@
             <v>r</v>
           </cell>
           <cell r="LX6" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="LY6" t="str">
             <v>p</v>
@@ -12305,7 +12297,7 @@
             <v>p</v>
           </cell>
           <cell r="JE9" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="JF9" t="str">
             <v>M/R</v>
@@ -12347,7 +12339,7 @@
             <v>p</v>
           </cell>
           <cell r="JS9" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="JT9" t="str">
             <v>r</v>
@@ -14652,7 +14644,7 @@
             <v>M</v>
           </cell>
           <cell r="IT12" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="IU12" t="str">
             <v>r</v>
@@ -14685,7 +14677,7 @@
             <v>m</v>
           </cell>
           <cell r="JE12" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="JF12" t="str">
             <v>r</v>
@@ -14895,7 +14887,7 @@
             <v>r</v>
           </cell>
           <cell r="LW12" t="str">
-            <v>M</v>
+            <v>p</v>
           </cell>
           <cell r="LX12" t="str">
             <v>N</v>
@@ -14955,7 +14947,7 @@
             <v>P</v>
           </cell>
           <cell r="MQ12" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="MR12" t="str">
             <v>N</v>
@@ -14970,7 +14962,7 @@
             <v>p</v>
           </cell>
           <cell r="MV12" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="MW12" t="str">
             <v>p</v>
@@ -19790,10 +19782,10 @@
             <v>R</v>
           </cell>
           <cell r="NP18" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="NQ18" t="str">
             <v>p</v>
-          </cell>
-          <cell r="NQ18" t="str">
-            <v>m</v>
           </cell>
           <cell r="NR18" t="str">
             <v>m/R</v>
@@ -21759,7 +21751,7 @@
             <v>R</v>
           </cell>
           <cell r="II21" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="IJ21" t="str">
             <v>m</v>
@@ -21852,7 +21844,7 @@
             <v>R</v>
           </cell>
           <cell r="JN21" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="JO21" t="str">
             <v>M/R</v>
@@ -21942,7 +21934,7 @@
             <v>r</v>
           </cell>
           <cell r="KR21" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="KS21" t="str">
             <v>m</v>
@@ -22095,7 +22087,7 @@
             <v>p</v>
           </cell>
           <cell r="MQ21" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="MR21" t="str">
             <v>p</v>
@@ -22110,7 +22102,7 @@
             <v>P</v>
           </cell>
           <cell r="MV21" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="MW21" t="str">
             <v>R</v>
@@ -24322,7 +24314,7 @@
             <v>R</v>
           </cell>
           <cell r="KR24" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="KS24" t="str">
             <v>M/R</v>
@@ -24415,7 +24407,7 @@
             <v>P</v>
           </cell>
           <cell r="LW24" t="str">
-            <v>m</v>
+            <v>M</v>
           </cell>
           <cell r="LX24" t="str">
             <v>r</v>
@@ -24559,7 +24551,7 @@
             <v>R</v>
           </cell>
           <cell r="NS24" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="NT24" t="str">
             <v>p</v>
@@ -26573,7 +26565,7 @@
             <v>R</v>
           </cell>
           <cell r="JA27" t="str">
-            <v>P</v>
+            <v>M</v>
           </cell>
           <cell r="JB27" t="str">
             <v>N</v>
@@ -26795,13 +26787,13 @@
             <v>p</v>
           </cell>
           <cell r="LW27" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="LX27" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="LY27" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="LZ27" t="str">
             <v>p</v>
@@ -26930,7 +26922,7 @@
             <v>P</v>
           </cell>
           <cell r="NP27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NQ27" t="str">
             <v>N</v>
@@ -28519,431 +28511,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28945,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31180,7 +31172,7 @@
       </c>
       <c r="IX3" s="16" t="str">
         <f>[1]CARTELLINO!JA$3</f>
-        <v>M</v>
+        <v>P</v>
       </c>
       <c r="IY3" s="16" t="str">
         <f>[1]CARTELLINO!JB$3</f>
@@ -31232,7 +31224,7 @@
       </c>
       <c r="JK3" s="16" t="str">
         <f>[1]CARTELLINO!JN$3</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="JL3" s="16" t="str">
         <f>[1]CARTELLINO!JO$3</f>
@@ -31252,7 +31244,7 @@
       </c>
       <c r="JP3" s="16" t="str">
         <f>[1]CARTELLINO!JS$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="JQ3" s="16" t="str">
         <f>[1]CARTELLINO!JT$3</f>
@@ -31320,7 +31312,7 @@
       </c>
       <c r="KG3" s="16" t="str">
         <f>[1]CARTELLINO!KJ$3</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="KH3" s="16" t="str">
         <f>[1]CARTELLINO!KK$3</f>
@@ -31476,11 +31468,11 @@
       </c>
       <c r="LT3" s="16" t="str">
         <f>[1]CARTELLINO!LW$3</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="LU3" s="16" t="str">
         <f>[1]CARTELLINO!LX$3</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="LV3" s="16" t="str">
         <f>[1]CARTELLINO!LY$3</f>
@@ -31644,31 +31636,31 @@
       </c>
       <c r="NJ3" s="16" t="str">
         <f>[1]CARTELLINO!NM$3</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="NK3" s="16" t="str">
         <f>[1]CARTELLINO!NN$3</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="NL3" s="16" t="str">
         <f>[1]CARTELLINO!NO$3</f>
-        <v>r</v>
+        <v>-</v>
       </c>
       <c r="NM3" s="16" t="str">
         <f>[1]CARTELLINO!NP$3</f>
-        <v>m/R</v>
+        <v>-</v>
       </c>
       <c r="NN3" s="16" t="str">
         <f>[1]CARTELLINO!NQ$3</f>
-        <v>p</v>
+        <v>R</v>
       </c>
       <c r="NO3" s="16" t="str">
         <f>[1]CARTELLINO!NR$3</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="NP3" s="16" t="str">
         <f>[1]CARTELLINO!NS$3</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="NQ3" s="16" t="str">
         <f>[1]CARTELLINO!NT$3</f>
@@ -33068,13 +33060,13 @@
         <f>[1]CARTELLINO!LV$4</f>
         <v>0</v>
       </c>
-      <c r="LT4" s="43">
+      <c r="LT4" s="43" t="str">
         <f>[1]CARTELLINO!LW$4</f>
-        <v>0</v>
-      </c>
-      <c r="LU4" s="43">
+        <v>pn</v>
+      </c>
+      <c r="LU4" s="43" t="str">
         <f>[1]CARTELLINO!LX$4</f>
-        <v>0</v>
+        <v>x</v>
       </c>
       <c r="LV4" s="43">
         <f>[1]CARTELLINO!LY$4</f>
@@ -33236,29 +33228,29 @@
         <f>[1]CARTELLINO!NL$4</f>
         <v>0</v>
       </c>
-      <c r="NJ4" s="43">
+      <c r="NJ4" s="43" t="str">
         <f>[1]CARTELLINO!NM$4</f>
-        <v>0</v>
-      </c>
-      <c r="NK4" s="43">
+        <v>v</v>
+      </c>
+      <c r="NK4" s="43" t="str">
         <f>[1]CARTELLINO!NN$4</f>
-        <v>0</v>
-      </c>
-      <c r="NL4" s="43">
+        <v>v</v>
+      </c>
+      <c r="NL4" s="43" t="str">
         <f>[1]CARTELLINO!NO$4</f>
-        <v>0</v>
-      </c>
-      <c r="NM4" s="43">
+        <v>v</v>
+      </c>
+      <c r="NM4" s="43" t="str">
         <f>[1]CARTELLINO!NP$4</f>
-        <v>0</v>
-      </c>
-      <c r="NN4" s="43">
+        <v>v</v>
+      </c>
+      <c r="NN4" s="43" t="str">
         <f>[1]CARTELLINO!NQ$4</f>
-        <v>0</v>
-      </c>
-      <c r="NO4" s="43">
+        <v>v</v>
+      </c>
+      <c r="NO4" s="43" t="str">
         <f>[1]CARTELLINO!NR$4</f>
-        <v>0</v>
+        <v>v</v>
       </c>
       <c r="NP4" s="43">
         <f>[1]CARTELLINO!NS$4</f>
@@ -34915,7 +34907,7 @@
       </c>
       <c r="KG6" s="22" t="str">
         <f>[1]CARTELLINO!KJ$6</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="KH6" s="22" t="str">
         <f>[1]CARTELLINO!KK$6</f>
@@ -35075,7 +35067,7 @@
       </c>
       <c r="LU6" s="22" t="str">
         <f>[1]CARTELLINO!LX$6</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="LV6" s="22" t="str">
         <f>[1]CARTELLINO!LY$6</f>
@@ -38387,7 +38379,7 @@
       </c>
       <c r="JB9" s="24" t="str">
         <f>[1]CARTELLINO!JE$9</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="JC9" s="24" t="str">
         <f>[1]CARTELLINO!JF$9</f>
@@ -38443,7 +38435,7 @@
       </c>
       <c r="JP9" s="24" t="str">
         <f>[1]CARTELLINO!JS$9</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="JQ9" s="24" t="str">
         <f>[1]CARTELLINO!JT$9</f>
@@ -41939,7 +41931,7 @@
       </c>
       <c r="IQ12" s="25" t="str">
         <f>[1]CARTELLINO!IT$12</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="IR12" s="25" t="str">
         <f>[1]CARTELLINO!IU$12</f>
@@ -41983,7 +41975,7 @@
       </c>
       <c r="JB12" s="25" t="str">
         <f>[1]CARTELLINO!JE$12</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="JC12" s="25" t="str">
         <f>[1]CARTELLINO!JF$12</f>
@@ -42263,7 +42255,7 @@
       </c>
       <c r="LT12" s="25" t="str">
         <f>[1]CARTELLINO!LW$12</f>
-        <v>M</v>
+        <v>p</v>
       </c>
       <c r="LU12" s="25" t="str">
         <f>[1]CARTELLINO!LX$12</f>
@@ -42343,7 +42335,7 @@
       </c>
       <c r="MN12" s="25" t="str">
         <f>[1]CARTELLINO!MQ$12</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="MO12" s="25" t="str">
         <f>[1]CARTELLINO!MR$12</f>
@@ -42363,7 +42355,7 @@
       </c>
       <c r="MS12" s="25" t="str">
         <f>[1]CARTELLINO!MV$12</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="MT12" s="25" t="str">
         <f>[1]CARTELLINO!MW$12</f>
@@ -49635,11 +49627,11 @@
       </c>
       <c r="NM18" s="27" t="str">
         <f>[1]CARTELLINO!NP$18</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="NN18" s="27" t="str">
         <f>[1]CARTELLINO!NQ$18</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NO18" s="27" t="str">
         <f>[1]CARTELLINO!NR$18</f>
@@ -52683,7 +52675,7 @@
       </c>
       <c r="IF21" s="28" t="str">
         <f>[1]CARTELLINO!II$21</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="IG21" s="28" t="str">
         <f>[1]CARTELLINO!IJ$21</f>
@@ -52807,7 +52799,7 @@
       </c>
       <c r="JK21" s="28" t="str">
         <f>[1]CARTELLINO!JN$21</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="JL21" s="28" t="str">
         <f>[1]CARTELLINO!JO$21</f>
@@ -52927,7 +52919,7 @@
       </c>
       <c r="KO21" s="28" t="str">
         <f>[1]CARTELLINO!KR$21</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="KP21" s="28" t="str">
         <f>[1]CARTELLINO!KS$21</f>
@@ -53131,7 +53123,7 @@
       </c>
       <c r="MN21" s="28" t="str">
         <f>[1]CARTELLINO!MQ$21</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="MO21" s="28" t="str">
         <f>[1]CARTELLINO!MR$21</f>
@@ -53151,7 +53143,7 @@
       </c>
       <c r="MS21" s="28" t="str">
         <f>[1]CARTELLINO!MV$21</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="MT21" s="28" t="str">
         <f>[1]CARTELLINO!MW$21</f>
@@ -56523,7 +56515,7 @@
       </c>
       <c r="KO24" s="29" t="str">
         <f>[1]CARTELLINO!KR$24</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="KP24" s="29" t="str">
         <f>[1]CARTELLINO!KS$24</f>
@@ -56647,7 +56639,7 @@
       </c>
       <c r="LT24" s="29" t="str">
         <f>[1]CARTELLINO!LW$24</f>
-        <v>m</v>
+        <v>M</v>
       </c>
       <c r="LU24" s="29" t="str">
         <f>[1]CARTELLINO!LX$24</f>
@@ -56839,7 +56831,7 @@
       </c>
       <c r="NP24" s="29" t="str">
         <f>[1]CARTELLINO!NS$24</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="NQ24" s="29" t="str">
         <f>[1]CARTELLINO!NT$24</f>
@@ -59947,7 +59939,7 @@
       </c>
       <c r="IX27" s="30" t="str">
         <f>[1]CARTELLINO!JA$27</f>
-        <v>P</v>
+        <v>M</v>
       </c>
       <c r="IY27" s="30" t="str">
         <f>[1]CARTELLINO!JB$27</f>
@@ -60243,15 +60235,15 @@
       </c>
       <c r="LT27" s="30" t="str">
         <f>[1]CARTELLINO!LW$27</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="LU27" s="30" t="str">
         <f>[1]CARTELLINO!LX$27</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="LV27" s="30" t="str">
         <f>[1]CARTELLINO!LY$27</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="LW27" s="30" t="str">
         <f>[1]CARTELLINO!LZ$27</f>
@@ -60423,7 +60415,7 @@
       </c>
       <c r="NM27" s="30" t="str">
         <f>[1]CARTELLINO!NP$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NN27" s="30" t="str">
         <f>[1]CARTELLINO!NQ$27</f>
@@ -63166,7 +63158,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="MO29" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BERARDI</v>
       </c>
       <c r="MP29" s="63" t="str">
         <v>FABBRI</v>
@@ -63180,8 +63172,8 @@
       <c r="MS29" s="63" t="str">
         <v>BIANCHI</v>
       </c>
-      <c r="MT29" s="63" t="str">
-        <v>BERARDI</v>
+      <c r="MT29" s="63">
+        <v>0</v>
       </c>
       <c r="MU29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -63195,8 +63187,8 @@
       <c r="MX29" s="63" t="str">
         <v>VOLPINI</v>
       </c>
-      <c r="MY29" s="63" t="str">
-        <v>BERARDI</v>
+      <c r="MY29" s="63">
+        <v>0</v>
       </c>
       <c r="MZ29" s="63" t="str">
         <v>MICHELOT.</v>
@@ -63939,7 +63931,7 @@
         <v>SARTI</v>
       </c>
       <c r="IJ30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="IK30" s="63" t="str">
         <v>VOLPINI</v>
@@ -63969,7 +63961,7 @@
         <v>SARTI</v>
       </c>
       <c r="IT30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>BIANCHI</v>
       </c>
       <c r="IU30" s="63" t="str">
         <v>VOLPINI</v>
@@ -64266,7 +64258,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="MO30" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BERARDI</v>
       </c>
       <c r="MP30" s="63" t="str">
         <v>FABBRI</v>
@@ -64280,8 +64272,8 @@
       <c r="MS30" s="63" t="str">
         <v>BIANCHI</v>
       </c>
-      <c r="MT30" s="63" t="str">
-        <v>BERARDI</v>
+      <c r="MT30" s="63">
+        <v>0</v>
       </c>
       <c r="MU30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -64295,8 +64287,8 @@
       <c r="MX30" s="63" t="str">
         <v>VOLPINI</v>
       </c>
-      <c r="MY30" s="63" t="str">
-        <v>BERARDI</v>
+      <c r="MY30" s="63">
+        <v>0</v>
       </c>
       <c r="MZ30" s="63" t="str">
         <v>MICHELOT.</v>
@@ -65363,7 +65355,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="MN31" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BERARDI</v>
       </c>
       <c r="MO31" s="63" t="str">
         <v>FABBRI</v>
@@ -65378,7 +65370,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="MS31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="MT31" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66463,7 +66455,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="MN32" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BERARDI</v>
       </c>
       <c r="MO32" s="63" t="str">
         <v>FABBRI</v>
@@ -66478,7 +66470,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="MS32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="MT32" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66531,12 +66523,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,6 +71021,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71037,13 +71036,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE82FA9-A218-4E09-93EA-BDF84E0C4DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB3AE14-04CB-4F14-9103-9FAEEDBD53DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="240" windowWidth="28800" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7858,13 +7858,13 @@
             <v>m</v>
           </cell>
           <cell r="NG3" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="NH3" t="str">
             <v>r</v>
           </cell>
           <cell r="NI3" t="str">
-            <v>p</v>
+            <v>r</v>
           </cell>
           <cell r="NJ3" t="str">
             <v>m</v>
@@ -17378,7 +17378,7 @@
             <v>P</v>
           </cell>
           <cell r="NH15" t="str">
-            <v>m/R</v>
+            <v>M/R</v>
           </cell>
           <cell r="NI15" t="str">
             <v>N</v>
@@ -22138,16 +22138,16 @@
             <v>-</v>
           </cell>
           <cell r="NH21" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="NI21" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="NJ21" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="NK21" t="str">
             <v>-</v>
-          </cell>
-          <cell r="NI21" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="NJ21" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="NK21" t="str">
-            <v>R</v>
           </cell>
           <cell r="NL21" t="str">
             <v>p</v>
@@ -23327,17 +23327,17 @@
           <cell r="NG22" t="str">
             <v>V</v>
           </cell>
-          <cell r="NH22" t="str">
-            <v>V</v>
-          </cell>
-          <cell r="NI22" t="str">
-            <v>V</v>
-          </cell>
-          <cell r="NJ22" t="str">
-            <v>V</v>
+          <cell r="NH22">
+            <v>0</v>
+          </cell>
+          <cell r="NI22">
+            <v>0</v>
+          </cell>
+          <cell r="NJ22">
+            <v>0</v>
           </cell>
           <cell r="NK22" t="str">
-            <v>V</v>
+            <v>ng</v>
           </cell>
           <cell r="NL22">
             <v>0</v>
@@ -28511,431 +28511,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28945,7 +28945,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31612,7 +31612,7 @@
       </c>
       <c r="ND3" s="16" t="str">
         <f>[1]CARTELLINO!NG$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NE3" s="16" t="str">
         <f>[1]CARTELLINO!NH$3</f>
@@ -31620,7 +31620,7 @@
       </c>
       <c r="NF3" s="16" t="str">
         <f>[1]CARTELLINO!NI$3</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="NG3" s="16" t="str">
         <f>[1]CARTELLINO!NJ$3</f>
@@ -45999,7 +45999,7 @@
       </c>
       <c r="NE15" s="26" t="str">
         <f>[1]CARTELLINO!NH$15</f>
-        <v>m/R</v>
+        <v>M/R</v>
       </c>
       <c r="NF15" s="26" t="str">
         <f>[1]CARTELLINO!NI$15</f>
@@ -53191,19 +53191,19 @@
       </c>
       <c r="NE21" s="28" t="str">
         <f>[1]CARTELLINO!NH$21</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="NF21" s="28" t="str">
         <f>[1]CARTELLINO!NI$21</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="NG21" s="28" t="str">
         <f>[1]CARTELLINO!NJ$21</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="NH21" s="28" t="str">
         <f>[1]CARTELLINO!NK$21</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="NI21" s="28" t="str">
         <f>[1]CARTELLINO!NL$21</f>
@@ -54783,21 +54783,21 @@
         <f>[1]CARTELLINO!NG$22</f>
         <v>V</v>
       </c>
-      <c r="NE22" s="46" t="str">
+      <c r="NE22" s="46">
         <f>[1]CARTELLINO!NH$22</f>
-        <v>V</v>
-      </c>
-      <c r="NF22" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="NF22" s="46">
         <f>[1]CARTELLINO!NI$22</f>
-        <v>V</v>
-      </c>
-      <c r="NG22" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="NG22" s="46">
         <f>[1]CARTELLINO!NJ$22</f>
-        <v>V</v>
+        <v>0</v>
       </c>
       <c r="NH22" s="46" t="str">
         <f>[1]CARTELLINO!NK$22</f>
-        <v>V</v>
+        <v>ng</v>
       </c>
       <c r="NI22" s="46">
         <f>[1]CARTELLINO!NL$22</f>
@@ -66523,12 +66523,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71021,13 +71021,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71036,6 +71029,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB3AE14-04CB-4F14-9103-9FAEEDBD53DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD29D44-F660-49A6-924A-6BF86201D347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="240" windowWidth="28800" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5295,7 +5295,7 @@
             <v>BERARDI</v>
           </cell>
           <cell r="AT268" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="269">
@@ -9917,10 +9917,10 @@
             <v>M/R</v>
           </cell>
           <cell r="JE6" t="str">
-            <v>N</v>
+            <v>p</v>
           </cell>
           <cell r="JF6" t="str">
-            <v>S</v>
+            <v>m</v>
           </cell>
           <cell r="JG6" t="str">
             <v>R</v>
@@ -12264,22 +12264,22 @@
             <v>R</v>
           </cell>
           <cell r="IT9" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="IU9" t="str">
             <v>m/R</v>
           </cell>
           <cell r="IV9" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="IW9" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="IX9" t="str">
-            <v>M</v>
+            <v>R</v>
           </cell>
           <cell r="IY9" t="str">
-            <v>r</v>
+            <v>P</v>
           </cell>
           <cell r="IZ9" t="str">
             <v>M/R</v>
@@ -12297,7 +12297,7 @@
             <v>p</v>
           </cell>
           <cell r="JE9" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="JF9" t="str">
             <v>M/R</v>
@@ -14677,13 +14677,13 @@
             <v>m</v>
           </cell>
           <cell r="JE12" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="JF12" t="str">
             <v>r</v>
           </cell>
           <cell r="JG12" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="JH12" t="str">
             <v>N</v>
@@ -19410,10 +19410,10 @@
             <v>M</v>
           </cell>
           <cell r="IV18" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="IW18" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="IX18" t="str">
             <v>R</v>
@@ -19437,10 +19437,10 @@
             <v>-</v>
           </cell>
           <cell r="JE18" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="JF18" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="JG18" t="str">
             <v>R</v>
@@ -20599,11 +20599,11 @@
           <cell r="IU19">
             <v>0</v>
           </cell>
-          <cell r="IV19">
-            <v>0</v>
-          </cell>
-          <cell r="IW19">
-            <v>0</v>
+          <cell r="IV19" t="str">
+            <v>pn</v>
+          </cell>
+          <cell r="IW19" t="str">
+            <v>x</v>
           </cell>
           <cell r="IX19">
             <v>0</v>
@@ -20626,11 +20626,11 @@
           <cell r="JD19">
             <v>7</v>
           </cell>
-          <cell r="JE19" t="str">
-            <v>pn</v>
-          </cell>
-          <cell r="JF19" t="str">
-            <v>x</v>
+          <cell r="JE19">
+            <v>0</v>
+          </cell>
+          <cell r="JF19">
+            <v>0</v>
           </cell>
           <cell r="JG19" t="str">
             <v>f</v>
@@ -24176,10 +24176,10 @@
             <v>P</v>
           </cell>
           <cell r="IX24" t="str">
-            <v>m/R</v>
+            <v>M/R</v>
           </cell>
           <cell r="IY24" t="str">
-            <v>P</v>
+            <v>p</v>
           </cell>
           <cell r="IZ24" t="str">
             <v>r</v>
@@ -26577,10 +26577,10 @@
             <v>R</v>
           </cell>
           <cell r="JE27" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="JF27" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="JG27" t="str">
             <v>r</v>
@@ -28511,431 +28511,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28945,7 +28945,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -34783,11 +34783,11 @@
       </c>
       <c r="JB6" s="22" t="str">
         <f>[1]CARTELLINO!JE$6</f>
-        <v>N</v>
+        <v>p</v>
       </c>
       <c r="JC6" s="22" t="str">
         <f>[1]CARTELLINO!JF$6</f>
-        <v>S</v>
+        <v>m</v>
       </c>
       <c r="JD6" s="22" t="str">
         <f>[1]CARTELLINO!JG$6</f>
@@ -38335,7 +38335,7 @@
       </c>
       <c r="IQ9" s="24" t="str">
         <f>[1]CARTELLINO!IT$9</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="IR9" s="24" t="str">
         <f>[1]CARTELLINO!IU$9</f>
@@ -38343,19 +38343,19 @@
       </c>
       <c r="IS9" s="24" t="str">
         <f>[1]CARTELLINO!IV$9</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="IT9" s="24" t="str">
         <f>[1]CARTELLINO!IW$9</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="IU9" s="24" t="str">
         <f>[1]CARTELLINO!IX$9</f>
-        <v>M</v>
+        <v>R</v>
       </c>
       <c r="IV9" s="24" t="str">
         <f>[1]CARTELLINO!IY$9</f>
-        <v>r</v>
+        <v>P</v>
       </c>
       <c r="IW9" s="24" t="str">
         <f>[1]CARTELLINO!IZ$9</f>
@@ -38379,7 +38379,7 @@
       </c>
       <c r="JB9" s="24" t="str">
         <f>[1]CARTELLINO!JE$9</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="JC9" s="24" t="str">
         <f>[1]CARTELLINO!JF$9</f>
@@ -41975,7 +41975,7 @@
       </c>
       <c r="JB12" s="25" t="str">
         <f>[1]CARTELLINO!JE$12</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="JC12" s="25" t="str">
         <f>[1]CARTELLINO!JF$12</f>
@@ -41983,7 +41983,7 @@
       </c>
       <c r="JD12" s="25" t="str">
         <f>[1]CARTELLINO!JG$12</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="JE12" s="25" t="str">
         <f>[1]CARTELLINO!JH$12</f>
@@ -49131,11 +49131,11 @@
       </c>
       <c r="IS18" s="27" t="str">
         <f>[1]CARTELLINO!IV$18</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="IT18" s="27" t="str">
         <f>[1]CARTELLINO!IW$18</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="IU18" s="27" t="str">
         <f>[1]CARTELLINO!IX$18</f>
@@ -49167,11 +49167,11 @@
       </c>
       <c r="JB18" s="27" t="str">
         <f>[1]CARTELLINO!JE$18</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="JC18" s="27" t="str">
         <f>[1]CARTELLINO!JF$18</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="JD18" s="27" t="str">
         <f>[1]CARTELLINO!JG$18</f>
@@ -50723,13 +50723,13 @@
         <f>[1]CARTELLINO!IU$19</f>
         <v>0</v>
       </c>
-      <c r="IS19" s="46">
+      <c r="IS19" s="46" t="str">
         <f>[1]CARTELLINO!IV$19</f>
-        <v>0</v>
-      </c>
-      <c r="IT19" s="46">
+        <v>pn</v>
+      </c>
+      <c r="IT19" s="46" t="str">
         <f>[1]CARTELLINO!IW$19</f>
-        <v>0</v>
+        <v>x</v>
       </c>
       <c r="IU19" s="46">
         <f>[1]CARTELLINO!IX$19</f>
@@ -50759,13 +50759,13 @@
         <f>[1]CARTELLINO!JD$19</f>
         <v>7</v>
       </c>
-      <c r="JB19" s="46" t="str">
+      <c r="JB19" s="46">
         <f>[1]CARTELLINO!JE$19</f>
-        <v>pn</v>
-      </c>
-      <c r="JC19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="JC19" s="46">
         <f>[1]CARTELLINO!JF$19</f>
-        <v>x</v>
+        <v>0</v>
       </c>
       <c r="JD19" s="46" t="str">
         <f>[1]CARTELLINO!JG$19</f>
@@ -56331,11 +56331,11 @@
       </c>
       <c r="IU24" s="29" t="str">
         <f>[1]CARTELLINO!IX$24</f>
-        <v>m/R</v>
+        <v>M/R</v>
       </c>
       <c r="IV24" s="29" t="str">
         <f>[1]CARTELLINO!IY$24</f>
-        <v>P</v>
+        <v>p</v>
       </c>
       <c r="IW24" s="29" t="str">
         <f>[1]CARTELLINO!IZ$24</f>
@@ -59955,11 +59955,11 @@
       </c>
       <c r="JB27" s="30" t="str">
         <f>[1]CARTELLINO!JE$27</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="JC27" s="30" t="str">
         <f>[1]CARTELLINO!JF$27</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="JD27" s="30" t="str">
         <f>[1]CARTELLINO!JG$27</f>
@@ -66185,7 +66185,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="JB32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="JC32" s="63" t="str">
         <v>SARTI</v>
@@ -66523,12 +66523,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71021,6 +71021,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71029,13 +71036,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD29D44-F660-49A6-924A-6BF86201D347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E05A9C01-E62F-469B-9A22-6AC8F6181624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -14677,13 +14677,13 @@
             <v>m</v>
           </cell>
           <cell r="JE12" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="JF12" t="str">
             <v>r</v>
           </cell>
           <cell r="JG12" t="str">
-            <v>p</v>
+            <v>r</v>
           </cell>
           <cell r="JH12" t="str">
             <v>N</v>
@@ -41975,7 +41975,7 @@
       </c>
       <c r="JB12" s="25" t="str">
         <f>[1]CARTELLINO!JE$12</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="JC12" s="25" t="str">
         <f>[1]CARTELLINO!JF$12</f>
@@ -41983,7 +41983,7 @@
       </c>
       <c r="JD12" s="25" t="str">
         <f>[1]CARTELLINO!JG$12</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="JE12" s="25" t="str">
         <f>[1]CARTELLINO!JH$12</f>

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E05A9C01-E62F-469B-9A22-6AC8F6181624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7EFEB6-989B-48C9-9EA2-E7CDF9E09BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5810,18 +5810,18 @@
             <v>SARTI</v>
           </cell>
           <cell r="AS305" t="str">
-            <v>VOLPINI</v>
+            <v/>
           </cell>
           <cell r="AT305" t="str">
-            <v>VOLPINI</v>
+            <v/>
           </cell>
         </row>
         <row r="306">
           <cell r="AQ306" t="str">
-            <v>VOLPINI</v>
+            <v/>
           </cell>
           <cell r="AR306" t="str">
-            <v>VOLPINI</v>
+            <v/>
           </cell>
           <cell r="AS306" t="str">
             <v>GHIOTTI</v>
@@ -7576,13 +7576,13 @@
             <v>m</v>
           </cell>
           <cell r="JQ3" t="str">
-            <v>r</v>
+            <v>M</v>
           </cell>
           <cell r="JR3" t="str">
             <v>m</v>
           </cell>
           <cell r="JS3" t="str">
-            <v>p</v>
+            <v>r</v>
           </cell>
           <cell r="JT3" t="str">
             <v>P</v>
@@ -7648,7 +7648,7 @@
             <v>p</v>
           </cell>
           <cell r="KO3" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="KP3" t="str">
             <v>r</v>
@@ -8718,7 +8718,7 @@
             <v>0</v>
           </cell>
           <cell r="JA4">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="JB4" t="str">
             <v>pn</v>
@@ -9956,7 +9956,7 @@
             <v>p</v>
           </cell>
           <cell r="JR6" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="JS6" t="str">
             <v>r</v>
@@ -11145,8 +11145,8 @@
           <cell r="JQ7">
             <v>0</v>
           </cell>
-          <cell r="JR7" t="str">
-            <v>ng</v>
+          <cell r="JR7">
+            <v>0</v>
           </cell>
           <cell r="JS7">
             <v>0</v>
@@ -12336,13 +12336,13 @@
             <v>m/R</v>
           </cell>
           <cell r="JR9" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="JS9" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="JT9" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="JU9" t="str">
             <v>r</v>
@@ -14713,16 +14713,16 @@
             <v>r</v>
           </cell>
           <cell r="JQ12" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="JR12" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="JS12" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="JT12" t="str">
-            <v>R</v>
+            <v>r</v>
           </cell>
           <cell r="JU12" t="str">
             <v>P</v>
@@ -14785,10 +14785,10 @@
             <v>r</v>
           </cell>
           <cell r="KO12" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="KP12" t="str">
-            <v>m/R</v>
+            <v>-</v>
           </cell>
           <cell r="KQ12" t="str">
             <v>p</v>
@@ -15902,14 +15902,14 @@
           <cell r="JP13">
             <v>0</v>
           </cell>
-          <cell r="JQ13">
-            <v>0</v>
-          </cell>
-          <cell r="JR13">
-            <v>0</v>
+          <cell r="JQ13" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="JR13" t="str">
+            <v>nl</v>
           </cell>
           <cell r="JS13">
-            <v>0</v>
+            <v>7</v>
           </cell>
           <cell r="JT13">
             <v>0</v>
@@ -15977,8 +15977,8 @@
           <cell r="KO13">
             <v>0</v>
           </cell>
-          <cell r="KP13">
-            <v>0</v>
+          <cell r="KP13" t="str">
+            <v>p</v>
           </cell>
           <cell r="KQ13">
             <v>0</v>
@@ -21805,13 +21805,13 @@
             <v>-</v>
           </cell>
           <cell r="JA21" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="JB21" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JC21" t="str">
-            <v>R</v>
+            <v>m</v>
           </cell>
           <cell r="JD21" t="str">
             <v>P</v>
@@ -22994,14 +22994,14 @@
           <cell r="IZ22" t="str">
             <v>f</v>
           </cell>
-          <cell r="JA22" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="JB22" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="JC22" t="str">
-            <v>f</v>
+          <cell r="JA22">
+            <v>0</v>
+          </cell>
+          <cell r="JB22">
+            <v>0</v>
+          </cell>
+          <cell r="JC22">
+            <v>0</v>
           </cell>
           <cell r="JD22">
             <v>0</v>
@@ -26565,7 +26565,7 @@
             <v>R</v>
           </cell>
           <cell r="JA27" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="JB27" t="str">
             <v>N</v>
@@ -27754,8 +27754,8 @@
           <cell r="IZ28">
             <v>0</v>
           </cell>
-          <cell r="JA28">
-            <v>0</v>
+          <cell r="JA28" t="str">
+            <v>r</v>
           </cell>
           <cell r="JB28">
             <v>0</v>
@@ -28511,431 +28511,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28945,7 +28945,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31236,7 +31236,7 @@
       </c>
       <c r="JN3" s="16" t="str">
         <f>[1]CARTELLINO!JQ$3</f>
-        <v>r</v>
+        <v>M</v>
       </c>
       <c r="JO3" s="16" t="str">
         <f>[1]CARTELLINO!JR$3</f>
@@ -31244,7 +31244,7 @@
       </c>
       <c r="JP3" s="16" t="str">
         <f>[1]CARTELLINO!JS$3</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="JQ3" s="16" t="str">
         <f>[1]CARTELLINO!JT$3</f>
@@ -31332,7 +31332,7 @@
       </c>
       <c r="KL3" s="16" t="str">
         <f>[1]CARTELLINO!KO$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KM3" s="16" t="str">
         <f>[1]CARTELLINO!KP$3</f>
@@ -32766,7 +32766,7 @@
       </c>
       <c r="IX4" s="43">
         <f>[1]CARTELLINO!JA$4</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IY4" s="43" t="str">
         <f>[1]CARTELLINO!JB$4</f>
@@ -34835,7 +34835,7 @@
       </c>
       <c r="JO6" s="22" t="str">
         <f>[1]CARTELLINO!JR$6</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="JP6" s="22" t="str">
         <f>[1]CARTELLINO!JS$6</f>
@@ -36427,9 +36427,9 @@
         <f>[1]CARTELLINO!JQ$7</f>
         <v>0</v>
       </c>
-      <c r="JO7" s="46" t="str">
+      <c r="JO7" s="46">
         <f>[1]CARTELLINO!JR$7</f>
-        <v>ng</v>
+        <v>0</v>
       </c>
       <c r="JP7" s="46">
         <f>[1]CARTELLINO!JS$7</f>
@@ -38431,15 +38431,15 @@
       </c>
       <c r="JO9" s="24" t="str">
         <f>[1]CARTELLINO!JR$9</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="JP9" s="24" t="str">
         <f>[1]CARTELLINO!JS$9</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="JQ9" s="24" t="str">
         <f>[1]CARTELLINO!JT$9</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="JR9" s="24" t="str">
         <f>[1]CARTELLINO!JU$9</f>
@@ -42023,19 +42023,19 @@
       </c>
       <c r="JN12" s="25" t="str">
         <f>[1]CARTELLINO!JQ$12</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="JO12" s="25" t="str">
         <f>[1]CARTELLINO!JR$12</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="JP12" s="25" t="str">
         <f>[1]CARTELLINO!JS$12</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="JQ12" s="25" t="str">
         <f>[1]CARTELLINO!JT$12</f>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="JR12" s="25" t="str">
         <f>[1]CARTELLINO!JU$12</f>
@@ -42119,11 +42119,11 @@
       </c>
       <c r="KL12" s="25" t="str">
         <f>[1]CARTELLINO!KO$12</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="KM12" s="25" t="str">
         <f>[1]CARTELLINO!KP$12</f>
-        <v>m/R</v>
+        <v>-</v>
       </c>
       <c r="KN12" s="25" t="str">
         <f>[1]CARTELLINO!KQ$12</f>
@@ -43615,17 +43615,17 @@
         <f>[1]CARTELLINO!JP$13</f>
         <v>0</v>
       </c>
-      <c r="JN13" s="46">
+      <c r="JN13" s="46" t="str">
         <f>[1]CARTELLINO!JQ$13</f>
-        <v>0</v>
-      </c>
-      <c r="JO13" s="46">
+        <v>p</v>
+      </c>
+      <c r="JO13" s="46" t="str">
         <f>[1]CARTELLINO!JR$13</f>
-        <v>0</v>
+        <v>nl</v>
       </c>
       <c r="JP13" s="46">
         <f>[1]CARTELLINO!JS$13</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="JQ13" s="46">
         <f>[1]CARTELLINO!JT$13</f>
@@ -43715,9 +43715,9 @@
         <f>[1]CARTELLINO!KO$13</f>
         <v>0</v>
       </c>
-      <c r="KM13" s="46">
+      <c r="KM13" s="46" t="str">
         <f>[1]CARTELLINO!KP$13</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="KN13" s="46">
         <f>[1]CARTELLINO!KQ$13</f>
@@ -52747,15 +52747,15 @@
       </c>
       <c r="IX21" s="28" t="str">
         <f>[1]CARTELLINO!JA$21</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="IY21" s="28" t="str">
         <f>[1]CARTELLINO!JB$21</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="IZ21" s="28" t="str">
         <f>[1]CARTELLINO!JC$21</f>
-        <v>R</v>
+        <v>m</v>
       </c>
       <c r="JA21" s="28" t="str">
         <f>[1]CARTELLINO!JD$21</f>
@@ -54339,17 +54339,17 @@
         <f>[1]CARTELLINO!IZ$22</f>
         <v>f</v>
       </c>
-      <c r="IX22" s="46" t="str">
+      <c r="IX22" s="46">
         <f>[1]CARTELLINO!JA$22</f>
-        <v>f</v>
-      </c>
-      <c r="IY22" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="IY22" s="46">
         <f>[1]CARTELLINO!JB$22</f>
-        <v>f</v>
-      </c>
-      <c r="IZ22" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="IZ22" s="46">
         <f>[1]CARTELLINO!JC$22</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="JA22" s="46">
         <f>[1]CARTELLINO!JD$22</f>
@@ -59939,7 +59939,7 @@
       </c>
       <c r="IX27" s="30" t="str">
         <f>[1]CARTELLINO!JA$27</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="IY27" s="30" t="str">
         <f>[1]CARTELLINO!JB$27</f>
@@ -61531,9 +61531,9 @@
         <f>[1]CARTELLINO!IZ$28</f>
         <v>0</v>
       </c>
-      <c r="IX28" s="62">
+      <c r="IX28" s="62" t="str">
         <f>[1]CARTELLINO!JA$28</f>
-        <v>0</v>
+        <v>r</v>
       </c>
       <c r="IY28" s="62">
         <f>[1]CARTELLINO!JB$28</f>
@@ -62999,7 +62999,7 @@
         <v>SARTI</v>
       </c>
       <c r="KN29" s="63" t="str">
-        <v>VOLPINI</v>
+        <v/>
       </c>
       <c r="KO29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -64099,7 +64099,7 @@
         <v>SARTI</v>
       </c>
       <c r="KN30" s="63" t="str">
-        <v>VOLPINI</v>
+        <v/>
       </c>
       <c r="KO30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -65196,7 +65196,7 @@
         <v>SARTI</v>
       </c>
       <c r="KM31" s="63" t="str">
-        <v>VOLPINI</v>
+        <v/>
       </c>
       <c r="KN31" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66296,7 +66296,7 @@
         <v>SARTI</v>
       </c>
       <c r="KM32" s="63" t="str">
-        <v>VOLPINI</v>
+        <v/>
       </c>
       <c r="KN32" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66523,12 +66523,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71021,13 +71021,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71036,6 +71029,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7EFEB6-989B-48C9-9EA2-E7CDF9E09BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32582E35-D004-4C88-843D-7B333407A6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -28511,431 +28511,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28945,7 +28945,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -66523,12 +66523,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71021,6 +71021,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71029,13 +71036,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32582E35-D004-4C88-843D-7B333407A6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5699AC15-7D0C-4E3C-A012-28C8102C2C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5292,7 +5292,7 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AS268" t="str">
-            <v>BERARDI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT268" t="str">
             <v>FABBRI</v>
@@ -5300,10 +5300,10 @@
         </row>
         <row r="269">
           <cell r="AQ269" t="str">
-            <v>BERARDI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR269" t="str">
-            <v>BERARDI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS269" t="str">
             <v>SARTI</v>
@@ -6629,8 +6629,6 @@
           </cell>
         </row>
         <row r="364">
-          <cell r="AQ364"/>
-          <cell r="AR364"/>
           <cell r="AS364" t="str">
             <v>GHIOTTI</v>
           </cell>
@@ -6695,8 +6693,6 @@
           </cell>
         </row>
         <row r="369">
-          <cell r="AQ369"/>
-          <cell r="AR369"/>
           <cell r="AS369" t="str">
             <v>MICHELOT.</v>
           </cell>
@@ -19437,7 +19433,7 @@
             <v>-</v>
           </cell>
           <cell r="JE18" t="str">
-            <v>N</v>
+            <v>m/R</v>
           </cell>
           <cell r="JF18" t="str">
             <v>S</v>
@@ -28511,431 +28507,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28945,7 +28941,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -49167,7 +49163,7 @@
       </c>
       <c r="JB18" s="27" t="str">
         <f>[1]CARTELLINO!JE$18</f>
-        <v>N</v>
+        <v>m/R</v>
       </c>
       <c r="JC18" s="27" t="str">
         <f>[1]CARTELLINO!JF$18</f>
@@ -62888,7 +62884,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="JC29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="JD29" s="63" t="str">
         <v>SARTI</v>
@@ -63988,7 +63984,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="JC30" s="63" t="str">
-        <v>BERARDI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="JD30" s="63" t="str">
         <v>SARTI</v>
@@ -65085,7 +65081,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="JB31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="JC31" s="63" t="str">
         <v>SARTI</v>
@@ -66523,12 +66519,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71021,13 +71017,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71036,6 +71025,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5699AC15-7D0C-4E3C-A012-28C8102C2C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062CD948-D68F-4645-9E8A-2A4B8187AF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5292,7 +5292,7 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AS268" t="str">
-            <v>MICHELOT.</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT268" t="str">
             <v>FABBRI</v>
@@ -5300,10 +5300,10 @@
         </row>
         <row r="269">
           <cell r="AQ269" t="str">
-            <v>MICHELOT.</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR269" t="str">
-            <v>MICHELOT.</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS269" t="str">
             <v>SARTI</v>
@@ -6629,6 +6629,8 @@
           </cell>
         </row>
         <row r="364">
+          <cell r="AQ364"/>
+          <cell r="AR364"/>
           <cell r="AS364" t="str">
             <v>GHIOTTI</v>
           </cell>
@@ -6693,6 +6695,8 @@
           </cell>
         </row>
         <row r="369">
+          <cell r="AQ369"/>
+          <cell r="AR369"/>
           <cell r="AS369" t="str">
             <v>MICHELOT.</v>
           </cell>
@@ -19433,7 +19437,7 @@
             <v>-</v>
           </cell>
           <cell r="JE18" t="str">
-            <v>m/R</v>
+            <v>N</v>
           </cell>
           <cell r="JF18" t="str">
             <v>S</v>
@@ -28507,431 +28511,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28941,7 +28945,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -49163,7 +49167,7 @@
       </c>
       <c r="JB18" s="27" t="str">
         <f>[1]CARTELLINO!JE$18</f>
-        <v>m/R</v>
+        <v>N</v>
       </c>
       <c r="JC18" s="27" t="str">
         <f>[1]CARTELLINO!JF$18</f>
@@ -62884,7 +62888,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="JC29" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BERARDI</v>
       </c>
       <c r="JD29" s="63" t="str">
         <v>SARTI</v>
@@ -63984,7 +63988,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="JC30" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BERARDI</v>
       </c>
       <c r="JD30" s="63" t="str">
         <v>SARTI</v>
@@ -65081,7 +65085,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="JB31" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BERARDI</v>
       </c>
       <c r="JC31" s="63" t="str">
         <v>SARTI</v>
@@ -66519,12 +66523,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71017,6 +71021,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71025,13 +71036,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062CD948-D68F-4645-9E8A-2A4B8187AF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF52817B-E212-417B-87D3-9CCE5FDC5632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5127,7 +5127,7 @@
             <v>MICHELOT.</v>
           </cell>
           <cell r="AT256" t="str">
-            <v>MICHELOT.</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="257">
@@ -5810,18 +5810,18 @@
             <v>SARTI</v>
           </cell>
           <cell r="AS305" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT305" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="306">
           <cell r="AQ306" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR306" t="str">
-            <v/>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS306" t="str">
             <v>GHIOTTI</v>
@@ -7609,13 +7609,13 @@
             <v>p</v>
           </cell>
           <cell r="KB3" t="str">
-            <v>m</v>
+            <v>N</v>
           </cell>
           <cell r="KC3" t="str">
-            <v>r</v>
+            <v>S</v>
           </cell>
           <cell r="KD3" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="KE3" t="str">
             <v>P</v>
@@ -10028,7 +10028,7 @@
             <v>P</v>
           </cell>
           <cell r="KP6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KQ6" t="str">
             <v>N</v>
@@ -14746,13 +14746,13 @@
             <v>M</v>
           </cell>
           <cell r="KB12" t="str">
-            <v>N</v>
+            <v>m</v>
           </cell>
           <cell r="KC12" t="str">
-            <v>S</v>
+            <v>r</v>
           </cell>
           <cell r="KD12" t="str">
-            <v>R</v>
+            <v>r</v>
           </cell>
           <cell r="KE12" t="str">
             <v>-</v>
@@ -28511,431 +28511,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28945,7 +28945,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31280,15 +31280,15 @@
       </c>
       <c r="JY3" s="16" t="str">
         <f>[1]CARTELLINO!KB$3</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="JZ3" s="16" t="str">
         <f>[1]CARTELLINO!KC$3</f>
-        <v>r</v>
+        <v>S</v>
       </c>
       <c r="KA3" s="16" t="str">
         <f>[1]CARTELLINO!KD$3</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="KB3" s="16" t="str">
         <f>[1]CARTELLINO!KE$3</f>
@@ -34931,7 +34931,7 @@
       </c>
       <c r="KM6" s="22" t="str">
         <f>[1]CARTELLINO!KP$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KN6" s="22" t="str">
         <f>[1]CARTELLINO!KQ$6</f>
@@ -42067,15 +42067,15 @@
       </c>
       <c r="JY12" s="25" t="str">
         <f>[1]CARTELLINO!KB$12</f>
-        <v>N</v>
+        <v>m</v>
       </c>
       <c r="JZ12" s="25" t="str">
         <f>[1]CARTELLINO!KC$12</f>
-        <v>S</v>
+        <v>r</v>
       </c>
       <c r="KA12" s="25" t="str">
         <f>[1]CARTELLINO!KD$12</f>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="KB12" s="25" t="str">
         <f>[1]CARTELLINO!KE$12</f>
@@ -62999,7 +62999,7 @@
         <v>SARTI</v>
       </c>
       <c r="KN29" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="KO29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -64099,7 +64099,7 @@
         <v>SARTI</v>
       </c>
       <c r="KN30" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="KO30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -65196,7 +65196,7 @@
         <v>SARTI</v>
       </c>
       <c r="KM31" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="KN31" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66149,7 +66149,7 @@
         <v>FABBRI</v>
       </c>
       <c r="IP32" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>VOLPINI</v>
       </c>
       <c r="IQ32" s="63" t="str">
         <v>BARBIERI</v>
@@ -66296,7 +66296,7 @@
         <v>SARTI</v>
       </c>
       <c r="KM32" s="63" t="str">
-        <v/>
+        <v>BARBIERI</v>
       </c>
       <c r="KN32" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66523,12 +66523,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71021,13 +71021,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71036,6 +71029,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF52817B-E212-417B-87D3-9CCE5FDC5632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A41B61-3C53-415B-8AF8-D716350F58F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7567,7 +7567,7 @@
             <v>p</v>
           </cell>
           <cell r="JN3" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="JO3" t="str">
             <v>p</v>
@@ -7576,7 +7576,7 @@
             <v>m</v>
           </cell>
           <cell r="JQ3" t="str">
-            <v>M</v>
+            <v>m</v>
           </cell>
           <cell r="JR3" t="str">
             <v>m</v>
@@ -12333,7 +12333,7 @@
             <v>P</v>
           </cell>
           <cell r="JQ9" t="str">
-            <v>m/R</v>
+            <v>M/R</v>
           </cell>
           <cell r="JR9" t="str">
             <v>N</v>
@@ -17039,13 +17039,13 @@
             <v>R</v>
           </cell>
           <cell r="IY15" t="str">
-            <v>N</v>
+            <v>p</v>
           </cell>
           <cell r="IZ15" t="str">
-            <v>S</v>
+            <v>m</v>
           </cell>
           <cell r="JA15" t="str">
-            <v>R</v>
+            <v>r</v>
           </cell>
           <cell r="JB15" t="str">
             <v>P</v>
@@ -19422,7 +19422,7 @@
             <v>r</v>
           </cell>
           <cell r="IZ18" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="JA18" t="str">
             <v>m/R</v>
@@ -20611,8 +20611,8 @@
           <cell r="IY19">
             <v>0</v>
           </cell>
-          <cell r="IZ19">
-            <v>0</v>
+          <cell r="IZ19" t="str">
+            <v>p</v>
           </cell>
           <cell r="JA19">
             <v>0</v>
@@ -20632,8 +20632,8 @@
           <cell r="JF19">
             <v>0</v>
           </cell>
-          <cell r="JG19" t="str">
-            <v>f</v>
+          <cell r="JG19">
+            <v>0</v>
           </cell>
           <cell r="JH19" t="str">
             <v>f</v>
@@ -21844,7 +21844,7 @@
             <v>R</v>
           </cell>
           <cell r="JN21" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="JO21" t="str">
             <v>M/R</v>
@@ -22919,8 +22919,8 @@
           <cell r="IA22">
             <v>0</v>
           </cell>
-          <cell r="IB22" t="str">
-            <v>r</v>
+          <cell r="IB22">
+            <v>0</v>
           </cell>
           <cell r="IC22">
             <v>0</v>
@@ -24179,13 +24179,13 @@
             <v>M/R</v>
           </cell>
           <cell r="IY24" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="IZ24" t="str">
-            <v>r</v>
+            <v>S</v>
           </cell>
           <cell r="JA24" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="JB24" t="str">
             <v>M/R</v>
@@ -28511,431 +28511,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28945,7 +28945,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31224,7 +31224,7 @@
       </c>
       <c r="JK3" s="16" t="str">
         <f>[1]CARTELLINO!JN$3</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="JL3" s="16" t="str">
         <f>[1]CARTELLINO!JO$3</f>
@@ -31236,7 +31236,7 @@
       </c>
       <c r="JN3" s="16" t="str">
         <f>[1]CARTELLINO!JQ$3</f>
-        <v>M</v>
+        <v>m</v>
       </c>
       <c r="JO3" s="16" t="str">
         <f>[1]CARTELLINO!JR$3</f>
@@ -38427,7 +38427,7 @@
       </c>
       <c r="JN9" s="24" t="str">
         <f>[1]CARTELLINO!JQ$9</f>
-        <v>m/R</v>
+        <v>M/R</v>
       </c>
       <c r="JO9" s="24" t="str">
         <f>[1]CARTELLINO!JR$9</f>
@@ -45547,15 +45547,15 @@
       </c>
       <c r="IV15" s="26" t="str">
         <f>[1]CARTELLINO!IY$15</f>
-        <v>N</v>
+        <v>p</v>
       </c>
       <c r="IW15" s="26" t="str">
         <f>[1]CARTELLINO!IZ$15</f>
-        <v>S</v>
+        <v>m</v>
       </c>
       <c r="IX15" s="26" t="str">
         <f>[1]CARTELLINO!JA$15</f>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="IY15" s="26" t="str">
         <f>[1]CARTELLINO!JB$15</f>
@@ -49147,7 +49147,7 @@
       </c>
       <c r="IW18" s="27" t="str">
         <f>[1]CARTELLINO!IZ$18</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="IX18" s="27" t="str">
         <f>[1]CARTELLINO!JA$18</f>
@@ -50739,9 +50739,9 @@
         <f>[1]CARTELLINO!IY$19</f>
         <v>0</v>
       </c>
-      <c r="IW19" s="46">
+      <c r="IW19" s="46" t="str">
         <f>[1]CARTELLINO!IZ$19</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="IX19" s="46">
         <f>[1]CARTELLINO!JA$19</f>
@@ -50767,9 +50767,9 @@
         <f>[1]CARTELLINO!JF$19</f>
         <v>0</v>
       </c>
-      <c r="JD19" s="46" t="str">
+      <c r="JD19" s="46">
         <f>[1]CARTELLINO!JG$19</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="JE19" s="46" t="str">
         <f>[1]CARTELLINO!JH$19</f>
@@ -52799,7 +52799,7 @@
       </c>
       <c r="JK21" s="28" t="str">
         <f>[1]CARTELLINO!JN$21</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="JL21" s="28" t="str">
         <f>[1]CARTELLINO!JO$21</f>
@@ -54239,9 +54239,9 @@
         <f>[1]CARTELLINO!IA$22</f>
         <v>0</v>
       </c>
-      <c r="HY22" s="46" t="str">
+      <c r="HY22" s="46">
         <f>[1]CARTELLINO!IB$22</f>
-        <v>r</v>
+        <v>0</v>
       </c>
       <c r="HZ22" s="46">
         <f>[1]CARTELLINO!IC$22</f>
@@ -56335,15 +56335,15 @@
       </c>
       <c r="IV24" s="29" t="str">
         <f>[1]CARTELLINO!IY$24</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="IW24" s="29" t="str">
         <f>[1]CARTELLINO!IZ$24</f>
-        <v>r</v>
+        <v>S</v>
       </c>
       <c r="IX24" s="29" t="str">
         <f>[1]CARTELLINO!JA$24</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="IY24" s="29" t="str">
         <f>[1]CARTELLINO!JB$24</f>
@@ -66523,12 +66523,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71021,6 +71021,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71029,13 +71036,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A41B61-3C53-415B-8AF8-D716350F58F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB5F43B-3704-451B-ABF4-09A7BE138B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5177,7 +5177,7 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR260" t="str">
-            <v>BIANCHI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS260" t="str">
             <v>VOLPINI</v>
@@ -28511,431 +28511,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28945,7 +28945,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -63961,7 +63961,7 @@
         <v>SARTI</v>
       </c>
       <c r="IT30" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="IU30" s="63" t="str">
         <v>VOLPINI</v>
@@ -66523,12 +66523,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71021,13 +71021,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71036,6 +71029,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB5F43B-3704-451B-ABF4-09A7BE138B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7AC6E3-8441-4FBB-84CB-C9E72E316C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5264,18 +5264,18 @@
             <v>BIANCHI</v>
           </cell>
           <cell r="AS266" t="str">
-            <v>GHIOTTI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT266" t="str">
-            <v>GHIOTTI</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="267">
           <cell r="AQ267" t="str">
-            <v>GHIOTTI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR267" t="str">
-            <v>GHIOTTI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS267" t="str">
             <v>BARBIERI</v>
@@ -5334,18 +5334,18 @@
             <v>BIANCHI</v>
           </cell>
           <cell r="AS271" t="str">
-            <v>GHIOTTI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT271" t="str">
-            <v>GHIOTTI</v>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="272">
           <cell r="AQ272" t="str">
-            <v>GHIOTTI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR272" t="str">
-            <v>GHIOTTI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS272" t="str">
             <v>FABBRI</v>
@@ -5362,18 +5362,18 @@
             <v>FABBRI</v>
           </cell>
           <cell r="AS273" t="str">
-            <v>BARBIERI</v>
+            <v>SARTI</v>
           </cell>
           <cell r="AT273" t="str">
-            <v>BARBIERI</v>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="274">
           <cell r="AQ274" t="str">
-            <v>BARBIERI</v>
+            <v>SARTI</v>
           </cell>
           <cell r="AR274" t="str">
-            <v>BARBIERI</v>
+            <v>SARTI</v>
           </cell>
           <cell r="AS274" t="str">
             <v>PAZZAGLIA</v>
@@ -5404,18 +5404,18 @@
             <v>VOLPINI</v>
           </cell>
           <cell r="AS276" t="str">
-            <v>MICHELOT.</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT276" t="str">
-            <v>MICHELOT.</v>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="277">
           <cell r="AQ277" t="str">
-            <v>MICHELOT.</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR277" t="str">
-            <v>MICHELOT.</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS277" t="str">
             <v>FABBRI</v>
@@ -5572,18 +5572,18 @@
             <v>MICHELOT.</v>
           </cell>
           <cell r="AS288" t="str">
-            <v>BARBIERI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT288" t="str">
-            <v>BARBIERI</v>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="289">
           <cell r="AQ289" t="str">
-            <v>BARBIERI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR289" t="str">
-            <v>BARBIERI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS289" t="str">
             <v>PAZZAGLIA</v>
@@ -6412,18 +6412,18 @@
             <v>FABBRI</v>
           </cell>
           <cell r="AS348" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT348" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="349">
           <cell r="AQ349" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR349" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS349" t="str">
             <v>MICHELOT.</v>
@@ -6454,18 +6454,18 @@
             <v>SARTI</v>
           </cell>
           <cell r="AS351" t="str">
-            <v>BARBIERI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT351" t="str">
-            <v>BARBIERI</v>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="352">
           <cell r="AQ352" t="str">
-            <v>BARBIERI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR352" t="str">
-            <v>BARBIERI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS352" t="str">
             <v>BIANCHI</v>
@@ -6629,8 +6629,6 @@
           </cell>
         </row>
         <row r="364">
-          <cell r="AQ364"/>
-          <cell r="AR364"/>
           <cell r="AS364" t="str">
             <v>GHIOTTI</v>
           </cell>
@@ -6695,21 +6693,19 @@
           </cell>
         </row>
         <row r="369">
-          <cell r="AQ369"/>
-          <cell r="AR369"/>
           <cell r="AS369" t="str">
-            <v>MICHELOT.</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT369" t="str">
-            <v>MICHELOT.</v>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="370">
           <cell r="AQ370" t="str">
-            <v>MICHELOT.</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR370" t="str">
-            <v>MICHELOT.</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS370" t="str">
             <v>GHIOTTI</v>
@@ -7576,7 +7572,7 @@
             <v>m</v>
           </cell>
           <cell r="JQ3" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="JR3" t="str">
             <v>m</v>
@@ -7780,7 +7776,7 @@
             <v>p</v>
           </cell>
           <cell r="MG3" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="MH3" t="str">
             <v>p</v>
@@ -7789,7 +7785,7 @@
             <v>p</v>
           </cell>
           <cell r="MJ3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MK3" t="str">
             <v>N</v>
@@ -9920,19 +9916,19 @@
             <v>p</v>
           </cell>
           <cell r="JF6" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="JG6" t="str">
-            <v>R</v>
+            <v>P</v>
           </cell>
           <cell r="JH6" t="str">
-            <v>m</v>
+            <v>M/R</v>
           </cell>
           <cell r="JI6" t="str">
             <v>p</v>
           </cell>
           <cell r="JJ6" t="str">
-            <v>m/R</v>
+            <v>r</v>
           </cell>
           <cell r="JK6" t="str">
             <v>p</v>
@@ -9977,7 +9973,7 @@
             <v>m</v>
           </cell>
           <cell r="JY6" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="JZ6" t="str">
             <v>p</v>
@@ -10166,7 +10162,7 @@
             <v>m</v>
           </cell>
           <cell r="MJ6" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="MK6" t="str">
             <v>p</v>
@@ -10220,7 +10216,7 @@
             <v>r</v>
           </cell>
           <cell r="NB6" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="NC6" t="str">
             <v>p</v>
@@ -12312,7 +12308,7 @@
             <v>R</v>
           </cell>
           <cell r="JJ9" t="str">
-            <v>p</v>
+            <v>m/R</v>
           </cell>
           <cell r="JK9" t="str">
             <v>N</v>
@@ -12357,10 +12353,10 @@
             <v>R</v>
           </cell>
           <cell r="JY9" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="JZ9" t="str">
-            <v>p</v>
+            <v>M</v>
           </cell>
           <cell r="KA9" t="str">
             <v>N</v>
@@ -13381,8 +13377,8 @@
           <cell r="HU10" t="str">
             <v>p</v>
           </cell>
-          <cell r="HV10" t="str">
-            <v>p</v>
+          <cell r="HV10">
+            <v>7</v>
           </cell>
           <cell r="HW10">
             <v>0</v>
@@ -13628,10 +13624,10 @@
             <v>f</v>
           </cell>
           <cell r="KZ10" t="str">
-            <v>f</v>
+            <v>pn</v>
           </cell>
           <cell r="LA10" t="str">
-            <v>f</v>
+            <v>x</v>
           </cell>
           <cell r="LB10" t="str">
             <v>f</v>
@@ -14668,19 +14664,19 @@
             <v>p</v>
           </cell>
           <cell r="JB12" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="JC12" t="str">
-            <v>p</v>
+            <v>M/R</v>
           </cell>
           <cell r="JD12" t="str">
-            <v>m</v>
+            <v>N</v>
           </cell>
           <cell r="JE12" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="JF12" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="JG12" t="str">
             <v>r</v>
@@ -14917,7 +14913,7 @@
             <v>P</v>
           </cell>
           <cell r="MG12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MH12" t="str">
             <v>N</v>
@@ -17039,49 +17035,49 @@
             <v>R</v>
           </cell>
           <cell r="IY15" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="IZ15" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JA15" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JB15" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JC15" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="JD15" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JE15" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JF15" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JG15" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JH15" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="JI15" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="JJ15" t="str">
             <v>p</v>
           </cell>
-          <cell r="IZ15" t="str">
+          <cell r="JK15" t="str">
             <v>m</v>
-          </cell>
-          <cell r="JA15" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="JB15" t="str">
-            <v>P</v>
-          </cell>
-          <cell r="JC15" t="str">
-            <v>M/R</v>
-          </cell>
-          <cell r="JD15" t="str">
-            <v>N</v>
-          </cell>
-          <cell r="JE15" t="str">
-            <v>S</v>
-          </cell>
-          <cell r="JF15" t="str">
-            <v>R</v>
-          </cell>
-          <cell r="JG15" t="str">
-            <v>P</v>
-          </cell>
-          <cell r="JH15" t="str">
-            <v>M/R</v>
-          </cell>
-          <cell r="JI15" t="str">
-            <v>N</v>
-          </cell>
-          <cell r="JJ15" t="str">
-            <v>S</v>
-          </cell>
-          <cell r="JK15" t="str">
-            <v>R</v>
           </cell>
           <cell r="JL15" t="str">
             <v>P</v>
           </cell>
           <cell r="JM15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JN15" t="str">
             <v>N</v>
@@ -17093,7 +17089,7 @@
             <v>R</v>
           </cell>
           <cell r="JQ15" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="JR15" t="str">
             <v>M/R</v>
@@ -18228,35 +18224,35 @@
           <cell r="IX16" t="str">
             <v>m</v>
           </cell>
-          <cell r="IY16">
-            <v>0</v>
-          </cell>
-          <cell r="IZ16">
-            <v>0</v>
-          </cell>
-          <cell r="JA16">
-            <v>0</v>
-          </cell>
-          <cell r="JB16">
-            <v>0</v>
-          </cell>
-          <cell r="JC16">
-            <v>0</v>
-          </cell>
-          <cell r="JD16">
-            <v>0</v>
-          </cell>
-          <cell r="JE16">
-            <v>0</v>
-          </cell>
-          <cell r="JF16">
-            <v>0</v>
-          </cell>
-          <cell r="JG16">
-            <v>0</v>
-          </cell>
-          <cell r="JH16">
-            <v>0</v>
+          <cell r="IY16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="IZ16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="JA16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="JB16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="JC16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="JD16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="JE16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="JF16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="JG16" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="JH16" t="str">
+            <v>m</v>
           </cell>
           <cell r="JI16">
             <v>0</v>
@@ -19461,7 +19457,7 @@
             <v>R</v>
           </cell>
           <cell r="JM18" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="JN18" t="str">
             <v>p</v>
@@ -19740,7 +19736,7 @@
             <v>P</v>
           </cell>
           <cell r="NB18" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="NC18" t="str">
             <v>N</v>
@@ -21877,7 +21873,7 @@
             <v>P</v>
           </cell>
           <cell r="JY21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="JZ21" t="str">
             <v>N</v>
@@ -24209,13 +24205,13 @@
             <v>p</v>
           </cell>
           <cell r="JI24" t="str">
-            <v>m</v>
+            <v>N</v>
           </cell>
           <cell r="JJ24" t="str">
-            <v>r</v>
+            <v>S</v>
           </cell>
           <cell r="JK24" t="str">
-            <v>m</v>
+            <v>R</v>
           </cell>
           <cell r="JL24" t="str">
             <v>N</v>
@@ -24257,10 +24253,10 @@
             <v>p</v>
           </cell>
           <cell r="JY24" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="JZ24" t="str">
-            <v>M</v>
+            <v>p</v>
           </cell>
           <cell r="KA24" t="str">
             <v>m</v>
@@ -28511,431 +28507,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28945,7 +28941,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31236,7 +31232,7 @@
       </c>
       <c r="JN3" s="16" t="str">
         <f>[1]CARTELLINO!JQ$3</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="JO3" s="16" t="str">
         <f>[1]CARTELLINO!JR$3</f>
@@ -31508,7 +31504,7 @@
       </c>
       <c r="MD3" s="16" t="str">
         <f>[1]CARTELLINO!MG$3</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="ME3" s="16" t="str">
         <f>[1]CARTELLINO!MH$3</f>
@@ -31520,7 +31516,7 @@
       </c>
       <c r="MG3" s="16" t="str">
         <f>[1]CARTELLINO!MJ$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MH3" s="16" t="str">
         <f>[1]CARTELLINO!MK$3</f>
@@ -34787,15 +34783,15 @@
       </c>
       <c r="JC6" s="22" t="str">
         <f>[1]CARTELLINO!JF$6</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="JD6" s="22" t="str">
         <f>[1]CARTELLINO!JG$6</f>
-        <v>R</v>
+        <v>P</v>
       </c>
       <c r="JE6" s="22" t="str">
         <f>[1]CARTELLINO!JH$6</f>
-        <v>m</v>
+        <v>M/R</v>
       </c>
       <c r="JF6" s="22" t="str">
         <f>[1]CARTELLINO!JI$6</f>
@@ -34803,7 +34799,7 @@
       </c>
       <c r="JG6" s="22" t="str">
         <f>[1]CARTELLINO!JJ$6</f>
-        <v>m/R</v>
+        <v>r</v>
       </c>
       <c r="JH6" s="22" t="str">
         <f>[1]CARTELLINO!JK$6</f>
@@ -34863,7 +34859,7 @@
       </c>
       <c r="JV6" s="22" t="str">
         <f>[1]CARTELLINO!JY$6</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="JW6" s="22" t="str">
         <f>[1]CARTELLINO!JZ$6</f>
@@ -35115,7 +35111,7 @@
       </c>
       <c r="MG6" s="22" t="str">
         <f>[1]CARTELLINO!MJ$6</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="MH6" s="22" t="str">
         <f>[1]CARTELLINO!MK$6</f>
@@ -35187,7 +35183,7 @@
       </c>
       <c r="MY6" s="22" t="str">
         <f>[1]CARTELLINO!NB$6</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="MZ6" s="22" t="str">
         <f>[1]CARTELLINO!NC$6</f>
@@ -38399,7 +38395,7 @@
       </c>
       <c r="JG9" s="24" t="str">
         <f>[1]CARTELLINO!JJ$9</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="JH9" s="24" t="str">
         <f>[1]CARTELLINO!JK$9</f>
@@ -38459,11 +38455,11 @@
       </c>
       <c r="JV9" s="24" t="str">
         <f>[1]CARTELLINO!JY$9</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="JW9" s="24" t="str">
         <f>[1]CARTELLINO!JZ$9</f>
-        <v>p</v>
+        <v>M</v>
       </c>
       <c r="JX9" s="24" t="str">
         <f>[1]CARTELLINO!KA$9</f>
@@ -39831,9 +39827,9 @@
         <f>[1]CARTELLINO!HU$10</f>
         <v>p</v>
       </c>
-      <c r="HS10" s="46" t="str">
+      <c r="HS10" s="46">
         <f>[1]CARTELLINO!HV$10</f>
-        <v>p</v>
+        <v>7</v>
       </c>
       <c r="HT10" s="46">
         <f>[1]CARTELLINO!HW$10</f>
@@ -40161,11 +40157,11 @@
       </c>
       <c r="KW10" s="46" t="str">
         <f>[1]CARTELLINO!KZ$10</f>
-        <v>f</v>
+        <v>pn</v>
       </c>
       <c r="KX10" s="46" t="str">
         <f>[1]CARTELLINO!LA$10</f>
-        <v>f</v>
+        <v>x</v>
       </c>
       <c r="KY10" s="46" t="str">
         <f>[1]CARTELLINO!LB$10</f>
@@ -41963,23 +41959,23 @@
       </c>
       <c r="IY12" s="25" t="str">
         <f>[1]CARTELLINO!JB$12</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="IZ12" s="25" t="str">
         <f>[1]CARTELLINO!JC$12</f>
-        <v>p</v>
+        <v>M/R</v>
       </c>
       <c r="JA12" s="25" t="str">
         <f>[1]CARTELLINO!JD$12</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="JB12" s="25" t="str">
         <f>[1]CARTELLINO!JE$12</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="JC12" s="25" t="str">
         <f>[1]CARTELLINO!JF$12</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="JD12" s="25" t="str">
         <f>[1]CARTELLINO!JG$12</f>
@@ -42295,7 +42291,7 @@
       </c>
       <c r="MD12" s="25" t="str">
         <f>[1]CARTELLINO!MG$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="ME12" s="25" t="str">
         <f>[1]CARTELLINO!MH$12</f>
@@ -45547,55 +45543,55 @@
       </c>
       <c r="IV15" s="26" t="str">
         <f>[1]CARTELLINO!IY$15</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="IW15" s="26" t="str">
         <f>[1]CARTELLINO!IZ$15</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="IX15" s="26" t="str">
         <f>[1]CARTELLINO!JA$15</f>
-        <v>r</v>
+        <v>-</v>
       </c>
       <c r="IY15" s="26" t="str">
         <f>[1]CARTELLINO!JB$15</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="IZ15" s="26" t="str">
         <f>[1]CARTELLINO!JC$15</f>
-        <v>M/R</v>
+        <v>R</v>
       </c>
       <c r="JA15" s="26" t="str">
         <f>[1]CARTELLINO!JD$15</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="JB15" s="26" t="str">
         <f>[1]CARTELLINO!JE$15</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="JC15" s="26" t="str">
         <f>[1]CARTELLINO!JF$15</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="JD15" s="26" t="str">
         <f>[1]CARTELLINO!JG$15</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="JE15" s="26" t="str">
         <f>[1]CARTELLINO!JH$15</f>
-        <v>M/R</v>
+        <v>R</v>
       </c>
       <c r="JF15" s="26" t="str">
         <f>[1]CARTELLINO!JI$15</f>
-        <v>N</v>
+        <v>m</v>
       </c>
       <c r="JG15" s="26" t="str">
         <f>[1]CARTELLINO!JJ$15</f>
-        <v>S</v>
+        <v>p</v>
       </c>
       <c r="JH15" s="26" t="str">
         <f>[1]CARTELLINO!JK$15</f>
-        <v>R</v>
+        <v>m</v>
       </c>
       <c r="JI15" s="26" t="str">
         <f>[1]CARTELLINO!JL$15</f>
@@ -45603,7 +45599,7 @@
       </c>
       <c r="JJ15" s="26" t="str">
         <f>[1]CARTELLINO!JM$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JK15" s="26" t="str">
         <f>[1]CARTELLINO!JN$15</f>
@@ -45619,7 +45615,7 @@
       </c>
       <c r="JN15" s="26" t="str">
         <f>[1]CARTELLINO!JQ$15</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="JO15" s="26" t="str">
         <f>[1]CARTELLINO!JR$15</f>
@@ -47139,45 +47135,45 @@
         <f>[1]CARTELLINO!IX$16</f>
         <v>m</v>
       </c>
-      <c r="IV16" s="46">
+      <c r="IV16" s="46" t="str">
         <f>[1]CARTELLINO!IY$16</f>
-        <v>0</v>
-      </c>
-      <c r="IW16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IW16" s="46" t="str">
         <f>[1]CARTELLINO!IZ$16</f>
-        <v>0</v>
-      </c>
-      <c r="IX16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IX16" s="46" t="str">
         <f>[1]CARTELLINO!JA$16</f>
-        <v>0</v>
-      </c>
-      <c r="IY16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IY16" s="46" t="str">
         <f>[1]CARTELLINO!JB$16</f>
-        <v>0</v>
-      </c>
-      <c r="IZ16" s="46">
+        <v>m</v>
+      </c>
+      <c r="IZ16" s="46" t="str">
         <f>[1]CARTELLINO!JC$16</f>
-        <v>0</v>
-      </c>
-      <c r="JA16" s="46">
+        <v>m</v>
+      </c>
+      <c r="JA16" s="46" t="str">
         <f>[1]CARTELLINO!JD$16</f>
-        <v>0</v>
-      </c>
-      <c r="JB16" s="46">
+        <v>m</v>
+      </c>
+      <c r="JB16" s="46" t="str">
         <f>[1]CARTELLINO!JE$16</f>
-        <v>0</v>
-      </c>
-      <c r="JC16" s="46">
+        <v>m</v>
+      </c>
+      <c r="JC16" s="46" t="str">
         <f>[1]CARTELLINO!JF$16</f>
-        <v>0</v>
-      </c>
-      <c r="JD16" s="46">
+        <v>m</v>
+      </c>
+      <c r="JD16" s="46" t="str">
         <f>[1]CARTELLINO!JG$16</f>
-        <v>0</v>
-      </c>
-      <c r="JE16" s="46">
+        <v>m</v>
+      </c>
+      <c r="JE16" s="46" t="str">
         <f>[1]CARTELLINO!JH$16</f>
-        <v>0</v>
+        <v>m</v>
       </c>
       <c r="JF16" s="46">
         <f>[1]CARTELLINO!JI$16</f>
@@ -49199,7 +49195,7 @@
       </c>
       <c r="JJ18" s="27" t="str">
         <f>[1]CARTELLINO!JM$18</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="JK18" s="27" t="str">
         <f>[1]CARTELLINO!JN$18</f>
@@ -49571,7 +49567,7 @@
       </c>
       <c r="MY18" s="27" t="str">
         <f>[1]CARTELLINO!NB$18</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="MZ18" s="27" t="str">
         <f>[1]CARTELLINO!NC$18</f>
@@ -52843,7 +52839,7 @@
       </c>
       <c r="JV21" s="28" t="str">
         <f>[1]CARTELLINO!JY$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="JW21" s="28" t="str">
         <f>[1]CARTELLINO!JZ$21</f>
@@ -56375,15 +56371,15 @@
       </c>
       <c r="JF24" s="29" t="str">
         <f>[1]CARTELLINO!JI$24</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="JG24" s="29" t="str">
         <f>[1]CARTELLINO!JJ$24</f>
-        <v>r</v>
+        <v>S</v>
       </c>
       <c r="JH24" s="29" t="str">
         <f>[1]CARTELLINO!JK$24</f>
-        <v>m</v>
+        <v>R</v>
       </c>
       <c r="JI24" s="29" t="str">
         <f>[1]CARTELLINO!JL$24</f>
@@ -56439,11 +56435,11 @@
       </c>
       <c r="JV24" s="29" t="str">
         <f>[1]CARTELLINO!JY$24</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="JW24" s="29" t="str">
         <f>[1]CARTELLINO!JZ$24</f>
-        <v>M</v>
+        <v>p</v>
       </c>
       <c r="JX24" s="29" t="str">
         <f>[1]CARTELLINO!KA$24</f>
@@ -62882,7 +62878,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="JA29" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="JB29" s="63" t="str">
         <v>BARBIERI</v>
@@ -62897,13 +62893,13 @@
         <v>BIANCHI</v>
       </c>
       <c r="JF29" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="JG29" s="63" t="str">
         <v>FABBRI</v>
       </c>
       <c r="JH29" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>SARTI</v>
       </c>
       <c r="JI29" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -62912,7 +62908,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="JK29" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="JL29" s="63" t="str">
         <v>FABBRI</v>
@@ -62948,7 +62944,7 @@
         <v>MICHELOT.</v>
       </c>
       <c r="JW29" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>BERARDI</v>
       </c>
       <c r="JX29" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -63128,7 +63124,7 @@
         <v>FABBRI</v>
       </c>
       <c r="ME29" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="MF29" s="63" t="str">
         <v>MICHELOT.</v>
@@ -63137,7 +63133,7 @@
         <v>SARTI</v>
       </c>
       <c r="MH29" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="MI29" s="63" t="str">
         <v>BIANCHI</v>
@@ -63191,7 +63187,7 @@
         <v>0</v>
       </c>
       <c r="MZ29" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BARBIERI</v>
       </c>
       <c r="NA29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -63982,7 +63978,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="JA30" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="JB30" s="63" t="str">
         <v>BARBIERI</v>
@@ -63997,13 +63993,13 @@
         <v>BIANCHI</v>
       </c>
       <c r="JF30" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="JG30" s="63" t="str">
         <v>FABBRI</v>
       </c>
       <c r="JH30" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>SARTI</v>
       </c>
       <c r="JI30" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -64012,7 +64008,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="JK30" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="JL30" s="63" t="str">
         <v>FABBRI</v>
@@ -64048,7 +64044,7 @@
         <v>MICHELOT.</v>
       </c>
       <c r="JW30" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>BERARDI</v>
       </c>
       <c r="JX30" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -64228,7 +64224,7 @@
         <v>FABBRI</v>
       </c>
       <c r="ME30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="MF30" s="63" t="str">
         <v>MICHELOT.</v>
@@ -64237,7 +64233,7 @@
         <v>SARTI</v>
       </c>
       <c r="MH30" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="MI30" s="63" t="str">
         <v>BIANCHI</v>
@@ -64291,7 +64287,7 @@
         <v>0</v>
       </c>
       <c r="MZ30" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BARBIERI</v>
       </c>
       <c r="NA30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -65079,7 +65075,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="IZ31" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="JA31" s="63" t="str">
         <v>BARBIERI</v>
@@ -65094,13 +65090,13 @@
         <v>BIANCHI</v>
       </c>
       <c r="JE31" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="JF31" s="63" t="str">
         <v>FABBRI</v>
       </c>
       <c r="JG31" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>SARTI</v>
       </c>
       <c r="JH31" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -65109,7 +65105,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="JJ31" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="JK31" s="63" t="str">
         <v>FABBRI</v>
@@ -65145,7 +65141,7 @@
         <v>MICHELOT.</v>
       </c>
       <c r="JV31" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>BERARDI</v>
       </c>
       <c r="JW31" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -65325,7 +65321,7 @@
         <v>FABBRI</v>
       </c>
       <c r="MD31" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="ME31" s="63" t="str">
         <v>MICHELOT.</v>
@@ -65334,7 +65330,7 @@
         <v>SARTI</v>
       </c>
       <c r="MG31" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="MH31" s="63" t="str">
         <v>BIANCHI</v>
@@ -65388,7 +65384,7 @@
         <v>BERARDI</v>
       </c>
       <c r="MY31" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BARBIERI</v>
       </c>
       <c r="MZ31" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66179,7 +66175,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="IZ32" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="JA32" s="63" t="str">
         <v>BARBIERI</v>
@@ -66194,13 +66190,13 @@
         <v>BIANCHI</v>
       </c>
       <c r="JE32" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="JF32" s="63" t="str">
         <v>FABBRI</v>
       </c>
       <c r="JG32" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>SARTI</v>
       </c>
       <c r="JH32" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -66209,7 +66205,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="JJ32" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="JK32" s="63" t="str">
         <v>FABBRI</v>
@@ -66245,7 +66241,7 @@
         <v>MICHELOT.</v>
       </c>
       <c r="JV32" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>BERARDI</v>
       </c>
       <c r="JW32" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -66425,7 +66421,7 @@
         <v>FABBRI</v>
       </c>
       <c r="MD32" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="ME32" s="63" t="str">
         <v>MICHELOT.</v>
@@ -66434,7 +66430,7 @@
         <v>SARTI</v>
       </c>
       <c r="MG32" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="MH32" s="63" t="str">
         <v>BIANCHI</v>
@@ -66488,7 +66484,7 @@
         <v>BERARDI</v>
       </c>
       <c r="MY32" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BARBIERI</v>
       </c>
       <c r="MZ32" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66523,12 +66519,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71021,6 +71017,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71029,13 +71032,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7AC6E3-8441-4FBB-84CB-C9E72E316C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BFA7E5-5B35-4281-A8EC-9DF04A9F121F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="6270" yWindow="390" windowWidth="20445" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6629,6 +6629,8 @@
           </cell>
         </row>
         <row r="364">
+          <cell r="AQ364"/>
+          <cell r="AR364"/>
           <cell r="AS364" t="str">
             <v>GHIOTTI</v>
           </cell>
@@ -6693,6 +6695,8 @@
           </cell>
         </row>
         <row r="369">
+          <cell r="AQ369"/>
+          <cell r="AR369"/>
           <cell r="AS369" t="str">
             <v>BARBIERI</v>
           </cell>
@@ -18251,8 +18255,8 @@
           <cell r="JG16" t="str">
             <v>m</v>
           </cell>
-          <cell r="JH16" t="str">
-            <v>m</v>
+          <cell r="JH16">
+            <v>0</v>
           </cell>
           <cell r="JI16">
             <v>0</v>
@@ -26576,7 +26580,7 @@
             <v>m</v>
           </cell>
           <cell r="JF27" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="JG27" t="str">
             <v>r</v>
@@ -28507,431 +28511,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28941,7 +28945,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -47171,9 +47175,9 @@
         <f>[1]CARTELLINO!JG$16</f>
         <v>m</v>
       </c>
-      <c r="JE16" s="46" t="str">
+      <c r="JE16" s="46">
         <f>[1]CARTELLINO!JH$16</f>
-        <v>m</v>
+        <v>0</v>
       </c>
       <c r="JF16" s="46">
         <f>[1]CARTELLINO!JI$16</f>
@@ -59955,7 +59959,7 @@
       </c>
       <c r="JC27" s="30" t="str">
         <f>[1]CARTELLINO!JF$27</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="JD27" s="30" t="str">
         <f>[1]CARTELLINO!JG$27</f>
@@ -66519,12 +66523,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71017,13 +71021,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71032,6 +71029,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BFA7E5-5B35-4281-A8EC-9DF04A9F121F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE581E7-9D14-4AB8-9A47-6A4AF5921B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6270" yWindow="390" windowWidth="20445" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7576,7 +7576,7 @@
             <v>m</v>
           </cell>
           <cell r="JQ3" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="JR3" t="str">
             <v>m</v>
@@ -14713,7 +14713,7 @@
             <v>r</v>
           </cell>
           <cell r="JQ12" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="JR12" t="str">
             <v>-</v>
@@ -14722,7 +14722,7 @@
             <v>-</v>
           </cell>
           <cell r="JT12" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="JU12" t="str">
             <v>P</v>
@@ -15902,8 +15902,8 @@
           <cell r="JP13">
             <v>0</v>
           </cell>
-          <cell r="JQ13" t="str">
-            <v>p</v>
+          <cell r="JQ13">
+            <v>0</v>
           </cell>
           <cell r="JR13" t="str">
             <v>nl</v>
@@ -17093,7 +17093,7 @@
             <v>R</v>
           </cell>
           <cell r="JQ15" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="JR15" t="str">
             <v>M/R</v>
@@ -28511,431 +28511,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28945,7 +28945,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31236,7 +31236,7 @@
       </c>
       <c r="JN3" s="16" t="str">
         <f>[1]CARTELLINO!JQ$3</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="JO3" s="16" t="str">
         <f>[1]CARTELLINO!JR$3</f>
@@ -42023,7 +42023,7 @@
       </c>
       <c r="JN12" s="25" t="str">
         <f>[1]CARTELLINO!JQ$12</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="JO12" s="25" t="str">
         <f>[1]CARTELLINO!JR$12</f>
@@ -42035,7 +42035,7 @@
       </c>
       <c r="JQ12" s="25" t="str">
         <f>[1]CARTELLINO!JT$12</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="JR12" s="25" t="str">
         <f>[1]CARTELLINO!JU$12</f>
@@ -43615,9 +43615,9 @@
         <f>[1]CARTELLINO!JP$13</f>
         <v>0</v>
       </c>
-      <c r="JN13" s="46" t="str">
+      <c r="JN13" s="46">
         <f>[1]CARTELLINO!JQ$13</f>
-        <v>p</v>
+        <v>0</v>
       </c>
       <c r="JO13" s="46" t="str">
         <f>[1]CARTELLINO!JR$13</f>
@@ -45619,7 +45619,7 @@
       </c>
       <c r="JN15" s="26" t="str">
         <f>[1]CARTELLINO!JQ$15</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="JO15" s="26" t="str">
         <f>[1]CARTELLINO!JR$15</f>
@@ -66523,12 +66523,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71021,6 +71021,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71029,13 +71036,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE581E7-9D14-4AB8-9A47-6A4AF5921B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B237A3-1A79-4725-8F45-A3D51E322929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5387,7 +5387,7 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR275" t="str">
-            <v>PAZZAGLIA</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS275" t="str">
             <v>VOLPINI</v>
@@ -28511,431 +28511,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28945,7 +28945,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -64006,7 +64006,7 @@
         <v>SARTI</v>
       </c>
       <c r="JI30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>BIANCHI</v>
       </c>
       <c r="JJ30" s="63" t="str">
         <v>VOLPINI</v>
@@ -66523,12 +66523,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71021,13 +71021,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71036,6 +71029,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B237A3-1A79-4725-8F45-A3D51E322929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103F9D08-A573-4E14-8329-FD714F6363F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -28511,431 +28511,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28945,7 +28945,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -66523,12 +66523,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71021,6 +71021,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71029,13 +71036,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103F9D08-A573-4E14-8329-FD714F6363F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C27CC7-3FB4-46B1-B413-BF96CE49E112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6629,8 +6629,6 @@
           </cell>
         </row>
         <row r="364">
-          <cell r="AQ364"/>
-          <cell r="AR364"/>
           <cell r="AS364" t="str">
             <v>GHIOTTI</v>
           </cell>
@@ -6695,8 +6693,6 @@
           </cell>
         </row>
         <row r="369">
-          <cell r="AQ369"/>
-          <cell r="AR369"/>
           <cell r="AS369" t="str">
             <v>BARBIERI</v>
           </cell>
@@ -9980,10 +9976,10 @@
             <v>m</v>
           </cell>
           <cell r="JZ6" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="KA6" t="str">
-            <v>p</v>
+            <v>S</v>
           </cell>
           <cell r="KB6" t="str">
             <v>m</v>
@@ -14743,10 +14739,10 @@
             <v>P</v>
           </cell>
           <cell r="KA12" t="str">
-            <v>M</v>
+            <v>N</v>
           </cell>
           <cell r="KB12" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="KC12" t="str">
             <v>r</v>
@@ -17120,10 +17116,10 @@
             <v>p</v>
           </cell>
           <cell r="JZ15" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="KA15" t="str">
-            <v>m/R</v>
+            <v>M/R</v>
           </cell>
           <cell r="KB15" t="str">
             <v>p</v>
@@ -21907,7 +21903,7 @@
             <v>p</v>
           </cell>
           <cell r="KI21" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="KJ21" t="str">
             <v>p</v>
@@ -24266,7 +24262,7 @@
             <v>m</v>
           </cell>
           <cell r="KB24" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="KC24" t="str">
             <v>m</v>
@@ -26940,25 +26936,25 @@
             <v>M</v>
           </cell>
           <cell r="NV27" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="NW27" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="NX27" t="str">
             <v>R</v>
           </cell>
           <cell r="NY27" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="NZ27" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="OA27" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="OB27" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="OC27" t="str">
             <v>R</v>
@@ -26976,7 +26972,7 @@
             <v>-</v>
           </cell>
           <cell r="OH27" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="OI27" t="str">
             <v>-</v>
@@ -28015,11 +28011,11 @@
           <cell r="MI28">
             <v>0</v>
           </cell>
-          <cell r="MJ28" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="MK28" t="str">
-            <v>f</v>
+          <cell r="MJ28">
+            <v>7</v>
+          </cell>
+          <cell r="MK28">
+            <v>7</v>
           </cell>
           <cell r="ML28" t="str">
             <v>f</v>
@@ -28031,10 +28027,10 @@
             <v>f</v>
           </cell>
           <cell r="MO28" t="str">
-            <v>f</v>
+            <v>p</v>
           </cell>
           <cell r="MP28" t="str">
-            <v>f</v>
+            <v>p</v>
           </cell>
           <cell r="MQ28">
             <v>0</v>
@@ -28129,50 +28125,50 @@
           <cell r="NU28">
             <v>0</v>
           </cell>
-          <cell r="NV28">
-            <v>0</v>
-          </cell>
-          <cell r="NW28">
-            <v>0</v>
-          </cell>
-          <cell r="NX28">
-            <v>0</v>
-          </cell>
-          <cell r="NY28">
-            <v>0</v>
-          </cell>
-          <cell r="NZ28">
-            <v>0</v>
-          </cell>
-          <cell r="OA28">
-            <v>0</v>
-          </cell>
-          <cell r="OB28">
-            <v>0</v>
-          </cell>
-          <cell r="OC28">
-            <v>0</v>
-          </cell>
-          <cell r="OD28">
-            <v>0</v>
-          </cell>
-          <cell r="OE28">
-            <v>0</v>
-          </cell>
-          <cell r="OF28">
-            <v>0</v>
-          </cell>
-          <cell r="OG28">
-            <v>0</v>
-          </cell>
-          <cell r="OH28">
-            <v>0</v>
-          </cell>
-          <cell r="OI28">
-            <v>0</v>
-          </cell>
-          <cell r="OJ28">
-            <v>0</v>
+          <cell r="NV28" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="NW28" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NX28" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NY28" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NZ28" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="OA28" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="OB28" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="OC28" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="OD28" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="OE28" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="OF28" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="OG28" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="OH28" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="OI28" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="OJ28" t="str">
+            <v>v</v>
           </cell>
         </row>
       </sheetData>
@@ -28511,431 +28507,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28945,7 +28941,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -34867,11 +34863,11 @@
       </c>
       <c r="JW6" s="22" t="str">
         <f>[1]CARTELLINO!JZ$6</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="JX6" s="22" t="str">
         <f>[1]CARTELLINO!KA$6</f>
-        <v>p</v>
+        <v>S</v>
       </c>
       <c r="JY6" s="22" t="str">
         <f>[1]CARTELLINO!KB$6</f>
@@ -42063,11 +42059,11 @@
       </c>
       <c r="JX12" s="25" t="str">
         <f>[1]CARTELLINO!KA$12</f>
-        <v>M</v>
+        <v>N</v>
       </c>
       <c r="JY12" s="25" t="str">
         <f>[1]CARTELLINO!KB$12</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="JZ12" s="25" t="str">
         <f>[1]CARTELLINO!KC$12</f>
@@ -45655,11 +45651,11 @@
       </c>
       <c r="JW15" s="26" t="str">
         <f>[1]CARTELLINO!JZ$15</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="JX15" s="26" t="str">
         <f>[1]CARTELLINO!KA$15</f>
-        <v>m/R</v>
+        <v>M/R</v>
       </c>
       <c r="JY15" s="26" t="str">
         <f>[1]CARTELLINO!KB$15</f>
@@ -52883,7 +52879,7 @@
       </c>
       <c r="KF21" s="28" t="str">
         <f>[1]CARTELLINO!KI$21</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="KG21" s="28" t="str">
         <f>[1]CARTELLINO!KJ$21</f>
@@ -56451,7 +56447,7 @@
       </c>
       <c r="JY24" s="29" t="str">
         <f>[1]CARTELLINO!KB$24</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="JZ24" s="29" t="str">
         <f>[1]CARTELLINO!KC$24</f>
@@ -60439,11 +60435,11 @@
       </c>
       <c r="NS27" s="30" t="str">
         <f>[1]CARTELLINO!NV$27</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="NT27" s="30" t="str">
         <f>[1]CARTELLINO!NW$27</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="NU27" s="30" t="str">
         <f>[1]CARTELLINO!NX$27</f>
@@ -60451,19 +60447,19 @@
       </c>
       <c r="NV27" s="30" t="str">
         <f>[1]CARTELLINO!NY$27</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="NW27" s="30" t="str">
         <f>[1]CARTELLINO!NZ$27</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="NX27" s="30" t="str">
         <f>[1]CARTELLINO!OA$27</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="NY27" s="30" t="str">
         <f>[1]CARTELLINO!OB$27</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="NZ27" s="30" t="str">
         <f>[1]CARTELLINO!OC$27</f>
@@ -60487,7 +60483,7 @@
       </c>
       <c r="OE27" s="30" t="str">
         <f>[1]CARTELLINO!OH$27</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="OF27" s="30" t="str">
         <f>[1]CARTELLINO!OI$27</f>
@@ -61879,13 +61875,13 @@
         <f>[1]CARTELLINO!MI$28</f>
         <v>0</v>
       </c>
-      <c r="MG28" s="62" t="str">
+      <c r="MG28" s="62">
         <f>[1]CARTELLINO!MJ$28</f>
-        <v>f</v>
-      </c>
-      <c r="MH28" s="62" t="str">
+        <v>7</v>
+      </c>
+      <c r="MH28" s="62">
         <f>[1]CARTELLINO!MK$28</f>
-        <v>f</v>
+        <v>7</v>
       </c>
       <c r="MI28" s="62" t="str">
         <f>[1]CARTELLINO!ML$28</f>
@@ -61901,11 +61897,11 @@
       </c>
       <c r="ML28" s="62" t="str">
         <f>[1]CARTELLINO!MO$28</f>
-        <v>f</v>
+        <v>p</v>
       </c>
       <c r="MM28" s="62" t="str">
         <f>[1]CARTELLINO!MP$28</f>
-        <v>f</v>
+        <v>p</v>
       </c>
       <c r="MN28" s="62">
         <f>[1]CARTELLINO!MQ$28</f>
@@ -62031,65 +62027,65 @@
         <f>[1]CARTELLINO!NU$28</f>
         <v>0</v>
       </c>
-      <c r="NS28" s="46">
+      <c r="NS28" s="46" t="str">
         <f>[1]CARTELLINO!NV$28</f>
-        <v>0</v>
-      </c>
-      <c r="NT28" s="46">
+        <v>r</v>
+      </c>
+      <c r="NT28" s="46" t="str">
         <f>[1]CARTELLINO!NW$28</f>
-        <v>0</v>
-      </c>
-      <c r="NU28" s="46">
+        <v>v</v>
+      </c>
+      <c r="NU28" s="46" t="str">
         <f>[1]CARTELLINO!NX$28</f>
-        <v>0</v>
-      </c>
-      <c r="NV28" s="46">
+        <v>v</v>
+      </c>
+      <c r="NV28" s="46" t="str">
         <f>[1]CARTELLINO!NY$28</f>
-        <v>0</v>
-      </c>
-      <c r="NW28" s="46">
+        <v>v</v>
+      </c>
+      <c r="NW28" s="46" t="str">
         <f>[1]CARTELLINO!NZ$28</f>
-        <v>0</v>
-      </c>
-      <c r="NX28" s="46">
+        <v>v</v>
+      </c>
+      <c r="NX28" s="46" t="str">
         <f>[1]CARTELLINO!OA$28</f>
-        <v>0</v>
-      </c>
-      <c r="NY28" s="46">
+        <v>v</v>
+      </c>
+      <c r="NY28" s="46" t="str">
         <f>[1]CARTELLINO!OB$28</f>
-        <v>0</v>
-      </c>
-      <c r="NZ28" s="46">
+        <v>v</v>
+      </c>
+      <c r="NZ28" s="46" t="str">
         <f>[1]CARTELLINO!OC$28</f>
-        <v>0</v>
-      </c>
-      <c r="OA28" s="46">
+        <v>v</v>
+      </c>
+      <c r="OA28" s="46" t="str">
         <f>[1]CARTELLINO!OD$28</f>
-        <v>0</v>
-      </c>
-      <c r="OB28" s="46">
+        <v>v</v>
+      </c>
+      <c r="OB28" s="46" t="str">
         <f>[1]CARTELLINO!OE$28</f>
-        <v>0</v>
-      </c>
-      <c r="OC28" s="46">
+        <v>v</v>
+      </c>
+      <c r="OC28" s="46" t="str">
         <f>[1]CARTELLINO!OF$28</f>
-        <v>0</v>
-      </c>
-      <c r="OD28" s="46">
+        <v>v</v>
+      </c>
+      <c r="OD28" s="46" t="str">
         <f>[1]CARTELLINO!OG$28</f>
-        <v>0</v>
-      </c>
-      <c r="OE28" s="46">
+        <v>v</v>
+      </c>
+      <c r="OE28" s="46" t="str">
         <f>[1]CARTELLINO!OH$28</f>
-        <v>0</v>
-      </c>
-      <c r="OF28" s="46">
+        <v>v</v>
+      </c>
+      <c r="OF28" s="46" t="str">
         <f>[1]CARTELLINO!OI$28</f>
-        <v>0</v>
-      </c>
-      <c r="OG28" s="46">
+        <v>v</v>
+      </c>
+      <c r="OG28" s="46" t="str">
         <f>[1]CARTELLINO!OJ$28</f>
-        <v>0</v>
+        <v>v</v>
       </c>
       <c r="OH28" s="44"/>
       <c r="OI28" s="44"/>
@@ -66523,12 +66519,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71021,13 +71017,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71036,6 +71025,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C27CC7-3FB4-46B1-B413-BF96CE49E112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB598283-A089-44E3-B8C7-EC9413F1B7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5337,7 +5337,7 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AT271" t="str">
-            <v>BARBIERI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="272">
@@ -5628,32 +5628,32 @@
             <v>FABBRI</v>
           </cell>
           <cell r="AS292" t="str">
-            <v>MICHELOT.</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT292" t="str">
-            <v>MICHELOT.</v>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="293">
           <cell r="AQ293" t="str">
-            <v>MICHELOT.</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR293" t="str">
-            <v>MICHELOT.</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS293" t="str">
-            <v>BARBIERI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT293" t="str">
-            <v>BARBIERI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="294">
           <cell r="AQ294" t="str">
-            <v>BARBIERI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR294" t="str">
-            <v>BARBIERI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS294" t="str">
             <v>SARTI</v>
@@ -5754,18 +5754,18 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AS301" t="str">
-            <v>FABBRI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT301" t="str">
-            <v>FABBRI</v>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="302">
           <cell r="AQ302" t="str">
-            <v>FABBRI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR302" t="str">
-            <v>FABBRI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS302" t="str">
             <v>BERARDI</v>
@@ -5852,32 +5852,32 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS308" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT308" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="309">
           <cell r="AQ309" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR309" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS309" t="str">
-            <v>SARTI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT309" t="str">
-            <v>SARTI</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="310">
           <cell r="AQ310" t="str">
-            <v>SARTI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR310" t="str">
-            <v>SARTI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS310" t="str">
             <v>BARBIERI</v>
@@ -5894,18 +5894,18 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AS311" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT311" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="312">
           <cell r="AQ312" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR312" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS312" t="str">
             <v>PAZZAGLIA</v>
@@ -5922,18 +5922,18 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS313" t="str">
-            <v>VOLPINI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT313" t="str">
-            <v>VOLPINI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="314">
           <cell r="AQ314" t="str">
-            <v>VOLPINI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR314" t="str">
-            <v>VOLPINI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS314" t="str">
             <v>GHIOTTI</v>
@@ -6118,18 +6118,18 @@
             <v>BERARDI</v>
           </cell>
           <cell r="AS327" t="str">
-            <v>MICHELOT.</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT327" t="str">
-            <v>MICHELOT.</v>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="328">
           <cell r="AQ328" t="str">
-            <v>MICHELOT.</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR328" t="str">
-            <v>MICHELOT.</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS328" t="str">
             <v>VOLPINI</v>
@@ -6426,18 +6426,18 @@
             <v>VOLPINI</v>
           </cell>
           <cell r="AS349" t="str">
-            <v>MICHELOT.</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT349" t="str">
-            <v>MICHELOT.</v>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="350">
           <cell r="AQ350" t="str">
-            <v>MICHELOT.</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR350" t="str">
-            <v>MICHELOT.</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS350" t="str">
             <v>SARTI</v>
@@ -6629,6 +6629,12 @@
           </cell>
         </row>
         <row r="364">
+          <cell r="AQ364" t="str">
+            <v>VOLPINI</v>
+          </cell>
+          <cell r="AR364" t="str">
+            <v>VOLPINI</v>
+          </cell>
           <cell r="AS364" t="str">
             <v>GHIOTTI</v>
           </cell>
@@ -6686,13 +6692,19 @@
             <v>VOLPINI</v>
           </cell>
           <cell r="AS368" t="str">
-            <v>BERARDI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT368" t="str">
-            <v>BERARDI</v>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="369">
+          <cell r="AQ369" t="str">
+            <v>MICHELOT.</v>
+          </cell>
+          <cell r="AR369" t="str">
+            <v>MICHELOT.</v>
+          </cell>
           <cell r="AS369" t="str">
             <v>BARBIERI</v>
           </cell>
@@ -6736,10 +6748,10 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS372" t="str">
-            <v>BIANCHI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT372" t="str">
-            <v>BIANCHI</v>
+            <v>BARBIERI</v>
           </cell>
         </row>
       </sheetData>
@@ -7569,7 +7581,7 @@
             <v>p</v>
           </cell>
           <cell r="JP3" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="JQ3" t="str">
             <v>m</v>
@@ -7635,19 +7647,19 @@
             <v>p</v>
           </cell>
           <cell r="KL3" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="KM3" t="str">
             <v>r</v>
           </cell>
           <cell r="KN3" t="str">
-            <v>p</v>
+            <v>r</v>
           </cell>
           <cell r="KO3" t="str">
             <v>p</v>
           </cell>
           <cell r="KP3" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="KQ3" t="str">
             <v>P</v>
@@ -7665,7 +7677,7 @@
             <v>R</v>
           </cell>
           <cell r="KV3" t="str">
-            <v>r</v>
+            <v>P</v>
           </cell>
           <cell r="KW3" t="str">
             <v>M/R</v>
@@ -7770,7 +7782,7 @@
             <v>R</v>
           </cell>
           <cell r="ME3" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="MF3" t="str">
             <v>p</v>
@@ -7860,7 +7872,7 @@
             <v>r</v>
           </cell>
           <cell r="NI3" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="NJ3" t="str">
             <v>m</v>
@@ -7908,16 +7920,16 @@
             <v>m</v>
           </cell>
           <cell r="NY3" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="NZ3" t="str">
             <v>p</v>
           </cell>
-          <cell r="NZ3" t="str">
-            <v>m</v>
-          </cell>
           <cell r="OA3" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="OB3" t="str">
             <v>p</v>
-          </cell>
-          <cell r="OB3" t="str">
-            <v>m</v>
           </cell>
           <cell r="OC3" t="str">
             <v>p</v>
@@ -8945,7 +8957,7 @@
             <v>0</v>
           </cell>
           <cell r="LZ4" t="str">
-            <v>f</v>
+            <v>p</v>
           </cell>
           <cell r="MA4" t="str">
             <v>f</v>
@@ -9631,7 +9643,7 @@
             <v>P</v>
           </cell>
           <cell r="FO6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="FP6" t="str">
             <v>N</v>
@@ -9943,7 +9955,7 @@
             <v>r</v>
           </cell>
           <cell r="JO6" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="JP6" t="str">
             <v>M/R</v>
@@ -9970,10 +9982,10 @@
             <v>p</v>
           </cell>
           <cell r="JX6" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="JY6" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="JZ6" t="str">
             <v>N</v>
@@ -9988,7 +10000,7 @@
             <v>r</v>
           </cell>
           <cell r="KD6" t="str">
-            <v>M/R</v>
+            <v>p</v>
           </cell>
           <cell r="KE6" t="str">
             <v>p</v>
@@ -10003,7 +10015,7 @@
             <v>r</v>
           </cell>
           <cell r="KI6" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="KJ6" t="str">
             <v>P</v>
@@ -10036,7 +10048,7 @@
             <v>R</v>
           </cell>
           <cell r="KT6" t="str">
-            <v>P</v>
+            <v>M</v>
           </cell>
           <cell r="KU6" t="str">
             <v>M/R</v>
@@ -10111,10 +10123,10 @@
             <v>R</v>
           </cell>
           <cell r="LS6" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="LT6" t="str">
-            <v>P</v>
+            <v>p</v>
           </cell>
           <cell r="LU6" t="str">
             <v>m</v>
@@ -10135,7 +10147,7 @@
             <v>m</v>
           </cell>
           <cell r="MA6" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="MB6" t="str">
             <v>p</v>
@@ -10144,19 +10156,19 @@
             <v>m/R</v>
           </cell>
           <cell r="MD6" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="ME6" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="MF6" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="MG6" t="str">
             <v>p</v>
           </cell>
           <cell r="MH6" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="MI6" t="str">
             <v>m</v>
@@ -10213,7 +10225,7 @@
             <v>-</v>
           </cell>
           <cell r="NA6" t="str">
-            <v>r</v>
+            <v>P</v>
           </cell>
           <cell r="NB6" t="str">
             <v>m/R</v>
@@ -10222,10 +10234,10 @@
             <v>p</v>
           </cell>
           <cell r="ND6" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="NE6" t="str">
-            <v>r</v>
+            <v>M/R</v>
           </cell>
           <cell r="NF6" t="str">
             <v>N</v>
@@ -10255,7 +10267,7 @@
             <v>P</v>
           </cell>
           <cell r="NO6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NP6" t="str">
             <v>N</v>
@@ -10270,7 +10282,7 @@
             <v>P</v>
           </cell>
           <cell r="NT6" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="NU6" t="str">
             <v>N</v>
@@ -10285,7 +10297,7 @@
             <v>P</v>
           </cell>
           <cell r="NY6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NZ6" t="str">
             <v>N</v>
@@ -10821,7 +10833,7 @@
             <v>0</v>
           </cell>
           <cell r="FO7">
-            <v>7</v>
+            <v>0</v>
           </cell>
           <cell r="FP7">
             <v>0</v>
@@ -11159,8 +11171,8 @@
           <cell r="JW7">
             <v>0</v>
           </cell>
-          <cell r="JX7">
-            <v>0</v>
+          <cell r="JX7" t="str">
+            <v>p</v>
           </cell>
           <cell r="JY7">
             <v>0</v>
@@ -12368,7 +12380,7 @@
             <v>R</v>
           </cell>
           <cell r="KD9" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="KE9" t="str">
             <v>M/R</v>
@@ -12380,7 +12392,7 @@
             <v>S</v>
           </cell>
           <cell r="KH9" t="str">
-            <v>R</v>
+            <v>m</v>
           </cell>
           <cell r="KI9" t="str">
             <v>P</v>
@@ -12413,16 +12425,16 @@
             <v>R</v>
           </cell>
           <cell r="KS9" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="KT9" t="str">
-            <v>M/R</v>
+            <v>-</v>
           </cell>
           <cell r="KU9" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="KV9" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="KW9" t="str">
             <v>R</v>
@@ -12446,7 +12458,7 @@
             <v>-</v>
           </cell>
           <cell r="LD9" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="LE9" t="str">
             <v>p</v>
@@ -12470,7 +12482,7 @@
             <v>m</v>
           </cell>
           <cell r="LL9" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="LM9" t="str">
             <v>p</v>
@@ -12485,10 +12497,10 @@
             <v>m</v>
           </cell>
           <cell r="LQ9" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="LR9" t="str">
-            <v>r</v>
+            <v>P</v>
           </cell>
           <cell r="LS9" t="str">
             <v>P</v>
@@ -12620,7 +12632,7 @@
             <v>m</v>
           </cell>
           <cell r="NJ9" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="NK9" t="str">
             <v>p</v>
@@ -12629,13 +12641,13 @@
             <v>m</v>
           </cell>
           <cell r="NM9" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="NN9" t="str">
             <v>r</v>
           </cell>
-          <cell r="NN9" t="str">
+          <cell r="NO9" t="str">
             <v>p</v>
-          </cell>
-          <cell r="NO9" t="str">
-            <v>m/R</v>
           </cell>
           <cell r="NP9" t="str">
             <v>p</v>
@@ -12647,58 +12659,58 @@
             <v>p</v>
           </cell>
           <cell r="NS9" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="NT9" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="NU9" t="str">
             <v>p</v>
           </cell>
-          <cell r="NT9" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="NU9" t="str">
-            <v>m</v>
-          </cell>
           <cell r="NV9" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="NW9" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="NX9" t="str">
-            <v>p</v>
+            <v>R</v>
           </cell>
           <cell r="NY9" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="NZ9" t="str">
-            <v>p</v>
+            <v>M/R</v>
           </cell>
           <cell r="OA9" t="str">
-            <v>m</v>
+            <v>N</v>
           </cell>
           <cell r="OB9" t="str">
-            <v>p</v>
+            <v>S</v>
           </cell>
           <cell r="OC9" t="str">
-            <v>m</v>
+            <v>R</v>
           </cell>
           <cell r="OD9" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="OE9" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="OF9" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="OG9" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="OH9" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="OI9" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="OJ9" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
         </row>
         <row r="10">
@@ -13602,17 +13614,17 @@
           <cell r="KR10">
             <v>0</v>
           </cell>
-          <cell r="KS10">
-            <v>0</v>
-          </cell>
-          <cell r="KT10">
-            <v>0</v>
-          </cell>
-          <cell r="KU10">
-            <v>0</v>
-          </cell>
-          <cell r="KV10">
-            <v>0</v>
+          <cell r="KS10" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="KT10" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="KU10" t="str">
+            <v>pn</v>
+          </cell>
+          <cell r="KV10" t="str">
+            <v>x</v>
           </cell>
           <cell r="KW10">
             <v>0</v>
@@ -13635,8 +13647,8 @@
           <cell r="LC10" t="str">
             <v>f</v>
           </cell>
-          <cell r="LD10" t="str">
-            <v>f</v>
+          <cell r="LD10">
+            <v>0</v>
           </cell>
           <cell r="LE10">
             <v>0</v>
@@ -14772,46 +14784,46 @@
             <v>-</v>
           </cell>
           <cell r="KL12" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="KM12" t="str">
             <v>m</v>
           </cell>
           <cell r="KN12" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="KO12" t="str">
             <v>r</v>
-          </cell>
-          <cell r="KO12" t="str">
-            <v>m</v>
           </cell>
           <cell r="KP12" t="str">
             <v>-</v>
           </cell>
           <cell r="KQ12" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="KR12" t="str">
             <v>p</v>
           </cell>
-          <cell r="KR12" t="str">
+          <cell r="KS12" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="KT12" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="KU12" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="KV12" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="KW12" t="str">
             <v>r</v>
           </cell>
-          <cell r="KS12" t="str">
+          <cell r="KX12" t="str">
             <v>p</v>
           </cell>
-          <cell r="KT12" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="KU12" t="str">
+          <cell r="KY12" t="str">
             <v>m</v>
-          </cell>
-          <cell r="KV12" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="KW12" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="KX12" t="str">
-            <v>m/R</v>
-          </cell>
-          <cell r="KY12" t="str">
-            <v>p</v>
           </cell>
           <cell r="KZ12" t="str">
             <v>p</v>
@@ -14823,10 +14835,10 @@
             <v>p</v>
           </cell>
           <cell r="LC12" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="LD12" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="LE12" t="str">
             <v>r</v>
@@ -14880,10 +14892,10 @@
             <v>R</v>
           </cell>
           <cell r="LV12" t="str">
-            <v>r</v>
+            <v>P</v>
           </cell>
           <cell r="LW12" t="str">
-            <v>p</v>
+            <v>M</v>
           </cell>
           <cell r="LX12" t="str">
             <v>N</v>
@@ -15042,7 +15054,7 @@
             <v>P</v>
           </cell>
           <cell r="NX12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NY12" t="str">
             <v>N</v>
@@ -17071,7 +17083,7 @@
             <v>p</v>
           </cell>
           <cell r="JK15" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="JL15" t="str">
             <v>P</v>
@@ -17110,10 +17122,10 @@
             <v>m</v>
           </cell>
           <cell r="JX15" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="JY15" t="str">
             <v>r</v>
-          </cell>
-          <cell r="JY15" t="str">
-            <v>p</v>
           </cell>
           <cell r="JZ15" t="str">
             <v>p</v>
@@ -17152,16 +17164,16 @@
             <v>R</v>
           </cell>
           <cell r="KL15" t="str">
-            <v>P</v>
+            <v>m/R</v>
           </cell>
           <cell r="KM15" t="str">
             <v>p</v>
           </cell>
           <cell r="KN15" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="KO15" t="str">
             <v>m</v>
-          </cell>
-          <cell r="KO15" t="str">
-            <v>r</v>
           </cell>
           <cell r="KP15" t="str">
             <v>p</v>
@@ -17170,22 +17182,22 @@
             <v>m/R</v>
           </cell>
           <cell r="KR15" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="KS15" t="str">
             <v>p</v>
           </cell>
-          <cell r="KS15" t="str">
-            <v>r</v>
-          </cell>
           <cell r="KT15" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="KU15" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="KV15" t="str">
             <v>p</v>
           </cell>
-          <cell r="KV15" t="str">
-            <v>P</v>
-          </cell>
           <cell r="KW15" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="KX15" t="str">
             <v>P</v>
@@ -17332,7 +17344,7 @@
             <v>r</v>
           </cell>
           <cell r="MT15" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="MU15" t="str">
             <v>m</v>
@@ -17356,7 +17368,7 @@
             <v>r</v>
           </cell>
           <cell r="NB15" t="str">
-            <v>P</v>
+            <v>M</v>
           </cell>
           <cell r="NC15" t="str">
             <v>M/R</v>
@@ -17419,7 +17431,7 @@
             <v>P</v>
           </cell>
           <cell r="NW15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NX15" t="str">
             <v>N</v>
@@ -18260,8 +18272,8 @@
           <cell r="JJ16">
             <v>0</v>
           </cell>
-          <cell r="JK16">
-            <v>0</v>
+          <cell r="JK16" t="str">
+            <v>k</v>
           </cell>
           <cell r="JL16">
             <v>0</v>
@@ -19463,7 +19475,7 @@
             <v>p</v>
           </cell>
           <cell r="JO18" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="JP18" t="str">
             <v>r</v>
@@ -19505,13 +19517,13 @@
             <v>P</v>
           </cell>
           <cell r="KC18" t="str">
-            <v>M/R</v>
+            <v>m</v>
           </cell>
           <cell r="KD18" t="str">
-            <v>N</v>
+            <v>P</v>
           </cell>
           <cell r="KE18" t="str">
-            <v>S</v>
+            <v>m</v>
           </cell>
           <cell r="KF18" t="str">
             <v>R</v>
@@ -19610,16 +19622,16 @@
             <v>-</v>
           </cell>
           <cell r="LL18" t="str">
-            <v>m/R</v>
+            <v>-</v>
           </cell>
           <cell r="LM18" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="LN18" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="LO18" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="LP18" t="str">
             <v>p</v>
@@ -19634,13 +19646,13 @@
             <v>m</v>
           </cell>
           <cell r="LT18" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="LU18" t="str">
             <v>r</v>
           </cell>
           <cell r="LV18" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="LW18" t="str">
             <v>m/R</v>
@@ -19664,19 +19676,19 @@
             <v>r</v>
           </cell>
           <cell r="MD18" t="str">
-            <v>N</v>
+            <v>p</v>
           </cell>
           <cell r="ME18" t="str">
-            <v>S</v>
+            <v>m</v>
           </cell>
           <cell r="MF18" t="str">
-            <v>R</v>
+            <v>m</v>
           </cell>
           <cell r="MG18" t="str">
             <v>P</v>
           </cell>
           <cell r="MH18" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="MI18" t="str">
             <v>N</v>
@@ -19733,10 +19745,10 @@
             <v>R</v>
           </cell>
           <cell r="NA18" t="str">
+            <v>M/R</v>
+          </cell>
+          <cell r="NB18" t="str">
             <v>P</v>
-          </cell>
-          <cell r="NB18" t="str">
-            <v>M</v>
           </cell>
           <cell r="NC18" t="str">
             <v>N</v>
@@ -19793,7 +19805,7 @@
             <v>m</v>
           </cell>
           <cell r="NU18" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="NV18" t="str">
             <v>p</v>
@@ -19805,19 +19817,19 @@
             <v>p</v>
           </cell>
           <cell r="NY18" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="NZ18" t="str">
             <v>m</v>
-          </cell>
-          <cell r="NZ18" t="str">
-            <v>p</v>
           </cell>
           <cell r="OA18" t="str">
             <v>m</v>
           </cell>
           <cell r="OB18" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="OC18" t="str">
             <v>p</v>
-          </cell>
-          <cell r="OC18" t="str">
-            <v>m</v>
           </cell>
           <cell r="OD18" t="str">
             <v>-</v>
@@ -20707,40 +20719,40 @@
             <v>0</v>
           </cell>
           <cell r="KG19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KH19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KI19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KJ19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KK19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KL19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KM19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KN19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KO19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KP19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KQ19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KR19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KS19" t="str">
             <v>pn</v>
@@ -20776,40 +20788,40 @@
             <v>f</v>
           </cell>
           <cell r="LD19" t="str">
-            <v>f</v>
+            <v>k</v>
           </cell>
           <cell r="LE19" t="str">
-            <v>f</v>
+            <v>k</v>
           </cell>
           <cell r="LF19" t="str">
-            <v>f</v>
+            <v>k</v>
           </cell>
           <cell r="LG19" t="str">
-            <v>f</v>
+            <v>k</v>
           </cell>
           <cell r="LH19" t="str">
-            <v>f</v>
+            <v>k</v>
           </cell>
           <cell r="LI19" t="str">
-            <v>f</v>
+            <v>k</v>
           </cell>
           <cell r="LJ19" t="str">
-            <v>f</v>
+            <v>k</v>
           </cell>
           <cell r="LK19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="LL19">
-            <v>0</v>
-          </cell>
-          <cell r="LM19">
-            <v>0</v>
-          </cell>
-          <cell r="LN19">
-            <v>0</v>
-          </cell>
-          <cell r="LO19">
-            <v>0</v>
+            <v>k</v>
+          </cell>
+          <cell r="LL19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="LM19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="LN19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="LO19" t="str">
+            <v>k</v>
           </cell>
           <cell r="LP19">
             <v>0</v>
@@ -21885,16 +21897,16 @@
             <v>R</v>
           </cell>
           <cell r="KC21" t="str">
-            <v>P</v>
+            <v>M/R</v>
           </cell>
           <cell r="KD21" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="KE21" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="KF21" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="KG21" t="str">
             <v>m/R</v>
@@ -21927,31 +21939,31 @@
             <v>R</v>
           </cell>
           <cell r="KQ21" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="KR21" t="str">
             <v>P</v>
           </cell>
           <cell r="KS21" t="str">
+            <v>M/R</v>
+          </cell>
+          <cell r="KT21" t="str">
+            <v>P</v>
+          </cell>
+          <cell r="KU21" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="KV21" t="str">
+            <v>S</v>
+          </cell>
+          <cell r="KW21" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="KX21" t="str">
             <v>m</v>
           </cell>
-          <cell r="KT21" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="KU21" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="KV21" t="str">
-            <v>m/R</v>
-          </cell>
-          <cell r="KW21" t="str">
-            <v>P</v>
-          </cell>
-          <cell r="KX21" t="str">
+          <cell r="KY21" t="str">
             <v>p</v>
-          </cell>
-          <cell r="KY21" t="str">
-            <v>m</v>
           </cell>
           <cell r="KZ21" t="str">
             <v>m/R</v>
@@ -21963,7 +21975,7 @@
             <v>m</v>
           </cell>
           <cell r="LC21" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="LD21" t="str">
             <v>P</v>
@@ -22014,7 +22026,7 @@
             <v>R</v>
           </cell>
           <cell r="LT21" t="str">
-            <v>r</v>
+            <v>P</v>
           </cell>
           <cell r="LU21" t="str">
             <v>M/R</v>
@@ -22029,7 +22041,7 @@
             <v>R</v>
           </cell>
           <cell r="LY21" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="LZ21" t="str">
             <v>M/R</v>
@@ -22113,7 +22125,7 @@
             <v>P</v>
           </cell>
           <cell r="NA21" t="str">
-            <v>M/R</v>
+            <v>p</v>
           </cell>
           <cell r="NB21" t="str">
             <v>-</v>
@@ -22149,13 +22161,13 @@
             <v>p</v>
           </cell>
           <cell r="NM21" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="NN21" t="str">
             <v>m</v>
           </cell>
-          <cell r="NN21" t="str">
+          <cell r="NO21" t="str">
             <v>r</v>
-          </cell>
-          <cell r="NO21" t="str">
-            <v>p</v>
           </cell>
           <cell r="NP21" t="str">
             <v>P</v>
@@ -22176,7 +22188,7 @@
             <v>P</v>
           </cell>
           <cell r="NV21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NW21" t="str">
             <v>N</v>
@@ -23218,8 +23230,8 @@
           <cell r="LX22">
             <v>0</v>
           </cell>
-          <cell r="LY22">
-            <v>0</v>
+          <cell r="LY22" t="str">
+            <v>r</v>
           </cell>
           <cell r="LZ22">
             <v>0</v>
@@ -24226,7 +24238,7 @@
             <v>r</v>
           </cell>
           <cell r="JP24" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="JQ24" t="str">
             <v>N</v>
@@ -24265,10 +24277,10 @@
             <v>m</v>
           </cell>
           <cell r="KC24" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="KD24" t="str">
-            <v>r</v>
+            <v>M/R</v>
           </cell>
           <cell r="KE24" t="str">
             <v>N</v>
@@ -24313,7 +24325,7 @@
             <v>m</v>
           </cell>
           <cell r="KS24" t="str">
-            <v>M/R</v>
+            <v>P</v>
           </cell>
           <cell r="KT24" t="str">
             <v>N</v>
@@ -24325,10 +24337,10 @@
             <v>R</v>
           </cell>
           <cell r="KW24" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="KX24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KY24" t="str">
             <v>N</v>
@@ -24385,31 +24397,31 @@
             <v>r</v>
           </cell>
           <cell r="LQ24" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="LR24" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="LS24" t="str">
             <v>m</v>
           </cell>
           <cell r="LT24" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="LU24" t="str">
             <v>p</v>
           </cell>
           <cell r="LV24" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="LW24" t="str">
-            <v>M</v>
+            <v>p</v>
           </cell>
           <cell r="LX24" t="str">
             <v>r</v>
           </cell>
           <cell r="LY24" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="LZ24" t="str">
             <v>P</v>
@@ -24490,22 +24502,22 @@
             <v>-</v>
           </cell>
           <cell r="MZ24" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="NA24" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="NB24" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="NC24" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="ND24" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="NE24" t="str">
             <v>-</v>
-          </cell>
-          <cell r="NA24" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="NB24" t="str">
-            <v>-</v>
-          </cell>
-          <cell r="NC24" t="str">
-            <v>R</v>
-          </cell>
-          <cell r="ND24" t="str">
-            <v>P</v>
-          </cell>
-          <cell r="NE24" t="str">
-            <v>M/R</v>
           </cell>
           <cell r="NF24" t="str">
             <v>-</v>
@@ -24547,16 +24559,16 @@
             <v>R</v>
           </cell>
           <cell r="NS24" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="NT24" t="str">
             <v>p</v>
           </cell>
           <cell r="NU24" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="NV24" t="str">
             <v>p</v>
-          </cell>
-          <cell r="NV24" t="str">
-            <v>m</v>
           </cell>
           <cell r="NW24" t="str">
             <v>p</v>
@@ -24565,10 +24577,10 @@
             <v>m</v>
           </cell>
           <cell r="NY24" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="NZ24" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="OA24" t="str">
             <v>p</v>
@@ -24577,7 +24589,7 @@
             <v>m</v>
           </cell>
           <cell r="OC24" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="OD24" t="str">
             <v>-</v>
@@ -25514,71 +25526,71 @@
           <cell r="KV25">
             <v>0</v>
           </cell>
-          <cell r="KW25" t="str">
+          <cell r="KW25">
+            <v>0</v>
+          </cell>
+          <cell r="KX25">
+            <v>0</v>
+          </cell>
+          <cell r="KY25">
+            <v>0</v>
+          </cell>
+          <cell r="KZ25">
+            <v>0</v>
+          </cell>
+          <cell r="LA25">
+            <v>0</v>
+          </cell>
+          <cell r="LB25">
+            <v>0</v>
+          </cell>
+          <cell r="LC25">
+            <v>0</v>
+          </cell>
+          <cell r="LD25">
+            <v>0</v>
+          </cell>
+          <cell r="LE25">
+            <v>0</v>
+          </cell>
+          <cell r="LF25">
+            <v>0</v>
+          </cell>
+          <cell r="LG25">
+            <v>0</v>
+          </cell>
+          <cell r="LH25">
+            <v>0</v>
+          </cell>
+          <cell r="LI25">
+            <v>0</v>
+          </cell>
+          <cell r="LJ25">
+            <v>0</v>
+          </cell>
+          <cell r="LK25">
+            <v>0</v>
+          </cell>
+          <cell r="LL25">
+            <v>0</v>
+          </cell>
+          <cell r="LM25">
+            <v>0</v>
+          </cell>
+          <cell r="LN25">
+            <v>0</v>
+          </cell>
+          <cell r="LO25">
+            <v>0</v>
+          </cell>
+          <cell r="LP25">
+            <v>0</v>
+          </cell>
+          <cell r="LQ25" t="str">
             <v>p</v>
           </cell>
-          <cell r="KX25">
-            <v>0</v>
-          </cell>
-          <cell r="KY25">
-            <v>0</v>
-          </cell>
-          <cell r="KZ25">
-            <v>0</v>
-          </cell>
-          <cell r="LA25">
-            <v>0</v>
-          </cell>
-          <cell r="LB25">
-            <v>0</v>
-          </cell>
-          <cell r="LC25">
-            <v>0</v>
-          </cell>
-          <cell r="LD25">
-            <v>0</v>
-          </cell>
-          <cell r="LE25">
-            <v>0</v>
-          </cell>
-          <cell r="LF25">
-            <v>0</v>
-          </cell>
-          <cell r="LG25">
-            <v>0</v>
-          </cell>
-          <cell r="LH25">
-            <v>0</v>
-          </cell>
-          <cell r="LI25">
-            <v>0</v>
-          </cell>
-          <cell r="LJ25">
-            <v>0</v>
-          </cell>
-          <cell r="LK25">
-            <v>0</v>
-          </cell>
-          <cell r="LL25">
-            <v>0</v>
-          </cell>
-          <cell r="LM25">
-            <v>0</v>
-          </cell>
-          <cell r="LN25">
-            <v>0</v>
-          </cell>
-          <cell r="LO25">
-            <v>0</v>
-          </cell>
-          <cell r="LP25">
-            <v>0</v>
-          </cell>
-          <cell r="LQ25">
-            <v>0</v>
-          </cell>
-          <cell r="LR25">
-            <v>0</v>
+          <cell r="LR25" t="str">
+            <v>p</v>
           </cell>
           <cell r="LS25">
             <v>0</v>
@@ -25679,14 +25691,14 @@
           <cell r="MY25" t="str">
             <v>nl</v>
           </cell>
-          <cell r="MZ25" t="str">
-            <v>nl</v>
-          </cell>
-          <cell r="NA25" t="str">
-            <v>pn</v>
-          </cell>
-          <cell r="NB25" t="str">
-            <v>x</v>
+          <cell r="MZ25">
+            <v>0</v>
+          </cell>
+          <cell r="NA25">
+            <v>0</v>
+          </cell>
+          <cell r="NB25">
+            <v>0</v>
           </cell>
           <cell r="NC25">
             <v>0</v>
@@ -25694,8 +25706,8 @@
           <cell r="ND25">
             <v>0</v>
           </cell>
-          <cell r="NE25">
-            <v>0</v>
+          <cell r="NE25" t="str">
+            <v>r</v>
           </cell>
           <cell r="NF25" t="str">
             <v>nl</v>
@@ -26672,7 +26684,7 @@
             <v>P</v>
           </cell>
           <cell r="KL27" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="KM27" t="str">
             <v>N</v>
@@ -26702,7 +26714,7 @@
             <v>P</v>
           </cell>
           <cell r="KV27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KW27" t="str">
             <v>N</v>
@@ -26750,7 +26762,7 @@
             <v>P</v>
           </cell>
           <cell r="LL27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LM27" t="str">
             <v>N</v>
@@ -26762,7 +26774,7 @@
             <v>R</v>
           </cell>
           <cell r="LP27" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="LQ27" t="str">
             <v>p</v>
@@ -26777,7 +26789,7 @@
             <v>m</v>
           </cell>
           <cell r="LU27" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="LV27" t="str">
             <v>p</v>
@@ -28507,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28941,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31228,7 +31240,7 @@
       </c>
       <c r="JM3" s="16" t="str">
         <f>[1]CARTELLINO!JP$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="JN3" s="16" t="str">
         <f>[1]CARTELLINO!JQ$3</f>
@@ -31316,7 +31328,7 @@
       </c>
       <c r="KI3" s="16" t="str">
         <f>[1]CARTELLINO!KL$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KJ3" s="16" t="str">
         <f>[1]CARTELLINO!KM$3</f>
@@ -31324,7 +31336,7 @@
       </c>
       <c r="KK3" s="16" t="str">
         <f>[1]CARTELLINO!KN$3</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="KL3" s="16" t="str">
         <f>[1]CARTELLINO!KO$3</f>
@@ -31332,7 +31344,7 @@
       </c>
       <c r="KM3" s="16" t="str">
         <f>[1]CARTELLINO!KP$3</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="KN3" s="16" t="str">
         <f>[1]CARTELLINO!KQ$3</f>
@@ -31356,7 +31368,7 @@
       </c>
       <c r="KS3" s="16" t="str">
         <f>[1]CARTELLINO!KV$3</f>
-        <v>r</v>
+        <v>P</v>
       </c>
       <c r="KT3" s="16" t="str">
         <f>[1]CARTELLINO!KW$3</f>
@@ -31496,7 +31508,7 @@
       </c>
       <c r="MB3" s="16" t="str">
         <f>[1]CARTELLINO!ME$3</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="MC3" s="16" t="str">
         <f>[1]CARTELLINO!MF$3</f>
@@ -31616,7 +31628,7 @@
       </c>
       <c r="NF3" s="16" t="str">
         <f>[1]CARTELLINO!NI$3</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="NG3" s="16" t="str">
         <f>[1]CARTELLINO!NJ$3</f>
@@ -31680,19 +31692,19 @@
       </c>
       <c r="NV3" s="16" t="str">
         <f>[1]CARTELLINO!NY$3</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="NW3" s="16" t="str">
         <f>[1]CARTELLINO!NZ$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NX3" s="16" t="str">
         <f>[1]CARTELLINO!OA$3</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="NY3" s="16" t="str">
         <f>[1]CARTELLINO!OB$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NZ3" s="16" t="str">
         <f>[1]CARTELLINO!OC$3</f>
@@ -33070,7 +33082,7 @@
       </c>
       <c r="LW4" s="43" t="str">
         <f>[1]CARTELLINO!LZ$4</f>
-        <v>f</v>
+        <v>p</v>
       </c>
       <c r="LX4" s="43" t="str">
         <f>[1]CARTELLINO!MA$4</f>
@@ -34403,7 +34415,7 @@
       </c>
       <c r="FL6" s="22" t="str">
         <f>[1]CARTELLINO!FO$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="FM6" s="22" t="str">
         <f>[1]CARTELLINO!FP$6</f>
@@ -34819,7 +34831,7 @@
       </c>
       <c r="JL6" s="22" t="str">
         <f>[1]CARTELLINO!JO$6</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="JM6" s="22" t="str">
         <f>[1]CARTELLINO!JP$6</f>
@@ -34855,11 +34867,11 @@
       </c>
       <c r="JU6" s="22" t="str">
         <f>[1]CARTELLINO!JX$6</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="JV6" s="22" t="str">
         <f>[1]CARTELLINO!JY$6</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="JW6" s="22" t="str">
         <f>[1]CARTELLINO!JZ$6</f>
@@ -34879,7 +34891,7 @@
       </c>
       <c r="KA6" s="22" t="str">
         <f>[1]CARTELLINO!KD$6</f>
-        <v>M/R</v>
+        <v>p</v>
       </c>
       <c r="KB6" s="22" t="str">
         <f>[1]CARTELLINO!KE$6</f>
@@ -34899,7 +34911,7 @@
       </c>
       <c r="KF6" s="22" t="str">
         <f>[1]CARTELLINO!KI$6</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="KG6" s="22" t="str">
         <f>[1]CARTELLINO!KJ$6</f>
@@ -34943,7 +34955,7 @@
       </c>
       <c r="KQ6" s="22" t="str">
         <f>[1]CARTELLINO!KT$6</f>
-        <v>P</v>
+        <v>M</v>
       </c>
       <c r="KR6" s="22" t="str">
         <f>[1]CARTELLINO!KU$6</f>
@@ -35043,11 +35055,11 @@
       </c>
       <c r="LP6" s="22" t="str">
         <f>[1]CARTELLINO!LS$6</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="LQ6" s="22" t="str">
         <f>[1]CARTELLINO!LT$6</f>
-        <v>P</v>
+        <v>p</v>
       </c>
       <c r="LR6" s="22" t="str">
         <f>[1]CARTELLINO!LU$6</f>
@@ -35075,7 +35087,7 @@
       </c>
       <c r="LX6" s="22" t="str">
         <f>[1]CARTELLINO!MA$6</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="LY6" s="22" t="str">
         <f>[1]CARTELLINO!MB$6</f>
@@ -35087,15 +35099,15 @@
       </c>
       <c r="MA6" s="22" t="str">
         <f>[1]CARTELLINO!MD$6</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="MB6" s="22" t="str">
         <f>[1]CARTELLINO!ME$6</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="MC6" s="22" t="str">
         <f>[1]CARTELLINO!MF$6</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="MD6" s="22" t="str">
         <f>[1]CARTELLINO!MG$6</f>
@@ -35103,7 +35115,7 @@
       </c>
       <c r="ME6" s="22" t="str">
         <f>[1]CARTELLINO!MH$6</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="MF6" s="22" t="str">
         <f>[1]CARTELLINO!MI$6</f>
@@ -35179,7 +35191,7 @@
       </c>
       <c r="MX6" s="22" t="str">
         <f>[1]CARTELLINO!NA$6</f>
-        <v>r</v>
+        <v>P</v>
       </c>
       <c r="MY6" s="22" t="str">
         <f>[1]CARTELLINO!NB$6</f>
@@ -35191,11 +35203,11 @@
       </c>
       <c r="NA6" s="22" t="str">
         <f>[1]CARTELLINO!ND$6</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="NB6" s="22" t="str">
         <f>[1]CARTELLINO!NE$6</f>
-        <v>r</v>
+        <v>M/R</v>
       </c>
       <c r="NC6" s="22" t="str">
         <f>[1]CARTELLINO!NF$6</f>
@@ -35235,7 +35247,7 @@
       </c>
       <c r="NL6" s="22" t="str">
         <f>[1]CARTELLINO!NO$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NM6" s="22" t="str">
         <f>[1]CARTELLINO!NP$6</f>
@@ -35255,7 +35267,7 @@
       </c>
       <c r="NQ6" s="22" t="str">
         <f>[1]CARTELLINO!NT$6</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="NR6" s="22" t="str">
         <f>[1]CARTELLINO!NU$6</f>
@@ -35275,7 +35287,7 @@
       </c>
       <c r="NV6" s="22" t="str">
         <f>[1]CARTELLINO!NY$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NW6" s="22" t="str">
         <f>[1]CARTELLINO!NZ$6</f>
@@ -35997,7 +36009,7 @@
       </c>
       <c r="FL7" s="46">
         <f>[1]CARTELLINO!FO$7</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="FM7" s="46">
         <f>[1]CARTELLINO!FP$7</f>
@@ -36447,9 +36459,9 @@
         <f>[1]CARTELLINO!JW$7</f>
         <v>0</v>
       </c>
-      <c r="JU7" s="46">
+      <c r="JU7" s="46" t="str">
         <f>[1]CARTELLINO!JX$7</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="JV7" s="46">
         <f>[1]CARTELLINO!JY$7</f>
@@ -38475,7 +38487,7 @@
       </c>
       <c r="KA9" s="24" t="str">
         <f>[1]CARTELLINO!KD$9</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="KB9" s="24" t="str">
         <f>[1]CARTELLINO!KE$9</f>
@@ -38491,7 +38503,7 @@
       </c>
       <c r="KE9" s="24" t="str">
         <f>[1]CARTELLINO!KH$9</f>
-        <v>R</v>
+        <v>m</v>
       </c>
       <c r="KF9" s="24" t="str">
         <f>[1]CARTELLINO!KI$9</f>
@@ -38535,19 +38547,19 @@
       </c>
       <c r="KP9" s="24" t="str">
         <f>[1]CARTELLINO!KS$9</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="KQ9" s="24" t="str">
         <f>[1]CARTELLINO!KT$9</f>
-        <v>M/R</v>
+        <v>-</v>
       </c>
       <c r="KR9" s="24" t="str">
         <f>[1]CARTELLINO!KU$9</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="KS9" s="24" t="str">
         <f>[1]CARTELLINO!KV$9</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="KT9" s="24" t="str">
         <f>[1]CARTELLINO!KW$9</f>
@@ -38579,7 +38591,7 @@
       </c>
       <c r="LA9" s="24" t="str">
         <f>[1]CARTELLINO!LD$9</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="LB9" s="24" t="str">
         <f>[1]CARTELLINO!LE$9</f>
@@ -38611,7 +38623,7 @@
       </c>
       <c r="LI9" s="24" t="str">
         <f>[1]CARTELLINO!LL$9</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="LJ9" s="24" t="str">
         <f>[1]CARTELLINO!LM$9</f>
@@ -38631,11 +38643,11 @@
       </c>
       <c r="LN9" s="24" t="str">
         <f>[1]CARTELLINO!LQ$9</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="LO9" s="24" t="str">
         <f>[1]CARTELLINO!LR$9</f>
-        <v>r</v>
+        <v>P</v>
       </c>
       <c r="LP9" s="24" t="str">
         <f>[1]CARTELLINO!LS$9</f>
@@ -38811,7 +38823,7 @@
       </c>
       <c r="NG9" s="24" t="str">
         <f>[1]CARTELLINO!NJ$9</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="NH9" s="24" t="str">
         <f>[1]CARTELLINO!NK$9</f>
@@ -38823,15 +38835,15 @@
       </c>
       <c r="NJ9" s="24" t="str">
         <f>[1]CARTELLINO!NM$9</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="NK9" s="24" t="str">
         <f>[1]CARTELLINO!NN$9</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="NL9" s="24" t="str">
         <f>[1]CARTELLINO!NO$9</f>
-        <v>m/R</v>
+        <v>p</v>
       </c>
       <c r="NM9" s="24" t="str">
         <f>[1]CARTELLINO!NP$9</f>
@@ -38847,75 +38859,75 @@
       </c>
       <c r="NP9" s="24" t="str">
         <f>[1]CARTELLINO!NS$9</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="NQ9" s="24" t="str">
         <f>[1]CARTELLINO!NT$9</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="NR9" s="24" t="str">
         <f>[1]CARTELLINO!NU$9</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NS9" s="24" t="str">
         <f>[1]CARTELLINO!NV$9</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="NT9" s="24" t="str">
         <f>[1]CARTELLINO!NW$9</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="NU9" s="24" t="str">
         <f>[1]CARTELLINO!NX$9</f>
-        <v>p</v>
+        <v>R</v>
       </c>
       <c r="NV9" s="24" t="str">
         <f>[1]CARTELLINO!NY$9</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="NW9" s="24" t="str">
         <f>[1]CARTELLINO!NZ$9</f>
-        <v>p</v>
+        <v>M/R</v>
       </c>
       <c r="NX9" s="24" t="str">
         <f>[1]CARTELLINO!OA$9</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="NY9" s="24" t="str">
         <f>[1]CARTELLINO!OB$9</f>
-        <v>p</v>
+        <v>S</v>
       </c>
       <c r="NZ9" s="24" t="str">
         <f>[1]CARTELLINO!OC$9</f>
-        <v>m</v>
+        <v>R</v>
       </c>
       <c r="OA9" s="24" t="str">
         <f>[1]CARTELLINO!OD$9</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="OB9" s="24" t="str">
         <f>[1]CARTELLINO!OE$9</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="OC9" s="24" t="str">
         <f>[1]CARTELLINO!OF$9</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="OD9" s="24" t="str">
         <f>[1]CARTELLINO!OG$9</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="OE9" s="24" t="str">
         <f>[1]CARTELLINO!OH$9</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="OF9" s="24" t="str">
         <f>[1]CARTELLINO!OI$9</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="OG9" s="24" t="str">
         <f>[1]CARTELLINO!OJ$9</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="OH9" s="17"/>
       <c r="OI9" s="17"/>
@@ -40127,21 +40139,21 @@
         <f>[1]CARTELLINO!KR$10</f>
         <v>0</v>
       </c>
-      <c r="KP10" s="46">
+      <c r="KP10" s="46" t="str">
         <f>[1]CARTELLINO!KS$10</f>
-        <v>0</v>
-      </c>
-      <c r="KQ10" s="46">
+        <v>f</v>
+      </c>
+      <c r="KQ10" s="46" t="str">
         <f>[1]CARTELLINO!KT$10</f>
-        <v>0</v>
-      </c>
-      <c r="KR10" s="46">
+        <v>f</v>
+      </c>
+      <c r="KR10" s="46" t="str">
         <f>[1]CARTELLINO!KU$10</f>
-        <v>0</v>
-      </c>
-      <c r="KS10" s="46">
+        <v>pn</v>
+      </c>
+      <c r="KS10" s="46" t="str">
         <f>[1]CARTELLINO!KV$10</f>
-        <v>0</v>
+        <v>x</v>
       </c>
       <c r="KT10" s="46">
         <f>[1]CARTELLINO!KW$10</f>
@@ -40171,9 +40183,9 @@
         <f>[1]CARTELLINO!LC$10</f>
         <v>f</v>
       </c>
-      <c r="LA10" s="46" t="str">
+      <c r="LA10" s="46">
         <f>[1]CARTELLINO!LD$10</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="LB10" s="46">
         <f>[1]CARTELLINO!LE$10</f>
@@ -42103,7 +42115,7 @@
       </c>
       <c r="KI12" s="25" t="str">
         <f>[1]CARTELLINO!KL$12</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="KJ12" s="25" t="str">
         <f>[1]CARTELLINO!KM$12</f>
@@ -42111,11 +42123,11 @@
       </c>
       <c r="KK12" s="25" t="str">
         <f>[1]CARTELLINO!KN$12</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="KL12" s="25" t="str">
         <f>[1]CARTELLINO!KO$12</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="KM12" s="25" t="str">
         <f>[1]CARTELLINO!KP$12</f>
@@ -42123,39 +42135,39 @@
       </c>
       <c r="KN12" s="25" t="str">
         <f>[1]CARTELLINO!KQ$12</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="KO12" s="25" t="str">
         <f>[1]CARTELLINO!KR$12</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="KP12" s="25" t="str">
         <f>[1]CARTELLINO!KS$12</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="KQ12" s="25" t="str">
         <f>[1]CARTELLINO!KT$12</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="KR12" s="25" t="str">
         <f>[1]CARTELLINO!KU$12</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KS12" s="25" t="str">
         <f>[1]CARTELLINO!KV$12</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="KT12" s="25" t="str">
         <f>[1]CARTELLINO!KW$12</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="KU12" s="25" t="str">
         <f>[1]CARTELLINO!KX$12</f>
-        <v>m/R</v>
+        <v>p</v>
       </c>
       <c r="KV12" s="25" t="str">
         <f>[1]CARTELLINO!KY$12</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="KW12" s="25" t="str">
         <f>[1]CARTELLINO!KZ$12</f>
@@ -42171,11 +42183,11 @@
       </c>
       <c r="KZ12" s="25" t="str">
         <f>[1]CARTELLINO!LC$12</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="LA12" s="25" t="str">
         <f>[1]CARTELLINO!LD$12</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="LB12" s="25" t="str">
         <f>[1]CARTELLINO!LE$12</f>
@@ -42247,11 +42259,11 @@
       </c>
       <c r="LS12" s="25" t="str">
         <f>[1]CARTELLINO!LV$12</f>
-        <v>r</v>
+        <v>P</v>
       </c>
       <c r="LT12" s="25" t="str">
         <f>[1]CARTELLINO!LW$12</f>
-        <v>p</v>
+        <v>M</v>
       </c>
       <c r="LU12" s="25" t="str">
         <f>[1]CARTELLINO!LX$12</f>
@@ -42463,7 +42475,7 @@
       </c>
       <c r="NU12" s="25" t="str">
         <f>[1]CARTELLINO!NX$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NV12" s="25" t="str">
         <f>[1]CARTELLINO!NY$12</f>
@@ -45591,7 +45603,7 @@
       </c>
       <c r="JH15" s="26" t="str">
         <f>[1]CARTELLINO!JK$15</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="JI15" s="26" t="str">
         <f>[1]CARTELLINO!JL$15</f>
@@ -45643,11 +45655,11 @@
       </c>
       <c r="JU15" s="26" t="str">
         <f>[1]CARTELLINO!JX$15</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="JV15" s="26" t="str">
         <f>[1]CARTELLINO!JY$15</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="JW15" s="26" t="str">
         <f>[1]CARTELLINO!JZ$15</f>
@@ -45699,7 +45711,7 @@
       </c>
       <c r="KI15" s="26" t="str">
         <f>[1]CARTELLINO!KL$15</f>
-        <v>P</v>
+        <v>m/R</v>
       </c>
       <c r="KJ15" s="26" t="str">
         <f>[1]CARTELLINO!KM$15</f>
@@ -45707,11 +45719,11 @@
       </c>
       <c r="KK15" s="26" t="str">
         <f>[1]CARTELLINO!KN$15</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KL15" s="26" t="str">
         <f>[1]CARTELLINO!KO$15</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="KM15" s="26" t="str">
         <f>[1]CARTELLINO!KP$15</f>
@@ -45723,27 +45735,27 @@
       </c>
       <c r="KO15" s="26" t="str">
         <f>[1]CARTELLINO!KR$15</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="KP15" s="26" t="str">
         <f>[1]CARTELLINO!KS$15</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="KQ15" s="26" t="str">
         <f>[1]CARTELLINO!KT$15</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="KR15" s="26" t="str">
         <f>[1]CARTELLINO!KU$15</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="KS15" s="26" t="str">
         <f>[1]CARTELLINO!KV$15</f>
-        <v>P</v>
+        <v>p</v>
       </c>
       <c r="KT15" s="26" t="str">
         <f>[1]CARTELLINO!KW$15</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="KU15" s="26" t="str">
         <f>[1]CARTELLINO!KX$15</f>
@@ -45939,7 +45951,7 @@
       </c>
       <c r="MQ15" s="26" t="str">
         <f>[1]CARTELLINO!MT$15</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="MR15" s="26" t="str">
         <f>[1]CARTELLINO!MU$15</f>
@@ -45971,7 +45983,7 @@
       </c>
       <c r="MY15" s="26" t="str">
         <f>[1]CARTELLINO!NB$15</f>
-        <v>P</v>
+        <v>M</v>
       </c>
       <c r="MZ15" s="26" t="str">
         <f>[1]CARTELLINO!NC$15</f>
@@ -46055,7 +46067,7 @@
       </c>
       <c r="NT15" s="26" t="str">
         <f>[1]CARTELLINO!NW$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NU15" s="26" t="str">
         <f>[1]CARTELLINO!NX$15</f>
@@ -47183,9 +47195,9 @@
         <f>[1]CARTELLINO!JJ$16</f>
         <v>0</v>
       </c>
-      <c r="JH16" s="46">
+      <c r="JH16" s="46" t="str">
         <f>[1]CARTELLINO!JK$16</f>
-        <v>0</v>
+        <v>k</v>
       </c>
       <c r="JI16" s="46">
         <f>[1]CARTELLINO!JL$16</f>
@@ -49203,7 +49215,7 @@
       </c>
       <c r="JL18" s="27" t="str">
         <f>[1]CARTELLINO!JO$18</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="JM18" s="27" t="str">
         <f>[1]CARTELLINO!JP$18</f>
@@ -49259,15 +49271,15 @@
       </c>
       <c r="JZ18" s="27" t="str">
         <f>[1]CARTELLINO!KC$18</f>
-        <v>M/R</v>
+        <v>m</v>
       </c>
       <c r="KA18" s="27" t="str">
         <f>[1]CARTELLINO!KD$18</f>
-        <v>N</v>
+        <v>P</v>
       </c>
       <c r="KB18" s="27" t="str">
         <f>[1]CARTELLINO!KE$18</f>
-        <v>S</v>
+        <v>m</v>
       </c>
       <c r="KC18" s="27" t="str">
         <f>[1]CARTELLINO!KF$18</f>
@@ -49399,19 +49411,19 @@
       </c>
       <c r="LI18" s="27" t="str">
         <f>[1]CARTELLINO!LL$18</f>
-        <v>m/R</v>
+        <v>-</v>
       </c>
       <c r="LJ18" s="27" t="str">
         <f>[1]CARTELLINO!LM$18</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="LK18" s="27" t="str">
         <f>[1]CARTELLINO!LN$18</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="LL18" s="27" t="str">
         <f>[1]CARTELLINO!LO$18</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="LM18" s="27" t="str">
         <f>[1]CARTELLINO!LP$18</f>
@@ -49431,7 +49443,7 @@
       </c>
       <c r="LQ18" s="27" t="str">
         <f>[1]CARTELLINO!LT$18</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="LR18" s="27" t="str">
         <f>[1]CARTELLINO!LU$18</f>
@@ -49439,7 +49451,7 @@
       </c>
       <c r="LS18" s="27" t="str">
         <f>[1]CARTELLINO!LV$18</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="LT18" s="27" t="str">
         <f>[1]CARTELLINO!LW$18</f>
@@ -49471,15 +49483,15 @@
       </c>
       <c r="MA18" s="27" t="str">
         <f>[1]CARTELLINO!MD$18</f>
-        <v>N</v>
+        <v>p</v>
       </c>
       <c r="MB18" s="27" t="str">
         <f>[1]CARTELLINO!ME$18</f>
-        <v>S</v>
+        <v>m</v>
       </c>
       <c r="MC18" s="27" t="str">
         <f>[1]CARTELLINO!MF$18</f>
-        <v>R</v>
+        <v>m</v>
       </c>
       <c r="MD18" s="27" t="str">
         <f>[1]CARTELLINO!MG$18</f>
@@ -49487,7 +49499,7 @@
       </c>
       <c r="ME18" s="27" t="str">
         <f>[1]CARTELLINO!MH$18</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="MF18" s="27" t="str">
         <f>[1]CARTELLINO!MI$18</f>
@@ -49563,11 +49575,11 @@
       </c>
       <c r="MX18" s="27" t="str">
         <f>[1]CARTELLINO!NA$18</f>
-        <v>P</v>
+        <v>M/R</v>
       </c>
       <c r="MY18" s="27" t="str">
         <f>[1]CARTELLINO!NB$18</f>
-        <v>M</v>
+        <v>P</v>
       </c>
       <c r="MZ18" s="27" t="str">
         <f>[1]CARTELLINO!NC$18</f>
@@ -49643,7 +49655,7 @@
       </c>
       <c r="NR18" s="27" t="str">
         <f>[1]CARTELLINO!NU$18</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="NS18" s="27" t="str">
         <f>[1]CARTELLINO!NV$18</f>
@@ -49659,11 +49671,11 @@
       </c>
       <c r="NV18" s="27" t="str">
         <f>[1]CARTELLINO!NY$18</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NW18" s="27" t="str">
         <f>[1]CARTELLINO!NZ$18</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="NX18" s="27" t="str">
         <f>[1]CARTELLINO!OA$18</f>
@@ -49671,11 +49683,11 @@
       </c>
       <c r="NY18" s="27" t="str">
         <f>[1]CARTELLINO!OB$18</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="NZ18" s="27" t="str">
         <f>[1]CARTELLINO!OC$18</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="OA18" s="27" t="str">
         <f>[1]CARTELLINO!OD$18</f>
@@ -50869,51 +50881,51 @@
       </c>
       <c r="KD19" s="46" t="str">
         <f>[1]CARTELLINO!KG$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KE19" s="46" t="str">
         <f>[1]CARTELLINO!KH$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KF19" s="46" t="str">
         <f>[1]CARTELLINO!KI$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KG19" s="46" t="str">
         <f>[1]CARTELLINO!KJ$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KH19" s="46" t="str">
         <f>[1]CARTELLINO!KK$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KI19" s="46" t="str">
         <f>[1]CARTELLINO!KL$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KJ19" s="46" t="str">
         <f>[1]CARTELLINO!KM$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KK19" s="46" t="str">
         <f>[1]CARTELLINO!KN$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KL19" s="46" t="str">
         <f>[1]CARTELLINO!KO$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KM19" s="46" t="str">
         <f>[1]CARTELLINO!KP$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KN19" s="46" t="str">
         <f>[1]CARTELLINO!KQ$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KO19" s="46" t="str">
         <f>[1]CARTELLINO!KR$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KP19" s="46" t="str">
         <f>[1]CARTELLINO!KS$19</f>
@@ -50961,51 +50973,51 @@
       </c>
       <c r="LA19" s="46" t="str">
         <f>[1]CARTELLINO!LD$19</f>
-        <v>f</v>
+        <v>k</v>
       </c>
       <c r="LB19" s="46" t="str">
         <f>[1]CARTELLINO!LE$19</f>
-        <v>f</v>
+        <v>k</v>
       </c>
       <c r="LC19" s="46" t="str">
         <f>[1]CARTELLINO!LF$19</f>
-        <v>f</v>
+        <v>k</v>
       </c>
       <c r="LD19" s="46" t="str">
         <f>[1]CARTELLINO!LG$19</f>
-        <v>f</v>
+        <v>k</v>
       </c>
       <c r="LE19" s="46" t="str">
         <f>[1]CARTELLINO!LH$19</f>
-        <v>f</v>
+        <v>k</v>
       </c>
       <c r="LF19" s="46" t="str">
         <f>[1]CARTELLINO!LI$19</f>
-        <v>f</v>
+        <v>k</v>
       </c>
       <c r="LG19" s="46" t="str">
         <f>[1]CARTELLINO!LJ$19</f>
-        <v>f</v>
+        <v>k</v>
       </c>
       <c r="LH19" s="46" t="str">
         <f>[1]CARTELLINO!LK$19</f>
-        <v>f</v>
-      </c>
-      <c r="LI19" s="46">
+        <v>k</v>
+      </c>
+      <c r="LI19" s="46" t="str">
         <f>[1]CARTELLINO!LL$19</f>
-        <v>0</v>
-      </c>
-      <c r="LJ19" s="46">
+        <v>k</v>
+      </c>
+      <c r="LJ19" s="46" t="str">
         <f>[1]CARTELLINO!LM$19</f>
-        <v>0</v>
-      </c>
-      <c r="LK19" s="46">
+        <v>k</v>
+      </c>
+      <c r="LK19" s="46" t="str">
         <f>[1]CARTELLINO!LN$19</f>
-        <v>0</v>
-      </c>
-      <c r="LL19" s="46">
+        <v>k</v>
+      </c>
+      <c r="LL19" s="46" t="str">
         <f>[1]CARTELLINO!LO$19</f>
-        <v>0</v>
+        <v>k</v>
       </c>
       <c r="LM19" s="46">
         <f>[1]CARTELLINO!LP$19</f>
@@ -52855,19 +52867,19 @@
       </c>
       <c r="JZ21" s="28" t="str">
         <f>[1]CARTELLINO!KC$21</f>
-        <v>P</v>
+        <v>M/R</v>
       </c>
       <c r="KA21" s="28" t="str">
         <f>[1]CARTELLINO!KD$21</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="KB21" s="28" t="str">
         <f>[1]CARTELLINO!KE$21</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="KC21" s="28" t="str">
         <f>[1]CARTELLINO!KF$21</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="KD21" s="28" t="str">
         <f>[1]CARTELLINO!KG$21</f>
@@ -52911,7 +52923,7 @@
       </c>
       <c r="KN21" s="28" t="str">
         <f>[1]CARTELLINO!KQ$21</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="KO21" s="28" t="str">
         <f>[1]CARTELLINO!KR$21</f>
@@ -52919,31 +52931,31 @@
       </c>
       <c r="KP21" s="28" t="str">
         <f>[1]CARTELLINO!KS$21</f>
-        <v>m</v>
+        <v>M/R</v>
       </c>
       <c r="KQ21" s="28" t="str">
         <f>[1]CARTELLINO!KT$21</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="KR21" s="28" t="str">
         <f>[1]CARTELLINO!KU$21</f>
-        <v>r</v>
+        <v>N</v>
       </c>
       <c r="KS21" s="28" t="str">
         <f>[1]CARTELLINO!KV$21</f>
-        <v>m/R</v>
+        <v>S</v>
       </c>
       <c r="KT21" s="28" t="str">
         <f>[1]CARTELLINO!KW$21</f>
-        <v>P</v>
+        <v>R</v>
       </c>
       <c r="KU21" s="28" t="str">
         <f>[1]CARTELLINO!KX$21</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="KV21" s="28" t="str">
         <f>[1]CARTELLINO!KY$21</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KW21" s="28" t="str">
         <f>[1]CARTELLINO!KZ$21</f>
@@ -52959,7 +52971,7 @@
       </c>
       <c r="KZ21" s="28" t="str">
         <f>[1]CARTELLINO!LC$21</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="LA21" s="28" t="str">
         <f>[1]CARTELLINO!LD$21</f>
@@ -53027,7 +53039,7 @@
       </c>
       <c r="LQ21" s="28" t="str">
         <f>[1]CARTELLINO!LT$21</f>
-        <v>r</v>
+        <v>P</v>
       </c>
       <c r="LR21" s="28" t="str">
         <f>[1]CARTELLINO!LU$21</f>
@@ -53047,7 +53059,7 @@
       </c>
       <c r="LV21" s="28" t="str">
         <f>[1]CARTELLINO!LY$21</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="LW21" s="28" t="str">
         <f>[1]CARTELLINO!LZ$21</f>
@@ -53159,7 +53171,7 @@
       </c>
       <c r="MX21" s="28" t="str">
         <f>[1]CARTELLINO!NA$21</f>
-        <v>M/R</v>
+        <v>p</v>
       </c>
       <c r="MY21" s="28" t="str">
         <f>[1]CARTELLINO!NB$21</f>
@@ -53207,15 +53219,15 @@
       </c>
       <c r="NJ21" s="28" t="str">
         <f>[1]CARTELLINO!NM$21</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NK21" s="28" t="str">
         <f>[1]CARTELLINO!NN$21</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="NL21" s="28" t="str">
         <f>[1]CARTELLINO!NO$21</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="NM21" s="28" t="str">
         <f>[1]CARTELLINO!NP$21</f>
@@ -53243,7 +53255,7 @@
       </c>
       <c r="NS21" s="28" t="str">
         <f>[1]CARTELLINO!NV$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NT21" s="28" t="str">
         <f>[1]CARTELLINO!NW$21</f>
@@ -54639,9 +54651,9 @@
         <f>[1]CARTELLINO!LX$22</f>
         <v>0</v>
       </c>
-      <c r="LV22" s="46">
+      <c r="LV22" s="46" t="str">
         <f>[1]CARTELLINO!LY$22</f>
-        <v>0</v>
+        <v>r</v>
       </c>
       <c r="LW22" s="46">
         <f>[1]CARTELLINO!LZ$22</f>
@@ -56399,7 +56411,7 @@
       </c>
       <c r="JM24" s="29" t="str">
         <f>[1]CARTELLINO!JP$24</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="JN24" s="29" t="str">
         <f>[1]CARTELLINO!JQ$24</f>
@@ -56451,11 +56463,11 @@
       </c>
       <c r="JZ24" s="29" t="str">
         <f>[1]CARTELLINO!KC$24</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="KA24" s="29" t="str">
         <f>[1]CARTELLINO!KD$24</f>
-        <v>r</v>
+        <v>M/R</v>
       </c>
       <c r="KB24" s="29" t="str">
         <f>[1]CARTELLINO!KE$24</f>
@@ -56515,7 +56527,7 @@
       </c>
       <c r="KP24" s="29" t="str">
         <f>[1]CARTELLINO!KS$24</f>
-        <v>M/R</v>
+        <v>P</v>
       </c>
       <c r="KQ24" s="29" t="str">
         <f>[1]CARTELLINO!KT$24</f>
@@ -56531,11 +56543,11 @@
       </c>
       <c r="KT24" s="29" t="str">
         <f>[1]CARTELLINO!KW$24</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="KU24" s="29" t="str">
         <f>[1]CARTELLINO!KX$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KV24" s="29" t="str">
         <f>[1]CARTELLINO!KY$24</f>
@@ -56611,11 +56623,11 @@
       </c>
       <c r="LN24" s="29" t="str">
         <f>[1]CARTELLINO!LQ$24</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="LO24" s="29" t="str">
         <f>[1]CARTELLINO!LR$24</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="LP24" s="29" t="str">
         <f>[1]CARTELLINO!LS$24</f>
@@ -56623,7 +56635,7 @@
       </c>
       <c r="LQ24" s="29" t="str">
         <f>[1]CARTELLINO!LT$24</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="LR24" s="29" t="str">
         <f>[1]CARTELLINO!LU$24</f>
@@ -56631,11 +56643,11 @@
       </c>
       <c r="LS24" s="29" t="str">
         <f>[1]CARTELLINO!LV$24</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="LT24" s="29" t="str">
         <f>[1]CARTELLINO!LW$24</f>
-        <v>M</v>
+        <v>p</v>
       </c>
       <c r="LU24" s="29" t="str">
         <f>[1]CARTELLINO!LX$24</f>
@@ -56643,7 +56655,7 @@
       </c>
       <c r="LV24" s="29" t="str">
         <f>[1]CARTELLINO!LY$24</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="LW24" s="29" t="str">
         <f>[1]CARTELLINO!LZ$24</f>
@@ -56751,27 +56763,27 @@
       </c>
       <c r="MW24" s="29" t="str">
         <f>[1]CARTELLINO!MZ$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MX24" s="29" t="str">
         <f>[1]CARTELLINO!NA$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MY24" s="29" t="str">
         <f>[1]CARTELLINO!NB$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MZ24" s="29" t="str">
         <f>[1]CARTELLINO!NC$24</f>
-        <v>R</v>
+        <v>m</v>
       </c>
       <c r="NA24" s="29" t="str">
         <f>[1]CARTELLINO!ND$24</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="NB24" s="29" t="str">
         <f>[1]CARTELLINO!NE$24</f>
-        <v>M/R</v>
+        <v>-</v>
       </c>
       <c r="NC24" s="29" t="str">
         <f>[1]CARTELLINO!NF$24</f>
@@ -56827,7 +56839,7 @@
       </c>
       <c r="NP24" s="29" t="str">
         <f>[1]CARTELLINO!NS$24</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NQ24" s="29" t="str">
         <f>[1]CARTELLINO!NT$24</f>
@@ -56835,11 +56847,11 @@
       </c>
       <c r="NR24" s="29" t="str">
         <f>[1]CARTELLINO!NU$24</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="NS24" s="29" t="str">
         <f>[1]CARTELLINO!NV$24</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NT24" s="29" t="str">
         <f>[1]CARTELLINO!NW$24</f>
@@ -56851,11 +56863,11 @@
       </c>
       <c r="NV24" s="29" t="str">
         <f>[1]CARTELLINO!NY$24</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="NW24" s="29" t="str">
         <f>[1]CARTELLINO!NZ$24</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="NX24" s="29" t="str">
         <f>[1]CARTELLINO!OA$24</f>
@@ -56867,7 +56879,7 @@
       </c>
       <c r="NZ24" s="29" t="str">
         <f>[1]CARTELLINO!OC$24</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="OA24" s="29" t="str">
         <f>[1]CARTELLINO!OD$24</f>
@@ -58123,9 +58135,9 @@
         <f>[1]CARTELLINO!KV$25</f>
         <v>0</v>
       </c>
-      <c r="KT25" s="46" t="str">
+      <c r="KT25" s="46">
         <f>[1]CARTELLINO!KW$25</f>
-        <v>p</v>
+        <v>0</v>
       </c>
       <c r="KU25" s="46">
         <f>[1]CARTELLINO!KX$25</f>
@@ -58203,13 +58215,13 @@
         <f>[1]CARTELLINO!LP$25</f>
         <v>0</v>
       </c>
-      <c r="LN25" s="46">
+      <c r="LN25" s="46" t="str">
         <f>[1]CARTELLINO!LQ$25</f>
-        <v>0</v>
-      </c>
-      <c r="LO25" s="46">
+        <v>p</v>
+      </c>
+      <c r="LO25" s="46" t="str">
         <f>[1]CARTELLINO!LR$25</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="LP25" s="46">
         <f>[1]CARTELLINO!LS$25</f>
@@ -58343,17 +58355,17 @@
         <f>[1]CARTELLINO!MY$25</f>
         <v>nl</v>
       </c>
-      <c r="MW25" s="46" t="str">
+      <c r="MW25" s="46">
         <f>[1]CARTELLINO!MZ$25</f>
-        <v>nl</v>
-      </c>
-      <c r="MX25" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="MX25" s="46">
         <f>[1]CARTELLINO!NA$25</f>
-        <v>pn</v>
-      </c>
-      <c r="MY25" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="MY25" s="46">
         <f>[1]CARTELLINO!NB$25</f>
-        <v>x</v>
+        <v>0</v>
       </c>
       <c r="MZ25" s="46">
         <f>[1]CARTELLINO!NC$25</f>
@@ -58363,9 +58375,9 @@
         <f>[1]CARTELLINO!ND$25</f>
         <v>0</v>
       </c>
-      <c r="NB25" s="46">
+      <c r="NB25" s="46" t="str">
         <f>[1]CARTELLINO!NE$25</f>
-        <v>0</v>
+        <v>r</v>
       </c>
       <c r="NC25" s="46" t="str">
         <f>[1]CARTELLINO!NF$25</f>
@@ -60083,7 +60095,7 @@
       </c>
       <c r="KI27" s="30" t="str">
         <f>[1]CARTELLINO!KL$27</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="KJ27" s="30" t="str">
         <f>[1]CARTELLINO!KM$27</f>
@@ -60123,7 +60135,7 @@
       </c>
       <c r="KS27" s="30" t="str">
         <f>[1]CARTELLINO!KV$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KT27" s="30" t="str">
         <f>[1]CARTELLINO!KW$27</f>
@@ -60187,7 +60199,7 @@
       </c>
       <c r="LI27" s="30" t="str">
         <f>[1]CARTELLINO!LL$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LJ27" s="30" t="str">
         <f>[1]CARTELLINO!LM$27</f>
@@ -60203,7 +60215,7 @@
       </c>
       <c r="LM27" s="30" t="str">
         <f>[1]CARTELLINO!LP$27</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="LN27" s="30" t="str">
         <f>[1]CARTELLINO!LQ$27</f>
@@ -60223,7 +60235,7 @@
       </c>
       <c r="LR27" s="30" t="str">
         <f>[1]CARTELLINO!LU$27</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="LS27" s="30" t="str">
         <f>[1]CARTELLINO!LV$27</f>
@@ -62956,10 +62968,10 @@
         <v>FABBRI</v>
       </c>
       <c r="KA29" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BERARDI</v>
       </c>
       <c r="KB29" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="KC29" s="63" t="str">
         <v>SARTI</v>
@@ -62983,7 +62995,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KJ29" s="63" t="str">
-        <v>FABBRI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KK29" s="63" t="str">
         <v>BERARDI</v>
@@ -63004,22 +63016,22 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="KQ29" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="KR29" s="63" t="str">
-        <v>SARTI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="KS29" s="63" t="str">
         <v>BARBIERI</v>
       </c>
       <c r="KT29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KU29" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="KV29" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="KW29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -63061,7 +63073,7 @@
         <v>BERARDI</v>
       </c>
       <c r="LJ29" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>FABBRI</v>
       </c>
       <c r="LK29" s="63" t="str">
         <v>VOLPINI</v>
@@ -63127,7 +63139,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="MF29" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BARBIERI</v>
       </c>
       <c r="MG29" s="63" t="str">
         <v>SARTI</v>
@@ -63168,8 +63180,8 @@
       <c r="MS29" s="63" t="str">
         <v>BIANCHI</v>
       </c>
-      <c r="MT29" s="63">
-        <v>0</v>
+      <c r="MT29" s="63" t="str">
+        <v>VOLPINI</v>
       </c>
       <c r="MU29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -63183,8 +63195,8 @@
       <c r="MX29" s="63" t="str">
         <v>VOLPINI</v>
       </c>
-      <c r="MY29" s="63">
-        <v>0</v>
+      <c r="MY29" s="63" t="str">
+        <v>MICHELOT.</v>
       </c>
       <c r="MZ29" s="63" t="str">
         <v>BARBIERI</v>
@@ -64056,10 +64068,10 @@
         <v>FABBRI</v>
       </c>
       <c r="KA30" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BERARDI</v>
       </c>
       <c r="KB30" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="KC30" s="63" t="str">
         <v>SARTI</v>
@@ -64083,7 +64095,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KJ30" s="63" t="str">
-        <v>FABBRI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KK30" s="63" t="str">
         <v>BERARDI</v>
@@ -64104,22 +64116,22 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="KQ30" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="KR30" s="63" t="str">
-        <v>SARTI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="KS30" s="63" t="str">
         <v>BARBIERI</v>
       </c>
       <c r="KT30" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KU30" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="KV30" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="KW30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -64161,7 +64173,7 @@
         <v>BERARDI</v>
       </c>
       <c r="LJ30" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>FABBRI</v>
       </c>
       <c r="LK30" s="63" t="str">
         <v>VOLPINI</v>
@@ -64227,7 +64239,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="MF30" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BARBIERI</v>
       </c>
       <c r="MG30" s="63" t="str">
         <v>SARTI</v>
@@ -64268,8 +64280,8 @@
       <c r="MS30" s="63" t="str">
         <v>BIANCHI</v>
       </c>
-      <c r="MT30" s="63">
-        <v>0</v>
+      <c r="MT30" s="63" t="str">
+        <v>VOLPINI</v>
       </c>
       <c r="MU30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -64283,8 +64295,8 @@
       <c r="MX30" s="63" t="str">
         <v>VOLPINI</v>
       </c>
-      <c r="MY30" s="63">
-        <v>0</v>
+      <c r="MY30" s="63" t="str">
+        <v>MICHELOT.</v>
       </c>
       <c r="MZ30" s="63" t="str">
         <v>BARBIERI</v>
@@ -65153,10 +65165,10 @@
         <v>FABBRI</v>
       </c>
       <c r="JZ31" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BERARDI</v>
       </c>
       <c r="KA31" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="KB31" s="63" t="str">
         <v>SARTI</v>
@@ -65180,7 +65192,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KI31" s="63" t="str">
-        <v>FABBRI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KJ31" s="63" t="str">
         <v>BERARDI</v>
@@ -65201,22 +65213,22 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="KP31" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="KQ31" s="63" t="str">
-        <v>SARTI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="KR31" s="63" t="str">
         <v>BARBIERI</v>
       </c>
       <c r="KS31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KT31" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="KU31" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="KV31" s="63" t="str">
         <v>GHIOTTI</v>
@@ -65258,7 +65270,7 @@
         <v>BERARDI</v>
       </c>
       <c r="LI31" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>FABBRI</v>
       </c>
       <c r="LJ31" s="63" t="str">
         <v>VOLPINI</v>
@@ -65324,7 +65336,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="ME31" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BARBIERI</v>
       </c>
       <c r="MF31" s="63" t="str">
         <v>SARTI</v>
@@ -65381,7 +65393,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="MX31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="MY31" s="63" t="str">
         <v>BARBIERI</v>
@@ -65393,7 +65405,7 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="NB31" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BARBIERI</v>
       </c>
     </row>
     <row r="32" spans="1:404" x14ac:dyDescent="0.25">
@@ -66190,7 +66202,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="JE32" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="JF32" s="63" t="str">
         <v>FABBRI</v>
@@ -66253,10 +66265,10 @@
         <v>FABBRI</v>
       </c>
       <c r="JZ32" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BERARDI</v>
       </c>
       <c r="KA32" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="KB32" s="63" t="str">
         <v>SARTI</v>
@@ -66280,7 +66292,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KI32" s="63" t="str">
-        <v>FABBRI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KJ32" s="63" t="str">
         <v>BERARDI</v>
@@ -66301,22 +66313,22 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="KP32" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="KQ32" s="63" t="str">
-        <v>SARTI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="KR32" s="63" t="str">
         <v>BARBIERI</v>
       </c>
       <c r="KS32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KT32" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="KU32" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="KV32" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66358,7 +66370,7 @@
         <v>BERARDI</v>
       </c>
       <c r="LI32" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>FABBRI</v>
       </c>
       <c r="LJ32" s="63" t="str">
         <v>VOLPINI</v>
@@ -66424,7 +66436,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="ME32" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BARBIERI</v>
       </c>
       <c r="MF32" s="63" t="str">
         <v>SARTI</v>
@@ -66481,7 +66493,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="MX32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="MY32" s="63" t="str">
         <v>BARBIERI</v>
@@ -66493,7 +66505,7 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="NB32" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BARBIERI</v>
       </c>
     </row>
     <row r="33" spans="1:285" x14ac:dyDescent="0.25">
@@ -66519,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71017,6 +71029,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71025,13 +71044,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB598283-A089-44E3-B8C7-EC9413F1B7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5349A2-8C7F-498D-980F-D402358D809C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -10054,13 +10054,13 @@
             <v>M/R</v>
           </cell>
           <cell r="KV6" t="str">
-            <v>N</v>
+            <v>p</v>
           </cell>
           <cell r="KW6" t="str">
-            <v>S</v>
+            <v>m</v>
           </cell>
           <cell r="KX6" t="str">
-            <v>R</v>
+            <v>p</v>
           </cell>
           <cell r="KY6" t="str">
             <v>P</v>
@@ -10147,7 +10147,7 @@
             <v>m</v>
           </cell>
           <cell r="MA6" t="str">
-            <v>p</v>
+            <v>r</v>
           </cell>
           <cell r="MB6" t="str">
             <v>p</v>
@@ -14790,10 +14790,10 @@
             <v>m</v>
           </cell>
           <cell r="KN12" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="KO12" t="str">
             <v>m</v>
-          </cell>
-          <cell r="KO12" t="str">
-            <v>r</v>
           </cell>
           <cell r="KP12" t="str">
             <v>-</v>
@@ -14814,13 +14814,13 @@
             <v>p</v>
           </cell>
           <cell r="KV12" t="str">
-            <v>m</v>
+            <v>N</v>
           </cell>
           <cell r="KW12" t="str">
-            <v>r</v>
+            <v>S</v>
           </cell>
           <cell r="KX12" t="str">
-            <v>p</v>
+            <v>R</v>
           </cell>
           <cell r="KY12" t="str">
             <v>m</v>
@@ -14976,7 +14976,7 @@
             <v>p</v>
           </cell>
           <cell r="MX12" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="MY12" t="str">
             <v>P</v>
@@ -17170,7 +17170,7 @@
             <v>p</v>
           </cell>
           <cell r="KN15" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="KO15" t="str">
             <v>m</v>
@@ -17194,7 +17194,7 @@
             <v>m</v>
           </cell>
           <cell r="KV15" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="KW15" t="str">
             <v>p</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -34963,15 +34963,15 @@
       </c>
       <c r="KS6" s="22" t="str">
         <f>[1]CARTELLINO!KV$6</f>
-        <v>N</v>
+        <v>p</v>
       </c>
       <c r="KT6" s="22" t="str">
         <f>[1]CARTELLINO!KW$6</f>
-        <v>S</v>
+        <v>m</v>
       </c>
       <c r="KU6" s="22" t="str">
         <f>[1]CARTELLINO!KX$6</f>
-        <v>R</v>
+        <v>p</v>
       </c>
       <c r="KV6" s="22" t="str">
         <f>[1]CARTELLINO!KY$6</f>
@@ -35087,7 +35087,7 @@
       </c>
       <c r="LX6" s="22" t="str">
         <f>[1]CARTELLINO!MA$6</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="LY6" s="22" t="str">
         <f>[1]CARTELLINO!MB$6</f>
@@ -42123,11 +42123,11 @@
       </c>
       <c r="KK12" s="25" t="str">
         <f>[1]CARTELLINO!KN$12</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KL12" s="25" t="str">
         <f>[1]CARTELLINO!KO$12</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="KM12" s="25" t="str">
         <f>[1]CARTELLINO!KP$12</f>
@@ -42155,15 +42155,15 @@
       </c>
       <c r="KS12" s="25" t="str">
         <f>[1]CARTELLINO!KV$12</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="KT12" s="25" t="str">
         <f>[1]CARTELLINO!KW$12</f>
-        <v>r</v>
+        <v>S</v>
       </c>
       <c r="KU12" s="25" t="str">
         <f>[1]CARTELLINO!KX$12</f>
-        <v>p</v>
+        <v>R</v>
       </c>
       <c r="KV12" s="25" t="str">
         <f>[1]CARTELLINO!KY$12</f>
@@ -42371,7 +42371,7 @@
       </c>
       <c r="MU12" s="25" t="str">
         <f>[1]CARTELLINO!MX$12</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="MV12" s="25" t="str">
         <f>[1]CARTELLINO!MY$12</f>
@@ -45719,7 +45719,7 @@
       </c>
       <c r="KK15" s="26" t="str">
         <f>[1]CARTELLINO!KN$15</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="KL15" s="26" t="str">
         <f>[1]CARTELLINO!KO$15</f>
@@ -45751,7 +45751,7 @@
       </c>
       <c r="KS15" s="26" t="str">
         <f>[1]CARTELLINO!KV$15</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="KT15" s="26" t="str">
         <f>[1]CARTELLINO!KW$15</f>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,13 +71029,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71044,6 +71037,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5349A2-8C7F-498D-980F-D402358D809C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D4B3CC-D3A1-4B9C-A2F3-EC3EFFE4DFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="13785" yWindow="390" windowWidth="14280" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -10015,7 +10015,7 @@
             <v>r</v>
           </cell>
           <cell r="KI6" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="KJ6" t="str">
             <v>P</v>
@@ -11204,8 +11204,8 @@
           <cell r="KH7">
             <v>0</v>
           </cell>
-          <cell r="KI7">
-            <v>0</v>
+          <cell r="KI7" t="str">
+            <v>p</v>
           </cell>
           <cell r="KJ7">
             <v>0</v>
@@ -23330,7 +23330,7 @@
             <v>f</v>
           </cell>
           <cell r="NF22" t="str">
-            <v>V</v>
+            <v>nl</v>
           </cell>
           <cell r="NG22" t="str">
             <v>V</v>
@@ -34911,7 +34911,7 @@
       </c>
       <c r="KF6" s="22" t="str">
         <f>[1]CARTELLINO!KI$6</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="KG6" s="22" t="str">
         <f>[1]CARTELLINO!KJ$6</f>
@@ -36503,9 +36503,9 @@
         <f>[1]CARTELLINO!KH$7</f>
         <v>0</v>
       </c>
-      <c r="KF7" s="46">
+      <c r="KF7" s="46" t="str">
         <f>[1]CARTELLINO!KI$7</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="KG7" s="46">
         <f>[1]CARTELLINO!KJ$7</f>
@@ -54785,7 +54785,7 @@
       </c>
       <c r="NC22" s="46" t="str">
         <f>[1]CARTELLINO!NF$22</f>
-        <v>V</v>
+        <v>nl</v>
       </c>
       <c r="ND22" s="46" t="str">
         <f>[1]CARTELLINO!NG$22</f>

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D4B3CC-D3A1-4B9C-A2F3-EC3EFFE4DFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE38F41C-5E8D-4963-8D41-915EBA06CCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13785" yWindow="390" windowWidth="14280" windowHeight="15090" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5684,18 +5684,18 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS296" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT296" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="297">
           <cell r="AQ297" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR297" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS297" t="str">
             <v>GHIOTTI</v>
@@ -5768,18 +5768,18 @@
             <v>GHIOTTI</v>
           </cell>
           <cell r="AS302" t="str">
-            <v>BERARDI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT302" t="str">
-            <v>BERARDI</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="303">
           <cell r="AQ303" t="str">
-            <v>BERARDI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR303" t="str">
-            <v>BERARDI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS303" t="str">
             <v>BIANCHI</v>
@@ -5824,18 +5824,18 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AS306" t="str">
-            <v>GHIOTTI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT306" t="str">
-            <v>GHIOTTI</v>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="307">
           <cell r="AQ307" t="str">
-            <v>GHIOTTI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR307" t="str">
-            <v>GHIOTTI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS307" t="str">
             <v>PAZZAGLIA</v>
@@ -5894,18 +5894,18 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AS311" t="str">
-            <v>FABBRI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT311" t="str">
-            <v>FABBRI</v>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="312">
           <cell r="AQ312" t="str">
-            <v>FABBRI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR312" t="str">
-            <v>FABBRI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS312" t="str">
             <v>PAZZAGLIA</v>
@@ -6258,18 +6258,18 @@
             <v>BERARDI</v>
           </cell>
           <cell r="AS337" t="str">
-            <v>PAZZAGLIA</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT337" t="str">
-            <v>PAZZAGLIA</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="338">
           <cell r="AQ338" t="str">
-            <v>PAZZAGLIA</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR338" t="str">
-            <v>PAZZAGLIA</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS338" t="str">
             <v>MICHELOT.</v>
@@ -6398,18 +6398,18 @@
             <v>BERARDI</v>
           </cell>
           <cell r="AS347" t="str">
-            <v>FABBRI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT347" t="str">
-            <v>FABBRI</v>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="348">
           <cell r="AQ348" t="str">
-            <v>FABBRI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR348" t="str">
-            <v>FABBRI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS348" t="str">
             <v>VOLPINI</v>
@@ -6426,18 +6426,18 @@
             <v>VOLPINI</v>
           </cell>
           <cell r="AS349" t="str">
-            <v>BARBIERI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT349" t="str">
-            <v>BARBIERI</v>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="350">
           <cell r="AQ350" t="str">
-            <v>BARBIERI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR350" t="str">
-            <v>BARBIERI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS350" t="str">
             <v>SARTI</v>
@@ -6538,18 +6538,18 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AS357" t="str">
-            <v>BIANCHI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT357" t="str">
-            <v>BIANCHI</v>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="358">
           <cell r="AQ358" t="str">
-            <v>BIANCHI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR358" t="str">
-            <v>BIANCHI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS358" t="str">
             <v>BERARDI</v>
@@ -7755,7 +7755,7 @@
             <v>P</v>
           </cell>
           <cell r="LV3" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="LW3" t="str">
             <v>-</v>
@@ -7794,7 +7794,7 @@
             <v>p</v>
           </cell>
           <cell r="MI3" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="MJ3" t="str">
             <v>M/R</v>
@@ -10168,10 +10168,10 @@
             <v>p</v>
           </cell>
           <cell r="MH6" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="MI6" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="MJ6" t="str">
             <v>m</v>
@@ -14757,7 +14757,7 @@
             <v>S</v>
           </cell>
           <cell r="KC12" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="KD12" t="str">
             <v>r</v>
@@ -14787,7 +14787,7 @@
             <v>P</v>
           </cell>
           <cell r="KM12" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="KN12" t="str">
             <v>p</v>
@@ -17179,7 +17179,7 @@
             <v>p</v>
           </cell>
           <cell r="KQ15" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="KR15" t="str">
             <v>r</v>
@@ -17194,7 +17194,7 @@
             <v>m</v>
           </cell>
           <cell r="KV15" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="KW15" t="str">
             <v>p</v>
@@ -17332,7 +17332,7 @@
             <v>p</v>
           </cell>
           <cell r="MP15" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="MQ15" t="str">
             <v>p</v>
@@ -19682,13 +19682,13 @@
             <v>m</v>
           </cell>
           <cell r="MF18" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="MG18" t="str">
             <v>P</v>
           </cell>
           <cell r="MH18" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MI18" t="str">
             <v>N</v>
@@ -21909,7 +21909,7 @@
             <v>R</v>
           </cell>
           <cell r="KG21" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="KH21" t="str">
             <v>p</v>
@@ -21927,7 +21927,7 @@
             <v>r</v>
           </cell>
           <cell r="KM21" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="KN21" t="str">
             <v>N</v>
@@ -24412,7 +24412,7 @@
             <v>p</v>
           </cell>
           <cell r="LV24" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="LW24" t="str">
             <v>p</v>
@@ -24472,7 +24472,7 @@
             <v>P</v>
           </cell>
           <cell r="MP24" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="MQ24" t="str">
             <v>N</v>
@@ -26669,7 +26669,7 @@
             <v>P</v>
           </cell>
           <cell r="KG27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KH27" t="str">
             <v>N</v>
@@ -26699,7 +26699,7 @@
             <v>P</v>
           </cell>
           <cell r="KQ27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KR27" t="str">
             <v>N</v>
@@ -26714,7 +26714,7 @@
             <v>P</v>
           </cell>
           <cell r="KV27" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="KW27" t="str">
             <v>N</v>
@@ -26822,7 +26822,7 @@
             <v>P</v>
           </cell>
           <cell r="MF27" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="MG27" t="str">
             <v>N</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31472,7 +31472,7 @@
       </c>
       <c r="LS3" s="16" t="str">
         <f>[1]CARTELLINO!LV$3</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="LT3" s="16" t="str">
         <f>[1]CARTELLINO!LW$3</f>
@@ -31524,7 +31524,7 @@
       </c>
       <c r="MF3" s="16" t="str">
         <f>[1]CARTELLINO!MI$3</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="MG3" s="16" t="str">
         <f>[1]CARTELLINO!MJ$3</f>
@@ -35115,11 +35115,11 @@
       </c>
       <c r="ME6" s="22" t="str">
         <f>[1]CARTELLINO!MH$6</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="MF6" s="22" t="str">
         <f>[1]CARTELLINO!MI$6</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="MG6" s="22" t="str">
         <f>[1]CARTELLINO!MJ$6</f>
@@ -42079,7 +42079,7 @@
       </c>
       <c r="JZ12" s="25" t="str">
         <f>[1]CARTELLINO!KC$12</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="KA12" s="25" t="str">
         <f>[1]CARTELLINO!KD$12</f>
@@ -42119,7 +42119,7 @@
       </c>
       <c r="KJ12" s="25" t="str">
         <f>[1]CARTELLINO!KM$12</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="KK12" s="25" t="str">
         <f>[1]CARTELLINO!KN$12</f>
@@ -45731,7 +45731,7 @@
       </c>
       <c r="KN15" s="26" t="str">
         <f>[1]CARTELLINO!KQ$15</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="KO15" s="26" t="str">
         <f>[1]CARTELLINO!KR$15</f>
@@ -45751,7 +45751,7 @@
       </c>
       <c r="KS15" s="26" t="str">
         <f>[1]CARTELLINO!KV$15</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="KT15" s="26" t="str">
         <f>[1]CARTELLINO!KW$15</f>
@@ -45935,7 +45935,7 @@
       </c>
       <c r="MM15" s="26" t="str">
         <f>[1]CARTELLINO!MP$15</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="MN15" s="26" t="str">
         <f>[1]CARTELLINO!MQ$15</f>
@@ -49491,7 +49491,7 @@
       </c>
       <c r="MC18" s="27" t="str">
         <f>[1]CARTELLINO!MF$18</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="MD18" s="27" t="str">
         <f>[1]CARTELLINO!MG$18</f>
@@ -49499,7 +49499,7 @@
       </c>
       <c r="ME18" s="27" t="str">
         <f>[1]CARTELLINO!MH$18</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MF18" s="27" t="str">
         <f>[1]CARTELLINO!MI$18</f>
@@ -52883,7 +52883,7 @@
       </c>
       <c r="KD21" s="28" t="str">
         <f>[1]CARTELLINO!KG$21</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="KE21" s="28" t="str">
         <f>[1]CARTELLINO!KH$21</f>
@@ -52907,7 +52907,7 @@
       </c>
       <c r="KJ21" s="28" t="str">
         <f>[1]CARTELLINO!KM$21</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="KK21" s="28" t="str">
         <f>[1]CARTELLINO!KN$21</f>
@@ -56643,7 +56643,7 @@
       </c>
       <c r="LS24" s="29" t="str">
         <f>[1]CARTELLINO!LV$24</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="LT24" s="29" t="str">
         <f>[1]CARTELLINO!LW$24</f>
@@ -56723,7 +56723,7 @@
       </c>
       <c r="MM24" s="29" t="str">
         <f>[1]CARTELLINO!MP$24</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="MN24" s="29" t="str">
         <f>[1]CARTELLINO!MQ$24</f>
@@ -60075,7 +60075,7 @@
       </c>
       <c r="KD27" s="30" t="str">
         <f>[1]CARTELLINO!KG$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KE27" s="30" t="str">
         <f>[1]CARTELLINO!KH$27</f>
@@ -60115,7 +60115,7 @@
       </c>
       <c r="KN27" s="30" t="str">
         <f>[1]CARTELLINO!KQ$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KO27" s="30" t="str">
         <f>[1]CARTELLINO!KR$27</f>
@@ -60135,7 +60135,7 @@
       </c>
       <c r="KS27" s="30" t="str">
         <f>[1]CARTELLINO!KV$27</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="KT27" s="30" t="str">
         <f>[1]CARTELLINO!KW$27</f>
@@ -60279,7 +60279,7 @@
       </c>
       <c r="MC27" s="30" t="str">
         <f>[1]CARTELLINO!MF$27</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="MD27" s="30" t="str">
         <f>[1]CARTELLINO!MG$27</f>
@@ -62980,7 +62980,7 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="KE29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KF29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -62998,7 +62998,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="KK29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="KL29" s="63" t="str">
         <v>BIANCHI</v>
@@ -63010,7 +63010,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KO29" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KP29" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -63025,7 +63025,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KT29" s="63" t="str">
-        <v>FABBRI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KU29" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -63103,7 +63103,7 @@
         <v>BERARDI</v>
       </c>
       <c r="LT29" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>BIANCHI</v>
       </c>
       <c r="LU29" s="63" t="str">
         <v>MICHELOT.</v>
@@ -63133,13 +63133,13 @@
         <v>BERARDI</v>
       </c>
       <c r="MD29" s="63" t="str">
-        <v>FABBRI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="ME29" s="63" t="str">
         <v>VOLPINI</v>
       </c>
       <c r="MF29" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="MG29" s="63" t="str">
         <v>SARTI</v>
@@ -63163,7 +63163,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="MN29" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="MO29" s="63" t="str">
         <v>BERARDI</v>
@@ -64080,7 +64080,7 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="KE30" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KF30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -64098,7 +64098,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="KK30" s="63" t="str">
-        <v>BERARDI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="KL30" s="63" t="str">
         <v>BIANCHI</v>
@@ -64110,7 +64110,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KO30" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KP30" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -64125,7 +64125,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KT30" s="63" t="str">
-        <v>FABBRI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KU30" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -64203,7 +64203,7 @@
         <v>BERARDI</v>
       </c>
       <c r="LT30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>BIANCHI</v>
       </c>
       <c r="LU30" s="63" t="str">
         <v>MICHELOT.</v>
@@ -64233,13 +64233,13 @@
         <v>BERARDI</v>
       </c>
       <c r="MD30" s="63" t="str">
-        <v>FABBRI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="ME30" s="63" t="str">
         <v>VOLPINI</v>
       </c>
       <c r="MF30" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="MG30" s="63" t="str">
         <v>SARTI</v>
@@ -64263,7 +64263,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="MN30" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="MO30" s="63" t="str">
         <v>BERARDI</v>
@@ -65177,7 +65177,7 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="KD31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KE31" s="63" t="str">
         <v>GHIOTTI</v>
@@ -65195,7 +65195,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="KJ31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="KK31" s="63" t="str">
         <v>BIANCHI</v>
@@ -65207,7 +65207,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KN31" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KO31" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -65222,7 +65222,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KS31" s="63" t="str">
-        <v>FABBRI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KT31" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -65300,7 +65300,7 @@
         <v>BERARDI</v>
       </c>
       <c r="LS31" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>BIANCHI</v>
       </c>
       <c r="LT31" s="63" t="str">
         <v>MICHELOT.</v>
@@ -65330,13 +65330,13 @@
         <v>BERARDI</v>
       </c>
       <c r="MC31" s="63" t="str">
-        <v>FABBRI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="MD31" s="63" t="str">
         <v>VOLPINI</v>
       </c>
       <c r="ME31" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="MF31" s="63" t="str">
         <v>SARTI</v>
@@ -65360,7 +65360,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="MM31" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="MN31" s="63" t="str">
         <v>BERARDI</v>
@@ -66277,7 +66277,7 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="KD32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KE32" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66295,7 +66295,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="KJ32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="KK32" s="63" t="str">
         <v>BIANCHI</v>
@@ -66307,7 +66307,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KN32" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KO32" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -66322,7 +66322,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KS32" s="63" t="str">
-        <v>FABBRI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KT32" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -66400,7 +66400,7 @@
         <v>BERARDI</v>
       </c>
       <c r="LS32" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>BIANCHI</v>
       </c>
       <c r="LT32" s="63" t="str">
         <v>MICHELOT.</v>
@@ -66430,13 +66430,13 @@
         <v>BERARDI</v>
       </c>
       <c r="MC32" s="63" t="str">
-        <v>FABBRI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="MD32" s="63" t="str">
         <v>VOLPINI</v>
       </c>
       <c r="ME32" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="MF32" s="63" t="str">
         <v>SARTI</v>
@@ -66460,7 +66460,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="MM32" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="MN32" s="63" t="str">
         <v>BERARDI</v>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,6 +71029,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71037,13 +71044,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE38F41C-5E8D-4963-8D41-915EBA06CCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6CF262-AFDD-4E00-B1B6-64449AB83DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5597,7 +5597,7 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR290" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS290" t="str">
             <v>GHIOTTI</v>
@@ -5681,7 +5681,7 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR296" t="str">
-            <v>PAZZAGLIA</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS296" t="str">
             <v>FABBRI</v>
@@ -7638,7 +7638,7 @@
             <v>S</v>
           </cell>
           <cell r="KI3" t="str">
-            <v>R</v>
+            <v>p</v>
           </cell>
           <cell r="KJ3" t="str">
             <v>m</v>
@@ -7656,10 +7656,10 @@
             <v>r</v>
           </cell>
           <cell r="KO3" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="KP3" t="str">
             <v>p</v>
-          </cell>
-          <cell r="KP3" t="str">
-            <v>m</v>
           </cell>
           <cell r="KQ3" t="str">
             <v>P</v>
@@ -9979,7 +9979,7 @@
             <v>r</v>
           </cell>
           <cell r="JW6" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="JX6" t="str">
             <v>-</v>
@@ -10009,7 +10009,7 @@
             <v>m</v>
           </cell>
           <cell r="KG6" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="KH6" t="str">
             <v>r</v>
@@ -17119,7 +17119,7 @@
             <v>P</v>
           </cell>
           <cell r="JW15" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="JX15" t="str">
             <v>m</v>
@@ -17173,10 +17173,10 @@
             <v>m</v>
           </cell>
           <cell r="KO15" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="KP15" t="str">
             <v>m</v>
-          </cell>
-          <cell r="KP15" t="str">
-            <v>p</v>
           </cell>
           <cell r="KQ15" t="str">
             <v>m</v>
@@ -21909,7 +21909,7 @@
             <v>R</v>
           </cell>
           <cell r="KG21" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="KH21" t="str">
             <v>p</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31316,7 +31316,7 @@
       </c>
       <c r="KF3" s="16" t="str">
         <f>[1]CARTELLINO!KI$3</f>
-        <v>R</v>
+        <v>p</v>
       </c>
       <c r="KG3" s="16" t="str">
         <f>[1]CARTELLINO!KJ$3</f>
@@ -31340,11 +31340,11 @@
       </c>
       <c r="KL3" s="16" t="str">
         <f>[1]CARTELLINO!KO$3</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="KM3" s="16" t="str">
         <f>[1]CARTELLINO!KP$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KN3" s="16" t="str">
         <f>[1]CARTELLINO!KQ$3</f>
@@ -34863,7 +34863,7 @@
       </c>
       <c r="JT6" s="22" t="str">
         <f>[1]CARTELLINO!JW$6</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="JU6" s="22" t="str">
         <f>[1]CARTELLINO!JX$6</f>
@@ -34903,7 +34903,7 @@
       </c>
       <c r="KD6" s="22" t="str">
         <f>[1]CARTELLINO!KG$6</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="KE6" s="22" t="str">
         <f>[1]CARTELLINO!KH$6</f>
@@ -45651,7 +45651,7 @@
       </c>
       <c r="JT15" s="26" t="str">
         <f>[1]CARTELLINO!JW$15</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="JU15" s="26" t="str">
         <f>[1]CARTELLINO!JX$15</f>
@@ -45723,11 +45723,11 @@
       </c>
       <c r="KL15" s="26" t="str">
         <f>[1]CARTELLINO!KO$15</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KM15" s="26" t="str">
         <f>[1]CARTELLINO!KP$15</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="KN15" s="26" t="str">
         <f>[1]CARTELLINO!KQ$15</f>
@@ -52883,7 +52883,7 @@
       </c>
       <c r="KD21" s="28" t="str">
         <f>[1]CARTELLINO!KG$21</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KE21" s="28" t="str">
         <f>[1]CARTELLINO!KH$21</f>
@@ -64059,7 +64059,7 @@
         <v>BERARDI</v>
       </c>
       <c r="JX30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="JY30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -64077,7 +64077,7 @@
         <v>SARTI</v>
       </c>
       <c r="KD30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KE30" s="63" t="str">
         <v>FABBRI</v>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,13 +71029,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71044,6 +71037,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6CF262-AFDD-4E00-B1B6-64449AB83DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0858776-C201-4957-B38C-08D2D4692032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6272,18 +6272,18 @@
             <v>BIANCHI</v>
           </cell>
           <cell r="AS338" t="str">
-            <v>MICHELOT.</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT338" t="str">
-            <v>MICHELOT.</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="339">
           <cell r="AQ339" t="str">
-            <v>MICHELOT.</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR339" t="str">
-            <v>MICHELOT.</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS339" t="str">
             <v>GHIOTTI</v>
@@ -10126,16 +10126,16 @@
             <v>p</v>
           </cell>
           <cell r="LT6" t="str">
-            <v>p</v>
+            <v>r</v>
           </cell>
           <cell r="LU6" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="LV6" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="LW6" t="str">
             <v>m</v>
-          </cell>
-          <cell r="LV6" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="LW6" t="str">
-            <v>r</v>
           </cell>
           <cell r="LX6" t="str">
             <v>m</v>
@@ -11319,10 +11319,10 @@
             <v>0</v>
           </cell>
           <cell r="LU7">
-            <v>0</v>
+            <v>6</v>
           </cell>
           <cell r="LV7">
-            <v>0</v>
+            <v>6</v>
           </cell>
           <cell r="LW7">
             <v>0</v>
@@ -14895,7 +14895,7 @@
             <v>P</v>
           </cell>
           <cell r="LW12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LX12" t="str">
             <v>N</v>
@@ -19646,16 +19646,16 @@
             <v>m</v>
           </cell>
           <cell r="LT18" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="LU18" t="str">
             <v>r</v>
           </cell>
           <cell r="LV18" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="LW18" t="str">
-            <v>m/R</v>
+            <v>S</v>
           </cell>
           <cell r="LX18" t="str">
             <v>p</v>
@@ -22032,10 +22032,10 @@
             <v>M/R</v>
           </cell>
           <cell r="LV21" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="LW21" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="LX21" t="str">
             <v>R</v>
@@ -23222,10 +23222,10 @@
             <v>0</v>
           </cell>
           <cell r="LV22">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="LW22">
-            <v>0</v>
+            <v>7</v>
           </cell>
           <cell r="LX22">
             <v>0</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -35059,19 +35059,19 @@
       </c>
       <c r="LQ6" s="22" t="str">
         <f>[1]CARTELLINO!LT$6</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="LR6" s="22" t="str">
         <f>[1]CARTELLINO!LU$6</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="LS6" s="22" t="str">
         <f>[1]CARTELLINO!LV$6</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="LT6" s="22" t="str">
         <f>[1]CARTELLINO!LW$6</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="LU6" s="22" t="str">
         <f>[1]CARTELLINO!LX$6</f>
@@ -36657,11 +36657,11 @@
       </c>
       <c r="LR7" s="46">
         <f>[1]CARTELLINO!LU$7</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="LS7" s="46">
         <f>[1]CARTELLINO!LV$7</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="LT7" s="46">
         <f>[1]CARTELLINO!LW$7</f>
@@ -42263,7 +42263,7 @@
       </c>
       <c r="LT12" s="25" t="str">
         <f>[1]CARTELLINO!LW$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LU12" s="25" t="str">
         <f>[1]CARTELLINO!LX$12</f>
@@ -49443,7 +49443,7 @@
       </c>
       <c r="LQ18" s="27" t="str">
         <f>[1]CARTELLINO!LT$18</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="LR18" s="27" t="str">
         <f>[1]CARTELLINO!LU$18</f>
@@ -49451,11 +49451,11 @@
       </c>
       <c r="LS18" s="27" t="str">
         <f>[1]CARTELLINO!LV$18</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="LT18" s="27" t="str">
         <f>[1]CARTELLINO!LW$18</f>
-        <v>m/R</v>
+        <v>S</v>
       </c>
       <c r="LU18" s="27" t="str">
         <f>[1]CARTELLINO!LX$18</f>
@@ -53047,11 +53047,11 @@
       </c>
       <c r="LS21" s="28" t="str">
         <f>[1]CARTELLINO!LV$21</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="LT21" s="28" t="str">
         <f>[1]CARTELLINO!LW$21</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="LU21" s="28" t="str">
         <f>[1]CARTELLINO!LX$21</f>
@@ -54641,11 +54641,11 @@
       </c>
       <c r="LS22" s="46">
         <f>[1]CARTELLINO!LV$22</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="LT22" s="46">
         <f>[1]CARTELLINO!LW$22</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="LU22" s="46">
         <f>[1]CARTELLINO!LX$22</f>
@@ -63106,7 +63106,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="LU29" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LV29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -64206,7 +64206,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="LU30" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LV30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -65303,7 +65303,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="LT31" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LU31" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66403,7 +66403,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="LT32" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LU32" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,6 +71029,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71037,13 +71044,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0858776-C201-4957-B38C-08D2D4692032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620B887C-E123-414D-822B-21B2198DFDFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -26774,7 +26774,7 @@
             <v>R</v>
           </cell>
           <cell r="LP27" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="LQ27" t="str">
             <v>p</v>
@@ -27963,8 +27963,8 @@
           <cell r="LO28">
             <v>0</v>
           </cell>
-          <cell r="LP28">
-            <v>0</v>
+          <cell r="LP28" t="str">
+            <v>r</v>
           </cell>
           <cell r="LQ28">
             <v>0</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -60215,7 +60215,7 @@
       </c>
       <c r="LM27" s="30" t="str">
         <f>[1]CARTELLINO!LP$27</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="LN27" s="30" t="str">
         <f>[1]CARTELLINO!LQ$27</f>
@@ -61807,9 +61807,9 @@
         <f>[1]CARTELLINO!LO$28</f>
         <v>0</v>
       </c>
-      <c r="LM28" s="62">
+      <c r="LM28" s="62" t="str">
         <f>[1]CARTELLINO!LP$28</f>
-        <v>0</v>
+        <v>r</v>
       </c>
       <c r="LN28" s="62">
         <f>[1]CARTELLINO!LQ$28</f>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,13 +71029,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71044,6 +71037,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620B887C-E123-414D-822B-21B2198DFDFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DA18EB-8895-4FAD-989D-E1EC52975005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5891,10 +5891,10 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AR311" t="str">
+            <v>GHIOTTI</v>
+          </cell>
+          <cell r="AS311" t="str">
             <v>BARBIERI</v>
-          </cell>
-          <cell r="AS311" t="str">
-            <v>GHIOTTI</v>
           </cell>
           <cell r="AT311" t="str">
             <v>GHIOTTI</v>
@@ -10051,10 +10051,10 @@
             <v>M</v>
           </cell>
           <cell r="KU6" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="KV6" t="str">
-            <v>p</v>
+            <v>m/R</v>
           </cell>
           <cell r="KW6" t="str">
             <v>m</v>
@@ -17191,10 +17191,10 @@
             <v>p</v>
           </cell>
           <cell r="KU15" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="KV15" t="str">
-            <v>m/R</v>
+            <v>p</v>
           </cell>
           <cell r="KW15" t="str">
             <v>p</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -34959,11 +34959,11 @@
       </c>
       <c r="KR6" s="22" t="str">
         <f>[1]CARTELLINO!KU$6</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="KS6" s="22" t="str">
         <f>[1]CARTELLINO!KV$6</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="KT6" s="22" t="str">
         <f>[1]CARTELLINO!KW$6</f>
@@ -45747,11 +45747,11 @@
       </c>
       <c r="KR15" s="26" t="str">
         <f>[1]CARTELLINO!KU$15</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="KS15" s="26" t="str">
         <f>[1]CARTELLINO!KV$15</f>
-        <v>m/R</v>
+        <v>p</v>
       </c>
       <c r="KT15" s="26" t="str">
         <f>[1]CARTELLINO!KW$15</f>
@@ -64122,7 +64122,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="KS30" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KT30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -65222,7 +65222,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KS31" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="KT31" s="63" t="str">
         <v>PAZZAGLIA</v>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,6 +71029,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71037,13 +71044,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DA18EB-8895-4FAD-989D-E1EC52975005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9817149-28EA-4694-9217-8AB22CE29228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6034,18 +6034,18 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AS321" t="str">
-            <v>FABBRI</v>
+            <v>SARTI</v>
           </cell>
           <cell r="AT321" t="str">
-            <v>FABBRI</v>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="322">
           <cell r="AQ322" t="str">
-            <v>FABBRI</v>
+            <v>SARTI</v>
           </cell>
           <cell r="AR322" t="str">
-            <v>FABBRI</v>
+            <v>SARTI</v>
           </cell>
           <cell r="AS322" t="str">
             <v>VOLPINI</v>
@@ -6216,18 +6216,18 @@
             <v>FABBRI</v>
           </cell>
           <cell r="AS334" t="str">
-            <v>GHIOTTI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT334" t="str">
-            <v>GHIOTTI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="335">
           <cell r="AQ335" t="str">
-            <v>GHIOTTI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR335" t="str">
-            <v>GHIOTTI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS335" t="str">
             <v>SARTI</v>
@@ -6244,18 +6244,18 @@
             <v>SARTI</v>
           </cell>
           <cell r="AS336" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT336" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="337">
           <cell r="AQ337" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR337" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS337" t="str">
             <v>BIANCHI</v>
@@ -6272,18 +6272,18 @@
             <v>BIANCHI</v>
           </cell>
           <cell r="AS338" t="str">
-            <v>VOLPINI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT338" t="str">
-            <v>VOLPINI</v>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="339">
           <cell r="AQ339" t="str">
-            <v>VOLPINI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR339" t="str">
-            <v>VOLPINI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS339" t="str">
             <v>GHIOTTI</v>
@@ -10135,10 +10135,10 @@
             <v>-</v>
           </cell>
           <cell r="LW6" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="LX6" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="LY6" t="str">
             <v>p</v>
@@ -12464,7 +12464,7 @@
             <v>p</v>
           </cell>
           <cell r="LF9" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="LG9" t="str">
             <v>p</v>
@@ -14895,7 +14895,7 @@
             <v>P</v>
           </cell>
           <cell r="LW12" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="LX12" t="str">
             <v>N</v>
@@ -17263,13 +17263,13 @@
             <v>r</v>
           </cell>
           <cell r="LS15" t="str">
-            <v>M/R</v>
+            <v>-</v>
           </cell>
           <cell r="LT15" t="str">
-            <v>N</v>
+            <v>m</v>
           </cell>
           <cell r="LU15" t="str">
-            <v>S</v>
+            <v>M</v>
           </cell>
           <cell r="LV15" t="str">
             <v>R</v>
@@ -18452,8 +18452,8 @@
           <cell r="LR16">
             <v>0</v>
           </cell>
-          <cell r="LS16">
-            <v>0</v>
+          <cell r="LS16" t="str">
+            <v>p</v>
           </cell>
           <cell r="LT16">
             <v>0</v>
@@ -19643,7 +19643,7 @@
             <v>p</v>
           </cell>
           <cell r="LS18" t="str">
-            <v>m</v>
+            <v>M</v>
           </cell>
           <cell r="LT18" t="str">
             <v>r</v>
@@ -19658,7 +19658,7 @@
             <v>S</v>
           </cell>
           <cell r="LX18" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="LY18" t="str">
             <v>m</v>
@@ -22026,19 +22026,19 @@
             <v>R</v>
           </cell>
           <cell r="LT21" t="str">
-            <v>P</v>
+            <v>N</v>
           </cell>
           <cell r="LU21" t="str">
-            <v>M/R</v>
+            <v>S</v>
           </cell>
           <cell r="LV21" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="LW21" t="str">
             <v>-</v>
           </cell>
           <cell r="LX21" t="str">
-            <v>R</v>
+            <v>-</v>
           </cell>
           <cell r="LY21" t="str">
             <v>-</v>
@@ -23222,13 +23222,13 @@
             <v>0</v>
           </cell>
           <cell r="LV22">
-            <v>4</v>
+            <v>0</v>
           </cell>
           <cell r="LW22">
-            <v>7</v>
+            <v>6</v>
           </cell>
           <cell r="LX22">
-            <v>0</v>
+            <v>6</v>
           </cell>
           <cell r="LY22" t="str">
             <v>r</v>
@@ -24403,10 +24403,10 @@
             <v>-</v>
           </cell>
           <cell r="LS24" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="LT24" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="LU24" t="str">
             <v>p</v>
@@ -26744,7 +26744,7 @@
             <v>P</v>
           </cell>
           <cell r="LF27" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="LG27" t="str">
             <v>N</v>
@@ -26786,10 +26786,10 @@
             <v>p</v>
           </cell>
           <cell r="LT27" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="LU27" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="LV27" t="str">
             <v>p</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -35071,11 +35071,11 @@
       </c>
       <c r="LT6" s="22" t="str">
         <f>[1]CARTELLINO!LW$6</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="LU6" s="22" t="str">
         <f>[1]CARTELLINO!LX$6</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="LV6" s="22" t="str">
         <f>[1]CARTELLINO!LY$6</f>
@@ -38599,7 +38599,7 @@
       </c>
       <c r="LC9" s="24" t="str">
         <f>[1]CARTELLINO!LF$9</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="LD9" s="24" t="str">
         <f>[1]CARTELLINO!LG$9</f>
@@ -42263,7 +42263,7 @@
       </c>
       <c r="LT12" s="25" t="str">
         <f>[1]CARTELLINO!LW$12</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="LU12" s="25" t="str">
         <f>[1]CARTELLINO!LX$12</f>
@@ -45843,15 +45843,15 @@
       </c>
       <c r="LP15" s="26" t="str">
         <f>[1]CARTELLINO!LS$15</f>
-        <v>M/R</v>
+        <v>-</v>
       </c>
       <c r="LQ15" s="26" t="str">
         <f>[1]CARTELLINO!LT$15</f>
-        <v>N</v>
+        <v>m</v>
       </c>
       <c r="LR15" s="26" t="str">
         <f>[1]CARTELLINO!LU$15</f>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="LS15" s="26" t="str">
         <f>[1]CARTELLINO!LV$15</f>
@@ -47435,9 +47435,9 @@
         <f>[1]CARTELLINO!LR$16</f>
         <v>0</v>
       </c>
-      <c r="LP16" s="46">
+      <c r="LP16" s="46" t="str">
         <f>[1]CARTELLINO!LS$16</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="LQ16" s="46">
         <f>[1]CARTELLINO!LT$16</f>
@@ -49439,7 +49439,7 @@
       </c>
       <c r="LP18" s="27" t="str">
         <f>[1]CARTELLINO!LS$18</f>
-        <v>m</v>
+        <v>M</v>
       </c>
       <c r="LQ18" s="27" t="str">
         <f>[1]CARTELLINO!LT$18</f>
@@ -49459,7 +49459,7 @@
       </c>
       <c r="LU18" s="27" t="str">
         <f>[1]CARTELLINO!LX$18</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="LV18" s="27" t="str">
         <f>[1]CARTELLINO!LY$18</f>
@@ -53039,15 +53039,15 @@
       </c>
       <c r="LQ21" s="28" t="str">
         <f>[1]CARTELLINO!LT$21</f>
-        <v>P</v>
+        <v>N</v>
       </c>
       <c r="LR21" s="28" t="str">
         <f>[1]CARTELLINO!LU$21</f>
-        <v>M/R</v>
+        <v>S</v>
       </c>
       <c r="LS21" s="28" t="str">
         <f>[1]CARTELLINO!LV$21</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="LT21" s="28" t="str">
         <f>[1]CARTELLINO!LW$21</f>
@@ -53055,7 +53055,7 @@
       </c>
       <c r="LU21" s="28" t="str">
         <f>[1]CARTELLINO!LX$21</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="LV21" s="28" t="str">
         <f>[1]CARTELLINO!LY$21</f>
@@ -54641,15 +54641,15 @@
       </c>
       <c r="LS22" s="46">
         <f>[1]CARTELLINO!LV$22</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="LT22" s="46">
         <f>[1]CARTELLINO!LW$22</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="LU22" s="46">
         <f>[1]CARTELLINO!LX$22</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="LV22" s="46" t="str">
         <f>[1]CARTELLINO!LY$22</f>
@@ -56631,11 +56631,11 @@
       </c>
       <c r="LP24" s="29" t="str">
         <f>[1]CARTELLINO!LS$24</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="LQ24" s="29" t="str">
         <f>[1]CARTELLINO!LT$24</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="LR24" s="29" t="str">
         <f>[1]CARTELLINO!LU$24</f>
@@ -60175,7 +60175,7 @@
       </c>
       <c r="LC27" s="30" t="str">
         <f>[1]CARTELLINO!LF$27</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="LD27" s="30" t="str">
         <f>[1]CARTELLINO!LG$27</f>
@@ -60231,11 +60231,11 @@
       </c>
       <c r="LQ27" s="30" t="str">
         <f>[1]CARTELLINO!LT$27</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="LR27" s="30" t="str">
         <f>[1]CARTELLINO!LU$27</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="LS27" s="30" t="str">
         <f>[1]CARTELLINO!LV$27</f>
@@ -63055,7 +63055,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="LD29" s="63" t="str">
-        <v>FABBRI</v>
+        <v>SARTI</v>
       </c>
       <c r="LE29" s="63" t="str">
         <v>VOLPINI</v>
@@ -63094,19 +63094,19 @@
         <v>FABBRI</v>
       </c>
       <c r="LQ29" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="LR29" s="63" t="str">
         <v>SARTI</v>
       </c>
       <c r="LS29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="LT29" s="63" t="str">
         <v>BIANCHI</v>
       </c>
       <c r="LU29" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="LV29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -64155,7 +64155,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="LD30" s="63" t="str">
-        <v>FABBRI</v>
+        <v>SARTI</v>
       </c>
       <c r="LE30" s="63" t="str">
         <v>VOLPINI</v>
@@ -64194,19 +64194,19 @@
         <v>FABBRI</v>
       </c>
       <c r="LQ30" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="LR30" s="63" t="str">
         <v>SARTI</v>
       </c>
       <c r="LS30" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="LT30" s="63" t="str">
         <v>BIANCHI</v>
       </c>
       <c r="LU30" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="LV30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -65252,7 +65252,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="LC31" s="63" t="str">
-        <v>FABBRI</v>
+        <v>SARTI</v>
       </c>
       <c r="LD31" s="63" t="str">
         <v>VOLPINI</v>
@@ -65291,19 +65291,19 @@
         <v>FABBRI</v>
       </c>
       <c r="LP31" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="LQ31" s="63" t="str">
         <v>SARTI</v>
       </c>
       <c r="LR31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="LS31" s="63" t="str">
         <v>BIANCHI</v>
       </c>
       <c r="LT31" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="LU31" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66352,7 +66352,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="LC32" s="63" t="str">
-        <v>FABBRI</v>
+        <v>SARTI</v>
       </c>
       <c r="LD32" s="63" t="str">
         <v>VOLPINI</v>
@@ -66391,19 +66391,19 @@
         <v>FABBRI</v>
       </c>
       <c r="LP32" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="LQ32" s="63" t="str">
         <v>SARTI</v>
       </c>
       <c r="LR32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="LS32" s="63" t="str">
         <v>BIANCHI</v>
       </c>
       <c r="LT32" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="LU32" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,13 +71029,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71044,6 +71037,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9817149-28EA-4694-9217-8AB22CE29228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC172EC-79C9-4EE4-83EA-A31BA2E3CFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6177,12 +6177,12 @@
             <v>BERARDI</v>
           </cell>
           <cell r="AT331" t="str">
-            <v>BERARDI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="332">
           <cell r="AQ332" t="str">
-            <v>BERARDI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR332" t="str">
             <v>BERARDI</v>
@@ -6297,7 +6297,7 @@
             <v>GHIOTTI</v>
           </cell>
           <cell r="AR340" t="str">
-            <v>GHIOTTI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS340" t="str">
             <v>SARTI</v>
@@ -10123,7 +10123,7 @@
             <v>R</v>
           </cell>
           <cell r="LS6" t="str">
-            <v>p</v>
+            <v>-</v>
           </cell>
           <cell r="LT6" t="str">
             <v>r</v>
@@ -10279,31 +10279,31 @@
             <v>R</v>
           </cell>
           <cell r="NS6" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="NT6" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="NU6" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="NV6" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="NW6" t="str">
             <v>R</v>
           </cell>
           <cell r="NX6" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="NY6" t="str">
-            <v>M/R</v>
+            <v>-</v>
           </cell>
           <cell r="NZ6" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="OA6" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="OB6" t="str">
             <v>R</v>
@@ -11312,8 +11312,8 @@
           <cell r="LR7">
             <v>0</v>
           </cell>
-          <cell r="LS7">
-            <v>0</v>
+          <cell r="LS7" t="str">
+            <v>R</v>
           </cell>
           <cell r="LT7">
             <v>0</v>
@@ -11468,32 +11468,32 @@
           <cell r="NR7">
             <v>0</v>
           </cell>
-          <cell r="NS7">
-            <v>0</v>
-          </cell>
-          <cell r="NT7">
-            <v>0</v>
-          </cell>
-          <cell r="NU7">
-            <v>0</v>
-          </cell>
-          <cell r="NV7">
-            <v>0</v>
-          </cell>
-          <cell r="NW7">
-            <v>0</v>
-          </cell>
-          <cell r="NX7">
-            <v>0</v>
-          </cell>
-          <cell r="NY7">
-            <v>0</v>
-          </cell>
-          <cell r="NZ7">
-            <v>0</v>
-          </cell>
-          <cell r="OA7">
-            <v>0</v>
+          <cell r="NS7" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NT7" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NU7" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NV7" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NW7" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NX7" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NY7" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NZ7" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="OA7" t="str">
+            <v>v</v>
           </cell>
           <cell r="OB7">
             <v>0</v>
@@ -17140,7 +17140,7 @@
             <v>p</v>
           </cell>
           <cell r="KD15" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="KE15" t="str">
             <v>r</v>
@@ -17416,7 +17416,7 @@
             <v>P</v>
           </cell>
           <cell r="NR15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NS15" t="str">
             <v>N</v>
@@ -19520,7 +19520,7 @@
             <v>m</v>
           </cell>
           <cell r="KD18" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="KE18" t="str">
             <v>m</v>
@@ -19796,37 +19796,37 @@
             <v>p</v>
           </cell>
           <cell r="NR18" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="NS18" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="NT18" t="str">
-            <v>m</v>
+            <v>M</v>
           </cell>
           <cell r="NU18" t="str">
-            <v>r</v>
+            <v>N</v>
           </cell>
           <cell r="NV18" t="str">
-            <v>p</v>
+            <v>S</v>
           </cell>
           <cell r="NW18" t="str">
-            <v>m</v>
+            <v>R</v>
           </cell>
           <cell r="NX18" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="NY18" t="str">
-            <v>p</v>
+            <v>M/R</v>
           </cell>
           <cell r="NZ18" t="str">
-            <v>m</v>
+            <v>N</v>
           </cell>
           <cell r="OA18" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="OB18" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="OC18" t="str">
             <v>p</v>
@@ -24571,10 +24571,10 @@
             <v>p</v>
           </cell>
           <cell r="NW24" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="NX24" t="str">
             <v>p</v>
-          </cell>
-          <cell r="NX24" t="str">
-            <v>m</v>
           </cell>
           <cell r="NY24" t="str">
             <v>m</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -35055,7 +35055,7 @@
       </c>
       <c r="LP6" s="22" t="str">
         <f>[1]CARTELLINO!LS$6</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="LQ6" s="22" t="str">
         <f>[1]CARTELLINO!LT$6</f>
@@ -35263,19 +35263,19 @@
       </c>
       <c r="NP6" s="22" t="str">
         <f>[1]CARTELLINO!NS$6</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="NQ6" s="22" t="str">
         <f>[1]CARTELLINO!NT$6</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="NR6" s="22" t="str">
         <f>[1]CARTELLINO!NU$6</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="NS6" s="22" t="str">
         <f>[1]CARTELLINO!NV$6</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="NT6" s="22" t="str">
         <f>[1]CARTELLINO!NW$6</f>
@@ -35283,19 +35283,19 @@
       </c>
       <c r="NU6" s="22" t="str">
         <f>[1]CARTELLINO!NX$6</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="NV6" s="22" t="str">
         <f>[1]CARTELLINO!NY$6</f>
-        <v>M/R</v>
+        <v>-</v>
       </c>
       <c r="NW6" s="22" t="str">
         <f>[1]CARTELLINO!NZ$6</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="NX6" s="22" t="str">
         <f>[1]CARTELLINO!OA$6</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="NY6" s="22" t="str">
         <f>[1]CARTELLINO!OB$6</f>
@@ -36647,9 +36647,9 @@
         <f>[1]CARTELLINO!LR$7</f>
         <v>0</v>
       </c>
-      <c r="LP7" s="46">
+      <c r="LP7" s="46" t="str">
         <f>[1]CARTELLINO!LS$7</f>
-        <v>0</v>
+        <v>R</v>
       </c>
       <c r="LQ7" s="46">
         <f>[1]CARTELLINO!LT$7</f>
@@ -36855,41 +36855,41 @@
         <f>[1]CARTELLINO!NR$7</f>
         <v>0</v>
       </c>
-      <c r="NP7" s="46">
+      <c r="NP7" s="46" t="str">
         <f>[1]CARTELLINO!NS$7</f>
-        <v>0</v>
-      </c>
-      <c r="NQ7" s="46">
+        <v>v</v>
+      </c>
+      <c r="NQ7" s="46" t="str">
         <f>[1]CARTELLINO!NT$7</f>
-        <v>0</v>
-      </c>
-      <c r="NR7" s="46">
+        <v>v</v>
+      </c>
+      <c r="NR7" s="46" t="str">
         <f>[1]CARTELLINO!NU$7</f>
-        <v>0</v>
-      </c>
-      <c r="NS7" s="46">
+        <v>v</v>
+      </c>
+      <c r="NS7" s="46" t="str">
         <f>[1]CARTELLINO!NV$7</f>
-        <v>0</v>
-      </c>
-      <c r="NT7" s="46">
+        <v>v</v>
+      </c>
+      <c r="NT7" s="46" t="str">
         <f>[1]CARTELLINO!NW$7</f>
-        <v>0</v>
-      </c>
-      <c r="NU7" s="46">
+        <v>v</v>
+      </c>
+      <c r="NU7" s="46" t="str">
         <f>[1]CARTELLINO!NX$7</f>
-        <v>0</v>
-      </c>
-      <c r="NV7" s="46">
+        <v>v</v>
+      </c>
+      <c r="NV7" s="46" t="str">
         <f>[1]CARTELLINO!NY$7</f>
-        <v>0</v>
-      </c>
-      <c r="NW7" s="46">
+        <v>v</v>
+      </c>
+      <c r="NW7" s="46" t="str">
         <f>[1]CARTELLINO!NZ$7</f>
-        <v>0</v>
-      </c>
-      <c r="NX7" s="46">
+        <v>v</v>
+      </c>
+      <c r="NX7" s="46" t="str">
         <f>[1]CARTELLINO!OA$7</f>
-        <v>0</v>
+        <v>v</v>
       </c>
       <c r="NY7" s="46">
         <f>[1]CARTELLINO!OB$7</f>
@@ -45679,7 +45679,7 @@
       </c>
       <c r="KA15" s="26" t="str">
         <f>[1]CARTELLINO!KD$15</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="KB15" s="26" t="str">
         <f>[1]CARTELLINO!KE$15</f>
@@ -46047,7 +46047,7 @@
       </c>
       <c r="NO15" s="26" t="str">
         <f>[1]CARTELLINO!NR$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NP15" s="26" t="str">
         <f>[1]CARTELLINO!NS$15</f>
@@ -49275,7 +49275,7 @@
       </c>
       <c r="KA18" s="27" t="str">
         <f>[1]CARTELLINO!KD$18</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="KB18" s="27" t="str">
         <f>[1]CARTELLINO!KE$18</f>
@@ -49643,47 +49643,47 @@
       </c>
       <c r="NO18" s="27" t="str">
         <f>[1]CARTELLINO!NR$18</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="NP18" s="27" t="str">
         <f>[1]CARTELLINO!NS$18</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="NQ18" s="27" t="str">
         <f>[1]CARTELLINO!NT$18</f>
-        <v>m</v>
+        <v>M</v>
       </c>
       <c r="NR18" s="27" t="str">
         <f>[1]CARTELLINO!NU$18</f>
-        <v>r</v>
+        <v>N</v>
       </c>
       <c r="NS18" s="27" t="str">
         <f>[1]CARTELLINO!NV$18</f>
-        <v>p</v>
+        <v>S</v>
       </c>
       <c r="NT18" s="27" t="str">
         <f>[1]CARTELLINO!NW$18</f>
-        <v>m</v>
+        <v>R</v>
       </c>
       <c r="NU18" s="27" t="str">
         <f>[1]CARTELLINO!NX$18</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="NV18" s="27" t="str">
         <f>[1]CARTELLINO!NY$18</f>
-        <v>p</v>
+        <v>M/R</v>
       </c>
       <c r="NW18" s="27" t="str">
         <f>[1]CARTELLINO!NZ$18</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="NX18" s="27" t="str">
         <f>[1]CARTELLINO!OA$18</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="NY18" s="27" t="str">
         <f>[1]CARTELLINO!OB$18</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="NZ18" s="27" t="str">
         <f>[1]CARTELLINO!OC$18</f>
@@ -56855,11 +56855,11 @@
       </c>
       <c r="NT24" s="29" t="str">
         <f>[1]CARTELLINO!NW$24</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="NU24" s="29" t="str">
         <f>[1]CARTELLINO!NX$24</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NV24" s="29" t="str">
         <f>[1]CARTELLINO!NY$24</f>
@@ -63085,7 +63085,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="LN29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LO29" s="63" t="str">
         <v>MICHELOT.</v>
@@ -64209,7 +64209,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="LV30" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="LW30" s="63" t="str">
         <v>SARTI</v>
@@ -66382,7 +66382,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="LM32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="LN32" s="63" t="str">
         <v>MICHELOT.</v>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,6 +71029,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71037,13 +71044,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC172EC-79C9-4EE4-83EA-A31BA2E3CFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED09491-BE17-4E55-95F3-0AAB85B97C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED09491-BE17-4E55-95F3-0AAB85B97C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85697CA9-8E6A-41EF-A56F-3A443608A994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5681,7 +5681,7 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR296" t="str">
-            <v>GHIOTTI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS296" t="str">
             <v>FABBRI</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -64077,7 +64077,7 @@
         <v>SARTI</v>
       </c>
       <c r="KD30" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="KE30" s="63" t="str">
         <v>FABBRI</v>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,13 +71029,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71044,6 +71037,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85697CA9-8E6A-41EF-A56F-3A443608A994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8910783F-25FC-47BE-90FE-E1A43855ACC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,66 +1195,6 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1325,6 +1265,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5768,18 +5768,18 @@
             <v>GHIOTTI</v>
           </cell>
           <cell r="AS302" t="str">
-            <v>VOLPINI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT302" t="str">
-            <v>VOLPINI</v>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="303">
           <cell r="AQ303" t="str">
-            <v>VOLPINI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR303" t="str">
-            <v>VOLPINI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS303" t="str">
             <v>BIANCHI</v>
@@ -6048,18 +6048,18 @@
             <v>SARTI</v>
           </cell>
           <cell r="AS322" t="str">
-            <v>VOLPINI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT322" t="str">
-            <v>VOLPINI</v>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="323">
           <cell r="AQ323" t="str">
-            <v>VOLPINI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR323" t="str">
-            <v>VOLPINI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS323" t="str">
             <v>BIANCHI</v>
@@ -6202,18 +6202,18 @@
             <v>MICHELOT.</v>
           </cell>
           <cell r="AS333" t="str">
-            <v>FABBRI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT333" t="str">
-            <v>FABBRI</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="334">
           <cell r="AQ334" t="str">
-            <v>FABBRI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR334" t="str">
-            <v>FABBRI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS334" t="str">
             <v>BIANCHI</v>
@@ -6258,18 +6258,18 @@
             <v>FABBRI</v>
           </cell>
           <cell r="AS337" t="str">
-            <v>BIANCHI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT337" t="str">
-            <v>BIANCHI</v>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="338">
           <cell r="AQ338" t="str">
-            <v>BIANCHI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR338" t="str">
-            <v>BIANCHI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS338" t="str">
             <v>BARBIERI</v>
@@ -6314,32 +6314,32 @@
             <v>SARTI</v>
           </cell>
           <cell r="AS341" t="str">
-            <v>BERARDI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT341" t="str">
-            <v>BERARDI</v>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="342">
           <cell r="AQ342" t="str">
-            <v>BERARDI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR342" t="str">
-            <v>BERARDI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS342" t="str">
-            <v>BIANCHI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT342" t="str">
-            <v>BIANCHI</v>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="343">
           <cell r="AQ343" t="str">
-            <v>BIANCHI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR343" t="str">
-            <v>BIANCHI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS343" t="str">
             <v>VOLPINI</v>
@@ -6398,18 +6398,18 @@
             <v>BERARDI</v>
           </cell>
           <cell r="AS347" t="str">
-            <v>MICHELOT.</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT347" t="str">
-            <v>MICHELOT.</v>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="348">
           <cell r="AQ348" t="str">
-            <v>MICHELOT.</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR348" t="str">
-            <v>MICHELOT.</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS348" t="str">
             <v>VOLPINI</v>
@@ -6538,18 +6538,18 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AS357" t="str">
-            <v>GHIOTTI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT357" t="str">
-            <v>GHIOTTI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="358">
           <cell r="AQ358" t="str">
-            <v>GHIOTTI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR358" t="str">
-            <v>GHIOTTI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS358" t="str">
             <v>BERARDI</v>
@@ -7710,7 +7710,7 @@
             <v>P</v>
           </cell>
           <cell r="LG3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LH3" t="str">
             <v>N</v>
@@ -7755,7 +7755,7 @@
             <v>P</v>
           </cell>
           <cell r="LV3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LW3" t="str">
             <v>-</v>
@@ -7785,10 +7785,10 @@
             <v>p</v>
           </cell>
           <cell r="MF3" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="MG3" t="str">
             <v>p</v>
-          </cell>
-          <cell r="MG3" t="str">
-            <v>m</v>
           </cell>
           <cell r="MH3" t="str">
             <v>p</v>
@@ -7863,10 +7863,10 @@
             <v>p</v>
           </cell>
           <cell r="NF3" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="NG3" t="str">
             <v>m</v>
-          </cell>
-          <cell r="NG3" t="str">
-            <v>p</v>
           </cell>
           <cell r="NH3" t="str">
             <v>r</v>
@@ -10141,34 +10141,34 @@
             <v>p</v>
           </cell>
           <cell r="LY6" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="LZ6" t="str">
-            <v>m</v>
+            <v>M</v>
           </cell>
           <cell r="MA6" t="str">
+            <v>M</v>
+          </cell>
+          <cell r="MB6" t="str">
             <v>r</v>
-          </cell>
-          <cell r="MB6" t="str">
-            <v>p</v>
           </cell>
           <cell r="MC6" t="str">
             <v>m/R</v>
           </cell>
           <cell r="MD6" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="ME6" t="str">
+            <v>M</v>
+          </cell>
+          <cell r="MF6" t="str">
             <v>N</v>
           </cell>
-          <cell r="ME6" t="str">
+          <cell r="MG6" t="str">
             <v>S</v>
           </cell>
-          <cell r="MF6" t="str">
+          <cell r="MH6" t="str">
             <v>R</v>
-          </cell>
-          <cell r="MG6" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="MH6" t="str">
-            <v>m</v>
           </cell>
           <cell r="MI6" t="str">
             <v>p</v>
@@ -10228,13 +10228,13 @@
             <v>P</v>
           </cell>
           <cell r="NB6" t="str">
-            <v>m/R</v>
+            <v>M/R</v>
           </cell>
           <cell r="NC6" t="str">
             <v>p</v>
           </cell>
           <cell r="ND6" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="NE6" t="str">
             <v>M/R</v>
@@ -12626,10 +12626,10 @@
             <v>R</v>
           </cell>
           <cell r="NH9" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="NI9" t="str">
-            <v>m</v>
+            <v>M/R</v>
           </cell>
           <cell r="NJ9" t="str">
             <v>p</v>
@@ -14787,7 +14787,7 @@
             <v>P</v>
           </cell>
           <cell r="KM12" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="KN12" t="str">
             <v>p</v>
@@ -14847,7 +14847,7 @@
             <v>p</v>
           </cell>
           <cell r="LG12" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="LH12" t="str">
             <v>p</v>
@@ -14880,7 +14880,7 @@
             <v>P</v>
           </cell>
           <cell r="LR12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LS12" t="str">
             <v>N</v>
@@ -15000,16 +15000,16 @@
             <v>m</v>
           </cell>
           <cell r="NF12" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="NG12" t="str">
             <v>p</v>
           </cell>
-          <cell r="NG12" t="str">
+          <cell r="NH12" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="NI12" t="str">
             <v>r</v>
-          </cell>
-          <cell r="NH12" t="str">
-            <v>P</v>
-          </cell>
-          <cell r="NI12" t="str">
-            <v>M/R</v>
           </cell>
           <cell r="NJ12" t="str">
             <v>N</v>
@@ -17266,13 +17266,13 @@
             <v>-</v>
           </cell>
           <cell r="LT15" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="LU15" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="LV15" t="str">
             <v>m</v>
-          </cell>
-          <cell r="LU15" t="str">
-            <v>M</v>
-          </cell>
-          <cell r="LV15" t="str">
-            <v>R</v>
           </cell>
           <cell r="LW15" t="str">
             <v>P</v>
@@ -17332,7 +17332,7 @@
             <v>p</v>
           </cell>
           <cell r="MP15" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="MQ15" t="str">
             <v>p</v>
@@ -17368,7 +17368,7 @@
             <v>r</v>
           </cell>
           <cell r="NB15" t="str">
-            <v>M</v>
+            <v>p</v>
           </cell>
           <cell r="NC15" t="str">
             <v>M/R</v>
@@ -19643,10 +19643,10 @@
             <v>p</v>
           </cell>
           <cell r="LS18" t="str">
-            <v>M</v>
+            <v>m</v>
           </cell>
           <cell r="LT18" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="LU18" t="str">
             <v>r</v>
@@ -19658,13 +19658,13 @@
             <v>S</v>
           </cell>
           <cell r="LX18" t="str">
-            <v>m</v>
+            <v>R</v>
           </cell>
           <cell r="LY18" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="LZ18" t="str">
-            <v>r</v>
+            <v>m/R</v>
           </cell>
           <cell r="MA18" t="str">
             <v>p</v>
@@ -19673,16 +19673,16 @@
             <v>m</v>
           </cell>
           <cell r="MC18" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="MD18" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="ME18" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="MF18" t="str">
-            <v>m/R</v>
+            <v>R</v>
           </cell>
           <cell r="MG18" t="str">
             <v>P</v>
@@ -21927,7 +21927,7 @@
             <v>r</v>
           </cell>
           <cell r="KM21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KN21" t="str">
             <v>N</v>
@@ -22026,13 +22026,13 @@
             <v>R</v>
           </cell>
           <cell r="LT21" t="str">
-            <v>N</v>
+            <v>P</v>
           </cell>
           <cell r="LU21" t="str">
-            <v>S</v>
+            <v>M</v>
           </cell>
           <cell r="LV21" t="str">
-            <v>R</v>
+            <v>r</v>
           </cell>
           <cell r="LW21" t="str">
             <v>-</v>
@@ -22044,7 +22044,7 @@
             <v>-</v>
           </cell>
           <cell r="LZ21" t="str">
-            <v>M/R</v>
+            <v>r</v>
           </cell>
           <cell r="MA21" t="str">
             <v>N</v>
@@ -22056,19 +22056,19 @@
             <v>R</v>
           </cell>
           <cell r="MD21" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="ME21" t="str">
-            <v>M/R</v>
+            <v>m/R</v>
           </cell>
           <cell r="MF21" t="str">
-            <v>N</v>
+            <v>p</v>
           </cell>
           <cell r="MG21" t="str">
-            <v>S</v>
+            <v>m</v>
           </cell>
           <cell r="MH21" t="str">
-            <v>R</v>
+            <v>m</v>
           </cell>
           <cell r="MI21" t="str">
             <v>P</v>
@@ -22125,7 +22125,7 @@
             <v>P</v>
           </cell>
           <cell r="NA21" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="NB21" t="str">
             <v>-</v>
@@ -22146,10 +22146,10 @@
             <v>-</v>
           </cell>
           <cell r="NH21" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="NI21" t="str">
             <v>m</v>
-          </cell>
-          <cell r="NI21" t="str">
-            <v>p</v>
           </cell>
           <cell r="NJ21" t="str">
             <v>r</v>
@@ -24403,22 +24403,22 @@
             <v>-</v>
           </cell>
           <cell r="LS24" t="str">
-            <v>m/R</v>
+            <v>M/R</v>
           </cell>
           <cell r="LT24" t="str">
-            <v>P</v>
+            <v>N</v>
           </cell>
           <cell r="LU24" t="str">
-            <v>p</v>
+            <v>S</v>
           </cell>
           <cell r="LV24" t="str">
-            <v>m/R</v>
+            <v>R</v>
           </cell>
           <cell r="LW24" t="str">
             <v>p</v>
           </cell>
           <cell r="LX24" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="LY24" t="str">
             <v>P</v>
@@ -24427,7 +24427,7 @@
             <v>P</v>
           </cell>
           <cell r="MA24" t="str">
-            <v>M/R</v>
+            <v>r</v>
           </cell>
           <cell r="MB24" t="str">
             <v>N</v>
@@ -24472,7 +24472,7 @@
             <v>P</v>
           </cell>
           <cell r="MP24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MQ24" t="str">
             <v>N</v>
@@ -24505,16 +24505,16 @@
             <v>p</v>
           </cell>
           <cell r="NA24" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="NB24" t="str">
             <v>m</v>
-          </cell>
-          <cell r="NB24" t="str">
-            <v>p</v>
           </cell>
           <cell r="NC24" t="str">
             <v>m</v>
           </cell>
           <cell r="ND24" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="NE24" t="str">
             <v>-</v>
@@ -25689,7 +25689,7 @@
             <v>0</v>
           </cell>
           <cell r="MY25" t="str">
-            <v>nl</v>
+            <v>p</v>
           </cell>
           <cell r="MZ25">
             <v>0</v>
@@ -26780,7 +26780,7 @@
             <v>p</v>
           </cell>
           <cell r="LR27" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="LS27" t="str">
             <v>p</v>
@@ -26807,22 +26807,22 @@
             <v>p</v>
           </cell>
           <cell r="MA27" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="MB27" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="MC27" t="str">
             <v>r</v>
           </cell>
-          <cell r="MC27" t="str">
-            <v>p</v>
-          </cell>
           <cell r="MD27" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="ME27" t="str">
             <v>P</v>
           </cell>
           <cell r="MF27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="MG27" t="str">
             <v>N</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75">
+      <c r="A1" s="99">
         <v>2026</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="80" t="s">
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="82"/>
-      <c r="BI1" s="89" t="s">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="105"/>
+      <c r="AW1" s="105"/>
+      <c r="AX1" s="105"/>
+      <c r="AY1" s="105"/>
+      <c r="AZ1" s="105"/>
+      <c r="BA1" s="105"/>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
+      <c r="BD1" s="105"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="105"/>
+      <c r="BH1" s="106"/>
+      <c r="BI1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="90"/>
-      <c r="BN1" s="90"/>
-      <c r="BO1" s="90"/>
-      <c r="BP1" s="90"/>
-      <c r="BQ1" s="90"/>
-      <c r="BR1" s="90"/>
-      <c r="BS1" s="90"/>
-      <c r="BT1" s="90"/>
-      <c r="BU1" s="90"/>
-      <c r="BV1" s="90"/>
-      <c r="BW1" s="90"/>
-      <c r="BX1" s="90"/>
-      <c r="BY1" s="90"/>
-      <c r="BZ1" s="90"/>
-      <c r="CA1" s="90"/>
-      <c r="CB1" s="90"/>
-      <c r="CC1" s="90"/>
-      <c r="CD1" s="90"/>
-      <c r="CE1" s="90"/>
-      <c r="CF1" s="90"/>
-      <c r="CG1" s="90"/>
-      <c r="CH1" s="90"/>
-      <c r="CI1" s="90"/>
-      <c r="CJ1" s="90"/>
-      <c r="CK1" s="90"/>
-      <c r="CL1" s="90"/>
-      <c r="CM1" s="91"/>
-      <c r="CN1" s="83" t="s">
+      <c r="BJ1" s="114"/>
+      <c r="BK1" s="114"/>
+      <c r="BL1" s="114"/>
+      <c r="BM1" s="114"/>
+      <c r="BN1" s="114"/>
+      <c r="BO1" s="114"/>
+      <c r="BP1" s="114"/>
+      <c r="BQ1" s="114"/>
+      <c r="BR1" s="114"/>
+      <c r="BS1" s="114"/>
+      <c r="BT1" s="114"/>
+      <c r="BU1" s="114"/>
+      <c r="BV1" s="114"/>
+      <c r="BW1" s="114"/>
+      <c r="BX1" s="114"/>
+      <c r="BY1" s="114"/>
+      <c r="BZ1" s="114"/>
+      <c r="CA1" s="114"/>
+      <c r="CB1" s="114"/>
+      <c r="CC1" s="114"/>
+      <c r="CD1" s="114"/>
+      <c r="CE1" s="114"/>
+      <c r="CF1" s="114"/>
+      <c r="CG1" s="114"/>
+      <c r="CH1" s="114"/>
+      <c r="CI1" s="114"/>
+      <c r="CJ1" s="114"/>
+      <c r="CK1" s="114"/>
+      <c r="CL1" s="114"/>
+      <c r="CM1" s="115"/>
+      <c r="CN1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="84"/>
-      <c r="CP1" s="84"/>
-      <c r="CQ1" s="84"/>
-      <c r="CR1" s="84"/>
-      <c r="CS1" s="84"/>
-      <c r="CT1" s="84"/>
-      <c r="CU1" s="84"/>
-      <c r="CV1" s="84"/>
-      <c r="CW1" s="84"/>
-      <c r="CX1" s="84"/>
-      <c r="CY1" s="84"/>
-      <c r="CZ1" s="84"/>
-      <c r="DA1" s="84"/>
-      <c r="DB1" s="84"/>
-      <c r="DC1" s="84"/>
-      <c r="DD1" s="84"/>
-      <c r="DE1" s="84"/>
-      <c r="DF1" s="84"/>
-      <c r="DG1" s="84"/>
-      <c r="DH1" s="84"/>
-      <c r="DI1" s="84"/>
-      <c r="DJ1" s="84"/>
-      <c r="DK1" s="84"/>
-      <c r="DL1" s="84"/>
-      <c r="DM1" s="84"/>
-      <c r="DN1" s="84"/>
-      <c r="DO1" s="84"/>
-      <c r="DP1" s="84"/>
-      <c r="DQ1" s="85"/>
-      <c r="DR1" s="86" t="s">
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="108"/>
+      <c r="CS1" s="108"/>
+      <c r="CT1" s="108"/>
+      <c r="CU1" s="108"/>
+      <c r="CV1" s="108"/>
+      <c r="CW1" s="108"/>
+      <c r="CX1" s="108"/>
+      <c r="CY1" s="108"/>
+      <c r="CZ1" s="108"/>
+      <c r="DA1" s="108"/>
+      <c r="DB1" s="108"/>
+      <c r="DC1" s="108"/>
+      <c r="DD1" s="108"/>
+      <c r="DE1" s="108"/>
+      <c r="DF1" s="108"/>
+      <c r="DG1" s="108"/>
+      <c r="DH1" s="108"/>
+      <c r="DI1" s="108"/>
+      <c r="DJ1" s="108"/>
+      <c r="DK1" s="108"/>
+      <c r="DL1" s="108"/>
+      <c r="DM1" s="108"/>
+      <c r="DN1" s="108"/>
+      <c r="DO1" s="108"/>
+      <c r="DP1" s="108"/>
+      <c r="DQ1" s="109"/>
+      <c r="DR1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="87"/>
-      <c r="DT1" s="87"/>
-      <c r="DU1" s="87"/>
-      <c r="DV1" s="87"/>
-      <c r="DW1" s="87"/>
-      <c r="DX1" s="87"/>
-      <c r="DY1" s="87"/>
-      <c r="DZ1" s="87"/>
-      <c r="EA1" s="87"/>
-      <c r="EB1" s="87"/>
-      <c r="EC1" s="87"/>
-      <c r="ED1" s="87"/>
-      <c r="EE1" s="87"/>
-      <c r="EF1" s="87"/>
-      <c r="EG1" s="87"/>
-      <c r="EH1" s="87"/>
-      <c r="EI1" s="87"/>
-      <c r="EJ1" s="87"/>
-      <c r="EK1" s="87"/>
-      <c r="EL1" s="87"/>
-      <c r="EM1" s="87"/>
-      <c r="EN1" s="87"/>
-      <c r="EO1" s="87"/>
-      <c r="EP1" s="87"/>
-      <c r="EQ1" s="87"/>
-      <c r="ER1" s="87"/>
-      <c r="ES1" s="87"/>
-      <c r="ET1" s="87"/>
-      <c r="EU1" s="87"/>
-      <c r="EV1" s="88"/>
-      <c r="EW1" s="98" t="s">
+      <c r="DS1" s="111"/>
+      <c r="DT1" s="111"/>
+      <c r="DU1" s="111"/>
+      <c r="DV1" s="111"/>
+      <c r="DW1" s="111"/>
+      <c r="DX1" s="111"/>
+      <c r="DY1" s="111"/>
+      <c r="DZ1" s="111"/>
+      <c r="EA1" s="111"/>
+      <c r="EB1" s="111"/>
+      <c r="EC1" s="111"/>
+      <c r="ED1" s="111"/>
+      <c r="EE1" s="111"/>
+      <c r="EF1" s="111"/>
+      <c r="EG1" s="111"/>
+      <c r="EH1" s="111"/>
+      <c r="EI1" s="111"/>
+      <c r="EJ1" s="111"/>
+      <c r="EK1" s="111"/>
+      <c r="EL1" s="111"/>
+      <c r="EM1" s="111"/>
+      <c r="EN1" s="111"/>
+      <c r="EO1" s="111"/>
+      <c r="EP1" s="111"/>
+      <c r="EQ1" s="111"/>
+      <c r="ER1" s="111"/>
+      <c r="ES1" s="111"/>
+      <c r="ET1" s="111"/>
+      <c r="EU1" s="111"/>
+      <c r="EV1" s="112"/>
+      <c r="EW1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="99"/>
-      <c r="EY1" s="99"/>
-      <c r="EZ1" s="99"/>
-      <c r="FA1" s="99"/>
-      <c r="FB1" s="99"/>
-      <c r="FC1" s="99"/>
-      <c r="FD1" s="99"/>
-      <c r="FE1" s="99"/>
-      <c r="FF1" s="99"/>
-      <c r="FG1" s="99"/>
-      <c r="FH1" s="99"/>
-      <c r="FI1" s="99"/>
-      <c r="FJ1" s="99"/>
-      <c r="FK1" s="99"/>
-      <c r="FL1" s="99"/>
-      <c r="FM1" s="99"/>
-      <c r="FN1" s="99"/>
-      <c r="FO1" s="99"/>
-      <c r="FP1" s="99"/>
-      <c r="FQ1" s="99"/>
-      <c r="FR1" s="99"/>
-      <c r="FS1" s="99"/>
-      <c r="FT1" s="99"/>
-      <c r="FU1" s="99"/>
-      <c r="FV1" s="99"/>
-      <c r="FW1" s="99"/>
-      <c r="FX1" s="99"/>
-      <c r="FY1" s="99"/>
-      <c r="FZ1" s="100"/>
-      <c r="GA1" s="101" t="s">
+      <c r="EX1" s="79"/>
+      <c r="EY1" s="79"/>
+      <c r="EZ1" s="79"/>
+      <c r="FA1" s="79"/>
+      <c r="FB1" s="79"/>
+      <c r="FC1" s="79"/>
+      <c r="FD1" s="79"/>
+      <c r="FE1" s="79"/>
+      <c r="FF1" s="79"/>
+      <c r="FG1" s="79"/>
+      <c r="FH1" s="79"/>
+      <c r="FI1" s="79"/>
+      <c r="FJ1" s="79"/>
+      <c r="FK1" s="79"/>
+      <c r="FL1" s="79"/>
+      <c r="FM1" s="79"/>
+      <c r="FN1" s="79"/>
+      <c r="FO1" s="79"/>
+      <c r="FP1" s="79"/>
+      <c r="FQ1" s="79"/>
+      <c r="FR1" s="79"/>
+      <c r="FS1" s="79"/>
+      <c r="FT1" s="79"/>
+      <c r="FU1" s="79"/>
+      <c r="FV1" s="79"/>
+      <c r="FW1" s="79"/>
+      <c r="FX1" s="79"/>
+      <c r="FY1" s="79"/>
+      <c r="FZ1" s="80"/>
+      <c r="GA1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="102"/>
-      <c r="GC1" s="102"/>
-      <c r="GD1" s="102"/>
-      <c r="GE1" s="102"/>
-      <c r="GF1" s="102"/>
-      <c r="GG1" s="102"/>
-      <c r="GH1" s="102"/>
-      <c r="GI1" s="102"/>
-      <c r="GJ1" s="102"/>
-      <c r="GK1" s="102"/>
-      <c r="GL1" s="102"/>
-      <c r="GM1" s="102"/>
-      <c r="GN1" s="102"/>
-      <c r="GO1" s="102"/>
-      <c r="GP1" s="102"/>
-      <c r="GQ1" s="102"/>
-      <c r="GR1" s="102"/>
-      <c r="GS1" s="102"/>
-      <c r="GT1" s="102"/>
-      <c r="GU1" s="102"/>
-      <c r="GV1" s="102"/>
-      <c r="GW1" s="102"/>
-      <c r="GX1" s="102"/>
-      <c r="GY1" s="102"/>
-      <c r="GZ1" s="102"/>
-      <c r="HA1" s="102"/>
-      <c r="HB1" s="102"/>
-      <c r="HC1" s="102"/>
-      <c r="HD1" s="102"/>
-      <c r="HE1" s="103"/>
-      <c r="HF1" s="104" t="s">
+      <c r="GB1" s="82"/>
+      <c r="GC1" s="82"/>
+      <c r="GD1" s="82"/>
+      <c r="GE1" s="82"/>
+      <c r="GF1" s="82"/>
+      <c r="GG1" s="82"/>
+      <c r="GH1" s="82"/>
+      <c r="GI1" s="82"/>
+      <c r="GJ1" s="82"/>
+      <c r="GK1" s="82"/>
+      <c r="GL1" s="82"/>
+      <c r="GM1" s="82"/>
+      <c r="GN1" s="82"/>
+      <c r="GO1" s="82"/>
+      <c r="GP1" s="82"/>
+      <c r="GQ1" s="82"/>
+      <c r="GR1" s="82"/>
+      <c r="GS1" s="82"/>
+      <c r="GT1" s="82"/>
+      <c r="GU1" s="82"/>
+      <c r="GV1" s="82"/>
+      <c r="GW1" s="82"/>
+      <c r="GX1" s="82"/>
+      <c r="GY1" s="82"/>
+      <c r="GZ1" s="82"/>
+      <c r="HA1" s="82"/>
+      <c r="HB1" s="82"/>
+      <c r="HC1" s="82"/>
+      <c r="HD1" s="82"/>
+      <c r="HE1" s="83"/>
+      <c r="HF1" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="105"/>
-      <c r="HH1" s="105"/>
-      <c r="HI1" s="105"/>
-      <c r="HJ1" s="105"/>
-      <c r="HK1" s="105"/>
-      <c r="HL1" s="105"/>
-      <c r="HM1" s="105"/>
-      <c r="HN1" s="105"/>
-      <c r="HO1" s="105"/>
-      <c r="HP1" s="105"/>
-      <c r="HQ1" s="105"/>
-      <c r="HR1" s="105"/>
-      <c r="HS1" s="105"/>
-      <c r="HT1" s="105"/>
-      <c r="HU1" s="105"/>
-      <c r="HV1" s="105"/>
-      <c r="HW1" s="105"/>
-      <c r="HX1" s="105"/>
-      <c r="HY1" s="105"/>
-      <c r="HZ1" s="105"/>
-      <c r="IA1" s="105"/>
-      <c r="IB1" s="105"/>
-      <c r="IC1" s="105"/>
-      <c r="ID1" s="105"/>
-      <c r="IE1" s="105"/>
-      <c r="IF1" s="105"/>
-      <c r="IG1" s="105"/>
-      <c r="IH1" s="105"/>
-      <c r="II1" s="105"/>
-      <c r="IJ1" s="106"/>
-      <c r="IK1" s="107" t="s">
+      <c r="HG1" s="85"/>
+      <c r="HH1" s="85"/>
+      <c r="HI1" s="85"/>
+      <c r="HJ1" s="85"/>
+      <c r="HK1" s="85"/>
+      <c r="HL1" s="85"/>
+      <c r="HM1" s="85"/>
+      <c r="HN1" s="85"/>
+      <c r="HO1" s="85"/>
+      <c r="HP1" s="85"/>
+      <c r="HQ1" s="85"/>
+      <c r="HR1" s="85"/>
+      <c r="HS1" s="85"/>
+      <c r="HT1" s="85"/>
+      <c r="HU1" s="85"/>
+      <c r="HV1" s="85"/>
+      <c r="HW1" s="85"/>
+      <c r="HX1" s="85"/>
+      <c r="HY1" s="85"/>
+      <c r="HZ1" s="85"/>
+      <c r="IA1" s="85"/>
+      <c r="IB1" s="85"/>
+      <c r="IC1" s="85"/>
+      <c r="ID1" s="85"/>
+      <c r="IE1" s="85"/>
+      <c r="IF1" s="85"/>
+      <c r="IG1" s="85"/>
+      <c r="IH1" s="85"/>
+      <c r="II1" s="85"/>
+      <c r="IJ1" s="86"/>
+      <c r="IK1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="108"/>
-      <c r="IM1" s="108"/>
-      <c r="IN1" s="108"/>
-      <c r="IO1" s="108"/>
-      <c r="IP1" s="108"/>
-      <c r="IQ1" s="108"/>
-      <c r="IR1" s="108"/>
-      <c r="IS1" s="108"/>
-      <c r="IT1" s="108"/>
-      <c r="IU1" s="108"/>
-      <c r="IV1" s="108"/>
-      <c r="IW1" s="108"/>
-      <c r="IX1" s="108"/>
-      <c r="IY1" s="108"/>
-      <c r="IZ1" s="108"/>
-      <c r="JA1" s="108"/>
-      <c r="JB1" s="108"/>
-      <c r="JC1" s="108"/>
-      <c r="JD1" s="108"/>
-      <c r="JE1" s="108"/>
-      <c r="JF1" s="108"/>
-      <c r="JG1" s="108"/>
-      <c r="JH1" s="108"/>
-      <c r="JI1" s="108"/>
-      <c r="JJ1" s="108"/>
-      <c r="JK1" s="108"/>
-      <c r="JL1" s="108"/>
-      <c r="JM1" s="108"/>
-      <c r="JN1" s="109"/>
-      <c r="JO1" s="110" t="s">
+      <c r="IL1" s="88"/>
+      <c r="IM1" s="88"/>
+      <c r="IN1" s="88"/>
+      <c r="IO1" s="88"/>
+      <c r="IP1" s="88"/>
+      <c r="IQ1" s="88"/>
+      <c r="IR1" s="88"/>
+      <c r="IS1" s="88"/>
+      <c r="IT1" s="88"/>
+      <c r="IU1" s="88"/>
+      <c r="IV1" s="88"/>
+      <c r="IW1" s="88"/>
+      <c r="IX1" s="88"/>
+      <c r="IY1" s="88"/>
+      <c r="IZ1" s="88"/>
+      <c r="JA1" s="88"/>
+      <c r="JB1" s="88"/>
+      <c r="JC1" s="88"/>
+      <c r="JD1" s="88"/>
+      <c r="JE1" s="88"/>
+      <c r="JF1" s="88"/>
+      <c r="JG1" s="88"/>
+      <c r="JH1" s="88"/>
+      <c r="JI1" s="88"/>
+      <c r="JJ1" s="88"/>
+      <c r="JK1" s="88"/>
+      <c r="JL1" s="88"/>
+      <c r="JM1" s="88"/>
+      <c r="JN1" s="89"/>
+      <c r="JO1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="111"/>
-      <c r="JQ1" s="111"/>
-      <c r="JR1" s="111"/>
-      <c r="JS1" s="111"/>
-      <c r="JT1" s="111"/>
-      <c r="JU1" s="111"/>
-      <c r="JV1" s="111"/>
-      <c r="JW1" s="111"/>
-      <c r="JX1" s="111"/>
-      <c r="JY1" s="111"/>
-      <c r="JZ1" s="111"/>
-      <c r="KA1" s="111"/>
-      <c r="KB1" s="111"/>
-      <c r="KC1" s="111"/>
-      <c r="KD1" s="111"/>
-      <c r="KE1" s="111"/>
-      <c r="KF1" s="111"/>
-      <c r="KG1" s="111"/>
-      <c r="KH1" s="111"/>
-      <c r="KI1" s="111"/>
-      <c r="KJ1" s="111"/>
-      <c r="KK1" s="111"/>
-      <c r="KL1" s="111"/>
-      <c r="KM1" s="111"/>
-      <c r="KN1" s="111"/>
-      <c r="KO1" s="111"/>
-      <c r="KP1" s="111"/>
-      <c r="KQ1" s="111"/>
-      <c r="KR1" s="111"/>
-      <c r="KS1" s="112"/>
-      <c r="KT1" s="113" t="s">
+      <c r="JP1" s="91"/>
+      <c r="JQ1" s="91"/>
+      <c r="JR1" s="91"/>
+      <c r="JS1" s="91"/>
+      <c r="JT1" s="91"/>
+      <c r="JU1" s="91"/>
+      <c r="JV1" s="91"/>
+      <c r="JW1" s="91"/>
+      <c r="JX1" s="91"/>
+      <c r="JY1" s="91"/>
+      <c r="JZ1" s="91"/>
+      <c r="KA1" s="91"/>
+      <c r="KB1" s="91"/>
+      <c r="KC1" s="91"/>
+      <c r="KD1" s="91"/>
+      <c r="KE1" s="91"/>
+      <c r="KF1" s="91"/>
+      <c r="KG1" s="91"/>
+      <c r="KH1" s="91"/>
+      <c r="KI1" s="91"/>
+      <c r="KJ1" s="91"/>
+      <c r="KK1" s="91"/>
+      <c r="KL1" s="91"/>
+      <c r="KM1" s="91"/>
+      <c r="KN1" s="91"/>
+      <c r="KO1" s="91"/>
+      <c r="KP1" s="91"/>
+      <c r="KQ1" s="91"/>
+      <c r="KR1" s="91"/>
+      <c r="KS1" s="92"/>
+      <c r="KT1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="114"/>
-      <c r="KV1" s="114"/>
-      <c r="KW1" s="114"/>
-      <c r="KX1" s="114"/>
-      <c r="KY1" s="114"/>
-      <c r="KZ1" s="114"/>
-      <c r="LA1" s="114"/>
-      <c r="LB1" s="114"/>
-      <c r="LC1" s="114"/>
-      <c r="LD1" s="114"/>
-      <c r="LE1" s="114"/>
-      <c r="LF1" s="114"/>
-      <c r="LG1" s="114"/>
-      <c r="LH1" s="114"/>
-      <c r="LI1" s="114"/>
-      <c r="LJ1" s="114"/>
-      <c r="LK1" s="114"/>
-      <c r="LL1" s="114"/>
-      <c r="LM1" s="114"/>
-      <c r="LN1" s="114"/>
-      <c r="LO1" s="114"/>
-      <c r="LP1" s="114"/>
-      <c r="LQ1" s="114"/>
-      <c r="LR1" s="114"/>
-      <c r="LS1" s="114"/>
-      <c r="LT1" s="114"/>
-      <c r="LU1" s="114"/>
-      <c r="LV1" s="114"/>
-      <c r="LW1" s="115"/>
-      <c r="LX1" s="92" t="s">
+      <c r="KU1" s="94"/>
+      <c r="KV1" s="94"/>
+      <c r="KW1" s="94"/>
+      <c r="KX1" s="94"/>
+      <c r="KY1" s="94"/>
+      <c r="KZ1" s="94"/>
+      <c r="LA1" s="94"/>
+      <c r="LB1" s="94"/>
+      <c r="LC1" s="94"/>
+      <c r="LD1" s="94"/>
+      <c r="LE1" s="94"/>
+      <c r="LF1" s="94"/>
+      <c r="LG1" s="94"/>
+      <c r="LH1" s="94"/>
+      <c r="LI1" s="94"/>
+      <c r="LJ1" s="94"/>
+      <c r="LK1" s="94"/>
+      <c r="LL1" s="94"/>
+      <c r="LM1" s="94"/>
+      <c r="LN1" s="94"/>
+      <c r="LO1" s="94"/>
+      <c r="LP1" s="94"/>
+      <c r="LQ1" s="94"/>
+      <c r="LR1" s="94"/>
+      <c r="LS1" s="94"/>
+      <c r="LT1" s="94"/>
+      <c r="LU1" s="94"/>
+      <c r="LV1" s="94"/>
+      <c r="LW1" s="95"/>
+      <c r="LX1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="93"/>
-      <c r="LZ1" s="93"/>
-      <c r="MA1" s="93"/>
-      <c r="MB1" s="93"/>
-      <c r="MC1" s="93"/>
-      <c r="MD1" s="93"/>
-      <c r="ME1" s="93"/>
-      <c r="MF1" s="93"/>
-      <c r="MG1" s="93"/>
-      <c r="MH1" s="93"/>
-      <c r="MI1" s="93"/>
-      <c r="MJ1" s="93"/>
-      <c r="MK1" s="93"/>
-      <c r="ML1" s="93"/>
-      <c r="MM1" s="93"/>
-      <c r="MN1" s="93"/>
-      <c r="MO1" s="93"/>
-      <c r="MP1" s="93"/>
-      <c r="MQ1" s="93"/>
-      <c r="MR1" s="93"/>
-      <c r="MS1" s="93"/>
-      <c r="MT1" s="93"/>
-      <c r="MU1" s="93"/>
-      <c r="MV1" s="93"/>
-      <c r="MW1" s="93"/>
-      <c r="MX1" s="93"/>
-      <c r="MY1" s="93"/>
-      <c r="MZ1" s="93"/>
-      <c r="NA1" s="93"/>
-      <c r="NB1" s="94"/>
-      <c r="NC1" s="95" t="s">
+      <c r="LY1" s="73"/>
+      <c r="LZ1" s="73"/>
+      <c r="MA1" s="73"/>
+      <c r="MB1" s="73"/>
+      <c r="MC1" s="73"/>
+      <c r="MD1" s="73"/>
+      <c r="ME1" s="73"/>
+      <c r="MF1" s="73"/>
+      <c r="MG1" s="73"/>
+      <c r="MH1" s="73"/>
+      <c r="MI1" s="73"/>
+      <c r="MJ1" s="73"/>
+      <c r="MK1" s="73"/>
+      <c r="ML1" s="73"/>
+      <c r="MM1" s="73"/>
+      <c r="MN1" s="73"/>
+      <c r="MO1" s="73"/>
+      <c r="MP1" s="73"/>
+      <c r="MQ1" s="73"/>
+      <c r="MR1" s="73"/>
+      <c r="MS1" s="73"/>
+      <c r="MT1" s="73"/>
+      <c r="MU1" s="73"/>
+      <c r="MV1" s="73"/>
+      <c r="MW1" s="73"/>
+      <c r="MX1" s="73"/>
+      <c r="MY1" s="73"/>
+      <c r="MZ1" s="73"/>
+      <c r="NA1" s="73"/>
+      <c r="NB1" s="74"/>
+      <c r="NC1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="96"/>
-      <c r="NE1" s="96"/>
-      <c r="NF1" s="96"/>
-      <c r="NG1" s="96"/>
-      <c r="NH1" s="96"/>
-      <c r="NI1" s="96"/>
-      <c r="NJ1" s="96"/>
-      <c r="NK1" s="96"/>
-      <c r="NL1" s="96"/>
-      <c r="NM1" s="96"/>
-      <c r="NN1" s="96"/>
-      <c r="NO1" s="96"/>
-      <c r="NP1" s="96"/>
-      <c r="NQ1" s="96"/>
-      <c r="NR1" s="96"/>
-      <c r="NS1" s="96"/>
-      <c r="NT1" s="96"/>
-      <c r="NU1" s="96"/>
-      <c r="NV1" s="96"/>
-      <c r="NW1" s="96"/>
-      <c r="NX1" s="96"/>
-      <c r="NY1" s="96"/>
-      <c r="NZ1" s="96"/>
-      <c r="OA1" s="96"/>
-      <c r="OB1" s="96"/>
-      <c r="OC1" s="96"/>
-      <c r="OD1" s="96"/>
-      <c r="OE1" s="96"/>
-      <c r="OF1" s="96"/>
-      <c r="OG1" s="97"/>
+      <c r="ND1" s="76"/>
+      <c r="NE1" s="76"/>
+      <c r="NF1" s="76"/>
+      <c r="NG1" s="76"/>
+      <c r="NH1" s="76"/>
+      <c r="NI1" s="76"/>
+      <c r="NJ1" s="76"/>
+      <c r="NK1" s="76"/>
+      <c r="NL1" s="76"/>
+      <c r="NM1" s="76"/>
+      <c r="NN1" s="76"/>
+      <c r="NO1" s="76"/>
+      <c r="NP1" s="76"/>
+      <c r="NQ1" s="76"/>
+      <c r="NR1" s="76"/>
+      <c r="NS1" s="76"/>
+      <c r="NT1" s="76"/>
+      <c r="NU1" s="76"/>
+      <c r="NV1" s="76"/>
+      <c r="NW1" s="76"/>
+      <c r="NX1" s="76"/>
+      <c r="NY1" s="76"/>
+      <c r="NZ1" s="76"/>
+      <c r="OA1" s="76"/>
+      <c r="OB1" s="76"/>
+      <c r="OC1" s="76"/>
+      <c r="OD1" s="76"/>
+      <c r="OE1" s="76"/>
+      <c r="OF1" s="76"/>
+      <c r="OG1" s="77"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="76"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31412,7 +31412,7 @@
       </c>
       <c r="LD3" s="16" t="str">
         <f>[1]CARTELLINO!LG$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LE3" s="16" t="str">
         <f>[1]CARTELLINO!LH$3</f>
@@ -31472,7 +31472,7 @@
       </c>
       <c r="LS3" s="16" t="str">
         <f>[1]CARTELLINO!LV$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LT3" s="16" t="str">
         <f>[1]CARTELLINO!LW$3</f>
@@ -31512,11 +31512,11 @@
       </c>
       <c r="MC3" s="16" t="str">
         <f>[1]CARTELLINO!MF$3</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="MD3" s="16" t="str">
         <f>[1]CARTELLINO!MG$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="ME3" s="16" t="str">
         <f>[1]CARTELLINO!MH$3</f>
@@ -31616,11 +31616,11 @@
       </c>
       <c r="NC3" s="16" t="str">
         <f>[1]CARTELLINO!NF$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="ND3" s="16" t="str">
         <f>[1]CARTELLINO!NG$3</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="NE3" s="16" t="str">
         <f>[1]CARTELLINO!NH$3</f>
@@ -35079,19 +35079,19 @@
       </c>
       <c r="LV6" s="22" t="str">
         <f>[1]CARTELLINO!LY$6</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="LW6" s="22" t="str">
         <f>[1]CARTELLINO!LZ$6</f>
-        <v>m</v>
+        <v>M</v>
       </c>
       <c r="LX6" s="22" t="str">
         <f>[1]CARTELLINO!MA$6</f>
-        <v>r</v>
+        <v>M</v>
       </c>
       <c r="LY6" s="22" t="str">
         <f>[1]CARTELLINO!MB$6</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="LZ6" s="22" t="str">
         <f>[1]CARTELLINO!MC$6</f>
@@ -35099,23 +35099,23 @@
       </c>
       <c r="MA6" s="22" t="str">
         <f>[1]CARTELLINO!MD$6</f>
-        <v>N</v>
+        <v>p</v>
       </c>
       <c r="MB6" s="22" t="str">
         <f>[1]CARTELLINO!ME$6</f>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="MC6" s="22" t="str">
         <f>[1]CARTELLINO!MF$6</f>
-        <v>R</v>
+        <v>N</v>
       </c>
       <c r="MD6" s="22" t="str">
         <f>[1]CARTELLINO!MG$6</f>
-        <v>p</v>
+        <v>S</v>
       </c>
       <c r="ME6" s="22" t="str">
         <f>[1]CARTELLINO!MH$6</f>
-        <v>m</v>
+        <v>R</v>
       </c>
       <c r="MF6" s="22" t="str">
         <f>[1]CARTELLINO!MI$6</f>
@@ -35195,7 +35195,7 @@
       </c>
       <c r="MY6" s="22" t="str">
         <f>[1]CARTELLINO!NB$6</f>
-        <v>m/R</v>
+        <v>M/R</v>
       </c>
       <c r="MZ6" s="22" t="str">
         <f>[1]CARTELLINO!NC$6</f>
@@ -35203,7 +35203,7 @@
       </c>
       <c r="NA6" s="22" t="str">
         <f>[1]CARTELLINO!ND$6</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="NB6" s="22" t="str">
         <f>[1]CARTELLINO!NE$6</f>
@@ -38815,11 +38815,11 @@
       </c>
       <c r="NE9" s="24" t="str">
         <f>[1]CARTELLINO!NH$9</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="NF9" s="24" t="str">
         <f>[1]CARTELLINO!NI$9</f>
-        <v>m</v>
+        <v>M/R</v>
       </c>
       <c r="NG9" s="24" t="str">
         <f>[1]CARTELLINO!NJ$9</f>
@@ -42119,7 +42119,7 @@
       </c>
       <c r="KJ12" s="25" t="str">
         <f>[1]CARTELLINO!KM$12</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="KK12" s="25" t="str">
         <f>[1]CARTELLINO!KN$12</f>
@@ -42199,7 +42199,7 @@
       </c>
       <c r="LD12" s="25" t="str">
         <f>[1]CARTELLINO!LG$12</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="LE12" s="25" t="str">
         <f>[1]CARTELLINO!LH$12</f>
@@ -42243,7 +42243,7 @@
       </c>
       <c r="LO12" s="25" t="str">
         <f>[1]CARTELLINO!LR$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LP12" s="25" t="str">
         <f>[1]CARTELLINO!LS$12</f>
@@ -42403,19 +42403,19 @@
       </c>
       <c r="NC12" s="25" t="str">
         <f>[1]CARTELLINO!NF$12</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="ND12" s="25" t="str">
         <f>[1]CARTELLINO!NG$12</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="NE12" s="25" t="str">
         <f>[1]CARTELLINO!NH$12</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="NF12" s="25" t="str">
         <f>[1]CARTELLINO!NI$12</f>
-        <v>M/R</v>
+        <v>r</v>
       </c>
       <c r="NG12" s="25" t="str">
         <f>[1]CARTELLINO!NJ$12</f>
@@ -45847,15 +45847,15 @@
       </c>
       <c r="LQ15" s="26" t="str">
         <f>[1]CARTELLINO!LT$15</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="LR15" s="26" t="str">
         <f>[1]CARTELLINO!LU$15</f>
-        <v>M</v>
+        <v>p</v>
       </c>
       <c r="LS15" s="26" t="str">
         <f>[1]CARTELLINO!LV$15</f>
-        <v>R</v>
+        <v>m</v>
       </c>
       <c r="LT15" s="26" t="str">
         <f>[1]CARTELLINO!LW$15</f>
@@ -45935,7 +45935,7 @@
       </c>
       <c r="MM15" s="26" t="str">
         <f>[1]CARTELLINO!MP$15</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="MN15" s="26" t="str">
         <f>[1]CARTELLINO!MQ$15</f>
@@ -45983,7 +45983,7 @@
       </c>
       <c r="MY15" s="26" t="str">
         <f>[1]CARTELLINO!NB$15</f>
-        <v>M</v>
+        <v>p</v>
       </c>
       <c r="MZ15" s="26" t="str">
         <f>[1]CARTELLINO!NC$15</f>
@@ -49439,11 +49439,11 @@
       </c>
       <c r="LP18" s="27" t="str">
         <f>[1]CARTELLINO!LS$18</f>
-        <v>M</v>
+        <v>m</v>
       </c>
       <c r="LQ18" s="27" t="str">
         <f>[1]CARTELLINO!LT$18</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="LR18" s="27" t="str">
         <f>[1]CARTELLINO!LU$18</f>
@@ -49459,15 +49459,15 @@
       </c>
       <c r="LU18" s="27" t="str">
         <f>[1]CARTELLINO!LX$18</f>
-        <v>m</v>
+        <v>R</v>
       </c>
       <c r="LV18" s="27" t="str">
         <f>[1]CARTELLINO!LY$18</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="LW18" s="27" t="str">
         <f>[1]CARTELLINO!LZ$18</f>
-        <v>r</v>
+        <v>m/R</v>
       </c>
       <c r="LX18" s="27" t="str">
         <f>[1]CARTELLINO!MA$18</f>
@@ -49479,19 +49479,19 @@
       </c>
       <c r="LZ18" s="27" t="str">
         <f>[1]CARTELLINO!MC$18</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="MA18" s="27" t="str">
         <f>[1]CARTELLINO!MD$18</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="MB18" s="27" t="str">
         <f>[1]CARTELLINO!ME$18</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="MC18" s="27" t="str">
         <f>[1]CARTELLINO!MF$18</f>
-        <v>m/R</v>
+        <v>R</v>
       </c>
       <c r="MD18" s="27" t="str">
         <f>[1]CARTELLINO!MG$18</f>
@@ -52907,7 +52907,7 @@
       </c>
       <c r="KJ21" s="28" t="str">
         <f>[1]CARTELLINO!KM$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KK21" s="28" t="str">
         <f>[1]CARTELLINO!KN$21</f>
@@ -53039,15 +53039,15 @@
       </c>
       <c r="LQ21" s="28" t="str">
         <f>[1]CARTELLINO!LT$21</f>
-        <v>N</v>
+        <v>P</v>
       </c>
       <c r="LR21" s="28" t="str">
         <f>[1]CARTELLINO!LU$21</f>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="LS21" s="28" t="str">
         <f>[1]CARTELLINO!LV$21</f>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="LT21" s="28" t="str">
         <f>[1]CARTELLINO!LW$21</f>
@@ -53063,7 +53063,7 @@
       </c>
       <c r="LW21" s="28" t="str">
         <f>[1]CARTELLINO!LZ$21</f>
-        <v>M/R</v>
+        <v>r</v>
       </c>
       <c r="LX21" s="28" t="str">
         <f>[1]CARTELLINO!MA$21</f>
@@ -53079,23 +53079,23 @@
       </c>
       <c r="MA21" s="28" t="str">
         <f>[1]CARTELLINO!MD$21</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="MB21" s="28" t="str">
         <f>[1]CARTELLINO!ME$21</f>
-        <v>M/R</v>
+        <v>m/R</v>
       </c>
       <c r="MC21" s="28" t="str">
         <f>[1]CARTELLINO!MF$21</f>
-        <v>N</v>
+        <v>p</v>
       </c>
       <c r="MD21" s="28" t="str">
         <f>[1]CARTELLINO!MG$21</f>
-        <v>S</v>
+        <v>m</v>
       </c>
       <c r="ME21" s="28" t="str">
         <f>[1]CARTELLINO!MH$21</f>
-        <v>R</v>
+        <v>m</v>
       </c>
       <c r="MF21" s="28" t="str">
         <f>[1]CARTELLINO!MI$21</f>
@@ -53171,7 +53171,7 @@
       </c>
       <c r="MX21" s="28" t="str">
         <f>[1]CARTELLINO!NA$21</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="MY21" s="28" t="str">
         <f>[1]CARTELLINO!NB$21</f>
@@ -53199,11 +53199,11 @@
       </c>
       <c r="NE21" s="28" t="str">
         <f>[1]CARTELLINO!NH$21</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NF21" s="28" t="str">
         <f>[1]CARTELLINO!NI$21</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="NG21" s="28" t="str">
         <f>[1]CARTELLINO!NJ$21</f>
@@ -56631,19 +56631,19 @@
       </c>
       <c r="LP24" s="29" t="str">
         <f>[1]CARTELLINO!LS$24</f>
-        <v>m/R</v>
+        <v>M/R</v>
       </c>
       <c r="LQ24" s="29" t="str">
         <f>[1]CARTELLINO!LT$24</f>
-        <v>P</v>
+        <v>N</v>
       </c>
       <c r="LR24" s="29" t="str">
         <f>[1]CARTELLINO!LU$24</f>
-        <v>p</v>
+        <v>S</v>
       </c>
       <c r="LS24" s="29" t="str">
         <f>[1]CARTELLINO!LV$24</f>
-        <v>m/R</v>
+        <v>R</v>
       </c>
       <c r="LT24" s="29" t="str">
         <f>[1]CARTELLINO!LW$24</f>
@@ -56651,7 +56651,7 @@
       </c>
       <c r="LU24" s="29" t="str">
         <f>[1]CARTELLINO!LX$24</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="LV24" s="29" t="str">
         <f>[1]CARTELLINO!LY$24</f>
@@ -56663,7 +56663,7 @@
       </c>
       <c r="LX24" s="29" t="str">
         <f>[1]CARTELLINO!MA$24</f>
-        <v>M/R</v>
+        <v>r</v>
       </c>
       <c r="LY24" s="29" t="str">
         <f>[1]CARTELLINO!MB$24</f>
@@ -56723,7 +56723,7 @@
       </c>
       <c r="MM24" s="29" t="str">
         <f>[1]CARTELLINO!MP$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MN24" s="29" t="str">
         <f>[1]CARTELLINO!MQ$24</f>
@@ -56767,11 +56767,11 @@
       </c>
       <c r="MX24" s="29" t="str">
         <f>[1]CARTELLINO!NA$24</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="MY24" s="29" t="str">
         <f>[1]CARTELLINO!NB$24</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="MZ24" s="29" t="str">
         <f>[1]CARTELLINO!NC$24</f>
@@ -56779,7 +56779,7 @@
       </c>
       <c r="NA24" s="29" t="str">
         <f>[1]CARTELLINO!ND$24</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="NB24" s="29" t="str">
         <f>[1]CARTELLINO!NE$24</f>
@@ -58353,7 +58353,7 @@
       </c>
       <c r="MV25" s="46" t="str">
         <f>[1]CARTELLINO!MY$25</f>
-        <v>nl</v>
+        <v>p</v>
       </c>
       <c r="MW25" s="46">
         <f>[1]CARTELLINO!MZ$25</f>
@@ -60223,7 +60223,7 @@
       </c>
       <c r="LO27" s="30" t="str">
         <f>[1]CARTELLINO!LR$27</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="LP27" s="30" t="str">
         <f>[1]CARTELLINO!LS$27</f>
@@ -60259,19 +60259,19 @@
       </c>
       <c r="LX27" s="30" t="str">
         <f>[1]CARTELLINO!MA$27</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="LY27" s="30" t="str">
         <f>[1]CARTELLINO!MB$27</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="LZ27" s="30" t="str">
         <f>[1]CARTELLINO!MC$27</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="MA27" s="30" t="str">
         <f>[1]CARTELLINO!MD$27</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="MB27" s="30" t="str">
         <f>[1]CARTELLINO!ME$27</f>
@@ -60279,7 +60279,7 @@
       </c>
       <c r="MC27" s="30" t="str">
         <f>[1]CARTELLINO!MF$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="MD27" s="30" t="str">
         <f>[1]CARTELLINO!MG$27</f>
@@ -62998,7 +62998,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="KK29" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BERARDI</v>
       </c>
       <c r="KL29" s="63" t="str">
         <v>BIANCHI</v>
@@ -63058,7 +63058,7 @@
         <v>SARTI</v>
       </c>
       <c r="LE29" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LF29" s="63" t="str">
         <v>BIANCHI</v>
@@ -63091,7 +63091,7 @@
         <v>MICHELOT.</v>
       </c>
       <c r="LP29" s="63" t="str">
-        <v>FABBRI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LQ29" s="63" t="str">
         <v>BIANCHI</v>
@@ -63103,7 +63103,7 @@
         <v>FABBRI</v>
       </c>
       <c r="LT29" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LU29" s="63" t="str">
         <v>BARBIERI</v>
@@ -63115,10 +63115,10 @@
         <v>SARTI</v>
       </c>
       <c r="LX29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="LY29" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>FABBRI</v>
       </c>
       <c r="LZ29" s="63" t="str">
         <v>VOLPINI</v>
@@ -63133,7 +63133,7 @@
         <v>BERARDI</v>
       </c>
       <c r="MD29" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>FABBRI</v>
       </c>
       <c r="ME29" s="63" t="str">
         <v>VOLPINI</v>
@@ -63163,7 +63163,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="MN29" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="MO29" s="63" t="str">
         <v>BERARDI</v>
@@ -64098,7 +64098,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="KK30" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BERARDI</v>
       </c>
       <c r="KL30" s="63" t="str">
         <v>BIANCHI</v>
@@ -64158,7 +64158,7 @@
         <v>SARTI</v>
       </c>
       <c r="LE30" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LF30" s="63" t="str">
         <v>BIANCHI</v>
@@ -64191,7 +64191,7 @@
         <v>MICHELOT.</v>
       </c>
       <c r="LP30" s="63" t="str">
-        <v>FABBRI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LQ30" s="63" t="str">
         <v>BIANCHI</v>
@@ -64203,7 +64203,7 @@
         <v>FABBRI</v>
       </c>
       <c r="LT30" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LU30" s="63" t="str">
         <v>BARBIERI</v>
@@ -64215,10 +64215,10 @@
         <v>SARTI</v>
       </c>
       <c r="LX30" s="63" t="str">
-        <v>BERARDI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="LY30" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>FABBRI</v>
       </c>
       <c r="LZ30" s="63" t="str">
         <v>VOLPINI</v>
@@ -64233,7 +64233,7 @@
         <v>BERARDI</v>
       </c>
       <c r="MD30" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>FABBRI</v>
       </c>
       <c r="ME30" s="63" t="str">
         <v>VOLPINI</v>
@@ -64263,7 +64263,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="MN30" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="MO30" s="63" t="str">
         <v>BERARDI</v>
@@ -65195,7 +65195,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="KJ31" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BERARDI</v>
       </c>
       <c r="KK31" s="63" t="str">
         <v>BIANCHI</v>
@@ -65255,7 +65255,7 @@
         <v>SARTI</v>
       </c>
       <c r="LD31" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LE31" s="63" t="str">
         <v>BIANCHI</v>
@@ -65288,7 +65288,7 @@
         <v>MICHELOT.</v>
       </c>
       <c r="LO31" s="63" t="str">
-        <v>FABBRI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LP31" s="63" t="str">
         <v>BIANCHI</v>
@@ -65300,7 +65300,7 @@
         <v>FABBRI</v>
       </c>
       <c r="LS31" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LT31" s="63" t="str">
         <v>BARBIERI</v>
@@ -65312,10 +65312,10 @@
         <v>SARTI</v>
       </c>
       <c r="LW31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="LX31" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>FABBRI</v>
       </c>
       <c r="LY31" s="63" t="str">
         <v>VOLPINI</v>
@@ -65330,7 +65330,7 @@
         <v>BERARDI</v>
       </c>
       <c r="MC31" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>FABBRI</v>
       </c>
       <c r="MD31" s="63" t="str">
         <v>VOLPINI</v>
@@ -65360,7 +65360,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="MM31" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="MN31" s="63" t="str">
         <v>BERARDI</v>
@@ -66295,7 +66295,7 @@
         <v>GHIOTTI</v>
       </c>
       <c r="KJ32" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BERARDI</v>
       </c>
       <c r="KK32" s="63" t="str">
         <v>BIANCHI</v>
@@ -66355,7 +66355,7 @@
         <v>SARTI</v>
       </c>
       <c r="LD32" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LE32" s="63" t="str">
         <v>BIANCHI</v>
@@ -66388,7 +66388,7 @@
         <v>MICHELOT.</v>
       </c>
       <c r="LO32" s="63" t="str">
-        <v>FABBRI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LP32" s="63" t="str">
         <v>BIANCHI</v>
@@ -66400,7 +66400,7 @@
         <v>FABBRI</v>
       </c>
       <c r="LS32" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LT32" s="63" t="str">
         <v>BARBIERI</v>
@@ -66412,10 +66412,10 @@
         <v>SARTI</v>
       </c>
       <c r="LW32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="LX32" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>FABBRI</v>
       </c>
       <c r="LY32" s="63" t="str">
         <v>VOLPINI</v>
@@ -66430,7 +66430,7 @@
         <v>BERARDI</v>
       </c>
       <c r="MC32" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>FABBRI</v>
       </c>
       <c r="MD32" s="63" t="str">
         <v>VOLPINI</v>
@@ -66460,7 +66460,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="MM32" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="MN32" s="63" t="str">
         <v>BERARDI</v>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="72" t="s">
+      <c r="JV35" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="73"/>
-      <c r="JX35" s="73"/>
-      <c r="JY35" s="74"/>
+      <c r="JW35" s="97"/>
+      <c r="JX35" s="97"/>
+      <c r="JY35" s="98"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,6 +71029,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71037,13 +71044,6 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8910783F-25FC-47BE-90FE-E1A43855ACC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA2450A-786D-4E17-9F56-7DD6CF50E828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -1195,6 +1195,66 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,66 +1325,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5978,18 +5978,18 @@
             <v>FABBRI</v>
           </cell>
           <cell r="AS317" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT317" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="318">
           <cell r="AQ318" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR318" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS318" t="str">
             <v>BIANCHI</v>
@@ -7695,16 +7695,16 @@
             <v>P</v>
           </cell>
           <cell r="LB3" t="str">
-            <v>M/R</v>
+            <v>p</v>
           </cell>
           <cell r="LC3" t="str">
-            <v>N</v>
+            <v>p</v>
           </cell>
           <cell r="LD3" t="str">
-            <v>S</v>
+            <v>p</v>
           </cell>
           <cell r="LE3" t="str">
-            <v>R</v>
+            <v>r</v>
           </cell>
           <cell r="LF3" t="str">
             <v>P</v>
@@ -12458,7 +12458,7 @@
             <v>-</v>
           </cell>
           <cell r="LD9" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="LE9" t="str">
             <v>p</v>
@@ -14832,16 +14832,16 @@
             <v>m</v>
           </cell>
           <cell r="LB12" t="str">
-            <v>p</v>
+            <v>M/R</v>
           </cell>
           <cell r="LC12" t="str">
-            <v>m</v>
+            <v>N</v>
           </cell>
           <cell r="LD12" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="LE12" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="LF12" t="str">
             <v>p</v>
@@ -19526,28 +19526,28 @@
             <v>m</v>
           </cell>
           <cell r="KF18" t="str">
-            <v>R</v>
+            <v>r</v>
           </cell>
           <cell r="KG18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KH18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KI18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KJ18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KK18" t="str">
-            <v>R</v>
+            <v>m</v>
           </cell>
           <cell r="KL18" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KM18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KN18" t="str">
             <v>-</v>
@@ -20718,26 +20718,26 @@
           <cell r="KF19">
             <v>0</v>
           </cell>
-          <cell r="KG19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="KH19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="KI19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="KJ19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="KK19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="KL19" t="str">
-            <v>f</v>
-          </cell>
-          <cell r="KM19" t="str">
-            <v>f</v>
+          <cell r="KG19">
+            <v>0</v>
+          </cell>
+          <cell r="KH19">
+            <v>0</v>
+          </cell>
+          <cell r="KI19">
+            <v>0</v>
+          </cell>
+          <cell r="KJ19">
+            <v>0</v>
+          </cell>
+          <cell r="KK19">
+            <v>0</v>
+          </cell>
+          <cell r="KL19">
+            <v>0</v>
+          </cell>
+          <cell r="KM19">
+            <v>0</v>
           </cell>
           <cell r="KN19" t="str">
             <v>f</v>
@@ -20788,28 +20788,28 @@
             <v>f</v>
           </cell>
           <cell r="LD19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="LE19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="LF19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="LG19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="LH19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="LI19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="LJ19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="LK19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="LL19" t="str">
             <v>k</v>
@@ -21975,7 +21975,7 @@
             <v>m</v>
           </cell>
           <cell r="LC21" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="LD21" t="str">
             <v>P</v>
@@ -28519,431 +28519,431 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:404" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99">
+      <c r="A1" s="75">
         <v>2026</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104" t="s">
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="113" t="s">
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="114"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="115"/>
-      <c r="CN1" s="107" t="s">
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
+      <c r="CA1" s="90"/>
+      <c r="CB1" s="90"/>
+      <c r="CC1" s="90"/>
+      <c r="CD1" s="90"/>
+      <c r="CE1" s="90"/>
+      <c r="CF1" s="90"/>
+      <c r="CG1" s="90"/>
+      <c r="CH1" s="90"/>
+      <c r="CI1" s="90"/>
+      <c r="CJ1" s="90"/>
+      <c r="CK1" s="90"/>
+      <c r="CL1" s="90"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="108"/>
-      <c r="CT1" s="108"/>
-      <c r="CU1" s="108"/>
-      <c r="CV1" s="108"/>
-      <c r="CW1" s="108"/>
-      <c r="CX1" s="108"/>
-      <c r="CY1" s="108"/>
-      <c r="CZ1" s="108"/>
-      <c r="DA1" s="108"/>
-      <c r="DB1" s="108"/>
-      <c r="DC1" s="108"/>
-      <c r="DD1" s="108"/>
-      <c r="DE1" s="108"/>
-      <c r="DF1" s="108"/>
-      <c r="DG1" s="108"/>
-      <c r="DH1" s="108"/>
-      <c r="DI1" s="108"/>
-      <c r="DJ1" s="108"/>
-      <c r="DK1" s="108"/>
-      <c r="DL1" s="108"/>
-      <c r="DM1" s="108"/>
-      <c r="DN1" s="108"/>
-      <c r="DO1" s="108"/>
-      <c r="DP1" s="108"/>
-      <c r="DQ1" s="109"/>
-      <c r="DR1" s="110" t="s">
+      <c r="CO1" s="84"/>
+      <c r="CP1" s="84"/>
+      <c r="CQ1" s="84"/>
+      <c r="CR1" s="84"/>
+      <c r="CS1" s="84"/>
+      <c r="CT1" s="84"/>
+      <c r="CU1" s="84"/>
+      <c r="CV1" s="84"/>
+      <c r="CW1" s="84"/>
+      <c r="CX1" s="84"/>
+      <c r="CY1" s="84"/>
+      <c r="CZ1" s="84"/>
+      <c r="DA1" s="84"/>
+      <c r="DB1" s="84"/>
+      <c r="DC1" s="84"/>
+      <c r="DD1" s="84"/>
+      <c r="DE1" s="84"/>
+      <c r="DF1" s="84"/>
+      <c r="DG1" s="84"/>
+      <c r="DH1" s="84"/>
+      <c r="DI1" s="84"/>
+      <c r="DJ1" s="84"/>
+      <c r="DK1" s="84"/>
+      <c r="DL1" s="84"/>
+      <c r="DM1" s="84"/>
+      <c r="DN1" s="84"/>
+      <c r="DO1" s="84"/>
+      <c r="DP1" s="84"/>
+      <c r="DQ1" s="85"/>
+      <c r="DR1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="DS1" s="111"/>
-      <c r="DT1" s="111"/>
-      <c r="DU1" s="111"/>
-      <c r="DV1" s="111"/>
-      <c r="DW1" s="111"/>
-      <c r="DX1" s="111"/>
-      <c r="DY1" s="111"/>
-      <c r="DZ1" s="111"/>
-      <c r="EA1" s="111"/>
-      <c r="EB1" s="111"/>
-      <c r="EC1" s="111"/>
-      <c r="ED1" s="111"/>
-      <c r="EE1" s="111"/>
-      <c r="EF1" s="111"/>
-      <c r="EG1" s="111"/>
-      <c r="EH1" s="111"/>
-      <c r="EI1" s="111"/>
-      <c r="EJ1" s="111"/>
-      <c r="EK1" s="111"/>
-      <c r="EL1" s="111"/>
-      <c r="EM1" s="111"/>
-      <c r="EN1" s="111"/>
-      <c r="EO1" s="111"/>
-      <c r="EP1" s="111"/>
-      <c r="EQ1" s="111"/>
-      <c r="ER1" s="111"/>
-      <c r="ES1" s="111"/>
-      <c r="ET1" s="111"/>
-      <c r="EU1" s="111"/>
-      <c r="EV1" s="112"/>
-      <c r="EW1" s="78" t="s">
+      <c r="DS1" s="87"/>
+      <c r="DT1" s="87"/>
+      <c r="DU1" s="87"/>
+      <c r="DV1" s="87"/>
+      <c r="DW1" s="87"/>
+      <c r="DX1" s="87"/>
+      <c r="DY1" s="87"/>
+      <c r="DZ1" s="87"/>
+      <c r="EA1" s="87"/>
+      <c r="EB1" s="87"/>
+      <c r="EC1" s="87"/>
+      <c r="ED1" s="87"/>
+      <c r="EE1" s="87"/>
+      <c r="EF1" s="87"/>
+      <c r="EG1" s="87"/>
+      <c r="EH1" s="87"/>
+      <c r="EI1" s="87"/>
+      <c r="EJ1" s="87"/>
+      <c r="EK1" s="87"/>
+      <c r="EL1" s="87"/>
+      <c r="EM1" s="87"/>
+      <c r="EN1" s="87"/>
+      <c r="EO1" s="87"/>
+      <c r="EP1" s="87"/>
+      <c r="EQ1" s="87"/>
+      <c r="ER1" s="87"/>
+      <c r="ES1" s="87"/>
+      <c r="ET1" s="87"/>
+      <c r="EU1" s="87"/>
+      <c r="EV1" s="88"/>
+      <c r="EW1" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="EX1" s="79"/>
-      <c r="EY1" s="79"/>
-      <c r="EZ1" s="79"/>
-      <c r="FA1" s="79"/>
-      <c r="FB1" s="79"/>
-      <c r="FC1" s="79"/>
-      <c r="FD1" s="79"/>
-      <c r="FE1" s="79"/>
-      <c r="FF1" s="79"/>
-      <c r="FG1" s="79"/>
-      <c r="FH1" s="79"/>
-      <c r="FI1" s="79"/>
-      <c r="FJ1" s="79"/>
-      <c r="FK1" s="79"/>
-      <c r="FL1" s="79"/>
-      <c r="FM1" s="79"/>
-      <c r="FN1" s="79"/>
-      <c r="FO1" s="79"/>
-      <c r="FP1" s="79"/>
-      <c r="FQ1" s="79"/>
-      <c r="FR1" s="79"/>
-      <c r="FS1" s="79"/>
-      <c r="FT1" s="79"/>
-      <c r="FU1" s="79"/>
-      <c r="FV1" s="79"/>
-      <c r="FW1" s="79"/>
-      <c r="FX1" s="79"/>
-      <c r="FY1" s="79"/>
-      <c r="FZ1" s="80"/>
-      <c r="GA1" s="81" t="s">
+      <c r="EX1" s="99"/>
+      <c r="EY1" s="99"/>
+      <c r="EZ1" s="99"/>
+      <c r="FA1" s="99"/>
+      <c r="FB1" s="99"/>
+      <c r="FC1" s="99"/>
+      <c r="FD1" s="99"/>
+      <c r="FE1" s="99"/>
+      <c r="FF1" s="99"/>
+      <c r="FG1" s="99"/>
+      <c r="FH1" s="99"/>
+      <c r="FI1" s="99"/>
+      <c r="FJ1" s="99"/>
+      <c r="FK1" s="99"/>
+      <c r="FL1" s="99"/>
+      <c r="FM1" s="99"/>
+      <c r="FN1" s="99"/>
+      <c r="FO1" s="99"/>
+      <c r="FP1" s="99"/>
+      <c r="FQ1" s="99"/>
+      <c r="FR1" s="99"/>
+      <c r="FS1" s="99"/>
+      <c r="FT1" s="99"/>
+      <c r="FU1" s="99"/>
+      <c r="FV1" s="99"/>
+      <c r="FW1" s="99"/>
+      <c r="FX1" s="99"/>
+      <c r="FY1" s="99"/>
+      <c r="FZ1" s="100"/>
+      <c r="GA1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="GB1" s="82"/>
-      <c r="GC1" s="82"/>
-      <c r="GD1" s="82"/>
-      <c r="GE1" s="82"/>
-      <c r="GF1" s="82"/>
-      <c r="GG1" s="82"/>
-      <c r="GH1" s="82"/>
-      <c r="GI1" s="82"/>
-      <c r="GJ1" s="82"/>
-      <c r="GK1" s="82"/>
-      <c r="GL1" s="82"/>
-      <c r="GM1" s="82"/>
-      <c r="GN1" s="82"/>
-      <c r="GO1" s="82"/>
-      <c r="GP1" s="82"/>
-      <c r="GQ1" s="82"/>
-      <c r="GR1" s="82"/>
-      <c r="GS1" s="82"/>
-      <c r="GT1" s="82"/>
-      <c r="GU1" s="82"/>
-      <c r="GV1" s="82"/>
-      <c r="GW1" s="82"/>
-      <c r="GX1" s="82"/>
-      <c r="GY1" s="82"/>
-      <c r="GZ1" s="82"/>
-      <c r="HA1" s="82"/>
-      <c r="HB1" s="82"/>
-      <c r="HC1" s="82"/>
-      <c r="HD1" s="82"/>
-      <c r="HE1" s="83"/>
-      <c r="HF1" s="84" t="s">
+      <c r="GB1" s="102"/>
+      <c r="GC1" s="102"/>
+      <c r="GD1" s="102"/>
+      <c r="GE1" s="102"/>
+      <c r="GF1" s="102"/>
+      <c r="GG1" s="102"/>
+      <c r="GH1" s="102"/>
+      <c r="GI1" s="102"/>
+      <c r="GJ1" s="102"/>
+      <c r="GK1" s="102"/>
+      <c r="GL1" s="102"/>
+      <c r="GM1" s="102"/>
+      <c r="GN1" s="102"/>
+      <c r="GO1" s="102"/>
+      <c r="GP1" s="102"/>
+      <c r="GQ1" s="102"/>
+      <c r="GR1" s="102"/>
+      <c r="GS1" s="102"/>
+      <c r="GT1" s="102"/>
+      <c r="GU1" s="102"/>
+      <c r="GV1" s="102"/>
+      <c r="GW1" s="102"/>
+      <c r="GX1" s="102"/>
+      <c r="GY1" s="102"/>
+      <c r="GZ1" s="102"/>
+      <c r="HA1" s="102"/>
+      <c r="HB1" s="102"/>
+      <c r="HC1" s="102"/>
+      <c r="HD1" s="102"/>
+      <c r="HE1" s="103"/>
+      <c r="HF1" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="HG1" s="85"/>
-      <c r="HH1" s="85"/>
-      <c r="HI1" s="85"/>
-      <c r="HJ1" s="85"/>
-      <c r="HK1" s="85"/>
-      <c r="HL1" s="85"/>
-      <c r="HM1" s="85"/>
-      <c r="HN1" s="85"/>
-      <c r="HO1" s="85"/>
-      <c r="HP1" s="85"/>
-      <c r="HQ1" s="85"/>
-      <c r="HR1" s="85"/>
-      <c r="HS1" s="85"/>
-      <c r="HT1" s="85"/>
-      <c r="HU1" s="85"/>
-      <c r="HV1" s="85"/>
-      <c r="HW1" s="85"/>
-      <c r="HX1" s="85"/>
-      <c r="HY1" s="85"/>
-      <c r="HZ1" s="85"/>
-      <c r="IA1" s="85"/>
-      <c r="IB1" s="85"/>
-      <c r="IC1" s="85"/>
-      <c r="ID1" s="85"/>
-      <c r="IE1" s="85"/>
-      <c r="IF1" s="85"/>
-      <c r="IG1" s="85"/>
-      <c r="IH1" s="85"/>
-      <c r="II1" s="85"/>
-      <c r="IJ1" s="86"/>
-      <c r="IK1" s="87" t="s">
+      <c r="HG1" s="105"/>
+      <c r="HH1" s="105"/>
+      <c r="HI1" s="105"/>
+      <c r="HJ1" s="105"/>
+      <c r="HK1" s="105"/>
+      <c r="HL1" s="105"/>
+      <c r="HM1" s="105"/>
+      <c r="HN1" s="105"/>
+      <c r="HO1" s="105"/>
+      <c r="HP1" s="105"/>
+      <c r="HQ1" s="105"/>
+      <c r="HR1" s="105"/>
+      <c r="HS1" s="105"/>
+      <c r="HT1" s="105"/>
+      <c r="HU1" s="105"/>
+      <c r="HV1" s="105"/>
+      <c r="HW1" s="105"/>
+      <c r="HX1" s="105"/>
+      <c r="HY1" s="105"/>
+      <c r="HZ1" s="105"/>
+      <c r="IA1" s="105"/>
+      <c r="IB1" s="105"/>
+      <c r="IC1" s="105"/>
+      <c r="ID1" s="105"/>
+      <c r="IE1" s="105"/>
+      <c r="IF1" s="105"/>
+      <c r="IG1" s="105"/>
+      <c r="IH1" s="105"/>
+      <c r="II1" s="105"/>
+      <c r="IJ1" s="106"/>
+      <c r="IK1" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="IL1" s="88"/>
-      <c r="IM1" s="88"/>
-      <c r="IN1" s="88"/>
-      <c r="IO1" s="88"/>
-      <c r="IP1" s="88"/>
-      <c r="IQ1" s="88"/>
-      <c r="IR1" s="88"/>
-      <c r="IS1" s="88"/>
-      <c r="IT1" s="88"/>
-      <c r="IU1" s="88"/>
-      <c r="IV1" s="88"/>
-      <c r="IW1" s="88"/>
-      <c r="IX1" s="88"/>
-      <c r="IY1" s="88"/>
-      <c r="IZ1" s="88"/>
-      <c r="JA1" s="88"/>
-      <c r="JB1" s="88"/>
-      <c r="JC1" s="88"/>
-      <c r="JD1" s="88"/>
-      <c r="JE1" s="88"/>
-      <c r="JF1" s="88"/>
-      <c r="JG1" s="88"/>
-      <c r="JH1" s="88"/>
-      <c r="JI1" s="88"/>
-      <c r="JJ1" s="88"/>
-      <c r="JK1" s="88"/>
-      <c r="JL1" s="88"/>
-      <c r="JM1" s="88"/>
-      <c r="JN1" s="89"/>
-      <c r="JO1" s="90" t="s">
+      <c r="IL1" s="108"/>
+      <c r="IM1" s="108"/>
+      <c r="IN1" s="108"/>
+      <c r="IO1" s="108"/>
+      <c r="IP1" s="108"/>
+      <c r="IQ1" s="108"/>
+      <c r="IR1" s="108"/>
+      <c r="IS1" s="108"/>
+      <c r="IT1" s="108"/>
+      <c r="IU1" s="108"/>
+      <c r="IV1" s="108"/>
+      <c r="IW1" s="108"/>
+      <c r="IX1" s="108"/>
+      <c r="IY1" s="108"/>
+      <c r="IZ1" s="108"/>
+      <c r="JA1" s="108"/>
+      <c r="JB1" s="108"/>
+      <c r="JC1" s="108"/>
+      <c r="JD1" s="108"/>
+      <c r="JE1" s="108"/>
+      <c r="JF1" s="108"/>
+      <c r="JG1" s="108"/>
+      <c r="JH1" s="108"/>
+      <c r="JI1" s="108"/>
+      <c r="JJ1" s="108"/>
+      <c r="JK1" s="108"/>
+      <c r="JL1" s="108"/>
+      <c r="JM1" s="108"/>
+      <c r="JN1" s="109"/>
+      <c r="JO1" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="JP1" s="91"/>
-      <c r="JQ1" s="91"/>
-      <c r="JR1" s="91"/>
-      <c r="JS1" s="91"/>
-      <c r="JT1" s="91"/>
-      <c r="JU1" s="91"/>
-      <c r="JV1" s="91"/>
-      <c r="JW1" s="91"/>
-      <c r="JX1" s="91"/>
-      <c r="JY1" s="91"/>
-      <c r="JZ1" s="91"/>
-      <c r="KA1" s="91"/>
-      <c r="KB1" s="91"/>
-      <c r="KC1" s="91"/>
-      <c r="KD1" s="91"/>
-      <c r="KE1" s="91"/>
-      <c r="KF1" s="91"/>
-      <c r="KG1" s="91"/>
-      <c r="KH1" s="91"/>
-      <c r="KI1" s="91"/>
-      <c r="KJ1" s="91"/>
-      <c r="KK1" s="91"/>
-      <c r="KL1" s="91"/>
-      <c r="KM1" s="91"/>
-      <c r="KN1" s="91"/>
-      <c r="KO1" s="91"/>
-      <c r="KP1" s="91"/>
-      <c r="KQ1" s="91"/>
-      <c r="KR1" s="91"/>
-      <c r="KS1" s="92"/>
-      <c r="KT1" s="93" t="s">
+      <c r="JP1" s="111"/>
+      <c r="JQ1" s="111"/>
+      <c r="JR1" s="111"/>
+      <c r="JS1" s="111"/>
+      <c r="JT1" s="111"/>
+      <c r="JU1" s="111"/>
+      <c r="JV1" s="111"/>
+      <c r="JW1" s="111"/>
+      <c r="JX1" s="111"/>
+      <c r="JY1" s="111"/>
+      <c r="JZ1" s="111"/>
+      <c r="KA1" s="111"/>
+      <c r="KB1" s="111"/>
+      <c r="KC1" s="111"/>
+      <c r="KD1" s="111"/>
+      <c r="KE1" s="111"/>
+      <c r="KF1" s="111"/>
+      <c r="KG1" s="111"/>
+      <c r="KH1" s="111"/>
+      <c r="KI1" s="111"/>
+      <c r="KJ1" s="111"/>
+      <c r="KK1" s="111"/>
+      <c r="KL1" s="111"/>
+      <c r="KM1" s="111"/>
+      <c r="KN1" s="111"/>
+      <c r="KO1" s="111"/>
+      <c r="KP1" s="111"/>
+      <c r="KQ1" s="111"/>
+      <c r="KR1" s="111"/>
+      <c r="KS1" s="112"/>
+      <c r="KT1" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="KU1" s="94"/>
-      <c r="KV1" s="94"/>
-      <c r="KW1" s="94"/>
-      <c r="KX1" s="94"/>
-      <c r="KY1" s="94"/>
-      <c r="KZ1" s="94"/>
-      <c r="LA1" s="94"/>
-      <c r="LB1" s="94"/>
-      <c r="LC1" s="94"/>
-      <c r="LD1" s="94"/>
-      <c r="LE1" s="94"/>
-      <c r="LF1" s="94"/>
-      <c r="LG1" s="94"/>
-      <c r="LH1" s="94"/>
-      <c r="LI1" s="94"/>
-      <c r="LJ1" s="94"/>
-      <c r="LK1" s="94"/>
-      <c r="LL1" s="94"/>
-      <c r="LM1" s="94"/>
-      <c r="LN1" s="94"/>
-      <c r="LO1" s="94"/>
-      <c r="LP1" s="94"/>
-      <c r="LQ1" s="94"/>
-      <c r="LR1" s="94"/>
-      <c r="LS1" s="94"/>
-      <c r="LT1" s="94"/>
-      <c r="LU1" s="94"/>
-      <c r="LV1" s="94"/>
-      <c r="LW1" s="95"/>
-      <c r="LX1" s="72" t="s">
+      <c r="KU1" s="114"/>
+      <c r="KV1" s="114"/>
+      <c r="KW1" s="114"/>
+      <c r="KX1" s="114"/>
+      <c r="KY1" s="114"/>
+      <c r="KZ1" s="114"/>
+      <c r="LA1" s="114"/>
+      <c r="LB1" s="114"/>
+      <c r="LC1" s="114"/>
+      <c r="LD1" s="114"/>
+      <c r="LE1" s="114"/>
+      <c r="LF1" s="114"/>
+      <c r="LG1" s="114"/>
+      <c r="LH1" s="114"/>
+      <c r="LI1" s="114"/>
+      <c r="LJ1" s="114"/>
+      <c r="LK1" s="114"/>
+      <c r="LL1" s="114"/>
+      <c r="LM1" s="114"/>
+      <c r="LN1" s="114"/>
+      <c r="LO1" s="114"/>
+      <c r="LP1" s="114"/>
+      <c r="LQ1" s="114"/>
+      <c r="LR1" s="114"/>
+      <c r="LS1" s="114"/>
+      <c r="LT1" s="114"/>
+      <c r="LU1" s="114"/>
+      <c r="LV1" s="114"/>
+      <c r="LW1" s="115"/>
+      <c r="LX1" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="LY1" s="73"/>
-      <c r="LZ1" s="73"/>
-      <c r="MA1" s="73"/>
-      <c r="MB1" s="73"/>
-      <c r="MC1" s="73"/>
-      <c r="MD1" s="73"/>
-      <c r="ME1" s="73"/>
-      <c r="MF1" s="73"/>
-      <c r="MG1" s="73"/>
-      <c r="MH1" s="73"/>
-      <c r="MI1" s="73"/>
-      <c r="MJ1" s="73"/>
-      <c r="MK1" s="73"/>
-      <c r="ML1" s="73"/>
-      <c r="MM1" s="73"/>
-      <c r="MN1" s="73"/>
-      <c r="MO1" s="73"/>
-      <c r="MP1" s="73"/>
-      <c r="MQ1" s="73"/>
-      <c r="MR1" s="73"/>
-      <c r="MS1" s="73"/>
-      <c r="MT1" s="73"/>
-      <c r="MU1" s="73"/>
-      <c r="MV1" s="73"/>
-      <c r="MW1" s="73"/>
-      <c r="MX1" s="73"/>
-      <c r="MY1" s="73"/>
-      <c r="MZ1" s="73"/>
-      <c r="NA1" s="73"/>
-      <c r="NB1" s="74"/>
-      <c r="NC1" s="75" t="s">
+      <c r="LY1" s="93"/>
+      <c r="LZ1" s="93"/>
+      <c r="MA1" s="93"/>
+      <c r="MB1" s="93"/>
+      <c r="MC1" s="93"/>
+      <c r="MD1" s="93"/>
+      <c r="ME1" s="93"/>
+      <c r="MF1" s="93"/>
+      <c r="MG1" s="93"/>
+      <c r="MH1" s="93"/>
+      <c r="MI1" s="93"/>
+      <c r="MJ1" s="93"/>
+      <c r="MK1" s="93"/>
+      <c r="ML1" s="93"/>
+      <c r="MM1" s="93"/>
+      <c r="MN1" s="93"/>
+      <c r="MO1" s="93"/>
+      <c r="MP1" s="93"/>
+      <c r="MQ1" s="93"/>
+      <c r="MR1" s="93"/>
+      <c r="MS1" s="93"/>
+      <c r="MT1" s="93"/>
+      <c r="MU1" s="93"/>
+      <c r="MV1" s="93"/>
+      <c r="MW1" s="93"/>
+      <c r="MX1" s="93"/>
+      <c r="MY1" s="93"/>
+      <c r="MZ1" s="93"/>
+      <c r="NA1" s="93"/>
+      <c r="NB1" s="94"/>
+      <c r="NC1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="ND1" s="76"/>
-      <c r="NE1" s="76"/>
-      <c r="NF1" s="76"/>
-      <c r="NG1" s="76"/>
-      <c r="NH1" s="76"/>
-      <c r="NI1" s="76"/>
-      <c r="NJ1" s="76"/>
-      <c r="NK1" s="76"/>
-      <c r="NL1" s="76"/>
-      <c r="NM1" s="76"/>
-      <c r="NN1" s="76"/>
-      <c r="NO1" s="76"/>
-      <c r="NP1" s="76"/>
-      <c r="NQ1" s="76"/>
-      <c r="NR1" s="76"/>
-      <c r="NS1" s="76"/>
-      <c r="NT1" s="76"/>
-      <c r="NU1" s="76"/>
-      <c r="NV1" s="76"/>
-      <c r="NW1" s="76"/>
-      <c r="NX1" s="76"/>
-      <c r="NY1" s="76"/>
-      <c r="NZ1" s="76"/>
-      <c r="OA1" s="76"/>
-      <c r="OB1" s="76"/>
-      <c r="OC1" s="76"/>
-      <c r="OD1" s="76"/>
-      <c r="OE1" s="76"/>
-      <c r="OF1" s="76"/>
-      <c r="OG1" s="77"/>
+      <c r="ND1" s="96"/>
+      <c r="NE1" s="96"/>
+      <c r="NF1" s="96"/>
+      <c r="NG1" s="96"/>
+      <c r="NH1" s="96"/>
+      <c r="NI1" s="96"/>
+      <c r="NJ1" s="96"/>
+      <c r="NK1" s="96"/>
+      <c r="NL1" s="96"/>
+      <c r="NM1" s="96"/>
+      <c r="NN1" s="96"/>
+      <c r="NO1" s="96"/>
+      <c r="NP1" s="96"/>
+      <c r="NQ1" s="96"/>
+      <c r="NR1" s="96"/>
+      <c r="NS1" s="96"/>
+      <c r="NT1" s="96"/>
+      <c r="NU1" s="96"/>
+      <c r="NV1" s="96"/>
+      <c r="NW1" s="96"/>
+      <c r="NX1" s="96"/>
+      <c r="NY1" s="96"/>
+      <c r="NZ1" s="96"/>
+      <c r="OA1" s="96"/>
+      <c r="OB1" s="96"/>
+      <c r="OC1" s="96"/>
+      <c r="OD1" s="96"/>
+      <c r="OE1" s="96"/>
+      <c r="OF1" s="96"/>
+      <c r="OG1" s="97"/>
       <c r="OH1" s="1"/>
       <c r="OI1" s="1"/>
       <c r="OJ1" s="1"/>
@@ -28953,7 +28953,7 @@
       <c r="ON1" s="1"/>
     </row>
     <row r="2" spans="1:404" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="76"/>
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -31392,19 +31392,19 @@
       </c>
       <c r="KY3" s="16" t="str">
         <f>[1]CARTELLINO!LB$3</f>
-        <v>M/R</v>
+        <v>p</v>
       </c>
       <c r="KZ3" s="16" t="str">
         <f>[1]CARTELLINO!LC$3</f>
-        <v>N</v>
+        <v>p</v>
       </c>
       <c r="LA3" s="16" t="str">
         <f>[1]CARTELLINO!LD$3</f>
-        <v>S</v>
+        <v>p</v>
       </c>
       <c r="LB3" s="16" t="str">
         <f>[1]CARTELLINO!LE$3</f>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="LC3" s="16" t="str">
         <f>[1]CARTELLINO!LF$3</f>
@@ -38591,7 +38591,7 @@
       </c>
       <c r="LA9" s="24" t="str">
         <f>[1]CARTELLINO!LD$9</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="LB9" s="24" t="str">
         <f>[1]CARTELLINO!LE$9</f>
@@ -42179,19 +42179,19 @@
       </c>
       <c r="KY12" s="25" t="str">
         <f>[1]CARTELLINO!LB$12</f>
-        <v>p</v>
+        <v>M/R</v>
       </c>
       <c r="KZ12" s="25" t="str">
         <f>[1]CARTELLINO!LC$12</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="LA12" s="25" t="str">
         <f>[1]CARTELLINO!LD$12</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="LB12" s="25" t="str">
         <f>[1]CARTELLINO!LE$12</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="LC12" s="25" t="str">
         <f>[1]CARTELLINO!LF$12</f>
@@ -49283,35 +49283,35 @@
       </c>
       <c r="KC18" s="27" t="str">
         <f>[1]CARTELLINO!KF$18</f>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="KD18" s="27" t="str">
         <f>[1]CARTELLINO!KG$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KE18" s="27" t="str">
         <f>[1]CARTELLINO!KH$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KF18" s="27" t="str">
         <f>[1]CARTELLINO!KI$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KG18" s="27" t="str">
         <f>[1]CARTELLINO!KJ$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KH18" s="27" t="str">
         <f>[1]CARTELLINO!KK$18</f>
-        <v>R</v>
+        <v>m</v>
       </c>
       <c r="KI18" s="27" t="str">
         <f>[1]CARTELLINO!KL$18</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KJ18" s="27" t="str">
         <f>[1]CARTELLINO!KM$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KK18" s="27" t="str">
         <f>[1]CARTELLINO!KN$18</f>
@@ -50879,33 +50879,33 @@
         <f>[1]CARTELLINO!KF$19</f>
         <v>0</v>
       </c>
-      <c r="KD19" s="46" t="str">
+      <c r="KD19" s="46">
         <f>[1]CARTELLINO!KG$19</f>
-        <v>f</v>
-      </c>
-      <c r="KE19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="KE19" s="46">
         <f>[1]CARTELLINO!KH$19</f>
-        <v>f</v>
-      </c>
-      <c r="KF19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="KF19" s="46">
         <f>[1]CARTELLINO!KI$19</f>
-        <v>f</v>
-      </c>
-      <c r="KG19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="KG19" s="46">
         <f>[1]CARTELLINO!KJ$19</f>
-        <v>f</v>
-      </c>
-      <c r="KH19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="KH19" s="46">
         <f>[1]CARTELLINO!KK$19</f>
-        <v>f</v>
-      </c>
-      <c r="KI19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="KI19" s="46">
         <f>[1]CARTELLINO!KL$19</f>
-        <v>f</v>
-      </c>
-      <c r="KJ19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="KJ19" s="46">
         <f>[1]CARTELLINO!KM$19</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="KK19" s="46" t="str">
         <f>[1]CARTELLINO!KN$19</f>
@@ -50973,35 +50973,35 @@
       </c>
       <c r="LA19" s="46" t="str">
         <f>[1]CARTELLINO!LD$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="LB19" s="46" t="str">
         <f>[1]CARTELLINO!LE$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="LC19" s="46" t="str">
         <f>[1]CARTELLINO!LF$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="LD19" s="46" t="str">
         <f>[1]CARTELLINO!LG$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="LE19" s="46" t="str">
         <f>[1]CARTELLINO!LH$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="LF19" s="46" t="str">
         <f>[1]CARTELLINO!LI$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="LG19" s="46" t="str">
         <f>[1]CARTELLINO!LJ$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="LH19" s="46" t="str">
         <f>[1]CARTELLINO!LK$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="LI19" s="46" t="str">
         <f>[1]CARTELLINO!LL$19</f>
@@ -52971,7 +52971,7 @@
       </c>
       <c r="KZ21" s="28" t="str">
         <f>[1]CARTELLINO!LC$21</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="LA21" s="28" t="str">
         <f>[1]CARTELLINO!LD$21</f>
@@ -63043,7 +63043,7 @@
         <v>FABBRI</v>
       </c>
       <c r="KZ29" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LA29" s="63" t="str">
         <v>BIANCHI</v>
@@ -64143,7 +64143,7 @@
         <v>FABBRI</v>
       </c>
       <c r="KZ30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LA30" s="63" t="str">
         <v>BIANCHI</v>
@@ -65240,7 +65240,7 @@
         <v>FABBRI</v>
       </c>
       <c r="KY31" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="KZ31" s="63" t="str">
         <v>BIANCHI</v>
@@ -66340,7 +66340,7 @@
         <v>FABBRI</v>
       </c>
       <c r="KY32" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="KZ32" s="63" t="str">
         <v>BIANCHI</v>
@@ -66531,12 +66531,12 @@
       <c r="B35" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="JV35" s="96" t="s">
+      <c r="JV35" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="JW35" s="97"/>
-      <c r="JX35" s="97"/>
-      <c r="JY35" s="98"/>
+      <c r="JW35" s="73"/>
+      <c r="JX35" s="73"/>
+      <c r="JY35" s="74"/>
     </row>
     <row r="36" spans="1:285" x14ac:dyDescent="0.25">
       <c r="A36" s="55" t="s">
@@ -71029,13 +71029,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="JV35:JY35"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:AF1"/>
-    <mergeCell ref="AG1:BH1"/>
-    <mergeCell ref="CN1:DQ1"/>
-    <mergeCell ref="DR1:EV1"/>
-    <mergeCell ref="BI1:CM1"/>
     <mergeCell ref="LX1:NB1"/>
     <mergeCell ref="NC1:OG1"/>
     <mergeCell ref="EW1:FZ1"/>
@@ -71044,6 +71037,13 @@
     <mergeCell ref="IK1:JN1"/>
     <mergeCell ref="JO1:KS1"/>
     <mergeCell ref="KT1:LW1"/>
+    <mergeCell ref="JV35:JY35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:AF1"/>
+    <mergeCell ref="AG1:BH1"/>
+    <mergeCell ref="CN1:DQ1"/>
+    <mergeCell ref="DR1:EV1"/>
+    <mergeCell ref="BI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <conditionalFormatting sqref="B3:OG3 B6:OG6 B9:OG9 B12:OG12 B15:OG15 B18:OG18 B21:OG21 B24:OG24 B27:OG27">

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA2450A-786D-4E17-9F56-7DD6CF50E828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCB1BF6-45B8-451E-92E0-3815AF48ADD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -5992,7 +5992,7 @@
             <v>VOLPINI</v>
           </cell>
           <cell r="AS318" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT318" t="str">
             <v>BIANCHI</v>
@@ -6269,7 +6269,7 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR338" t="str">
-            <v>PAZZAGLIA</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS338" t="str">
             <v>BARBIERI</v>
@@ -7692,7 +7692,7 @@
             <v>R</v>
           </cell>
           <cell r="LA3" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="LB3" t="str">
             <v>p</v>
@@ -14829,7 +14829,7 @@
             <v>p</v>
           </cell>
           <cell r="LA12" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="LB12" t="str">
             <v>M/R</v>
@@ -17215,7 +17215,7 @@
             <v>R</v>
           </cell>
           <cell r="LC15" t="str">
-            <v>P</v>
+            <v>M</v>
           </cell>
           <cell r="LD15" t="str">
             <v>M/R</v>
@@ -19547,7 +19547,7 @@
             <v>r</v>
           </cell>
           <cell r="KM18" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="KN18" t="str">
             <v>-</v>
@@ -19556,10 +19556,10 @@
             <v>-</v>
           </cell>
           <cell r="KP18" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="KQ18" t="str">
             <v>R</v>
-          </cell>
-          <cell r="KQ18" t="str">
-            <v>-</v>
           </cell>
           <cell r="KR18" t="str">
             <v>-</v>
@@ -19571,10 +19571,10 @@
             <v>-</v>
           </cell>
           <cell r="KU18" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="KV18" t="str">
             <v>R</v>
-          </cell>
-          <cell r="KV18" t="str">
-            <v>-</v>
           </cell>
           <cell r="KW18" t="str">
             <v>-</v>
@@ -19586,10 +19586,10 @@
             <v>-</v>
           </cell>
           <cell r="KZ18" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="LA18" t="str">
             <v>R</v>
-          </cell>
-          <cell r="LA18" t="str">
-            <v>-</v>
           </cell>
           <cell r="LB18" t="str">
             <v>-</v>
@@ -19601,10 +19601,10 @@
             <v>-</v>
           </cell>
           <cell r="LE18" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="LF18" t="str">
             <v>R</v>
-          </cell>
-          <cell r="LF18" t="str">
-            <v>-</v>
           </cell>
           <cell r="LG18" t="str">
             <v>-</v>
@@ -19616,10 +19616,10 @@
             <v>-</v>
           </cell>
           <cell r="LJ18" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="LK18" t="str">
             <v>R</v>
-          </cell>
-          <cell r="LK18" t="str">
-            <v>-</v>
           </cell>
           <cell r="LL18" t="str">
             <v>-</v>
@@ -19631,7 +19631,7 @@
             <v>-</v>
           </cell>
           <cell r="LO18" t="str">
-            <v>R</v>
+            <v>-</v>
           </cell>
           <cell r="LP18" t="str">
             <v>p</v>
@@ -20736,8 +20736,8 @@
           <cell r="KL19">
             <v>0</v>
           </cell>
-          <cell r="KM19">
-            <v>0</v>
+          <cell r="KM19" t="str">
+            <v>f</v>
           </cell>
           <cell r="KN19" t="str">
             <v>f</v>
@@ -20755,13 +20755,13 @@
             <v>f</v>
           </cell>
           <cell r="KS19" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="KT19" t="str">
             <v>pn</v>
           </cell>
-          <cell r="KT19" t="str">
+          <cell r="KU19" t="str">
             <v>x</v>
-          </cell>
-          <cell r="KU19" t="str">
-            <v>f</v>
           </cell>
           <cell r="KV19" t="str">
             <v>f</v>
@@ -24355,7 +24355,7 @@
             <v>P</v>
           </cell>
           <cell r="LC24" t="str">
-            <v>M/R</v>
+            <v>P</v>
           </cell>
           <cell r="LD24" t="str">
             <v>N</v>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="KX3" s="16" t="str">
         <f>[1]CARTELLINO!LA$3</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="KY3" s="16" t="str">
         <f>[1]CARTELLINO!LB$3</f>
@@ -42175,7 +42175,7 @@
       </c>
       <c r="KX12" s="25" t="str">
         <f>[1]CARTELLINO!LA$12</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="KY12" s="25" t="str">
         <f>[1]CARTELLINO!LB$12</f>
@@ -45779,7 +45779,7 @@
       </c>
       <c r="KZ15" s="26" t="str">
         <f>[1]CARTELLINO!LC$15</f>
-        <v>P</v>
+        <v>M</v>
       </c>
       <c r="LA15" s="26" t="str">
         <f>[1]CARTELLINO!LD$15</f>
@@ -49311,7 +49311,7 @@
       </c>
       <c r="KJ18" s="27" t="str">
         <f>[1]CARTELLINO!KM$18</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="KK18" s="27" t="str">
         <f>[1]CARTELLINO!KN$18</f>
@@ -49323,11 +49323,11 @@
       </c>
       <c r="KM18" s="27" t="str">
         <f>[1]CARTELLINO!KP$18</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="KN18" s="27" t="str">
         <f>[1]CARTELLINO!KQ$18</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="KO18" s="27" t="str">
         <f>[1]CARTELLINO!KR$18</f>
@@ -49343,11 +49343,11 @@
       </c>
       <c r="KR18" s="27" t="str">
         <f>[1]CARTELLINO!KU$18</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="KS18" s="27" t="str">
         <f>[1]CARTELLINO!KV$18</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="KT18" s="27" t="str">
         <f>[1]CARTELLINO!KW$18</f>
@@ -49363,11 +49363,11 @@
       </c>
       <c r="KW18" s="27" t="str">
         <f>[1]CARTELLINO!KZ$18</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="KX18" s="27" t="str">
         <f>[1]CARTELLINO!LA$18</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="KY18" s="27" t="str">
         <f>[1]CARTELLINO!LB$18</f>
@@ -49383,11 +49383,11 @@
       </c>
       <c r="LB18" s="27" t="str">
         <f>[1]CARTELLINO!LE$18</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="LC18" s="27" t="str">
         <f>[1]CARTELLINO!LF$18</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="LD18" s="27" t="str">
         <f>[1]CARTELLINO!LG$18</f>
@@ -49403,11 +49403,11 @@
       </c>
       <c r="LG18" s="27" t="str">
         <f>[1]CARTELLINO!LJ$18</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="LH18" s="27" t="str">
         <f>[1]CARTELLINO!LK$18</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="LI18" s="27" t="str">
         <f>[1]CARTELLINO!LL$18</f>
@@ -49423,7 +49423,7 @@
       </c>
       <c r="LL18" s="27" t="str">
         <f>[1]CARTELLINO!LO$18</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="LM18" s="27" t="str">
         <f>[1]CARTELLINO!LP$18</f>
@@ -50903,9 +50903,9 @@
         <f>[1]CARTELLINO!KL$19</f>
         <v>0</v>
       </c>
-      <c r="KJ19" s="46">
+      <c r="KJ19" s="46" t="str">
         <f>[1]CARTELLINO!KM$19</f>
-        <v>0</v>
+        <v>f</v>
       </c>
       <c r="KK19" s="46" t="str">
         <f>[1]CARTELLINO!KN$19</f>
@@ -50929,15 +50929,15 @@
       </c>
       <c r="KP19" s="46" t="str">
         <f>[1]CARTELLINO!KS$19</f>
-        <v>pn</v>
+        <v>f</v>
       </c>
       <c r="KQ19" s="46" t="str">
         <f>[1]CARTELLINO!KT$19</f>
-        <v>x</v>
+        <v>pn</v>
       </c>
       <c r="KR19" s="46" t="str">
         <f>[1]CARTELLINO!KU$19</f>
-        <v>f</v>
+        <v>x</v>
       </c>
       <c r="KS19" s="46" t="str">
         <f>[1]CARTELLINO!KV$19</f>
@@ -56567,7 +56567,7 @@
       </c>
       <c r="KZ24" s="29" t="str">
         <f>[1]CARTELLINO!LC$24</f>
-        <v>M/R</v>
+        <v>P</v>
       </c>
       <c r="LA24" s="29" t="str">
         <f>[1]CARTELLINO!LD$24</f>
@@ -64203,7 +64203,7 @@
         <v>FABBRI</v>
       </c>
       <c r="LT30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>BIANCHI</v>
       </c>
       <c r="LU30" s="63" t="str">
         <v>BARBIERI</v>
@@ -65243,7 +65243,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="KZ31" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="LA31" s="63" t="str">
         <v>GHIOTTI</v>
